--- a/output_data/Offgrid_Pareto_Results_3D.xlsx
+++ b/output_data/Offgrid_Pareto_Results_3D.xlsx
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2262527.473394678</v>
+        <v>-5527143.052154474</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.09918049913777358</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>11.29069814592244</v>
       </c>
       <c r="E2" t="n">
-        <v>2445.624800473277</v>
+        <v>2579.874217924712</v>
       </c>
       <c r="F2" t="n">
-        <v>1229.919600753746</v>
+        <v>8206.484528945562</v>
       </c>
       <c r="G2" t="n">
-        <v>3199.466359338174</v>
+        <v>1255.004996872778</v>
       </c>
       <c r="H2" t="n">
-        <v>3715.060207671528</v>
+        <v>14117.78845111284</v>
       </c>
       <c r="I2" t="n">
-        <v>86.54095031632029</v>
+        <v>93.87855623110815</v>
       </c>
       <c r="J2" t="n">
-        <v>192.7168897442297</v>
+        <v>1931.602045834714</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>681359.0461114979</v>
+        <v>-3168624.409700077</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0999896367838037</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8.09906516166996</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2479.351916855386</v>
+        <v>2439.281048987979</v>
       </c>
       <c r="F3" t="n">
-        <v>1275.76719043691</v>
+        <v>7753.342438923796</v>
       </c>
       <c r="G3" t="n">
-        <v>1259.006393377027</v>
+        <v>2808.256004783841</v>
       </c>
       <c r="H3" t="n">
-        <v>3119.964155679429</v>
+        <v>20413.9174823673</v>
       </c>
       <c r="I3" t="n">
-        <v>84.11666304032418</v>
+        <v>101.9804949063454</v>
       </c>
       <c r="J3" t="n">
-        <v>195.5177300484219</v>
+        <v>1932.07697256901</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>681365.0009409791</v>
+        <v>-5534315.230625564</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09999886231192776</v>
+        <v>0.09999928290216027</v>
       </c>
       <c r="D4" t="n">
-        <v>7.677560409540396</v>
+        <v>6.871742562030647</v>
       </c>
       <c r="E4" t="n">
-        <v>2476.453616702008</v>
+        <v>2480.637016194424</v>
       </c>
       <c r="F4" t="n">
-        <v>1257.279665294598</v>
+        <v>7746.181249115866</v>
       </c>
       <c r="G4" t="n">
-        <v>1259.227952444258</v>
+        <v>1255.50927433805</v>
       </c>
       <c r="H4" t="n">
-        <v>3121.482159448227</v>
+        <v>14128.00982829043</v>
       </c>
       <c r="I4" t="n">
-        <v>86.24189720488927</v>
+        <v>102.4124367335388</v>
       </c>
       <c r="J4" t="n">
-        <v>189.3739197240937</v>
+        <v>1947.860642760818</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>683695.5036083584</v>
+        <v>-3968798.746106579</v>
       </c>
       <c r="C5" t="n">
-        <v>0.099368219210203</v>
+        <v>5.799556634528432e-18</v>
       </c>
       <c r="D5" t="n">
-        <v>10.91158512708942</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2591.839618915055</v>
+        <v>2439.004809198354</v>
       </c>
       <c r="F5" t="n">
-        <v>1280.532300147903</v>
+        <v>8217.827259650472</v>
       </c>
       <c r="G5" t="n">
-        <v>1259.214982866438</v>
+        <v>1255.99028831829</v>
       </c>
       <c r="H5" t="n">
-        <v>3119.964155679429</v>
+        <v>22352.67981603129</v>
       </c>
       <c r="I5" t="n">
-        <v>87.34846749924377</v>
+        <v>90.91701497304481</v>
       </c>
       <c r="J5" t="n">
-        <v>195.5282953165672</v>
+        <v>1960.889382772369</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1674602.696689928</v>
+        <v>-4759423.999838138</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01233556050149605</v>
+        <v>0.02572238587391343</v>
       </c>
       <c r="D6" t="n">
-        <v>2.249915341563125</v>
+        <v>4.12339760144893</v>
       </c>
       <c r="E6" t="n">
-        <v>2486.359218097603</v>
+        <v>2566.583927209051</v>
       </c>
       <c r="F6" t="n">
-        <v>1256.850843079779</v>
+        <v>7961.92784603958</v>
       </c>
       <c r="G6" t="n">
-        <v>2417.670675859649</v>
+        <v>1255.005927623688</v>
       </c>
       <c r="H6" t="n">
-        <v>3730.886265325716</v>
+        <v>18188.37541770581</v>
       </c>
       <c r="I6" t="n">
-        <v>84.70453095195438</v>
+        <v>84.14387049899641</v>
       </c>
       <c r="J6" t="n">
-        <v>198.8550770339694</v>
+        <v>2021.567306408631</v>
       </c>
     </row>
     <row r="7">
@@ -657,31 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2205823.950474695</v>
+        <v>-4071075.542879527</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007593546245475965</v>
+        <v>0.0003159806016485007</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03177809475233273</v>
+        <v>0.3349539838912508</v>
       </c>
       <c r="E7" t="n">
-        <v>2478.843533898473</v>
+        <v>2477.602321983828</v>
       </c>
       <c r="F7" t="n">
-        <v>1234.416291758311</v>
+        <v>7768.696219296604</v>
       </c>
       <c r="G7" t="n">
-        <v>3120.00101142272</v>
+        <v>1255.184204013477</v>
       </c>
       <c r="H7" t="n">
-        <v>3730.270242789567</v>
+        <v>21855.54403096996</v>
       </c>
       <c r="I7" t="n">
-        <v>85.07228615487415</v>
+        <v>84.07048124747918</v>
       </c>
       <c r="J7" t="n">
-        <v>190.2871726449585</v>
+        <v>1951.991623052525</v>
       </c>
     </row>
     <row r="8">
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1958512.200560351</v>
+        <v>-4646071.43703105</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00554959422367817</v>
+        <v>0.01921768100909338</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6160292885103669</v>
+        <v>0.9635808788896361</v>
       </c>
       <c r="E8" t="n">
-        <v>2469.183013227859</v>
+        <v>2486.81292378771</v>
       </c>
       <c r="F8" t="n">
-        <v>1270.924200846472</v>
+        <v>7761.897123080382</v>
       </c>
       <c r="G8" t="n">
-        <v>2792.450902624094</v>
+        <v>1255.005930315895</v>
       </c>
       <c r="H8" t="n">
-        <v>3730.415473476707</v>
+        <v>18818.27327849833</v>
       </c>
       <c r="I8" t="n">
-        <v>86.3762442520389</v>
+        <v>102.1166590869425</v>
       </c>
       <c r="J8" t="n">
-        <v>206.4623415090938</v>
+        <v>1949.119589541992</v>
       </c>
     </row>
     <row r="9">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1378303.005392575</v>
+        <v>-4869333.954188436</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02651160856218619</v>
+        <v>0.03450685226731102</v>
       </c>
       <c r="D9" t="n">
-        <v>3.162814289641691</v>
+        <v>2.693318000304901</v>
       </c>
       <c r="E9" t="n">
-        <v>2476.769713517493</v>
+        <v>2514.991972187145</v>
       </c>
       <c r="F9" t="n">
-        <v>1269.229160927291</v>
+        <v>7759.582616838838</v>
       </c>
       <c r="G9" t="n">
-        <v>2025.193955583396</v>
+        <v>1255.001649157395</v>
       </c>
       <c r="H9" t="n">
-        <v>3731.956485015048</v>
+        <v>17638.75158711349</v>
       </c>
       <c r="I9" t="n">
-        <v>90.47138588434039</v>
+        <v>98.76559409480002</v>
       </c>
       <c r="J9" t="n">
-        <v>235.5814544712377</v>
+        <v>1932.388159514398</v>
       </c>
     </row>
     <row r="10">
@@ -759,31 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>703712.7232174372</v>
+        <v>-4409188.358806739</v>
       </c>
       <c r="C10" t="n">
-        <v>0.09342086465368107</v>
+        <v>0.009545341767291058</v>
       </c>
       <c r="D10" t="n">
-        <v>10.63241457584122</v>
+        <v>1.136234732896124</v>
       </c>
       <c r="E10" t="n">
-        <v>2591.804549571526</v>
+        <v>2470.764356092696</v>
       </c>
       <c r="F10" t="n">
-        <v>1280.532300147903</v>
+        <v>7971.573909797311</v>
       </c>
       <c r="G10" t="n">
-        <v>1259.634409326384</v>
+        <v>1258.3803074417</v>
       </c>
       <c r="H10" t="n">
-        <v>3224.302280933114</v>
+        <v>20038.90239193784</v>
       </c>
       <c r="I10" t="n">
-        <v>84.09391745078169</v>
+        <v>101.7416141724329</v>
       </c>
       <c r="J10" t="n">
-        <v>195.5282953165672</v>
+        <v>1935.626573711769</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1188248.093248005</v>
+        <v>-5320318.326165648</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03776743413706277</v>
+        <v>0.07699703088430017</v>
       </c>
       <c r="D11" t="n">
-        <v>2.910330116934956</v>
+        <v>5.547367397591563</v>
       </c>
       <c r="E11" t="n">
-        <v>2443.251390131463</v>
+        <v>2453.455925298807</v>
       </c>
       <c r="F11" t="n">
-        <v>1242.885358537689</v>
+        <v>7787.514028084443</v>
       </c>
       <c r="G11" t="n">
-        <v>1777.349994417789</v>
+        <v>1263.81251746952</v>
       </c>
       <c r="H11" t="n">
-        <v>3730.309774715133</v>
+        <v>15221.51417971986</v>
       </c>
       <c r="I11" t="n">
-        <v>86.04799888327595</v>
+        <v>115.0819771070584</v>
       </c>
       <c r="J11" t="n">
-        <v>187.5445535493415</v>
+        <v>1956.734926623041</v>
       </c>
     </row>
     <row r="12">
@@ -827,31 +827,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>687413.676510339</v>
+        <v>-4260610.603329181</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09910594690613414</v>
+        <v>0.005473633036743836</v>
       </c>
       <c r="D12" t="n">
-        <v>10.05203657607735</v>
+        <v>0.9284847532324836</v>
       </c>
       <c r="E12" t="n">
-        <v>2590.908397588512</v>
+        <v>2551.42769572309</v>
       </c>
       <c r="F12" t="n">
-        <v>1280.605934992027</v>
+        <v>7764.333832684227</v>
       </c>
       <c r="G12" t="n">
-        <v>1263.772937286108</v>
+        <v>1255.91528471508</v>
       </c>
       <c r="H12" t="n">
-        <v>3119.964155679429</v>
+        <v>20841.43613350237</v>
       </c>
       <c r="I12" t="n">
-        <v>87.37342715626131</v>
+        <v>125.5035396047535</v>
       </c>
       <c r="J12" t="n">
-        <v>211.4049851801432</v>
+        <v>1949.119589541992</v>
       </c>
     </row>
     <row r="13">
@@ -861,31 +861,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1613221.334644447</v>
+        <v>-5289203.023202432</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01482852028402788</v>
+        <v>0.07316031603786137</v>
       </c>
       <c r="D13" t="n">
-        <v>1.821737947635205</v>
+        <v>5.334262445701842</v>
       </c>
       <c r="E13" t="n">
-        <v>2448.186875668126</v>
+        <v>2534.281310438076</v>
       </c>
       <c r="F13" t="n">
-        <v>1274.634603699455</v>
+        <v>7765.21519651334</v>
       </c>
       <c r="G13" t="n">
-        <v>2337.425520689635</v>
+        <v>1255.505854208947</v>
       </c>
       <c r="H13" t="n">
-        <v>3725.782350050844</v>
+        <v>15408.82511455337</v>
       </c>
       <c r="I13" t="n">
-        <v>90.69415394873452</v>
+        <v>102.6212230293565</v>
       </c>
       <c r="J13" t="n">
-        <v>235.0045598683767</v>
+        <v>2018.551559010011</v>
       </c>
     </row>
     <row r="14">
@@ -895,31 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1823868.135277582</v>
+        <v>-4804114.36717044</v>
       </c>
       <c r="C14" t="n">
-        <v>0.008135651423441085</v>
+        <v>0.02913118483148266</v>
       </c>
       <c r="D14" t="n">
-        <v>1.471527283557938</v>
+        <v>4.398026865077343</v>
       </c>
       <c r="E14" t="n">
-        <v>2506.960266816843</v>
+        <v>2559.019996203059</v>
       </c>
       <c r="F14" t="n">
-        <v>1257.636970323809</v>
+        <v>7977.060768817728</v>
       </c>
       <c r="G14" t="n">
-        <v>2614.16017034683</v>
+        <v>1255.108972760845</v>
       </c>
       <c r="H14" t="n">
-        <v>3731.998657610159</v>
+        <v>17956.27575271097</v>
       </c>
       <c r="I14" t="n">
-        <v>85.88827222203969</v>
+        <v>97.94681114712324</v>
       </c>
       <c r="J14" t="n">
-        <v>187.8722480021102</v>
+        <v>1953.961962473518</v>
       </c>
     </row>
     <row r="15">
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>692756.7525525027</v>
+        <v>-4686598.784058019</v>
       </c>
       <c r="C15" t="n">
-        <v>0.09661766245756589</v>
+        <v>0.02199078451320437</v>
       </c>
       <c r="D15" t="n">
-        <v>9.66301284229959</v>
+        <v>4.650919570917733</v>
       </c>
       <c r="E15" t="n">
-        <v>2570.649084639864</v>
+        <v>2463.273290354301</v>
       </c>
       <c r="F15" t="n">
-        <v>1280.303231461833</v>
+        <v>8198.204317372103</v>
       </c>
       <c r="G15" t="n">
-        <v>1259.214982866438</v>
+        <v>1258.217176709443</v>
       </c>
       <c r="H15" t="n">
-        <v>3170.379588278549</v>
+        <v>18546.11755301013</v>
       </c>
       <c r="I15" t="n">
-        <v>84.07093639624057</v>
+        <v>102.1019554821396</v>
       </c>
       <c r="J15" t="n">
-        <v>193.3017164076681</v>
+        <v>2022.337696612046</v>
       </c>
     </row>
     <row r="16">
@@ -963,31 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1037864.016238468</v>
+        <v>-4949074.134291212</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04664610478056134</v>
+        <v>0.04102965412106421</v>
       </c>
       <c r="D16" t="n">
-        <v>6.427510096388556</v>
+        <v>2.890899902135891</v>
       </c>
       <c r="E16" t="n">
-        <v>2567.44195195691</v>
+        <v>2485.170823794454</v>
       </c>
       <c r="F16" t="n">
-        <v>1241.532441113226</v>
+        <v>7754.09722118244</v>
       </c>
       <c r="G16" t="n">
-        <v>1576.739413769623</v>
+        <v>1255.004449000447</v>
       </c>
       <c r="H16" t="n">
-        <v>3727.063140748736</v>
+        <v>17220.16675943619</v>
       </c>
       <c r="I16" t="n">
-        <v>84.09391745078169</v>
+        <v>100.867129562172</v>
       </c>
       <c r="J16" t="n">
-        <v>187.8393754938811</v>
+        <v>1939.503555343999</v>
       </c>
     </row>
     <row r="17">
@@ -997,31 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1729625.94154022</v>
+        <v>-5152173.037431834</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01020028818585918</v>
+        <v>0.05798167934827218</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9521648155499052</v>
+        <v>4.234410514260345</v>
       </c>
       <c r="E17" t="n">
-        <v>2442.121432803445</v>
+        <v>2486.81292378771</v>
       </c>
       <c r="F17" t="n">
-        <v>1268.746886592394</v>
+        <v>7762.05339626386</v>
       </c>
       <c r="G17" t="n">
-        <v>2489.625250309293</v>
+        <v>1255.005930315895</v>
       </c>
       <c r="H17" t="n">
-        <v>3731.935281113267</v>
+        <v>16145.77499451522</v>
       </c>
       <c r="I17" t="n">
-        <v>84.7416893477221</v>
+        <v>102.1166590869425</v>
       </c>
       <c r="J17" t="n">
-        <v>250.2599963219752</v>
+        <v>1949.119589541992</v>
       </c>
     </row>
     <row r="18">
@@ -1031,31 +1031,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2062579.154545473</v>
+        <v>-5400437.006598361</v>
       </c>
       <c r="C18" t="n">
-        <v>0.003525658317585085</v>
+        <v>0.08585115632283186</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3869154006962194</v>
+        <v>9.194105542026954</v>
       </c>
       <c r="E18" t="n">
-        <v>2459.805191255863</v>
+        <v>2439.043301201575</v>
       </c>
       <c r="F18" t="n">
-        <v>1280.127567260412</v>
+        <v>8185.685627818119</v>
       </c>
       <c r="G18" t="n">
-        <v>2929.518953528451</v>
+        <v>1263.964404568589</v>
       </c>
       <c r="H18" t="n">
-        <v>3731.721071073676</v>
+        <v>14761.94530044853</v>
       </c>
       <c r="I18" t="n">
-        <v>86.89567467687641</v>
+        <v>106.5356617061908</v>
       </c>
       <c r="J18" t="n">
-        <v>205.7997308057579</v>
+        <v>1966.630243122453</v>
       </c>
     </row>
     <row r="19">
@@ -1065,31 +1065,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>715042.5639114092</v>
+        <v>-4900315.539218769</v>
       </c>
       <c r="C19" t="n">
-        <v>0.08995576413828062</v>
+        <v>0.03692608908210501</v>
       </c>
       <c r="D19" t="n">
-        <v>9.638865226129067</v>
+        <v>5.862434123954685</v>
       </c>
       <c r="E19" t="n">
-        <v>2583.762012517836</v>
+        <v>2512.774253019626</v>
       </c>
       <c r="F19" t="n">
-        <v>1280.533420340303</v>
+        <v>8150.618817529073</v>
       </c>
       <c r="G19" t="n">
-        <v>1259.215254682566</v>
+        <v>1255.757424900388</v>
       </c>
       <c r="H19" t="n">
-        <v>3286.511762119011</v>
+        <v>17435.55266394868</v>
       </c>
       <c r="I19" t="n">
-        <v>84.09392713193954</v>
+        <v>102.3034529090464</v>
       </c>
       <c r="J19" t="n">
-        <v>196.2041806120098</v>
+        <v>1931.893508564642</v>
       </c>
     </row>
     <row r="20">
@@ -1099,31 +1099,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>773174.9954360955</v>
+        <v>-5030495.733283517</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07261462347386032</v>
+        <v>0.04753905339631937</v>
       </c>
       <c r="D20" t="n">
-        <v>7.227554835701799</v>
+        <v>7.141648672310885</v>
       </c>
       <c r="E20" t="n">
-        <v>2527.111403833361</v>
+        <v>2477.369597039583</v>
       </c>
       <c r="F20" t="n">
-        <v>1252.479554942167</v>
+        <v>8207.175652811426</v>
       </c>
       <c r="G20" t="n">
-        <v>1259.629263685685</v>
+        <v>1255.09137451589</v>
       </c>
       <c r="H20" t="n">
-        <v>3599.247754560383</v>
+        <v>16748.80417028758</v>
       </c>
       <c r="I20" t="n">
-        <v>92.91842723578988</v>
+        <v>105.830014964169</v>
       </c>
       <c r="J20" t="n">
-        <v>193.7004463550273</v>
+        <v>1929.322289306476</v>
       </c>
     </row>
     <row r="21">
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1552082.187602865</v>
+        <v>-5362566.190354522</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01704125486494924</v>
+        <v>0.08116313953386395</v>
       </c>
       <c r="D21" t="n">
-        <v>1.718024898205517</v>
+        <v>7.933326766005466</v>
       </c>
       <c r="E21" t="n">
-        <v>2475.637670042175</v>
+        <v>2536.135560105189</v>
       </c>
       <c r="F21" t="n">
-        <v>1236.518178518453</v>
+        <v>7967.574827289371</v>
       </c>
       <c r="G21" t="n">
-        <v>2256.558306241924</v>
+        <v>1255.139181768638</v>
       </c>
       <c r="H21" t="n">
-        <v>3731.192505939175</v>
+        <v>15006.72600061902</v>
       </c>
       <c r="I21" t="n">
-        <v>84.03293261042565</v>
+        <v>88.12946268549926</v>
       </c>
       <c r="J21" t="n">
-        <v>200.533431017197</v>
+        <v>2002.375419589873</v>
       </c>
     </row>
     <row r="22">
@@ -1167,31 +1167,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>766160.9225927965</v>
+        <v>-4769996.184589582</v>
       </c>
       <c r="C22" t="n">
-        <v>0.07463868172166425</v>
+        <v>0.02668786807318508</v>
       </c>
       <c r="D22" t="n">
-        <v>8.993872198017272</v>
+        <v>3.281046719474401</v>
       </c>
       <c r="E22" t="n">
-        <v>2591.040499942143</v>
+        <v>2500.80225983012</v>
       </c>
       <c r="F22" t="n">
-        <v>1278.87753309306</v>
+        <v>7925.285905605249</v>
       </c>
       <c r="G22" t="n">
-        <v>1259.128400562588</v>
+        <v>1255.475772159283</v>
       </c>
       <c r="H22" t="n">
-        <v>3555.903913147895</v>
+        <v>18127.40058221515</v>
       </c>
       <c r="I22" t="n">
-        <v>85.38855464765192</v>
+        <v>134.8486929509013</v>
       </c>
       <c r="J22" t="n">
-        <v>198.5884648648545</v>
+        <v>2108.667269862934</v>
       </c>
     </row>
     <row r="23">
@@ -1201,31 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2130287.156678388</v>
+        <v>-5013411.726126028</v>
       </c>
       <c r="C23" t="n">
-        <v>0.002232446365620235</v>
+        <v>0.04674504139629375</v>
       </c>
       <c r="D23" t="n">
-        <v>0.277988649242833</v>
+        <v>3.696782730766779</v>
       </c>
       <c r="E23" t="n">
-        <v>2558.953659771351</v>
+        <v>2517.915110725818</v>
       </c>
       <c r="F23" t="n">
-        <v>1223.191399880456</v>
+        <v>7759.418438788941</v>
       </c>
       <c r="G23" t="n">
-        <v>3017.641353308029</v>
+        <v>1256.027675203795</v>
       </c>
       <c r="H23" t="n">
-        <v>3731.997003063208</v>
+        <v>16845.95079298121</v>
       </c>
       <c r="I23" t="n">
-        <v>103.9066595564151</v>
+        <v>93.15386744259668</v>
       </c>
       <c r="J23" t="n">
-        <v>194.9015316023748</v>
+        <v>2234.126083729188</v>
       </c>
     </row>
     <row r="24">
@@ -1235,31 +1235,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1206549.498751314</v>
+        <v>-5197415.561018024</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0365360256615243</v>
+        <v>0.06301776435687229</v>
       </c>
       <c r="D24" t="n">
-        <v>3.475460911580264</v>
+        <v>8.040841305147939</v>
       </c>
       <c r="E24" t="n">
-        <v>2447.080925576727</v>
+        <v>2439.510241007569</v>
       </c>
       <c r="F24" t="n">
-        <v>1270.097967371231</v>
+        <v>8216.774960499673</v>
       </c>
       <c r="G24" t="n">
-        <v>1800.402237440011</v>
+        <v>1255.063327083697</v>
       </c>
       <c r="H24" t="n">
-        <v>3731.774436256457</v>
+        <v>15866.58100025538</v>
       </c>
       <c r="I24" t="n">
-        <v>85.8059001772731</v>
+        <v>84.85318649874364</v>
       </c>
       <c r="J24" t="n">
-        <v>188.4532164137371</v>
+        <v>1989.715672360175</v>
       </c>
     </row>
     <row r="25">
@@ -1269,31 +1269,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>847985.5607383823</v>
+        <v>-5124569.204323435</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06118442482954803</v>
+        <v>0.05527542475230176</v>
       </c>
       <c r="D25" t="n">
-        <v>6.80121005974671</v>
+        <v>8.360061197929603</v>
       </c>
       <c r="E25" t="n">
-        <v>2556.062027863618</v>
+        <v>2549.378203419731</v>
       </c>
       <c r="F25" t="n">
-        <v>1241.640361249409</v>
+        <v>8208.041651238424</v>
       </c>
       <c r="G25" t="n">
-        <v>1325.062382210346</v>
+        <v>1255.677691612791</v>
       </c>
       <c r="H25" t="n">
-        <v>3731.453341208289</v>
+        <v>16243.05649164534</v>
       </c>
       <c r="I25" t="n">
-        <v>84.17117571243701</v>
+        <v>102.7386612656678</v>
       </c>
       <c r="J25" t="n">
-        <v>195.6541060592459</v>
+        <v>1929.092516267709</v>
       </c>
     </row>
     <row r="26">
@@ -1303,31 +1303,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1751142.529354327</v>
+        <v>-4453504.753510242</v>
       </c>
       <c r="C26" t="n">
-        <v>0.009535309784964687</v>
+        <v>0.01069313292498646</v>
       </c>
       <c r="D26" t="n">
-        <v>1.1343880903669</v>
+        <v>1.34530097765474</v>
       </c>
       <c r="E26" t="n">
-        <v>2512.47774941039</v>
+        <v>2471.588283837383</v>
       </c>
       <c r="F26" t="n">
-        <v>1222.790453559174</v>
+        <v>7973.994552793459</v>
       </c>
       <c r="G26" t="n">
-        <v>2518.818126411305</v>
+        <v>1255.260930598945</v>
       </c>
       <c r="H26" t="n">
-        <v>3731.665110140006</v>
+        <v>19816.60498770711</v>
       </c>
       <c r="I26" t="n">
-        <v>86.21200559758891</v>
+        <v>88.69874977780393</v>
       </c>
       <c r="J26" t="n">
-        <v>191.7969112688129</v>
+        <v>1953.868789114823</v>
       </c>
     </row>
     <row r="27">
@@ -1337,31 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>741899.1183303449</v>
+        <v>-4122096.68335914</v>
       </c>
       <c r="C27" t="n">
-        <v>0.08184988760619401</v>
+        <v>0.001757079093592286</v>
       </c>
       <c r="D27" t="n">
-        <v>7.408434350156091</v>
+        <v>0.2384022541674358</v>
       </c>
       <c r="E27" t="n">
-        <v>2560.984549965616</v>
+        <v>2495.272566294555</v>
       </c>
       <c r="F27" t="n">
-        <v>1207.563039029751</v>
+        <v>7759.338837082356</v>
       </c>
       <c r="G27" t="n">
-        <v>1259.057889081738</v>
+        <v>1259.987950115714</v>
       </c>
       <c r="H27" t="n">
-        <v>3438.03889828397</v>
+        <v>21567.45064754443</v>
       </c>
       <c r="I27" t="n">
-        <v>84.07052129981216</v>
+        <v>92.17707921077175</v>
       </c>
       <c r="J27" t="n">
-        <v>195.2231143673777</v>
+        <v>1929.170951094427</v>
       </c>
     </row>
     <row r="28">
@@ -1371,31 +1371,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1223924.000895457</v>
+        <v>-4728752.864347586</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0353863486400214</v>
+        <v>0.02397408095216737</v>
       </c>
       <c r="D28" t="n">
-        <v>3.879524048708805</v>
+        <v>1.287232762751789</v>
       </c>
       <c r="E28" t="n">
-        <v>2509.166434639037</v>
+        <v>2441.730902813903</v>
       </c>
       <c r="F28" t="n">
-        <v>1241.537906077148</v>
+        <v>7776.971100573835</v>
       </c>
       <c r="G28" t="n">
-        <v>1822.409454631358</v>
+        <v>1264.075909024716</v>
       </c>
       <c r="H28" t="n">
-        <v>3731.888903264749</v>
+        <v>18348.30169261121</v>
       </c>
       <c r="I28" t="n">
-        <v>87.75185513590429</v>
+        <v>102.3565509337825</v>
       </c>
       <c r="J28" t="n">
-        <v>190.0630786124664</v>
+        <v>1948.777639426283</v>
       </c>
     </row>
     <row r="29">
@@ -1405,31 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1525140.752075259</v>
+        <v>-4207828.691850781</v>
       </c>
       <c r="C29" t="n">
-        <v>0.018128220631421</v>
+        <v>0.004247866368078184</v>
       </c>
       <c r="D29" t="n">
-        <v>2.46578483016453</v>
+        <v>1.56485541081135</v>
       </c>
       <c r="E29" t="n">
-        <v>2469.183013227859</v>
+        <v>2478.040800221947</v>
       </c>
       <c r="F29" t="n">
-        <v>1270.91648872515</v>
+        <v>8189.856305664589</v>
       </c>
       <c r="G29" t="n">
-        <v>2220.167025499059</v>
+        <v>1259.54230646817</v>
       </c>
       <c r="H29" t="n">
-        <v>3730.41378308618</v>
+        <v>21078.53049816635</v>
       </c>
       <c r="I29" t="n">
-        <v>94.31003209159981</v>
+        <v>84.63816468056235</v>
       </c>
       <c r="J29" t="n">
-        <v>205.9235219405215</v>
+        <v>1931.075885204623</v>
       </c>
     </row>
     <row r="30">
@@ -1439,31 +1439,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1426063.709695836</v>
+        <v>-4537084.07748178</v>
       </c>
       <c r="C30" t="n">
-        <v>0.02355595496273795</v>
+        <v>0.01357417550653847</v>
       </c>
       <c r="D30" t="n">
-        <v>6.03713503806399</v>
+        <v>0.7665149838408492</v>
       </c>
       <c r="E30" t="n">
-        <v>2591.804549571526</v>
+        <v>2541.723083338826</v>
       </c>
       <c r="F30" t="n">
-        <v>1278.478497471534</v>
+        <v>7760.183617490939</v>
       </c>
       <c r="G30" t="n">
-        <v>2088.632611181341</v>
+        <v>1259.958002793328</v>
       </c>
       <c r="H30" t="n">
-        <v>3720.825708856273</v>
+        <v>19367.57435217172</v>
       </c>
       <c r="I30" t="n">
-        <v>84.09391745078169</v>
+        <v>98.19938547389256</v>
       </c>
       <c r="J30" t="n">
-        <v>217.7079486475342</v>
+        <v>1967.213013411328</v>
       </c>
     </row>
     <row r="31">
@@ -1473,31 +1473,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>696549.5844427095</v>
+        <v>-5124692.961348871</v>
       </c>
       <c r="C31" t="n">
-        <v>0.09540858138174789</v>
+        <v>0.0552904540398854</v>
       </c>
       <c r="D31" t="n">
-        <v>7.972960798925033</v>
+        <v>8.256618515570647</v>
       </c>
       <c r="E31" t="n">
-        <v>2586.773415482055</v>
+        <v>2536.509468825272</v>
       </c>
       <c r="F31" t="n">
-        <v>1208.333418376845</v>
+        <v>8208.041651238424</v>
       </c>
       <c r="G31" t="n">
-        <v>1259.057889081738</v>
+        <v>1255.677691612791</v>
       </c>
       <c r="H31" t="n">
-        <v>3196.76016585026</v>
+        <v>16243.63266828426</v>
       </c>
       <c r="I31" t="n">
-        <v>84.07052129981216</v>
+        <v>102.7386612656678</v>
       </c>
       <c r="J31" t="n">
-        <v>187.4346334506563</v>
+        <v>1929.092516267709</v>
       </c>
     </row>
     <row r="32">
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1467298.392438665</v>
+        <v>-5475975.968380434</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02146236945514173</v>
+        <v>0.09357804770346444</v>
       </c>
       <c r="D32" t="n">
-        <v>2.551007694655194</v>
+        <v>6.206318860106874</v>
       </c>
       <c r="E32" t="n">
-        <v>2454.172698316053</v>
+        <v>2511.743091060035</v>
       </c>
       <c r="F32" t="n">
-        <v>1275.03227984318</v>
+        <v>7768.273125751211</v>
       </c>
       <c r="G32" t="n">
-        <v>2144.935641079925</v>
+        <v>1255.015148759647</v>
       </c>
       <c r="H32" t="n">
-        <v>3729.179736243337</v>
+        <v>14430.90205885456</v>
       </c>
       <c r="I32" t="n">
-        <v>88.16049970601094</v>
+        <v>130.8647691310956</v>
       </c>
       <c r="J32" t="n">
-        <v>188.3433320567673</v>
+        <v>1941.360686705649</v>
       </c>
     </row>
     <row r="33">
@@ -1541,31 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1294005.294142435</v>
+        <v>-5137915.597564991</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03131281199165288</v>
+        <v>0.05659489432067574</v>
       </c>
       <c r="D33" t="n">
-        <v>3.608914925507556</v>
+        <v>4.874863453060573</v>
       </c>
       <c r="E33" t="n">
-        <v>2509.917950793435</v>
+        <v>2566.583927209051</v>
       </c>
       <c r="F33" t="n">
-        <v>1243.0777916677</v>
+        <v>7778.973173492232</v>
       </c>
       <c r="G33" t="n">
-        <v>1914.844720976491</v>
+        <v>1255.000608122828</v>
       </c>
       <c r="H33" t="n">
-        <v>3731.998538652998</v>
+        <v>16206.83696559927</v>
       </c>
       <c r="I33" t="n">
-        <v>87.75185513590429</v>
+        <v>84.14387049899641</v>
       </c>
       <c r="J33" t="n">
-        <v>190.0630786124664</v>
+        <v>2021.567306408631</v>
       </c>
     </row>
     <row r="34">
@@ -1575,31 +1575,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>870279.085452376</v>
+        <v>-5301491.233698626</v>
       </c>
       <c r="C34" t="n">
-        <v>0.05975504063822711</v>
+        <v>0.07442008285348296</v>
       </c>
       <c r="D34" t="n">
-        <v>5.079588137762925</v>
+        <v>8.90138605222932</v>
       </c>
       <c r="E34" t="n">
-        <v>2480.029742985157</v>
+        <v>2510.00013952939</v>
       </c>
       <c r="F34" t="n">
-        <v>1234.105844624996</v>
+        <v>8165.950754338794</v>
       </c>
       <c r="G34" t="n">
-        <v>1356.365875909924</v>
+        <v>1256.10040829</v>
       </c>
       <c r="H34" t="n">
-        <v>3731.998604200347</v>
+        <v>15314.03493258723</v>
       </c>
       <c r="I34" t="n">
-        <v>84.52506337810468</v>
+        <v>103.7872498136758</v>
       </c>
       <c r="J34" t="n">
-        <v>194.551152830133</v>
+        <v>1936.378563719078</v>
       </c>
     </row>
     <row r="35">
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1560676.514376212</v>
+        <v>-5313160.748898895</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02488467629862494</v>
+        <v>0.07622441390352107</v>
       </c>
       <c r="D35" t="n">
-        <v>1.221358856173282</v>
+        <v>7.194052902580284</v>
       </c>
       <c r="E35" t="n">
-        <v>2446.650264375015</v>
+        <v>2561.714895727501</v>
       </c>
       <c r="F35" t="n">
-        <v>1209.824039007227</v>
+        <v>7972.101682950751</v>
       </c>
       <c r="G35" t="n">
-        <v>2337.425520689635</v>
+        <v>1263.547288924148</v>
       </c>
       <c r="H35" t="n">
-        <v>3459.001911839228</v>
+        <v>15232.64371095627</v>
       </c>
       <c r="I35" t="n">
-        <v>86.1224579394984</v>
+        <v>106.7796374481807</v>
       </c>
       <c r="J35" t="n">
-        <v>191.5978758467302</v>
+        <v>1966.887547909903</v>
       </c>
     </row>
     <row r="36">
@@ -1643,31 +1643,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1924979.021530244</v>
+        <v>-5428752.16365378</v>
       </c>
       <c r="C36" t="n">
-        <v>0.006538583229373547</v>
+        <v>0.08832792497799898</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3262859359221437</v>
+        <v>9.100323717299197</v>
       </c>
       <c r="E36" t="n">
-        <v>2442.121432803445</v>
+        <v>2451.13653526834</v>
       </c>
       <c r="F36" t="n">
-        <v>1211.164380622746</v>
+        <v>8139.580518264252</v>
       </c>
       <c r="G36" t="n">
-        <v>2758.443153672046</v>
+        <v>1255.429437231378</v>
       </c>
       <c r="H36" t="n">
-        <v>3695.787743835533</v>
+        <v>14654.69252533234</v>
       </c>
       <c r="I36" t="n">
-        <v>84.73697045292919</v>
+        <v>90.60002265493661</v>
       </c>
       <c r="J36" t="n">
-        <v>226.8831504977843</v>
+        <v>1929.601350432817</v>
       </c>
     </row>
     <row r="37">
@@ -1677,31 +1677,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1853961.435922892</v>
+        <v>-4558633.800596589</v>
       </c>
       <c r="C37" t="n">
-        <v>0.007559859512139473</v>
+        <v>0.01473398957721732</v>
       </c>
       <c r="D37" t="n">
-        <v>1.010133933149071</v>
+        <v>0.5840785805891313</v>
       </c>
       <c r="E37" t="n">
-        <v>2503.004410580291</v>
+        <v>2485.314993985168</v>
       </c>
       <c r="F37" t="n">
-        <v>1240.771062486394</v>
+        <v>7756.519386763222</v>
       </c>
       <c r="G37" t="n">
-        <v>2654.323120066807</v>
+        <v>1260.108196311729</v>
       </c>
       <c r="H37" t="n">
-        <v>3731.165657297861</v>
+        <v>19253.4817790763</v>
       </c>
       <c r="I37" t="n">
-        <v>85.97882294965767</v>
+        <v>101.1820727084636</v>
       </c>
       <c r="J37" t="n">
-        <v>198.942489126048</v>
+        <v>2022.337696612046</v>
       </c>
     </row>
     <row r="38">
@@ -1711,31 +1711,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2228297.969042489</v>
+        <v>-5073375.443389332</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0003218879720269817</v>
+        <v>0.05115172883136266</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1031195429434861</v>
+        <v>7.754246351458283</v>
       </c>
       <c r="E38" t="n">
-        <v>2511.568147610441</v>
+        <v>2509.10771369551</v>
       </c>
       <c r="F38" t="n">
-        <v>1234.416291758311</v>
+        <v>8212.152122815436</v>
       </c>
       <c r="G38" t="n">
-        <v>3148.444561117439</v>
+        <v>1255.384588777215</v>
       </c>
       <c r="H38" t="n">
-        <v>3731.772266954855</v>
+        <v>16512.30920432305</v>
       </c>
       <c r="I38" t="n">
-        <v>87.01969572778252</v>
+        <v>109.0917838560822</v>
       </c>
       <c r="J38" t="n">
-        <v>191.2017238784111</v>
+        <v>1983.811854674758</v>
       </c>
     </row>
     <row r="39">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2029330.439054097</v>
+        <v>-4892349.313586939</v>
       </c>
       <c r="C39" t="n">
-        <v>0.004183277947149651</v>
+        <v>0.0362750945287481</v>
       </c>
       <c r="D39" t="n">
-        <v>2.081837651788909</v>
+        <v>6.167791011090618</v>
       </c>
       <c r="E39" t="n">
-        <v>2558.061032877674</v>
+        <v>2510.565831525945</v>
       </c>
       <c r="F39" t="n">
-        <v>1223.006405260286</v>
+        <v>8201.681710484665</v>
       </c>
       <c r="G39" t="n">
-        <v>2884.34426214616</v>
+        <v>1255.029242901052</v>
       </c>
       <c r="H39" t="n">
-        <v>3731.954977906547</v>
+        <v>17472.77249810152</v>
       </c>
       <c r="I39" t="n">
-        <v>107.7049537067409</v>
+        <v>101.0342029520661</v>
       </c>
       <c r="J39" t="n">
-        <v>193.457500732836</v>
+        <v>1967.520786279073</v>
       </c>
     </row>
     <row r="40">
@@ -1779,31 +1779,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1863780.248135504</v>
+        <v>-4600340.419759238</v>
       </c>
       <c r="C40" t="n">
-        <v>0.007359613079304759</v>
+        <v>0.01683499347028236</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3971085739083446</v>
+        <v>1.660020998405209</v>
       </c>
       <c r="E40" t="n">
-        <v>2476.454038788183</v>
+        <v>2568.689545807602</v>
       </c>
       <c r="F40" t="n">
-        <v>1236.518178518453</v>
+        <v>7756.217709558556</v>
       </c>
       <c r="G40" t="n">
-        <v>2667.958244853266</v>
+        <v>1255.001649157395</v>
       </c>
       <c r="H40" t="n">
-        <v>3731.218818812573</v>
+        <v>19052.34798562045</v>
       </c>
       <c r="I40" t="n">
-        <v>85.20843743902414</v>
+        <v>98.76559409480002</v>
       </c>
       <c r="J40" t="n">
-        <v>201.7543318329893</v>
+        <v>1953.971687405852</v>
       </c>
     </row>
     <row r="41">
@@ -1813,31 +1813,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1359049.837889201</v>
+        <v>-4858730.182917642</v>
       </c>
       <c r="C41" t="n">
-        <v>0.02819832555384488</v>
+        <v>0.03358167510646164</v>
       </c>
       <c r="D41" t="n">
-        <v>2.959464595376959</v>
+        <v>5.265293830398665</v>
       </c>
       <c r="E41" t="n">
-        <v>2442.207631453415</v>
+        <v>2440.707883546773</v>
       </c>
       <c r="F41" t="n">
-        <v>1280.019680536568</v>
+        <v>8165.706948368557</v>
       </c>
       <c r="G41" t="n">
-        <v>2005.19576686087</v>
+        <v>1256.09979571145</v>
       </c>
       <c r="H41" t="n">
-        <v>3715.900111135601</v>
+        <v>17658.94602306865</v>
       </c>
       <c r="I41" t="n">
-        <v>85.57696817640036</v>
+        <v>102.7376527050134</v>
       </c>
       <c r="J41" t="n">
-        <v>204.9965643470921</v>
+        <v>1934.748055641917</v>
       </c>
     </row>
     <row r="42">
@@ -1847,31 +1847,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1493979.288300973</v>
+        <v>-5503528.795713481</v>
       </c>
       <c r="C42" t="n">
-        <v>0.02008413776579952</v>
+        <v>0.09695014533969344</v>
       </c>
       <c r="D42" t="n">
-        <v>1.303854714151509</v>
+        <v>10.02978599873765</v>
       </c>
       <c r="E42" t="n">
-        <v>2454.172698316053</v>
+        <v>2483.325845528352</v>
       </c>
       <c r="F42" t="n">
-        <v>1224.260339586211</v>
+        <v>8161.855091722919</v>
       </c>
       <c r="G42" t="n">
-        <v>2180.86130210881</v>
+        <v>1255.180967616242</v>
       </c>
       <c r="H42" t="n">
-        <v>3730.531895419269</v>
+        <v>14236.42770990912</v>
       </c>
       <c r="I42" t="n">
-        <v>94.15837396960571</v>
+        <v>130.7424130459194</v>
       </c>
       <c r="J42" t="n">
-        <v>188.3433320567673</v>
+        <v>2094.686363669468</v>
       </c>
     </row>
     <row r="43">
@@ -1881,31 +1881,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>784137.1793199984</v>
+        <v>-5370585.764781444</v>
       </c>
       <c r="C43" t="n">
-        <v>0.06931358482764394</v>
+        <v>0.08218963116474862</v>
       </c>
       <c r="D43" t="n">
-        <v>5.399924177670279</v>
+        <v>9.248550699512503</v>
       </c>
       <c r="E43" t="n">
-        <v>2445.838815615331</v>
+        <v>2474.781577790494</v>
       </c>
       <c r="F43" t="n">
-        <v>1256.408426817949</v>
+        <v>8185.554375083798</v>
       </c>
       <c r="G43" t="n">
-        <v>1259.419695452528</v>
+        <v>1256.619262558703</v>
       </c>
       <c r="H43" t="n">
-        <v>3664.712613047983</v>
+        <v>14941.93007722241</v>
       </c>
       <c r="I43" t="n">
-        <v>92.69874680859665</v>
+        <v>92.27940260787993</v>
       </c>
       <c r="J43" t="n">
-        <v>200.9848562777562</v>
+        <v>2020.047763448135</v>
       </c>
     </row>
     <row r="44">
@@ -1915,31 +1915,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>724420.6918114532</v>
+        <v>-5226674.097093882</v>
       </c>
       <c r="C44" t="n">
-        <v>0.08710630176974372</v>
+        <v>0.06631193857543215</v>
       </c>
       <c r="D44" t="n">
-        <v>6.911604678234773</v>
+        <v>4.531151578462477</v>
       </c>
       <c r="E44" t="n">
-        <v>2510.866162008637</v>
+        <v>2482.717179967476</v>
       </c>
       <c r="F44" t="n">
-        <v>1215.61053197555</v>
+        <v>7749.991637935958</v>
       </c>
       <c r="G44" t="n">
-        <v>1259.181598701559</v>
+        <v>1255.001174717437</v>
       </c>
       <c r="H44" t="n">
-        <v>3349.192926575827</v>
+        <v>15744.26261889275</v>
       </c>
       <c r="I44" t="n">
-        <v>84.09392713193954</v>
+        <v>98.73795270604548</v>
       </c>
       <c r="J44" t="n">
-        <v>196.2041806120098</v>
+        <v>2055.903002319106</v>
       </c>
     </row>
     <row r="45">
@@ -1949,31 +1949,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1263168.397428869</v>
+        <v>-5102952.663079329</v>
       </c>
       <c r="C45" t="n">
-        <v>0.03274717255060745</v>
+        <v>0.05355629367245274</v>
       </c>
       <c r="D45" t="n">
-        <v>6.79852991438562</v>
+        <v>7.280710232612564</v>
       </c>
       <c r="E45" t="n">
-        <v>2591.504533538561</v>
+        <v>2439.510241007569</v>
       </c>
       <c r="F45" t="n">
-        <v>1279.980754424365</v>
+        <v>8201.614286559106</v>
       </c>
       <c r="G45" t="n">
-        <v>1872.065343423552</v>
+        <v>1255.064374456588</v>
       </c>
       <c r="H45" t="n">
-        <v>3728.068880332715</v>
+        <v>16367.89001685039</v>
       </c>
       <c r="I45" t="n">
-        <v>92.62960196170179</v>
+        <v>84.91777154915486</v>
       </c>
       <c r="J45" t="n">
-        <v>195.4807229276234</v>
+        <v>1978.032828096574</v>
       </c>
     </row>
     <row r="46">
@@ -1983,31 +1983,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1345367.850736614</v>
+        <v>-5244728.141297955</v>
       </c>
       <c r="C46" t="n">
-        <v>0.028760334115666</v>
+        <v>0.0683590669546829</v>
       </c>
       <c r="D46" t="n">
-        <v>4.764368131515817</v>
+        <v>8.524145448137777</v>
       </c>
       <c r="E46" t="n">
-        <v>2514.712357399516</v>
+        <v>2463.594245503822</v>
       </c>
       <c r="F46" t="n">
-        <v>1280.72784176871</v>
+        <v>8212.75603916084</v>
       </c>
       <c r="G46" t="n">
-        <v>1984.531622216715</v>
+        <v>1258.265308903365</v>
       </c>
       <c r="H46" t="n">
-        <v>3715.060207671528</v>
+        <v>15603.14471430659</v>
       </c>
       <c r="I46" t="n">
-        <v>87.19427649381896</v>
+        <v>125.8619426250893</v>
       </c>
       <c r="J46" t="n">
-        <v>248.919755619008</v>
+        <v>1935.587911706854</v>
       </c>
     </row>
     <row r="47">
@@ -2017,31 +2017,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1981391.217627142</v>
+        <v>-4526239.750547319</v>
       </c>
       <c r="C47" t="n">
-        <v>0.00507894852465694</v>
+        <v>0.01317655485188307</v>
       </c>
       <c r="D47" t="n">
-        <v>1.225788837550468</v>
+        <v>3.601521945695674</v>
       </c>
       <c r="E47" t="n">
-        <v>2443.462745806448</v>
+        <v>2477.980136999559</v>
       </c>
       <c r="F47" t="n">
-        <v>1273.496449899064</v>
+        <v>8188.718882289706</v>
       </c>
       <c r="G47" t="n">
-        <v>2823.301474672976</v>
+        <v>1255.745181239897</v>
       </c>
       <c r="H47" t="n">
-        <v>3731.773930890703</v>
+        <v>19410.9788975321</v>
       </c>
       <c r="I47" t="n">
-        <v>85.86382372746041</v>
+        <v>98.76559409480002</v>
       </c>
       <c r="J47" t="n">
-        <v>188.4532164137371</v>
+        <v>1932.399909849296</v>
       </c>
     </row>
     <row r="48">
@@ -2051,31 +2051,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>751443.3301625039</v>
+        <v>-4619915.059664169</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0791951190304211</v>
+        <v>0.01804196308879566</v>
       </c>
       <c r="D48" t="n">
-        <v>9.154642622537867</v>
+        <v>2.060545888794396</v>
       </c>
       <c r="E48" t="n">
-        <v>2590.804438978694</v>
+        <v>2476.557634015469</v>
       </c>
       <c r="F48" t="n">
-        <v>1280.532300147903</v>
+        <v>7927.795650528826</v>
       </c>
       <c r="G48" t="n">
-        <v>1259.214982866438</v>
+        <v>1255.51657614506</v>
       </c>
       <c r="H48" t="n">
-        <v>3475.4239818535</v>
+        <v>18933.24693519417</v>
       </c>
       <c r="I48" t="n">
-        <v>84.09391745078169</v>
+        <v>132.9818642207859</v>
       </c>
       <c r="J48" t="n">
-        <v>224.3966523904666</v>
+        <v>1988.226624815904</v>
       </c>
     </row>
     <row r="49">
@@ -2085,31 +2085,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>732529.5867852956</v>
+        <v>-5081065.674501826</v>
       </c>
       <c r="C49" t="n">
-        <v>0.08471005975010529</v>
+        <v>0.05193353579417021</v>
       </c>
       <c r="D49" t="n">
-        <v>9.397958274331353</v>
+        <v>4.147025244496206</v>
       </c>
       <c r="E49" t="n">
-        <v>2592.150969736272</v>
+        <v>2509.10771369551</v>
       </c>
       <c r="F49" t="n">
-        <v>1272.556929165534</v>
+        <v>7780.138228195602</v>
       </c>
       <c r="G49" t="n">
-        <v>1259.214982866438</v>
+        <v>1255.384182569081</v>
       </c>
       <c r="H49" t="n">
-        <v>3378.859508823897</v>
+        <v>16512.30920432305</v>
       </c>
       <c r="I49" t="n">
-        <v>84.09391745078169</v>
+        <v>109.1807898677032</v>
       </c>
       <c r="J49" t="n">
-        <v>195.5282953165672</v>
+        <v>1980.661163847135</v>
       </c>
     </row>
     <row r="50">
@@ -2119,31 +2119,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1094157.316600375</v>
+        <v>-5326770.596060876</v>
       </c>
       <c r="C50" t="n">
-        <v>0.04288215015062576</v>
+        <v>0.07717331081578066</v>
       </c>
       <c r="D50" t="n">
-        <v>5.027474965419043</v>
+        <v>5.07302060329593</v>
       </c>
       <c r="E50" t="n">
-        <v>2480.029742985157</v>
+        <v>2454.914052489735</v>
       </c>
       <c r="F50" t="n">
-        <v>1276.915438685011</v>
+        <v>7780.307295895598</v>
       </c>
       <c r="G50" t="n">
-        <v>1650.917166047342</v>
+        <v>1255.260793505338</v>
       </c>
       <c r="H50" t="n">
-        <v>3731.993001385082</v>
+        <v>15222.1829795744</v>
       </c>
       <c r="I50" t="n">
-        <v>84.52673929068912</v>
+        <v>115.0819771070584</v>
       </c>
       <c r="J50" t="n">
-        <v>194.551152830133</v>
+        <v>1956.734926623041</v>
       </c>
     </row>
     <row r="51">
@@ -2153,31 +2153,31 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>988292.9872480334</v>
+        <v>-5165765.407297585</v>
       </c>
       <c r="C51" t="n">
-        <v>0.05048416295696952</v>
+        <v>0.05976841780138462</v>
       </c>
       <c r="D51" t="n">
-        <v>5.533193832960026</v>
+        <v>4.734037018895965</v>
       </c>
       <c r="E51" t="n">
-        <v>2517.80593475866</v>
+        <v>2487.112752057426</v>
       </c>
       <c r="F51" t="n">
-        <v>1240.364178618387</v>
+        <v>7788.284000274549</v>
       </c>
       <c r="G51" t="n">
-        <v>1510.944636860073</v>
+        <v>1259.733203907482</v>
       </c>
       <c r="H51" t="n">
-        <v>3731.934798331079</v>
+        <v>16052.22631645302</v>
       </c>
       <c r="I51" t="n">
-        <v>85.17203197313871</v>
+        <v>102.2714839658116</v>
       </c>
       <c r="J51" t="n">
-        <v>201.7171190485092</v>
+        <v>1953.116649975475</v>
       </c>
     </row>
     <row r="52">
@@ -2187,31 +2187,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1011976.440970554</v>
+        <v>-4840463.900817614</v>
       </c>
       <c r="C52" t="n">
-        <v>0.04937032850752101</v>
+        <v>0.03217169125250845</v>
       </c>
       <c r="D52" t="n">
-        <v>3.732372976716536</v>
+        <v>3.067245194301449</v>
       </c>
       <c r="E52" t="n">
-        <v>2462.173517782859</v>
+        <v>2561.730569889617</v>
       </c>
       <c r="F52" t="n">
-        <v>1222.120191702949</v>
+        <v>7788.284000274549</v>
       </c>
       <c r="G52" t="n">
-        <v>1545.778829095646</v>
+        <v>1255.098353436334</v>
       </c>
       <c r="H52" t="n">
-        <v>3722.364059216356</v>
+        <v>17781.00724018748</v>
       </c>
       <c r="I52" t="n">
-        <v>85.86424235771922</v>
+        <v>102.2802057121545</v>
       </c>
       <c r="J52" t="n">
-        <v>225.799897799819</v>
+        <v>1957.308381641483</v>
       </c>
     </row>
     <row r="53">
@@ -2221,31 +2221,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1397445.605667787</v>
+        <v>-4936427.371340033</v>
       </c>
       <c r="C53" t="n">
-        <v>0.02593240744846368</v>
+        <v>0.03988330901545426</v>
       </c>
       <c r="D53" t="n">
-        <v>2.828735598494692</v>
+        <v>6.155591044443931</v>
       </c>
       <c r="E53" t="n">
-        <v>2509.933603089557</v>
+        <v>2510.086822049452</v>
       </c>
       <c r="F53" t="n">
-        <v>1230.170969668671</v>
+        <v>8165.950754338794</v>
       </c>
       <c r="G53" t="n">
-        <v>2055.339040211556</v>
+        <v>1256.10040829</v>
       </c>
       <c r="H53" t="n">
-        <v>3715.060207671528</v>
+        <v>17242.03127002849</v>
       </c>
       <c r="I53" t="n">
-        <v>86.54095031632029</v>
+        <v>102.7376527050134</v>
       </c>
       <c r="J53" t="n">
-        <v>216.8420491185615</v>
+        <v>1934.510427796211</v>
       </c>
     </row>
     <row r="54">
@@ -2255,31 +2255,31 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1581635.389724855</v>
+        <v>-5519988.665747834</v>
       </c>
       <c r="C54" t="n">
-        <v>0.02018496222068797</v>
+        <v>0.09843171354371447</v>
       </c>
       <c r="D54" t="n">
-        <v>0.7888968682355446</v>
+        <v>10.88988920489602</v>
       </c>
       <c r="E54" t="n">
-        <v>2447.730859760201</v>
+        <v>2549.396203199878</v>
       </c>
       <c r="F54" t="n">
-        <v>1209.824039007227</v>
+        <v>8191.917331594314</v>
       </c>
       <c r="G54" t="n">
-        <v>2337.425520689635</v>
+        <v>1255.026870053335</v>
       </c>
       <c r="H54" t="n">
-        <v>3569.255407641305</v>
+        <v>14157.44678325964</v>
       </c>
       <c r="I54" t="n">
-        <v>85.86424235771922</v>
+        <v>90.10982389012359</v>
       </c>
       <c r="J54" t="n">
-        <v>195.2605594826683</v>
+        <v>1960.157602404039</v>
       </c>
     </row>
     <row r="55">
@@ -2289,31 +2289,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>692800.5719850768</v>
+        <v>-5171515.984815619</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0966165065815846</v>
+        <v>0.06019956693683273</v>
       </c>
       <c r="D55" t="n">
-        <v>10.40536391663424</v>
+        <v>7.855086073497375</v>
       </c>
       <c r="E55" t="n">
-        <v>2570.649084639864</v>
+        <v>2438.955569292856</v>
       </c>
       <c r="F55" t="n">
-        <v>1280.532300147903</v>
+        <v>8216.138234137128</v>
       </c>
       <c r="G55" t="n">
-        <v>1259.214982866438</v>
+        <v>1255.748614426199</v>
       </c>
       <c r="H55" t="n">
-        <v>3170.379588278549</v>
+        <v>16002.30998511903</v>
       </c>
       <c r="I55" t="n">
-        <v>84.09391745078169</v>
+        <v>91.47111743497874</v>
       </c>
       <c r="J55" t="n">
-        <v>195.5282953165672</v>
+        <v>1965.85875253177</v>
       </c>
     </row>
     <row r="56">
@@ -2323,31 +2323,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1646357.65634337</v>
+        <v>-5204929.931988206</v>
       </c>
       <c r="C56" t="n">
-        <v>0.01342690189595792</v>
+        <v>0.06406119967749896</v>
       </c>
       <c r="D56" t="n">
-        <v>1.986308806808912</v>
+        <v>5.003487341482948</v>
       </c>
       <c r="E56" t="n">
-        <v>2477.104346711269</v>
+        <v>2486.81292378771</v>
       </c>
       <c r="F56" t="n">
-        <v>1237.510295920878</v>
+        <v>7788.284000274549</v>
       </c>
       <c r="G56" t="n">
-        <v>2381.008073826752</v>
+        <v>1259.733203907482</v>
       </c>
       <c r="H56" t="n">
-        <v>3730.233094912576</v>
+        <v>15844.60738964249</v>
       </c>
       <c r="I56" t="n">
-        <v>84.5099597110451</v>
+        <v>106.9708080845436</v>
       </c>
       <c r="J56" t="n">
-        <v>208.100596143392</v>
+        <v>1957.286213228019</v>
       </c>
     </row>
     <row r="57">
@@ -2357,31 +2357,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2011390.917103368</v>
+        <v>-5270919.191655843</v>
       </c>
       <c r="C57" t="n">
-        <v>0.004523097349159737</v>
+        <v>0.0713943260280509</v>
       </c>
       <c r="D57" t="n">
-        <v>1.110223024625157e-14</v>
+        <v>9.568621525552679</v>
       </c>
       <c r="E57" t="n">
-        <v>2442.228060785573</v>
+        <v>2574.493354587281</v>
       </c>
       <c r="F57" t="n">
-        <v>1268.956690790284</v>
+        <v>8206.484528945562</v>
       </c>
       <c r="G57" t="n">
-        <v>2861.074861668464</v>
+        <v>1255.253169555717</v>
       </c>
       <c r="H57" t="n">
-        <v>3731.999310569461</v>
+        <v>15450.7350734365</v>
       </c>
       <c r="I57" t="n">
-        <v>103.9066595564151</v>
+        <v>84.50589787288011</v>
       </c>
       <c r="J57" t="n">
-        <v>251.8059913535859</v>
+        <v>2150.899378702939</v>
       </c>
     </row>
     <row r="58">
@@ -2391,31 +2391,31 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1322121.083203467</v>
+        <v>-4306997.176461095</v>
       </c>
       <c r="C58" t="n">
-        <v>0.02987166381921702</v>
+        <v>0.006684531796669171</v>
       </c>
       <c r="D58" t="n">
-        <v>2.686619030808202</v>
+        <v>0.3201795464947255</v>
       </c>
       <c r="E58" t="n">
-        <v>2480.029742985157</v>
+        <v>2469.098342243915</v>
       </c>
       <c r="F58" t="n">
-        <v>1227.57814723571</v>
+        <v>7821.202802604879</v>
       </c>
       <c r="G58" t="n">
-        <v>1953.011622320739</v>
+        <v>1255.193869945822</v>
       </c>
       <c r="H58" t="n">
-        <v>3731.989346715555</v>
+        <v>20604.26748290098</v>
       </c>
       <c r="I58" t="n">
-        <v>84.52673929068912</v>
+        <v>107.4668627791198</v>
       </c>
       <c r="J58" t="n">
-        <v>194.5480244228917</v>
+        <v>1942.599627834065</v>
       </c>
     </row>
     <row r="59">
@@ -2425,31 +2425,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1014806.89302542</v>
+        <v>-5468047.096578842</v>
       </c>
       <c r="C59" t="n">
-        <v>0.04888185122843726</v>
+        <v>0.09268334270847396</v>
       </c>
       <c r="D59" t="n">
-        <v>3.303045250432313</v>
+        <v>10.66159296629966</v>
       </c>
       <c r="E59" t="n">
-        <v>2445.54407885717</v>
+        <v>2585.981914236754</v>
       </c>
       <c r="F59" t="n">
-        <v>1222.242658400345</v>
+        <v>8173.605762116894</v>
       </c>
       <c r="G59" t="n">
-        <v>1547.690688591744</v>
+        <v>1255.015148759647</v>
       </c>
       <c r="H59" t="n">
-        <v>3730.510983105602</v>
+        <v>14430.90205885456</v>
       </c>
       <c r="I59" t="n">
-        <v>86.00716959064668</v>
+        <v>99.02848105207883</v>
       </c>
       <c r="J59" t="n">
-        <v>233.4699031185949</v>
+        <v>1941.208395095426</v>
       </c>
     </row>
     <row r="60">
@@ -2459,31 +2459,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1021604.314393705</v>
+        <v>-5182604.46081673</v>
       </c>
       <c r="C60" t="n">
-        <v>0.04810371609287201</v>
+        <v>0.06132281099400774</v>
       </c>
       <c r="D60" t="n">
-        <v>4.46786935345802</v>
+        <v>5.134990245809822</v>
       </c>
       <c r="E60" t="n">
-        <v>2448.718903547516</v>
+        <v>2559.019996203059</v>
       </c>
       <c r="F60" t="n">
-        <v>1268.839183610466</v>
+        <v>7794.119082669431</v>
       </c>
       <c r="G60" t="n">
-        <v>1555.305493176955</v>
+        <v>1255.10533582891</v>
       </c>
       <c r="H60" t="n">
-        <v>3731.935281113267</v>
+        <v>15974.73730060442</v>
       </c>
       <c r="I60" t="n">
-        <v>84.77894614820507</v>
+        <v>97.94681114712324</v>
       </c>
       <c r="J60" t="n">
-        <v>227.8496205131487</v>
+        <v>1953.961962473518</v>
       </c>
     </row>
     <row r="61">
@@ -2493,31 +2493,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>820761.6043824913</v>
+        <v>-5342550.729796441</v>
       </c>
       <c r="C61" t="n">
-        <v>0.06302094646699738</v>
+        <v>0.07888574446311061</v>
       </c>
       <c r="D61" t="n">
-        <v>8.359665391352555</v>
+        <v>9.112528903737049</v>
       </c>
       <c r="E61" t="n">
-        <v>2592.59200251648</v>
+        <v>2465.157070276316</v>
       </c>
       <c r="F61" t="n">
-        <v>1273.61765568844</v>
+        <v>8204.708915973926</v>
       </c>
       <c r="G61" t="n">
-        <v>1287.342703413538</v>
+        <v>1255.011890769073</v>
       </c>
       <c r="H61" t="n">
-        <v>3731.797879461202</v>
+        <v>15101.30060558328</v>
       </c>
       <c r="I61" t="n">
-        <v>87.91161411363615</v>
+        <v>102.3970942194325</v>
       </c>
       <c r="J61" t="n">
-        <v>195.0616330151345</v>
+        <v>1947.874876310771</v>
       </c>
     </row>
     <row r="62">
@@ -2527,31 +2527,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1811116.821436365</v>
+        <v>-4640514.050270997</v>
       </c>
       <c r="C62" t="n">
-        <v>0.008411182450817234</v>
+        <v>0.01901182453750033</v>
       </c>
       <c r="D62" t="n">
-        <v>1.946685733394493</v>
+        <v>1.365947405181545</v>
       </c>
       <c r="E62" t="n">
-        <v>2582.981337833131</v>
+        <v>2514.997049418864</v>
       </c>
       <c r="F62" t="n">
-        <v>1219.241741415662</v>
+        <v>7779.981955012998</v>
       </c>
       <c r="G62" t="n">
-        <v>2595.710702769236</v>
+        <v>1255.384182569081</v>
       </c>
       <c r="H62" t="n">
-        <v>3731.603947627427</v>
+        <v>18838.10624153302</v>
       </c>
       <c r="I62" t="n">
-        <v>92.89670783193422</v>
+        <v>109.1807898677032</v>
       </c>
       <c r="J62" t="n">
-        <v>214.7493970309359</v>
+        <v>1980.661163847135</v>
       </c>
     </row>
     <row r="63">
@@ -2561,31 +2561,31 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>745910.4367494012</v>
+        <v>-4967482.547674109</v>
       </c>
       <c r="C63" t="n">
-        <v>0.08070289713234217</v>
+        <v>0.04260854348261988</v>
       </c>
       <c r="D63" t="n">
-        <v>9.200165798809179</v>
+        <v>6.961378918986972</v>
       </c>
       <c r="E63" t="n">
-        <v>2583.876564210336</v>
+        <v>2495.651009896355</v>
       </c>
       <c r="F63" t="n">
-        <v>1280.920016395885</v>
+        <v>8216.566723001479</v>
       </c>
       <c r="G63" t="n">
-        <v>1259.215254682566</v>
+        <v>1258.239781347412</v>
       </c>
       <c r="H63" t="n">
-        <v>3449.463402221316</v>
+        <v>17058.99665184658</v>
       </c>
       <c r="I63" t="n">
-        <v>84.09392713193954</v>
+        <v>94.32951825409658</v>
       </c>
       <c r="J63" t="n">
-        <v>196.2041806120098</v>
+        <v>2019.668696392658</v>
       </c>
     </row>
     <row r="64">
@@ -2595,31 +2595,31 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>760928.9255113086</v>
+        <v>-5341563.371619412</v>
       </c>
       <c r="C64" t="n">
-        <v>0.076549325765284</v>
+        <v>0.07913935235583129</v>
       </c>
       <c r="D64" t="n">
-        <v>8.66687065758952</v>
+        <v>8.889003218241875</v>
       </c>
       <c r="E64" t="n">
-        <v>2590.137615162349</v>
+        <v>2439.068484314829</v>
       </c>
       <c r="F64" t="n">
-        <v>1257.51784358422</v>
+        <v>8199.381775111735</v>
       </c>
       <c r="G64" t="n">
-        <v>1259.214528229732</v>
+        <v>1260.260220640117</v>
       </c>
       <c r="H64" t="n">
-        <v>3524.139007661841</v>
+        <v>15086.65166915146</v>
       </c>
       <c r="I64" t="n">
-        <v>84.0244366517385</v>
+        <v>102.7440196188687</v>
       </c>
       <c r="J64" t="n">
-        <v>262.9050704397296</v>
+        <v>1967.442890482333</v>
       </c>
     </row>
     <row r="65">
@@ -2629,31 +2629,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1153978.86069012</v>
+        <v>-5233556.286334843</v>
       </c>
       <c r="C65" t="n">
-        <v>0.03956628642068265</v>
+        <v>0.06687132715334036</v>
       </c>
       <c r="D65" t="n">
-        <v>4.463892339922992</v>
+        <v>7.616958054973299</v>
       </c>
       <c r="E65" t="n">
-        <v>2488.200079291773</v>
+        <v>2439.4750088122</v>
       </c>
       <c r="F65" t="n">
-        <v>1256.900415627084</v>
+        <v>8133.4181230451</v>
       </c>
       <c r="G65" t="n">
-        <v>1727.840153170875</v>
+        <v>1255.430075444035</v>
       </c>
       <c r="H65" t="n">
-        <v>3731.946868887059</v>
+        <v>15687.1079728604</v>
       </c>
       <c r="I65" t="n">
-        <v>84.70612636471991</v>
+        <v>90.60002265493661</v>
       </c>
       <c r="J65" t="n">
-        <v>294.3411395546052</v>
+        <v>1929.695487455846</v>
       </c>
     </row>
     <row r="66">
@@ -2663,31 +2663,31 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2107315.568725627</v>
+        <v>-4696078.484109431</v>
       </c>
       <c r="C66" t="n">
-        <v>0.002696371319604166</v>
+        <v>0.0220191971924462</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8386003380988494</v>
+        <v>1.223851753959526</v>
       </c>
       <c r="E66" t="n">
-        <v>2589.914016853753</v>
+        <v>2486.81292378771</v>
       </c>
       <c r="F66" t="n">
-        <v>1219.106617857395</v>
+        <v>7753.804697302319</v>
       </c>
       <c r="G66" t="n">
-        <v>2986.459787380991</v>
+        <v>1255.509709976747</v>
       </c>
       <c r="H66" t="n">
-        <v>3731.453341208289</v>
+        <v>18546.11755301013</v>
       </c>
       <c r="I66" t="n">
-        <v>84.24104672553754</v>
+        <v>102.1019554821396</v>
       </c>
       <c r="J66" t="n">
-        <v>229.9349071884814</v>
+        <v>2022.337696612046</v>
       </c>
     </row>
     <row r="67">
@@ -2697,31 +2697,31 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>930737.7496861106</v>
+        <v>-5498392.250621079</v>
       </c>
       <c r="C67" t="n">
-        <v>0.05516458713238149</v>
+        <v>0.09602323809307377</v>
       </c>
       <c r="D67" t="n">
-        <v>4.715440195158516</v>
+        <v>6.734117283333418</v>
       </c>
       <c r="E67" t="n">
-        <v>2492.54115500578</v>
+        <v>2485.055486813118</v>
       </c>
       <c r="F67" t="n">
-        <v>1217.782153830841</v>
+        <v>7755.604483375063</v>
       </c>
       <c r="G67" t="n">
-        <v>1435.105318366942</v>
+        <v>1255.50927433805</v>
       </c>
       <c r="H67" t="n">
-        <v>3731.992829750696</v>
+        <v>14316.54653439611</v>
       </c>
       <c r="I67" t="n">
-        <v>86.3584293978697</v>
+        <v>115.510140052735</v>
       </c>
       <c r="J67" t="n">
-        <v>242.2779212097666</v>
+        <v>1932.88558510729</v>
       </c>
     </row>
     <row r="68">
@@ -2731,31 +2731,31 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1647253.95077963</v>
+        <v>-4833749.077012093</v>
       </c>
       <c r="C68" t="n">
-        <v>0.01338041197255918</v>
+        <v>0.03174858259782366</v>
       </c>
       <c r="D68" t="n">
-        <v>2.158621186393261</v>
+        <v>1.967516887830811</v>
       </c>
       <c r="E68" t="n">
-        <v>2509.931588894074</v>
+        <v>2436.629491336082</v>
       </c>
       <c r="F68" t="n">
-        <v>1237.510295920878</v>
+        <v>7777.80217928589</v>
       </c>
       <c r="G68" t="n">
-        <v>2381.008073826752</v>
+        <v>1255.956165283309</v>
       </c>
       <c r="H68" t="n">
-        <v>3731.871007759169</v>
+        <v>17823.9183728047</v>
       </c>
       <c r="I68" t="n">
-        <v>84.70500056168606</v>
+        <v>91.95105129283434</v>
       </c>
       <c r="J68" t="n">
-        <v>207.4527297149541</v>
+        <v>1989.824630705073</v>
       </c>
     </row>
     <row r="69">
@@ -2765,31 +2765,31 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1054616.00040741</v>
+        <v>-5493205.655179165</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0451552571139788</v>
+        <v>0.09555393634396607</v>
       </c>
       <c r="D69" t="n">
-        <v>6.31829834810429</v>
+        <v>10.18138554493085</v>
       </c>
       <c r="E69" t="n">
-        <v>2590.665037854736</v>
+        <v>2480.559666664724</v>
       </c>
       <c r="F69" t="n">
-        <v>1217.532769110703</v>
+        <v>8195.156986868762</v>
       </c>
       <c r="G69" t="n">
-        <v>1597.437017390858</v>
+        <v>1255.50927433805</v>
       </c>
       <c r="H69" t="n">
-        <v>3731.993041052162</v>
+        <v>14300.1116353524</v>
       </c>
       <c r="I69" t="n">
-        <v>88.00763231292697</v>
+        <v>115.510140052735</v>
       </c>
       <c r="J69" t="n">
-        <v>191.9740705313258</v>
+        <v>1967.466606955419</v>
       </c>
     </row>
     <row r="70">
@@ -2799,31 +2799,31 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1589496.828136327</v>
+        <v>-5377166.784444997</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0156845504718186</v>
+        <v>0.08350893510215436</v>
       </c>
       <c r="D70" t="n">
-        <v>4.162387866895012</v>
+        <v>7.31206981346647</v>
       </c>
       <c r="E70" t="n">
-        <v>2585.964593260787</v>
+        <v>2575.535110991356</v>
       </c>
       <c r="F70" t="n">
-        <v>1278.759508126346</v>
+        <v>7833.694035625397</v>
       </c>
       <c r="G70" t="n">
-        <v>2302.24046604739</v>
+        <v>1256.025230395052</v>
       </c>
       <c r="H70" t="n">
-        <v>3731.896317426207</v>
+        <v>14901.68411051628</v>
       </c>
       <c r="I70" t="n">
-        <v>88.00763231292697</v>
+        <v>100.4297897480496</v>
       </c>
       <c r="J70" t="n">
-        <v>192.7326707079728</v>
+        <v>2344.741622202006</v>
       </c>
     </row>
     <row r="71">
@@ -2833,31 +2833,31 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1131994.426242305</v>
+        <v>-4910417.842328825</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0403770025531482</v>
+        <v>0.03791087709486255</v>
       </c>
       <c r="D71" t="n">
-        <v>6.553106676750742</v>
+        <v>5.913286011218455</v>
       </c>
       <c r="E71" t="n">
-        <v>2592.931188584174</v>
+        <v>2511.071694061482</v>
       </c>
       <c r="F71" t="n">
-        <v>1241.653767266167</v>
+        <v>8150.618817529073</v>
       </c>
       <c r="G71" t="n">
-        <v>1698.860189612138</v>
+        <v>1255.757424900388</v>
       </c>
       <c r="H71" t="n">
-        <v>3731.791793697182</v>
+        <v>17371.92099496725</v>
       </c>
       <c r="I71" t="n">
-        <v>85.1853905967606</v>
+        <v>107.6524422432934</v>
       </c>
       <c r="J71" t="n">
-        <v>201.7171190485092</v>
+        <v>2038.369265676572</v>
       </c>
     </row>
     <row r="72">
@@ -2867,31 +2867,31 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>904894.9456783739</v>
+        <v>-4222586.424179119</v>
       </c>
       <c r="C72" t="n">
-        <v>0.05676318682885951</v>
+        <v>0.004409315398213045</v>
       </c>
       <c r="D72" t="n">
-        <v>6.711825485840972</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>2587.312883536992</v>
+        <v>2464.050188742262</v>
       </c>
       <c r="F72" t="n">
-        <v>1242.492951148266</v>
+        <v>7780.307295895598</v>
       </c>
       <c r="G72" t="n">
-        <v>1398.798024558932</v>
+        <v>1255.233594426257</v>
       </c>
       <c r="H72" t="n">
-        <v>3730.381233674271</v>
+        <v>21051.25163204323</v>
       </c>
       <c r="I72" t="n">
-        <v>86.04467081749218</v>
+        <v>115.046493970844</v>
       </c>
       <c r="J72" t="n">
-        <v>232.0435808976093</v>
+        <v>1965.799436996922</v>
       </c>
     </row>
     <row r="73">
@@ -2901,31 +2901,31 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1535715.827282244</v>
+        <v>-4482585.74859315</v>
       </c>
       <c r="C73" t="n">
-        <v>0.01774629390240798</v>
+        <v>0.01152283895836657</v>
       </c>
       <c r="D73" t="n">
-        <v>1.38203709011252</v>
+        <v>2.267296742169467</v>
       </c>
       <c r="E73" t="n">
-        <v>2449.683968297591</v>
+        <v>2561.714895727501</v>
       </c>
       <c r="F73" t="n">
-        <v>1241.532441113226</v>
+        <v>7971.384359417307</v>
       </c>
       <c r="G73" t="n">
-        <v>2236.46934935892</v>
+        <v>1255.299689489241</v>
       </c>
       <c r="H73" t="n">
-        <v>3727.063140748736</v>
+        <v>19653.54782230453</v>
       </c>
       <c r="I73" t="n">
-        <v>84.05752761998019</v>
+        <v>98.76559409480002</v>
       </c>
       <c r="J73" t="n">
-        <v>201.3031483461789</v>
+        <v>1953.961962473518</v>
       </c>
     </row>
     <row r="74">
@@ -2935,31 +2935,31 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>798913.4004300741</v>
+        <v>-4377713.845440855</v>
       </c>
       <c r="C74" t="n">
-        <v>0.06639557208748756</v>
+        <v>0.00857613528289242</v>
       </c>
       <c r="D74" t="n">
-        <v>4.256413052952135</v>
+        <v>0.1294196701506989</v>
       </c>
       <c r="E74" t="n">
-        <v>2442.779415535266</v>
+        <v>2487.272422961994</v>
       </c>
       <c r="F74" t="n">
-        <v>1219.54510345679</v>
+        <v>7759.229404232497</v>
       </c>
       <c r="G74" t="n">
-        <v>1269.022347534137</v>
+        <v>1255.557521033971</v>
       </c>
       <c r="H74" t="n">
-        <v>3709.773149517732</v>
+        <v>20232.23816010924</v>
       </c>
       <c r="I74" t="n">
-        <v>86.07562966286267</v>
+        <v>113.6662281230495</v>
       </c>
       <c r="J74" t="n">
-        <v>189.4230753822649</v>
+        <v>1949.119589541992</v>
       </c>
     </row>
     <row r="75">
@@ -2969,31 +2969,31 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1075953.934356044</v>
+        <v>-5100355.846024428</v>
       </c>
       <c r="C75" t="n">
-        <v>0.04400731832788546</v>
+        <v>0.05340378773463268</v>
       </c>
       <c r="D75" t="n">
-        <v>4.907805816801247</v>
+        <v>7.569354944979157</v>
       </c>
       <c r="E75" t="n">
-        <v>2527.111403833361</v>
+        <v>2466.614919425309</v>
       </c>
       <c r="F75" t="n">
-        <v>1222.078294306764</v>
+        <v>8212.396711167774</v>
       </c>
       <c r="G75" t="n">
-        <v>1627.325669958152</v>
+        <v>1255.748614426199</v>
       </c>
       <c r="H75" t="n">
-        <v>3730.633095689709</v>
+        <v>16372.48804584764</v>
       </c>
       <c r="I75" t="n">
-        <v>92.73846105359763</v>
+        <v>91.47111743497874</v>
       </c>
       <c r="J75" t="n">
-        <v>188.5186139339589</v>
+        <v>2001.122173696595</v>
       </c>
     </row>
     <row r="76">
@@ -3003,31 +3003,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1259829.251296169</v>
+        <v>-5181170.234024459</v>
       </c>
       <c r="C76" t="n">
-        <v>0.03360448352889207</v>
+        <v>0.06145815101929018</v>
       </c>
       <c r="D76" t="n">
-        <v>5.304131256775091</v>
+        <v>4.838600500585699</v>
       </c>
       <c r="E76" t="n">
-        <v>2528.461374103187</v>
+        <v>2486.81292378771</v>
       </c>
       <c r="F76" t="n">
-        <v>1273.487900644294</v>
+        <v>7788.284000274549</v>
       </c>
       <c r="G76" t="n">
-        <v>1872.065343423552</v>
+        <v>1259.733203907482</v>
       </c>
       <c r="H76" t="n">
-        <v>3716.404998913496</v>
+        <v>15970.51935438183</v>
       </c>
       <c r="I76" t="n">
-        <v>92.89248504971265</v>
+        <v>102.2802057121545</v>
       </c>
       <c r="J76" t="n">
-        <v>202.2996207511111</v>
+        <v>1957.286213228019</v>
       </c>
     </row>
     <row r="77">
@@ -3037,31 +3037,31 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>708868.7975052925</v>
+        <v>-5260950.41625172</v>
       </c>
       <c r="C77" t="n">
-        <v>0.09173325429260476</v>
+        <v>0.06998936952842759</v>
       </c>
       <c r="D77" t="n">
-        <v>7.834516205760799</v>
+        <v>9.070459847506774</v>
       </c>
       <c r="E77" t="n">
-        <v>2589.039678552999</v>
+        <v>2545.699468391321</v>
       </c>
       <c r="F77" t="n">
-        <v>1207.455898466425</v>
+        <v>8184.192555972839</v>
       </c>
       <c r="G77" t="n">
-        <v>1259.057889081738</v>
+        <v>1255.571170823853</v>
       </c>
       <c r="H77" t="n">
-        <v>3261.374257855209</v>
+        <v>15522.43550003021</v>
       </c>
       <c r="I77" t="n">
-        <v>87.64453301492931</v>
+        <v>103.1363312423891</v>
       </c>
       <c r="J77" t="n">
-        <v>187.0241618474446</v>
+        <v>1965.753575481235</v>
       </c>
     </row>
     <row r="78">
@@ -3071,31 +3071,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>726144.9901699013</v>
+        <v>-5339031.141301891</v>
       </c>
       <c r="C78" t="n">
-        <v>0.08661695316873733</v>
+        <v>0.07909707110124974</v>
       </c>
       <c r="D78" t="n">
-        <v>8.450851388490477</v>
+        <v>8.747220711089444</v>
       </c>
       <c r="E78" t="n">
-        <v>2567.705580197266</v>
+        <v>2439.068484314829</v>
       </c>
       <c r="F78" t="n">
-        <v>1241.994191395353</v>
+        <v>8179.118486069965</v>
       </c>
       <c r="G78" t="n">
-        <v>1259.230440973854</v>
+        <v>1264.075909024716</v>
       </c>
       <c r="H78" t="n">
-        <v>3350.20896623827</v>
+        <v>15086.65166915146</v>
       </c>
       <c r="I78" t="n">
-        <v>84.09392754969986</v>
+        <v>102.7440196188687</v>
       </c>
       <c r="J78" t="n">
-        <v>196.2041806120098</v>
+        <v>1967.442890482333</v>
       </c>
     </row>
     <row r="79">
@@ -3105,31 +3105,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1054742.800723623</v>
+        <v>-5445053.107985483</v>
       </c>
       <c r="C79" t="n">
-        <v>0.04512330906529771</v>
+        <v>0.09018676837019297</v>
       </c>
       <c r="D79" t="n">
-        <v>6.482789707540515</v>
+        <v>9.532233674919798</v>
       </c>
       <c r="E79" t="n">
-        <v>2585.964593260787</v>
+        <v>2485.16882835969</v>
       </c>
       <c r="F79" t="n">
-        <v>1229.837149248563</v>
+        <v>8150.036898050281</v>
       </c>
       <c r="G79" t="n">
-        <v>1597.437017390858</v>
+        <v>1255.432444068512</v>
       </c>
       <c r="H79" t="n">
-        <v>3731.892847762214</v>
+        <v>14561.47047407296</v>
       </c>
       <c r="I79" t="n">
-        <v>88.00763231292697</v>
+        <v>102.5542991252319</v>
       </c>
       <c r="J79" t="n">
-        <v>192.7295423007315</v>
+        <v>1948.482376477148</v>
       </c>
     </row>
     <row r="80">
@@ -3139,31 +3139,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>727596.2017938538</v>
+        <v>-4593338.711699007</v>
       </c>
       <c r="C80" t="n">
-        <v>0.08627129073746249</v>
+        <v>0.01646713634148808</v>
       </c>
       <c r="D80" t="n">
-        <v>9.600675184901529</v>
+        <v>0.5864690835132413</v>
       </c>
       <c r="E80" t="n">
-        <v>2591.804549571526</v>
+        <v>2485.314993985168</v>
       </c>
       <c r="F80" t="n">
-        <v>1279.867836301202</v>
+        <v>7756.519386763222</v>
       </c>
       <c r="G80" t="n">
-        <v>1259.693345553427</v>
+        <v>1256.105203733453</v>
       </c>
       <c r="H80" t="n">
-        <v>3350.245931271977</v>
+        <v>19087.34782365341</v>
       </c>
       <c r="I80" t="n">
-        <v>84.09391745078169</v>
+        <v>89.52047015742495</v>
       </c>
       <c r="J80" t="n">
-        <v>195.5282953165672</v>
+        <v>2022.337696612046</v>
       </c>
     </row>
     <row r="81">
@@ -3173,31 +3173,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>835342.9037167263</v>
+        <v>-4292243.054534852</v>
       </c>
       <c r="C81" t="n">
-        <v>0.06292296149658877</v>
+        <v>0.006289958514110348</v>
       </c>
       <c r="D81" t="n">
-        <v>4.931109902885112</v>
+        <v>0.3182248365442453</v>
       </c>
       <c r="E81" t="n">
-        <v>2457.633126014229</v>
+        <v>2467.742674294681</v>
       </c>
       <c r="F81" t="n">
-        <v>1241.713632206269</v>
+        <v>7821.202802604879</v>
       </c>
       <c r="G81" t="n">
-        <v>1312.982177370471</v>
+        <v>1255.367314930004</v>
       </c>
       <c r="H81" t="n">
-        <v>3722.29479284592</v>
+        <v>20681.61279929433</v>
       </c>
       <c r="I81" t="n">
-        <v>88.07330672893119</v>
+        <v>107.4668627791198</v>
       </c>
       <c r="J81" t="n">
-        <v>192.9239146612555</v>
+        <v>1942.599627834065</v>
       </c>
     </row>
     <row r="82">
@@ -3207,31 +3207,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>682995.1431651918</v>
+        <v>-4378010.62986298</v>
       </c>
       <c r="C82" t="n">
-        <v>0.09956354419634414</v>
+        <v>0.00857767963492026</v>
       </c>
       <c r="D82" t="n">
-        <v>10.08582268673371</v>
+        <v>0.8253138949636973</v>
       </c>
       <c r="E82" t="n">
-        <v>2592.991276532166</v>
+        <v>2487.272422961994</v>
       </c>
       <c r="F82" t="n">
-        <v>1280.608306914651</v>
+        <v>7755.985402463376</v>
       </c>
       <c r="G82" t="n">
-        <v>1259.214982866438</v>
+        <v>1255.263195975544</v>
       </c>
       <c r="H82" t="n">
-        <v>3116.411061228725</v>
+        <v>20232.23816010924</v>
       </c>
       <c r="I82" t="n">
-        <v>84.09392713193954</v>
+        <v>112.7546669479291</v>
       </c>
       <c r="J82" t="n">
-        <v>196.049755831427</v>
+        <v>1949.119589541992</v>
       </c>
     </row>
     <row r="83">
@@ -3241,31 +3241,31 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1440562.544454424</v>
+        <v>-5214085.329688484</v>
       </c>
       <c r="C83" t="n">
-        <v>0.02261967663849678</v>
+        <v>0.06480249713079528</v>
       </c>
       <c r="D83" t="n">
-        <v>3.734011147737171</v>
+        <v>6.369770994946789</v>
       </c>
       <c r="E83" t="n">
-        <v>2590.386363020007</v>
+        <v>2460.694288809373</v>
       </c>
       <c r="F83" t="n">
-        <v>1219.241741415662</v>
+        <v>7973.475535970632</v>
       </c>
       <c r="G83" t="n">
-        <v>2106.534531270115</v>
+        <v>1255.14116255774</v>
       </c>
       <c r="H83" t="n">
-        <v>3731.555088415016</v>
+        <v>15799.55831452257</v>
       </c>
       <c r="I83" t="n">
-        <v>92.78866719324965</v>
+        <v>87.1851986441485</v>
       </c>
       <c r="J83" t="n">
-        <v>207.6139303137879</v>
+        <v>1980.576588665195</v>
       </c>
     </row>
     <row r="84">
@@ -3275,31 +3275,31 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1791653.277423762</v>
+        <v>-5462126.790368449</v>
       </c>
       <c r="C84" t="n">
-        <v>0.008763179947440183</v>
+        <v>0.09197452243287943</v>
       </c>
       <c r="D84" t="n">
-        <v>1.256151237485137</v>
+        <v>6.469389692984495</v>
       </c>
       <c r="E84" t="n">
-        <v>2503.004410580291</v>
+        <v>2451.131891734442</v>
       </c>
       <c r="F84" t="n">
-        <v>1240.771062486394</v>
+        <v>7787.956318755813</v>
       </c>
       <c r="G84" t="n">
-        <v>2571.366009172804</v>
+        <v>1255.014280830339</v>
       </c>
       <c r="H84" t="n">
-        <v>3731.898723187048</v>
+        <v>14511.54640157627</v>
       </c>
       <c r="I84" t="n">
-        <v>85.97882294965767</v>
+        <v>101.9911223925</v>
       </c>
       <c r="J84" t="n">
-        <v>221.1789049853484</v>
+        <v>1932.829738439393</v>
       </c>
     </row>
     <row r="85">
@@ -3309,31 +3309,31 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1904188.438793119</v>
+        <v>-4921427.714283964</v>
       </c>
       <c r="C85" t="n">
-        <v>0.006583604217398438</v>
+        <v>0.03863260051038481</v>
       </c>
       <c r="D85" t="n">
-        <v>0.936792123718333</v>
+        <v>5.993082932013949</v>
       </c>
       <c r="E85" t="n">
-        <v>2509.979017405278</v>
+        <v>2463.622652879647</v>
       </c>
       <c r="F85" t="n">
-        <v>1244.935557401252</v>
+        <v>8202.033580847337</v>
       </c>
       <c r="G85" t="n">
-        <v>2720.348368924267</v>
+        <v>1255.723949052234</v>
       </c>
       <c r="H85" t="n">
-        <v>3731.888397898935</v>
+        <v>17324.87732971011</v>
       </c>
       <c r="I85" t="n">
-        <v>87.80977868958456</v>
+        <v>84.20394449576358</v>
       </c>
       <c r="J85" t="n">
-        <v>190.0630786124664</v>
+        <v>1942.107552209469</v>
       </c>
     </row>
     <row r="86">
@@ -3343,31 +3343,31 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>759065.9327606919</v>
+        <v>-4920937.447117816</v>
       </c>
       <c r="C86" t="n">
-        <v>0.07710196155957058</v>
+        <v>0.03896121050644072</v>
       </c>
       <c r="D86" t="n">
-        <v>8.682208310692218</v>
+        <v>2.640260534327277</v>
       </c>
       <c r="E86" t="n">
-        <v>2589.487723996563</v>
+        <v>2463.622652879647</v>
       </c>
       <c r="F86" t="n">
-        <v>1257.51784358422</v>
+        <v>7761.218946986049</v>
       </c>
       <c r="G86" t="n">
-        <v>1259.180872248725</v>
+        <v>1255.147555726393</v>
       </c>
       <c r="H86" t="n">
-        <v>3514.49814681546</v>
+        <v>17355.87536886432</v>
       </c>
       <c r="I86" t="n">
-        <v>84.0244366517385</v>
+        <v>101.5375921393414</v>
       </c>
       <c r="J86" t="n">
-        <v>262.9050704397296</v>
+        <v>2085.494443316891</v>
       </c>
     </row>
     <row r="87">
@@ -3377,31 +3377,31 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>692995.6208560978</v>
+        <v>-5395639.69157475</v>
       </c>
       <c r="C87" t="n">
-        <v>0.09657299304473409</v>
+        <v>0.08539410238637518</v>
       </c>
       <c r="D87" t="n">
-        <v>10.555838051031</v>
+        <v>9.37589637241153</v>
       </c>
       <c r="E87" t="n">
-        <v>2579.013789164976</v>
+        <v>2466.711357950993</v>
       </c>
       <c r="F87" t="n">
-        <v>1280.532300147903</v>
+        <v>8185.685627818119</v>
       </c>
       <c r="G87" t="n">
-        <v>1259.214982866438</v>
+        <v>1263.964404568589</v>
       </c>
       <c r="H87" t="n">
-        <v>3170.379588278549</v>
+        <v>14781.40840692102</v>
       </c>
       <c r="I87" t="n">
-        <v>86.5078749208476</v>
+        <v>105.8466479789357</v>
       </c>
       <c r="J87" t="n">
-        <v>195.5282953165672</v>
+        <v>2001.893664302716</v>
       </c>
     </row>
     <row r="88">
@@ -3411,31 +3411,31 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>740208.2288151287</v>
+        <v>-5261727.749019803</v>
       </c>
       <c r="C88" t="n">
-        <v>0.08235328398726524</v>
+        <v>0.07025082815069064</v>
       </c>
       <c r="D88" t="n">
-        <v>5.934875412325735</v>
+        <v>8.612721837517689</v>
       </c>
       <c r="E88" t="n">
-        <v>2443.117566714646</v>
+        <v>2463.594245503822</v>
       </c>
       <c r="F88" t="n">
-        <v>1257.279665294598</v>
+        <v>8209.345173751541</v>
       </c>
       <c r="G88" t="n">
-        <v>1259.227952444258</v>
+        <v>1258.215520085859</v>
       </c>
       <c r="H88" t="n">
-        <v>3435.377696043836</v>
+        <v>15512.32044190985</v>
       </c>
       <c r="I88" t="n">
-        <v>86.24189720488927</v>
+        <v>125.8619426250893</v>
       </c>
       <c r="J88" t="n">
-        <v>189.5156020957446</v>
+        <v>1952.461515025369</v>
       </c>
     </row>
     <row r="89">
@@ -3445,31 +3445,31 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>781093.7870703492</v>
+        <v>-4965674.748130498</v>
       </c>
       <c r="C89" t="n">
-        <v>0.07045469535896598</v>
+        <v>0.04293046471581998</v>
       </c>
       <c r="D89" t="n">
-        <v>8.835350987384727</v>
+        <v>2.892380317116972</v>
       </c>
       <c r="E89" t="n">
-        <v>2591.498660104785</v>
+        <v>2478.197147990667</v>
       </c>
       <c r="F89" t="n">
-        <v>1280.982054616899</v>
+        <v>7743.795551513714</v>
       </c>
       <c r="G89" t="n">
-        <v>1259.208821420971</v>
+        <v>1264.068404714532</v>
       </c>
       <c r="H89" t="n">
-        <v>3629.296149303707</v>
+        <v>17089.75216626409</v>
       </c>
       <c r="I89" t="n">
-        <v>84.01741063550429</v>
+        <v>84.68663506493601</v>
       </c>
       <c r="J89" t="n">
-        <v>252.4846312559625</v>
+        <v>2043.140291264604</v>
       </c>
     </row>
     <row r="90">
@@ -3479,31 +3479,31 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1143408.609566523</v>
+        <v>-5095844.334660021</v>
       </c>
       <c r="C90" t="n">
-        <v>0.04157457413709619</v>
+        <v>0.05314160646054523</v>
       </c>
       <c r="D90" t="n">
-        <v>3.958823795061239</v>
+        <v>4.225574734901572</v>
       </c>
       <c r="E90" t="n">
-        <v>2442.000602461651</v>
+        <v>2509.10771369551</v>
       </c>
       <c r="F90" t="n">
-        <v>1280.655055123354</v>
+        <v>7780.138228195602</v>
       </c>
       <c r="G90" t="n">
-        <v>1727.944338557445</v>
+        <v>1255.210737584945</v>
       </c>
       <c r="H90" t="n">
-        <v>3687.498853273488</v>
+        <v>16434.96385471136</v>
       </c>
       <c r="I90" t="n">
-        <v>84.09359380220909</v>
+        <v>109.1807898677032</v>
       </c>
       <c r="J90" t="n">
-        <v>192.2427220025201</v>
+        <v>1980.661163847135</v>
       </c>
     </row>
     <row r="91">
@@ -3513,31 +3513,31 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>926154.7304914756</v>
+        <v>-4978618.751596168</v>
       </c>
       <c r="C91" t="n">
-        <v>0.05513591387227368</v>
+        <v>0.04368841559958235</v>
       </c>
       <c r="D91" t="n">
-        <v>7.108978686904743</v>
+        <v>3.151856100529804</v>
       </c>
       <c r="E91" t="n">
-        <v>2586.200037210767</v>
+        <v>2496.296085247841</v>
       </c>
       <c r="F91" t="n">
-        <v>1242.227808749074</v>
+        <v>7746.540866181781</v>
       </c>
       <c r="G91" t="n">
-        <v>1427.944062013249</v>
+        <v>1258.239781347412</v>
       </c>
       <c r="H91" t="n">
-        <v>3729.125007659857</v>
+        <v>17044.05569773833</v>
       </c>
       <c r="I91" t="n">
-        <v>84.83021237096773</v>
+        <v>94.32951825409658</v>
       </c>
       <c r="J91" t="n">
-        <v>201.8517932951373</v>
+        <v>2019.061799953132</v>
       </c>
     </row>
     <row r="92">
@@ -3547,31 +3547,31 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>734597.2905847452</v>
+        <v>-4187010.021228179</v>
       </c>
       <c r="C92" t="n">
-        <v>0.08409217755575606</v>
+        <v>0.003687885979999048</v>
       </c>
       <c r="D92" t="n">
-        <v>9.407180240742319</v>
+        <v>1.728885721880014</v>
       </c>
       <c r="E92" t="n">
-        <v>2591.804549571526</v>
+        <v>2544.533458458555</v>
       </c>
       <c r="F92" t="n">
-        <v>1280.532300147903</v>
+        <v>8161.445423660882</v>
       </c>
       <c r="G92" t="n">
-        <v>1259.214982866438</v>
+        <v>1257.816919862456</v>
       </c>
       <c r="H92" t="n">
-        <v>3389.066811154727</v>
+        <v>21190.33187647179</v>
       </c>
       <c r="I92" t="n">
-        <v>84.09391745078169</v>
+        <v>92.21816433653068</v>
       </c>
       <c r="J92" t="n">
-        <v>195.5282953165672</v>
+        <v>1937.58342848447</v>
       </c>
     </row>
     <row r="93">
@@ -3581,31 +3581,31 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2129918.711583275</v>
+        <v>-5054938.670591385</v>
       </c>
       <c r="C93" t="n">
-        <v>0.002226013468879904</v>
+        <v>0.04972508470601622</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3217688661280582</v>
+        <v>7.749286212045392</v>
       </c>
       <c r="E93" t="n">
-        <v>2462.389166062893</v>
+        <v>2583.791876012651</v>
       </c>
       <c r="F93" t="n">
-        <v>1279.727869988603</v>
+        <v>8154.9075510609</v>
       </c>
       <c r="G93" t="n">
-        <v>3018.34043225498</v>
+        <v>1259.465527711358</v>
       </c>
       <c r="H93" t="n">
-        <v>3731.729585181685</v>
+        <v>16597.43982076561</v>
       </c>
       <c r="I93" t="n">
-        <v>87.58968799456382</v>
+        <v>90.83045118193783</v>
       </c>
       <c r="J93" t="n">
-        <v>205.9932960537112</v>
+        <v>1939.377950905123</v>
       </c>
     </row>
     <row r="94">
@@ -3615,31 +3615,31 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>910475.6810272477</v>
+        <v>-4987469.747487668</v>
       </c>
       <c r="C94" t="n">
-        <v>0.05734476579834596</v>
+        <v>0.04510427272083675</v>
       </c>
       <c r="D94" t="n">
-        <v>5.170918130876856</v>
+        <v>6.573857484329459</v>
       </c>
       <c r="E94" t="n">
-        <v>2442.000602461651</v>
+        <v>2480.059156245241</v>
       </c>
       <c r="F94" t="n">
-        <v>1280.995654017543</v>
+        <v>8207.640012743414</v>
       </c>
       <c r="G94" t="n">
-        <v>1411.975053425369</v>
+        <v>1272.606893348136</v>
       </c>
       <c r="H94" t="n">
-        <v>3716.44536730948</v>
+        <v>16886.97298015234</v>
       </c>
       <c r="I94" t="n">
-        <v>89.39706095851281</v>
+        <v>84.03382942057493</v>
       </c>
       <c r="J94" t="n">
-        <v>239.2055570521754</v>
+        <v>2151.659187539085</v>
       </c>
     </row>
     <row r="95">
@@ -3649,31 +3649,31 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1731195.649820971</v>
+        <v>-5511938.621013692</v>
       </c>
       <c r="C95" t="n">
-        <v>0.01009300600078905</v>
+        <v>0.09749221003339677</v>
       </c>
       <c r="D95" t="n">
-        <v>0.7033870573529</v>
+        <v>11.01914512599294</v>
       </c>
       <c r="E95" t="n">
-        <v>2442.827169885707</v>
+        <v>2558.185308929768</v>
       </c>
       <c r="F95" t="n">
-        <v>1240.732711023373</v>
+        <v>8206.484528945562</v>
       </c>
       <c r="G95" t="n">
-        <v>2493.823376330359</v>
+        <v>1255.00447774289</v>
       </c>
       <c r="H95" t="n">
-        <v>3731.387035624019</v>
+        <v>14200.1560769448</v>
       </c>
       <c r="I95" t="n">
-        <v>84.0565326789612</v>
+        <v>93.87855623110815</v>
       </c>
       <c r="J95" t="n">
-        <v>193.0169944984708</v>
+        <v>1931.541741568791</v>
       </c>
     </row>
     <row r="96">
@@ -3683,31 +3683,31 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>810029.3159218082</v>
+        <v>-4709868.017454644</v>
       </c>
       <c r="C96" t="n">
-        <v>0.06431871794583982</v>
+        <v>0.02321834257772881</v>
       </c>
       <c r="D96" t="n">
-        <v>5.980432002770907</v>
+        <v>2.380641311907028</v>
       </c>
       <c r="E96" t="n">
-        <v>2504.497152368929</v>
+        <v>2569.523078495736</v>
       </c>
       <c r="F96" t="n">
-        <v>1240.364178618387</v>
+        <v>7794.714384855599</v>
       </c>
       <c r="G96" t="n">
-        <v>1275.758632836178</v>
+        <v>1256.025230395052</v>
       </c>
       <c r="H96" t="n">
-        <v>3731.907662050968</v>
+        <v>18429.58655305488</v>
       </c>
       <c r="I96" t="n">
-        <v>84.02021853379198</v>
+        <v>100.4297897480496</v>
       </c>
       <c r="J96" t="n">
-        <v>210.5738198657721</v>
+        <v>2344.741622202006</v>
       </c>
     </row>
     <row r="97">
@@ -3717,31 +3717,31 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>708778.6230305595</v>
+        <v>-5386543.584488722</v>
       </c>
       <c r="C97" t="n">
-        <v>0.09174061553846291</v>
+        <v>0.08384765103073251</v>
       </c>
       <c r="D97" t="n">
-        <v>7.845815254217314</v>
+        <v>9.426201261852396</v>
       </c>
       <c r="E97" t="n">
-        <v>2586.773415482055</v>
+        <v>2485.432873715014</v>
       </c>
       <c r="F97" t="n">
-        <v>1208.333418376845</v>
+        <v>8186.247115269192</v>
       </c>
       <c r="G97" t="n">
-        <v>1259.057889081738</v>
+        <v>1255.568345854221</v>
       </c>
       <c r="H97" t="n">
-        <v>3261.374257855209</v>
+        <v>14862.37898817654</v>
       </c>
       <c r="I97" t="n">
-        <v>84.07052129981216</v>
+        <v>128.5831802783165</v>
       </c>
       <c r="J97" t="n">
-        <v>187.0241618474446</v>
+        <v>1965.80741355986</v>
       </c>
     </row>
     <row r="98">
@@ -3751,31 +3751,31 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>751117.4267469732</v>
+        <v>-4001897.133103886</v>
       </c>
       <c r="C98" t="n">
-        <v>0.07923934827600945</v>
+        <v>5.799556634528432e-18</v>
       </c>
       <c r="D98" t="n">
-        <v>8.69773218526837</v>
+        <v>0.1010270010697645</v>
       </c>
       <c r="E98" t="n">
-        <v>2586.989447668781</v>
+        <v>2454.914052489735</v>
       </c>
       <c r="F98" t="n">
-        <v>1255.191188505578</v>
+        <v>7799.121213392675</v>
       </c>
       <c r="G98" t="n">
-        <v>1259.621679437566</v>
+        <v>1257.97510366496</v>
       </c>
       <c r="H98" t="n">
-        <v>3476.827715769743</v>
+        <v>22206.09834728213</v>
       </c>
       <c r="I98" t="n">
-        <v>92.91842723578988</v>
+        <v>109.8799099459591</v>
       </c>
       <c r="J98" t="n">
-        <v>193.7004463550273</v>
+        <v>1956.734926623041</v>
       </c>
     </row>
     <row r="99">
@@ -3785,31 +3785,31 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>763605.1079212009</v>
+        <v>-5274731.914293238</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0753732397977996</v>
+        <v>0.07140556435428699</v>
       </c>
       <c r="D99" t="n">
-        <v>6.164988795712212</v>
+        <v>9.49825939250889</v>
       </c>
       <c r="E99" t="n">
-        <v>2449.848236134796</v>
+        <v>2574.493354587281</v>
       </c>
       <c r="F99" t="n">
-        <v>1278.863637921475</v>
+        <v>8200.460665721332</v>
       </c>
       <c r="G99" t="n">
-        <v>1259.128400562588</v>
+        <v>1255.253169555717</v>
       </c>
       <c r="H99" t="n">
-        <v>3555.903913147895</v>
+        <v>15450.7350734365</v>
       </c>
       <c r="I99" t="n">
-        <v>85.35664671540496</v>
+        <v>84.50589787288011</v>
       </c>
       <c r="J99" t="n">
-        <v>198.5884648648545</v>
+        <v>1941.21050430932</v>
       </c>
     </row>
     <row r="100">
@@ -3819,31 +3819,31 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2240352.439224448</v>
+        <v>-4469726.629230129</v>
       </c>
       <c r="C100" t="n">
-        <v>8.907635213222609e-05</v>
+        <v>0.01130662674270547</v>
       </c>
       <c r="D100" t="n">
-        <v>1.742193244590218</v>
+        <v>3.203350164119834</v>
       </c>
       <c r="E100" t="n">
-        <v>2511.568147610441</v>
+        <v>2463.273290354301</v>
       </c>
       <c r="F100" t="n">
-        <v>1234.313492690015</v>
+        <v>8198.204317372103</v>
       </c>
       <c r="G100" t="n">
-        <v>3164.357058352475</v>
+        <v>1257.643416849234</v>
       </c>
       <c r="H100" t="n">
-        <v>3731.772266954855</v>
+        <v>19693.61208989197</v>
       </c>
       <c r="I100" t="n">
-        <v>87.01969572778252</v>
+        <v>102.1019554821396</v>
       </c>
       <c r="J100" t="n">
-        <v>191.3471552759158</v>
+        <v>2022.337696612046</v>
       </c>
     </row>
     <row r="101">
@@ -3853,31 +3853,31 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1306503.874273063</v>
+        <v>-4709866.363586869</v>
       </c>
       <c r="C101" t="n">
-        <v>0.03040387910946099</v>
+        <v>0.02321782007355564</v>
       </c>
       <c r="D101" t="n">
-        <v>5.347649097805595</v>
+        <v>2.29898344760997</v>
       </c>
       <c r="E101" t="n">
-        <v>2585.106277320041</v>
+        <v>2569.523078495736</v>
       </c>
       <c r="F101" t="n">
-        <v>1231.373430765649</v>
+        <v>7793.276727699611</v>
       </c>
       <c r="G101" t="n">
-        <v>1930.600813537884</v>
+        <v>1256.075020231994</v>
       </c>
       <c r="H101" t="n">
-        <v>3729.304267400314</v>
+        <v>18429.58655305488</v>
       </c>
       <c r="I101" t="n">
-        <v>85.93685433092823</v>
+        <v>100.4297897480496</v>
       </c>
       <c r="J101" t="n">
-        <v>187.3864584949264</v>
+        <v>2344.139000223059</v>
       </c>
     </row>
     <row r="102">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>

--- a/output_data/Offgrid_Pareto_Results_3D.xlsx
+++ b/output_data/Offgrid_Pareto_Results_3D.xlsx
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-5527143.052154474</v>
+        <v>302600.4375273865</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09918049913777358</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>11.29069814592244</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2579.874217924712</v>
+        <v>2454.359737971311</v>
       </c>
       <c r="F2" t="n">
-        <v>8206.484528945562</v>
+        <v>2960.434845345824</v>
       </c>
       <c r="G2" t="n">
-        <v>1255.004996872778</v>
+        <v>2230.095223922531</v>
       </c>
       <c r="H2" t="n">
-        <v>14117.78845111284</v>
+        <v>8675.514169274191</v>
       </c>
       <c r="I2" t="n">
-        <v>93.87855623110815</v>
+        <v>100.4364177857256</v>
       </c>
       <c r="J2" t="n">
-        <v>1931.602045834714</v>
+        <v>659.136535958222</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-3168624.409700077</v>
+        <v>-954402.0918039726</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.09999540812959239</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>8.301774116405092</v>
       </c>
       <c r="E3" t="n">
-        <v>2439.281048987979</v>
+        <v>2588.58888960435</v>
       </c>
       <c r="F3" t="n">
-        <v>7753.342438923796</v>
+        <v>2921.44556046302</v>
       </c>
       <c r="G3" t="n">
-        <v>2808.256004783841</v>
+        <v>1264.046558389344</v>
       </c>
       <c r="H3" t="n">
-        <v>20413.9174823673</v>
+        <v>5892.646911059362</v>
       </c>
       <c r="I3" t="n">
-        <v>101.9804949063454</v>
+        <v>102.921918415785</v>
       </c>
       <c r="J3" t="n">
-        <v>1932.07697256901</v>
+        <v>659.1360767326823</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-5534315.230625564</v>
+        <v>-950698.7851677081</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09999928290216027</v>
+        <v>0.09924701512664022</v>
       </c>
       <c r="D4" t="n">
-        <v>6.871742562030647</v>
+        <v>11.0275596804852</v>
       </c>
       <c r="E4" t="n">
-        <v>2480.637016194424</v>
+        <v>2597.986743311546</v>
       </c>
       <c r="F4" t="n">
-        <v>7746.181249115866</v>
+        <v>3094.964521314998</v>
       </c>
       <c r="G4" t="n">
-        <v>1255.50927433805</v>
+        <v>1264.095685272923</v>
       </c>
       <c r="H4" t="n">
-        <v>14128.00982829043</v>
+        <v>5895.167955092041</v>
       </c>
       <c r="I4" t="n">
-        <v>102.4124367335388</v>
+        <v>100.1869665380485</v>
       </c>
       <c r="J4" t="n">
-        <v>1947.860642760818</v>
+        <v>659.201248680894</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-3968798.746106579</v>
+        <v>117680.7061045798</v>
       </c>
       <c r="C5" t="n">
-        <v>5.799556634528432e-18</v>
+        <v>3.141060155051287e-18</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2439.004809198354</v>
+        <v>2453.574241963405</v>
       </c>
       <c r="F5" t="n">
-        <v>8217.827259650472</v>
+        <v>2915.096811801545</v>
       </c>
       <c r="G5" t="n">
-        <v>1255.99028831829</v>
+        <v>1902.303635602449</v>
       </c>
       <c r="H5" t="n">
-        <v>22352.67981603129</v>
+        <v>9013.680148403828</v>
       </c>
       <c r="I5" t="n">
-        <v>90.91701497304481</v>
+        <v>109.1242885764577</v>
       </c>
       <c r="J5" t="n">
-        <v>1960.889382772369</v>
+        <v>659.1684521035145</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-4759423.999838138</v>
+        <v>302317.4915887844</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02572238587391343</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>4.12339760144893</v>
+        <v>2.220446049250313e-14</v>
       </c>
       <c r="E6" t="n">
-        <v>2566.583927209051</v>
+        <v>2454.527809840055</v>
       </c>
       <c r="F6" t="n">
-        <v>7961.92784603958</v>
+        <v>2939.693558482216</v>
       </c>
       <c r="G6" t="n">
-        <v>1255.005927623688</v>
+        <v>2230.095223922531</v>
       </c>
       <c r="H6" t="n">
-        <v>18188.37541770581</v>
+        <v>8675.514169274191</v>
       </c>
       <c r="I6" t="n">
-        <v>84.14387049899641</v>
+        <v>104.8010431982274</v>
       </c>
       <c r="J6" t="n">
-        <v>2021.567306408631</v>
+        <v>659.2289473958849</v>
       </c>
     </row>
     <row r="7">
@@ -657,31 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-4071075.542879527</v>
+        <v>-165838.7820244692</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003159806016485007</v>
+        <v>0.003655968324573565</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3349539838912508</v>
+        <v>1.076332618885356</v>
       </c>
       <c r="E7" t="n">
-        <v>2477.602321983828</v>
+        <v>2454.051598136455</v>
       </c>
       <c r="F7" t="n">
-        <v>7768.696219296604</v>
+        <v>2916.658383892748</v>
       </c>
       <c r="G7" t="n">
-        <v>1255.184204013477</v>
+        <v>1528.045051662658</v>
       </c>
       <c r="H7" t="n">
-        <v>21855.54403096996</v>
+        <v>9014.113697816458</v>
       </c>
       <c r="I7" t="n">
-        <v>84.07048124747918</v>
+        <v>100.447566217883</v>
       </c>
       <c r="J7" t="n">
-        <v>1951.991623052525</v>
+        <v>660.3033523889835</v>
       </c>
     </row>
     <row r="8">
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-4646071.43703105</v>
+        <v>-833502.1981422273</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01921768100909338</v>
+        <v>0.07516528316686058</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9635808788896361</v>
+        <v>8.975616829619081</v>
       </c>
       <c r="E8" t="n">
-        <v>2486.81292378771</v>
+        <v>2564.300699897325</v>
       </c>
       <c r="F8" t="n">
-        <v>7761.897123080382</v>
+        <v>3091.006087529586</v>
       </c>
       <c r="G8" t="n">
-        <v>1255.005930315895</v>
+        <v>1264.007291463638</v>
       </c>
       <c r="H8" t="n">
-        <v>18818.27327849833</v>
+        <v>6515.177633326085</v>
       </c>
       <c r="I8" t="n">
-        <v>102.1166590869425</v>
+        <v>129.381423971176</v>
       </c>
       <c r="J8" t="n">
-        <v>1949.119589541992</v>
+        <v>659.2270947298247</v>
       </c>
     </row>
     <row r="9">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-4869333.954188436</v>
+        <v>-524395.7410627506</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03450685226731102</v>
+        <v>0.02341873871804938</v>
       </c>
       <c r="D9" t="n">
-        <v>2.693318000304901</v>
+        <v>3.259925530483476</v>
       </c>
       <c r="E9" t="n">
-        <v>2514.991972187145</v>
+        <v>2476.000353336311</v>
       </c>
       <c r="F9" t="n">
-        <v>7759.582616838838</v>
+        <v>3063.707329356251</v>
       </c>
       <c r="G9" t="n">
-        <v>1255.001649157395</v>
+        <v>1266.001081053548</v>
       </c>
       <c r="H9" t="n">
-        <v>17638.75158711349</v>
+        <v>8152.34956294245</v>
       </c>
       <c r="I9" t="n">
-        <v>98.76559409480002</v>
+        <v>106.8126418594116</v>
       </c>
       <c r="J9" t="n">
-        <v>1932.388159514398</v>
+        <v>661.8014720429138</v>
       </c>
     </row>
     <row r="10">
@@ -759,31 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-4409188.358806739</v>
+        <v>-648964.8220931799</v>
       </c>
       <c r="C10" t="n">
-        <v>0.009545341767291058</v>
+        <v>0.04241612832209076</v>
       </c>
       <c r="D10" t="n">
-        <v>1.136234732896124</v>
+        <v>4.548165511955937</v>
       </c>
       <c r="E10" t="n">
-        <v>2470.764356092696</v>
+        <v>2465.156176227782</v>
       </c>
       <c r="F10" t="n">
-        <v>7971.573909797311</v>
+        <v>3062.316038792906</v>
       </c>
       <c r="G10" t="n">
-        <v>1258.3803074417</v>
+        <v>1264.201104919608</v>
       </c>
       <c r="H10" t="n">
-        <v>20038.90239193784</v>
+        <v>7499.349798462164</v>
       </c>
       <c r="I10" t="n">
-        <v>101.7416141724329</v>
+        <v>146.0348590322824</v>
       </c>
       <c r="J10" t="n">
-        <v>1935.626573711769</v>
+        <v>659.9512919502162</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-5320318.326165648</v>
+        <v>-907354.1463182936</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07699703088430017</v>
+        <v>0.09149902562090255</v>
       </c>
       <c r="D11" t="n">
-        <v>5.547367397591563</v>
+        <v>10.10966077090077</v>
       </c>
       <c r="E11" t="n">
-        <v>2453.455925298807</v>
+        <v>2586.965064165037</v>
       </c>
       <c r="F11" t="n">
-        <v>7787.514028084443</v>
+        <v>3076.305861438036</v>
       </c>
       <c r="G11" t="n">
-        <v>1263.81251746952</v>
+        <v>1274.649286597097</v>
       </c>
       <c r="H11" t="n">
-        <v>15221.51417971986</v>
+        <v>6084.268249193617</v>
       </c>
       <c r="I11" t="n">
-        <v>115.0819771070584</v>
+        <v>102.7230901215207</v>
       </c>
       <c r="J11" t="n">
-        <v>1956.734926623041</v>
+        <v>660.4890938521805</v>
       </c>
     </row>
     <row r="12">
@@ -827,31 +827,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-4260610.603329181</v>
+        <v>-929605.9422906162</v>
       </c>
       <c r="C12" t="n">
-        <v>0.005473633036743836</v>
+        <v>0.09491675377797523</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9284847532324836</v>
+        <v>10.45902177967086</v>
       </c>
       <c r="E12" t="n">
-        <v>2551.42769572309</v>
+        <v>2587.948163348668</v>
       </c>
       <c r="F12" t="n">
-        <v>7764.333832684227</v>
+        <v>3084.610680100116</v>
       </c>
       <c r="G12" t="n">
-        <v>1255.91528471508</v>
+        <v>1264.120152521927</v>
       </c>
       <c r="H12" t="n">
-        <v>20841.43613350237</v>
+        <v>6006.930750454039</v>
       </c>
       <c r="I12" t="n">
-        <v>125.5035396047535</v>
+        <v>115.2914057433549</v>
       </c>
       <c r="J12" t="n">
-        <v>1949.119589541992</v>
+        <v>659.2330881844097</v>
       </c>
     </row>
     <row r="13">
@@ -861,31 +861,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-5289203.023202432</v>
+        <v>-777912.1805606764</v>
       </c>
       <c r="C13" t="n">
-        <v>0.07316031603786137</v>
+        <v>0.06387306981317006</v>
       </c>
       <c r="D13" t="n">
-        <v>5.334262445701842</v>
+        <v>6.636116632656231</v>
       </c>
       <c r="E13" t="n">
-        <v>2534.281310438076</v>
+        <v>2454.494875779611</v>
       </c>
       <c r="F13" t="n">
-        <v>7765.21519651334</v>
+        <v>3088.654973526817</v>
       </c>
       <c r="G13" t="n">
-        <v>1255.505854208947</v>
+        <v>1264.104009506432</v>
       </c>
       <c r="H13" t="n">
-        <v>15408.82511455337</v>
+        <v>6817.952305920225</v>
       </c>
       <c r="I13" t="n">
-        <v>102.6212230293565</v>
+        <v>108.4287628145966</v>
       </c>
       <c r="J13" t="n">
-        <v>2018.551559010011</v>
+        <v>692.4118040967981</v>
       </c>
     </row>
     <row r="14">
@@ -895,31 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-4804114.36717044</v>
+        <v>-824739.9313409519</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02913118483148266</v>
+        <v>0.07351045283083733</v>
       </c>
       <c r="D14" t="n">
-        <v>4.398026865077343</v>
+        <v>6.824608520827113</v>
       </c>
       <c r="E14" t="n">
-        <v>2559.019996203059</v>
+        <v>2470.13285625801</v>
       </c>
       <c r="F14" t="n">
-        <v>7977.060768817728</v>
+        <v>3046.333752785451</v>
       </c>
       <c r="G14" t="n">
-        <v>1255.108972760845</v>
+        <v>1266.002001007868</v>
       </c>
       <c r="H14" t="n">
-        <v>17956.27575271097</v>
+        <v>6568.601303950204</v>
       </c>
       <c r="I14" t="n">
-        <v>97.94681114712324</v>
+        <v>106.5707793157358</v>
       </c>
       <c r="J14" t="n">
-        <v>1953.961962473518</v>
+        <v>661.5226218273632</v>
       </c>
     </row>
     <row r="15">
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-4686598.784058019</v>
+        <v>-5624.887555170804</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02199078451320437</v>
+        <v>0.001675520313081665</v>
       </c>
       <c r="D15" t="n">
-        <v>4.650919570917733</v>
+        <v>1.172425897386298</v>
       </c>
       <c r="E15" t="n">
-        <v>2463.273290354301</v>
+        <v>2572.285623320831</v>
       </c>
       <c r="F15" t="n">
-        <v>8198.204317372103</v>
+        <v>2928.709594628872</v>
       </c>
       <c r="G15" t="n">
-        <v>1258.217176709443</v>
+        <v>1738.52423797798</v>
       </c>
       <c r="H15" t="n">
-        <v>18546.11755301013</v>
+        <v>9002.393740718649</v>
       </c>
       <c r="I15" t="n">
-        <v>102.1019554821396</v>
+        <v>101.5788378921921</v>
       </c>
       <c r="J15" t="n">
-        <v>2022.337696612046</v>
+        <v>695.5145571041164</v>
       </c>
     </row>
     <row r="16">
@@ -963,31 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-4949074.134291212</v>
+        <v>-794838.0876630894</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04102965412106421</v>
+        <v>0.06721718499724776</v>
       </c>
       <c r="D16" t="n">
-        <v>2.890899902135891</v>
+        <v>6.410444339551025</v>
       </c>
       <c r="E16" t="n">
-        <v>2485.170823794454</v>
+        <v>2595.366139457452</v>
       </c>
       <c r="F16" t="n">
-        <v>7754.09722118244</v>
+        <v>2923.44377166731</v>
       </c>
       <c r="G16" t="n">
-        <v>1255.004449000447</v>
+        <v>1264.196234202306</v>
       </c>
       <c r="H16" t="n">
-        <v>17220.16675943619</v>
+        <v>6732.981036519729</v>
       </c>
       <c r="I16" t="n">
-        <v>100.867129562172</v>
+        <v>107.9352916538794</v>
       </c>
       <c r="J16" t="n">
-        <v>1939.503555343999</v>
+        <v>662.7383494409092</v>
       </c>
     </row>
     <row r="17">
@@ -997,31 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-5152173.037431834</v>
+        <v>-532945.1195389885</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05798167934827218</v>
+        <v>0.02472333870726673</v>
       </c>
       <c r="D17" t="n">
-        <v>4.234410514260345</v>
+        <v>3.74476781819495</v>
       </c>
       <c r="E17" t="n">
-        <v>2486.81292378771</v>
+        <v>2471.261318710392</v>
       </c>
       <c r="F17" t="n">
-        <v>7762.05339626386</v>
+        <v>3089.606663804324</v>
       </c>
       <c r="G17" t="n">
-        <v>1255.005930315895</v>
+        <v>1264.01997172911</v>
       </c>
       <c r="H17" t="n">
-        <v>16145.77499451522</v>
+        <v>8106.828494955463</v>
       </c>
       <c r="I17" t="n">
-        <v>102.1166590869425</v>
+        <v>104.9307364597616</v>
       </c>
       <c r="J17" t="n">
-        <v>1949.119589541992</v>
+        <v>731.6122091237421</v>
       </c>
     </row>
     <row r="18">
@@ -1031,31 +1031,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-5400437.006598361</v>
+        <v>-896316.7728934493</v>
       </c>
       <c r="C18" t="n">
-        <v>0.08585115632283186</v>
+        <v>0.08929504780156892</v>
       </c>
       <c r="D18" t="n">
-        <v>9.194105542026954</v>
+        <v>6.248049956595714</v>
       </c>
       <c r="E18" t="n">
-        <v>2439.043301201575</v>
+        <v>2454.359737971311</v>
       </c>
       <c r="F18" t="n">
-        <v>8185.685627818119</v>
+        <v>2960.434845345824</v>
       </c>
       <c r="G18" t="n">
-        <v>1263.964404568589</v>
+        <v>1275.907455105359</v>
       </c>
       <c r="H18" t="n">
-        <v>14761.94530044853</v>
+        <v>6161.339985674605</v>
       </c>
       <c r="I18" t="n">
-        <v>106.5356617061908</v>
+        <v>100.4364177857256</v>
       </c>
       <c r="J18" t="n">
-        <v>1966.630243122453</v>
+        <v>659.2361386367932</v>
       </c>
     </row>
     <row r="19">
@@ -1065,31 +1065,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-4900315.539218769</v>
+        <v>-778856.5087451385</v>
       </c>
       <c r="C19" t="n">
-        <v>0.03692608908210501</v>
+        <v>0.06406021457430401</v>
       </c>
       <c r="D19" t="n">
-        <v>5.862434123954685</v>
+        <v>5.604287083923132</v>
       </c>
       <c r="E19" t="n">
-        <v>2512.774253019626</v>
+        <v>2454.494875779611</v>
       </c>
       <c r="F19" t="n">
-        <v>8150.618817529073</v>
+        <v>3022.604671167619</v>
       </c>
       <c r="G19" t="n">
-        <v>1255.757424900388</v>
+        <v>1265.095210462723</v>
       </c>
       <c r="H19" t="n">
-        <v>17435.55266394868</v>
+        <v>6817.952305920225</v>
       </c>
       <c r="I19" t="n">
-        <v>102.3034529090464</v>
+        <v>109.442522175316</v>
       </c>
       <c r="J19" t="n">
-        <v>1931.893508564642</v>
+        <v>661.5168318147252</v>
       </c>
     </row>
     <row r="20">
@@ -1099,31 +1099,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-5030495.733283517</v>
+        <v>-849893.3442024658</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04753905339631937</v>
+        <v>0.0787091252360389</v>
       </c>
       <c r="D20" t="n">
-        <v>7.141648672310885</v>
+        <v>9.232519290101814</v>
       </c>
       <c r="E20" t="n">
-        <v>2477.369597039583</v>
+        <v>2564.01998251193</v>
       </c>
       <c r="F20" t="n">
-        <v>8207.175652811426</v>
+        <v>3094.617343197567</v>
       </c>
       <c r="G20" t="n">
-        <v>1255.09137451589</v>
+        <v>1264.088011412587</v>
       </c>
       <c r="H20" t="n">
-        <v>16748.80417028758</v>
+        <v>6423.078100494287</v>
       </c>
       <c r="I20" t="n">
-        <v>105.830014964169</v>
+        <v>180.3796084032732</v>
       </c>
       <c r="J20" t="n">
-        <v>1929.322289306476</v>
+        <v>659.6488109254489</v>
       </c>
     </row>
     <row r="21">
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-5362566.190354522</v>
+        <v>-558945.7969092336</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08116313953386395</v>
+        <v>0.02912419456673532</v>
       </c>
       <c r="D21" t="n">
-        <v>7.933326766005466</v>
+        <v>3.810487818265096</v>
       </c>
       <c r="E21" t="n">
-        <v>2536.135560105189</v>
+        <v>2461.321235046245</v>
       </c>
       <c r="F21" t="n">
-        <v>7967.574827289371</v>
+        <v>3079.640237388961</v>
       </c>
       <c r="G21" t="n">
-        <v>1255.139181768638</v>
+        <v>1269.653202975438</v>
       </c>
       <c r="H21" t="n">
-        <v>15006.72600061902</v>
+        <v>7951.370559842803</v>
       </c>
       <c r="I21" t="n">
-        <v>88.12946268549926</v>
+        <v>149.1465623774301</v>
       </c>
       <c r="J21" t="n">
-        <v>2002.375419589873</v>
+        <v>659.6407743467212</v>
       </c>
     </row>
     <row r="22">
@@ -1167,31 +1167,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-4769996.184589582</v>
+        <v>-766394.4512698576</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02668786807318508</v>
+        <v>0.06138967448314243</v>
       </c>
       <c r="D22" t="n">
-        <v>3.281046719474401</v>
+        <v>5.749719340398962</v>
       </c>
       <c r="E22" t="n">
-        <v>2500.80225983012</v>
+        <v>2592.123962361539</v>
       </c>
       <c r="F22" t="n">
-        <v>7925.285905605249</v>
+        <v>2937.066474079016</v>
       </c>
       <c r="G22" t="n">
-        <v>1255.475772159283</v>
+        <v>1264.121080354627</v>
       </c>
       <c r="H22" t="n">
-        <v>18127.40058221515</v>
+        <v>6883.146739798627</v>
       </c>
       <c r="I22" t="n">
-        <v>134.8486929509013</v>
+        <v>100.9233360741876</v>
       </c>
       <c r="J22" t="n">
-        <v>2108.667269862934</v>
+        <v>663.1746258288041</v>
       </c>
     </row>
     <row r="23">
@@ -1201,31 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-5013411.726126028</v>
+        <v>-585970.6487126942</v>
       </c>
       <c r="C23" t="n">
-        <v>0.04674504139629375</v>
+        <v>0.03279125721083113</v>
       </c>
       <c r="D23" t="n">
-        <v>3.696782730766779</v>
+        <v>3.508524317295725</v>
       </c>
       <c r="E23" t="n">
-        <v>2517.915110725818</v>
+        <v>2467.3571137865</v>
       </c>
       <c r="F23" t="n">
-        <v>7759.418438788941</v>
+        <v>3038.310210264528</v>
       </c>
       <c r="G23" t="n">
-        <v>1256.027675203795</v>
+        <v>1264.046513845323</v>
       </c>
       <c r="H23" t="n">
-        <v>16845.95079298121</v>
+        <v>7834.61732604952</v>
       </c>
       <c r="I23" t="n">
-        <v>93.15386744259668</v>
+        <v>137.3376515718435</v>
       </c>
       <c r="J23" t="n">
-        <v>2234.126083729188</v>
+        <v>669.1080964237093</v>
       </c>
     </row>
     <row r="24">
@@ -1235,31 +1235,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-5197415.561018024</v>
+        <v>-602451.1065021688</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06301776435687229</v>
+        <v>0.03515852951086217</v>
       </c>
       <c r="D24" t="n">
-        <v>8.040841305147939</v>
+        <v>6.168065657615518</v>
       </c>
       <c r="E24" t="n">
-        <v>2439.510241007569</v>
+        <v>2586.965064165037</v>
       </c>
       <c r="F24" t="n">
-        <v>8216.774960499673</v>
+        <v>3077.546992072284</v>
       </c>
       <c r="G24" t="n">
-        <v>1255.063327083697</v>
+        <v>1264.869314649435</v>
       </c>
       <c r="H24" t="n">
-        <v>15866.58100025538</v>
+        <v>7732.717161586336</v>
       </c>
       <c r="I24" t="n">
-        <v>84.85318649874364</v>
+        <v>109.0460262382915</v>
       </c>
       <c r="J24" t="n">
-        <v>1989.715672360175</v>
+        <v>660.4890938521805</v>
       </c>
     </row>
     <row r="25">
@@ -1269,31 +1269,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-5124569.204323435</v>
+        <v>-888496.1217478928</v>
       </c>
       <c r="C25" t="n">
-        <v>0.05527542475230176</v>
+        <v>0.08637833937724862</v>
       </c>
       <c r="D25" t="n">
-        <v>8.360061197929603</v>
+        <v>9.725855988727394</v>
       </c>
       <c r="E25" t="n">
-        <v>2549.378203419731</v>
+        <v>2585.600179553976</v>
       </c>
       <c r="F25" t="n">
-        <v>8208.041651238424</v>
+        <v>3083.556757043163</v>
       </c>
       <c r="G25" t="n">
-        <v>1255.677691612791</v>
+        <v>1264.140429066491</v>
       </c>
       <c r="H25" t="n">
-        <v>16243.05649164534</v>
+        <v>6225.091836444712</v>
       </c>
       <c r="I25" t="n">
-        <v>102.7386612656678</v>
+        <v>104.6966351853381</v>
       </c>
       <c r="J25" t="n">
-        <v>1929.092516267709</v>
+        <v>661.1025884053366</v>
       </c>
     </row>
     <row r="26">
@@ -1303,31 +1303,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-4453504.753510242</v>
+        <v>-631742.3364727302</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01069313292498646</v>
+        <v>0.03973171832919841</v>
       </c>
       <c r="D26" t="n">
-        <v>1.34530097765474</v>
+        <v>4.663636610072519</v>
       </c>
       <c r="E26" t="n">
-        <v>2471.588283837383</v>
+        <v>2466.795535647158</v>
       </c>
       <c r="F26" t="n">
-        <v>7973.994552793459</v>
+        <v>3082.039630905748</v>
       </c>
       <c r="G26" t="n">
-        <v>1255.260930598945</v>
+        <v>1264.859791548107</v>
       </c>
       <c r="H26" t="n">
-        <v>19816.60498770711</v>
+        <v>7588.877138875784</v>
       </c>
       <c r="I26" t="n">
-        <v>88.69874977780393</v>
+        <v>109.0005973363496</v>
       </c>
       <c r="J26" t="n">
-        <v>1953.868789114823</v>
+        <v>663.4124614202801</v>
       </c>
     </row>
     <row r="27">
@@ -1337,31 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-4122096.68335914</v>
+        <v>-738855.0093042157</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001757079093592286</v>
+        <v>0.05595751879442328</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2384022541674358</v>
+        <v>7.300577802142838</v>
       </c>
       <c r="E27" t="n">
-        <v>2495.272566294555</v>
+        <v>2585.693911150631</v>
       </c>
       <c r="F27" t="n">
-        <v>7759.338837082356</v>
+        <v>3037.86476434554</v>
       </c>
       <c r="G27" t="n">
-        <v>1259.987950115714</v>
+        <v>1264.121141016195</v>
       </c>
       <c r="H27" t="n">
-        <v>21567.45064754443</v>
+        <v>7019.757687252127</v>
       </c>
       <c r="I27" t="n">
-        <v>92.17707921077175</v>
+        <v>101.1039625386306</v>
       </c>
       <c r="J27" t="n">
-        <v>1929.170951094427</v>
+        <v>663.1846178332044</v>
       </c>
     </row>
     <row r="28">
@@ -1371,31 +1371,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-4728752.864347586</v>
+        <v>-836374.2817356889</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02397408095216737</v>
+        <v>0.0761242422463925</v>
       </c>
       <c r="D28" t="n">
-        <v>1.287232762751789</v>
+        <v>4.458076758761676</v>
       </c>
       <c r="E28" t="n">
-        <v>2441.730902813903</v>
+        <v>2454.754600323166</v>
       </c>
       <c r="F28" t="n">
-        <v>7776.971100573835</v>
+        <v>2927.37225817771</v>
       </c>
       <c r="G28" t="n">
-        <v>1264.075909024716</v>
+        <v>1265.486407687956</v>
       </c>
       <c r="H28" t="n">
-        <v>18348.30169261121</v>
+        <v>6513.388111879618</v>
       </c>
       <c r="I28" t="n">
-        <v>102.3565509337825</v>
+        <v>128.9474035306305</v>
       </c>
       <c r="J28" t="n">
-        <v>1948.777639426283</v>
+        <v>728.7482458530574</v>
       </c>
     </row>
     <row r="29">
@@ -1405,31 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4207828.691850781</v>
+        <v>-548359.2030811096</v>
       </c>
       <c r="C29" t="n">
-        <v>0.004247866368078184</v>
+        <v>0.02689108716201273</v>
       </c>
       <c r="D29" t="n">
-        <v>1.56485541081135</v>
+        <v>5.359852598308413</v>
       </c>
       <c r="E29" t="n">
-        <v>2478.040800221947</v>
+        <v>2586.965064165037</v>
       </c>
       <c r="F29" t="n">
-        <v>8189.856305664589</v>
+        <v>3077.546992072284</v>
       </c>
       <c r="G29" t="n">
-        <v>1259.54230646817</v>
+        <v>1264.869314649435</v>
       </c>
       <c r="H29" t="n">
-        <v>21078.53049816635</v>
+        <v>8018.350975030876</v>
       </c>
       <c r="I29" t="n">
-        <v>84.63816468056235</v>
+        <v>109.0460262382915</v>
       </c>
       <c r="J29" t="n">
-        <v>1931.075885204623</v>
+        <v>660.4890938521805</v>
       </c>
     </row>
     <row r="30">
@@ -1439,31 +1439,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-4537084.07748178</v>
+        <v>-307219.9377984572</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01357417550653847</v>
+        <v>0.005556012533310286</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7665149838408492</v>
+        <v>0.2743961184428878</v>
       </c>
       <c r="E30" t="n">
-        <v>2541.723083338826</v>
+        <v>2469.936412431849</v>
       </c>
       <c r="F30" t="n">
-        <v>7760.183617490939</v>
+        <v>2919.099809665691</v>
       </c>
       <c r="G30" t="n">
-        <v>1259.958002793328</v>
+        <v>1342.030666864206</v>
       </c>
       <c r="H30" t="n">
-        <v>19367.57435217172</v>
+        <v>9008.945879822892</v>
       </c>
       <c r="I30" t="n">
-        <v>98.19938547389256</v>
+        <v>108.9019389860996</v>
       </c>
       <c r="J30" t="n">
-        <v>1967.213013411328</v>
+        <v>661.4239277928276</v>
       </c>
     </row>
     <row r="31">
@@ -1473,31 +1473,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-5124692.961348871</v>
+        <v>-845577.5644497126</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0552904540398854</v>
+        <v>0.07762852167879841</v>
       </c>
       <c r="D31" t="n">
-        <v>8.256618515570647</v>
+        <v>9.41884459717539</v>
       </c>
       <c r="E31" t="n">
-        <v>2536.509468825272</v>
+        <v>2583.936222451917</v>
       </c>
       <c r="F31" t="n">
-        <v>8208.041651238424</v>
+        <v>3093.561227568808</v>
       </c>
       <c r="G31" t="n">
-        <v>1255.677691612791</v>
+        <v>1264.935870762397</v>
       </c>
       <c r="H31" t="n">
-        <v>16243.63266828426</v>
+        <v>6448.366595171121</v>
       </c>
       <c r="I31" t="n">
-        <v>102.7386612656678</v>
+        <v>100.2077822930924</v>
       </c>
       <c r="J31" t="n">
-        <v>1929.092516267709</v>
+        <v>659.2844264458279</v>
       </c>
     </row>
     <row r="32">
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-5475975.968380434</v>
+        <v>-484458.523151808</v>
       </c>
       <c r="C32" t="n">
-        <v>0.09357804770346444</v>
+        <v>0.01704517883194842</v>
       </c>
       <c r="D32" t="n">
-        <v>6.206318860106874</v>
+        <v>4.778167361078589</v>
       </c>
       <c r="E32" t="n">
-        <v>2511.743091060035</v>
+        <v>2595.383742149232</v>
       </c>
       <c r="F32" t="n">
-        <v>7768.273125751211</v>
+        <v>3077.462181701395</v>
       </c>
       <c r="G32" t="n">
-        <v>1255.015148759647</v>
+        <v>1264.129513871299</v>
       </c>
       <c r="H32" t="n">
-        <v>14430.90205885456</v>
+        <v>8358.26368626158</v>
       </c>
       <c r="I32" t="n">
-        <v>130.8647691310956</v>
+        <v>103.0579631255053</v>
       </c>
       <c r="J32" t="n">
-        <v>1941.360686705649</v>
+        <v>663.1835408745006</v>
       </c>
     </row>
     <row r="33">
@@ -1541,31 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-5137915.597564991</v>
+        <v>-924560.3326751054</v>
       </c>
       <c r="C33" t="n">
-        <v>0.05659489432067574</v>
+        <v>0.09384401265864807</v>
       </c>
       <c r="D33" t="n">
-        <v>4.874863453060573</v>
+        <v>9.074444076977761</v>
       </c>
       <c r="E33" t="n">
-        <v>2566.583927209051</v>
+        <v>2569.38025094354</v>
       </c>
       <c r="F33" t="n">
-        <v>7778.973173492232</v>
+        <v>3022.931013529485</v>
       </c>
       <c r="G33" t="n">
-        <v>1255.000608122828</v>
+        <v>1264.147607880569</v>
       </c>
       <c r="H33" t="n">
-        <v>16206.83696559927</v>
+        <v>6041.351125305911</v>
       </c>
       <c r="I33" t="n">
-        <v>84.14387049899641</v>
+        <v>110.953707767348</v>
       </c>
       <c r="J33" t="n">
-        <v>2021.567306408631</v>
+        <v>659.8632385808544</v>
       </c>
     </row>
     <row r="34">
@@ -1575,31 +1575,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-5301491.233698626</v>
+        <v>-510252.8463912932</v>
       </c>
       <c r="C34" t="n">
-        <v>0.07442008285348296</v>
+        <v>0.02119456147500085</v>
       </c>
       <c r="D34" t="n">
-        <v>8.90138605222932</v>
+        <v>2.112734423474116</v>
       </c>
       <c r="E34" t="n">
-        <v>2510.00013952939</v>
+        <v>2453.079557047171</v>
       </c>
       <c r="F34" t="n">
-        <v>8165.950754338794</v>
+        <v>3021.569396919227</v>
       </c>
       <c r="G34" t="n">
-        <v>1256.10040829</v>
+        <v>1264.121347894295</v>
       </c>
       <c r="H34" t="n">
-        <v>15314.03493258723</v>
+        <v>8238.925736554625</v>
       </c>
       <c r="I34" t="n">
-        <v>103.7872498136758</v>
+        <v>123.472029143791</v>
       </c>
       <c r="J34" t="n">
-        <v>1936.378563719078</v>
+        <v>663.471799137271</v>
       </c>
     </row>
     <row r="35">
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-5313160.748898895</v>
+        <v>-814194.5833421941</v>
       </c>
       <c r="C35" t="n">
-        <v>0.07622441390352107</v>
+        <v>0.07144513693997749</v>
       </c>
       <c r="D35" t="n">
-        <v>7.194052902580284</v>
+        <v>9.065934117861341</v>
       </c>
       <c r="E35" t="n">
-        <v>2561.714895727501</v>
+        <v>2579.357998608352</v>
       </c>
       <c r="F35" t="n">
-        <v>7972.101682950751</v>
+        <v>3094.65331616696</v>
       </c>
       <c r="G35" t="n">
-        <v>1263.547288924148</v>
+        <v>1264.068283871091</v>
       </c>
       <c r="H35" t="n">
-        <v>15232.64371095627</v>
+        <v>6609.806891585564</v>
       </c>
       <c r="I35" t="n">
-        <v>106.7796374481807</v>
+        <v>185.0834250513102</v>
       </c>
       <c r="J35" t="n">
-        <v>1966.887547909903</v>
+        <v>659.005539229359</v>
       </c>
     </row>
     <row r="36">
@@ -1643,31 +1643,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-5428752.16365378</v>
+        <v>-752841.4479023656</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08832792497799898</v>
+        <v>0.05924855878504808</v>
       </c>
       <c r="D36" t="n">
-        <v>9.100323717299197</v>
+        <v>8.19795160659833</v>
       </c>
       <c r="E36" t="n">
-        <v>2451.13653526834</v>
+        <v>2595.998580222385</v>
       </c>
       <c r="F36" t="n">
-        <v>8139.580518264252</v>
+        <v>3073.58995529692</v>
       </c>
       <c r="G36" t="n">
-        <v>1255.429437231378</v>
+        <v>1264.12968918328</v>
       </c>
       <c r="H36" t="n">
-        <v>14654.69252533234</v>
+        <v>6926.12781482853</v>
       </c>
       <c r="I36" t="n">
-        <v>90.60002265493661</v>
+        <v>103.362075636616</v>
       </c>
       <c r="J36" t="n">
-        <v>1929.601350432817</v>
+        <v>826.0964420533061</v>
       </c>
     </row>
     <row r="37">
@@ -1677,31 +1677,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-4558633.800596589</v>
+        <v>-747953.1378341606</v>
       </c>
       <c r="C37" t="n">
-        <v>0.01473398957721732</v>
+        <v>0.05764874556387757</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5840785805891313</v>
+        <v>7.511103847860601</v>
       </c>
       <c r="E37" t="n">
-        <v>2485.314993985168</v>
+        <v>2592.123962361539</v>
       </c>
       <c r="F37" t="n">
-        <v>7756.519386763222</v>
+        <v>3037.86476434554</v>
       </c>
       <c r="G37" t="n">
-        <v>1260.108196311729</v>
+        <v>1264.121080354627</v>
       </c>
       <c r="H37" t="n">
-        <v>19253.4817790763</v>
+        <v>6971.121567695291</v>
       </c>
       <c r="I37" t="n">
-        <v>101.1820727084636</v>
+        <v>100.9233360741876</v>
       </c>
       <c r="J37" t="n">
-        <v>2022.337696612046</v>
+        <v>663.1446751812931</v>
       </c>
     </row>
     <row r="38">
@@ -1711,31 +1711,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-5073375.443389332</v>
+        <v>-489939.3245343454</v>
       </c>
       <c r="C38" t="n">
-        <v>0.05115172883136266</v>
+        <v>0.01810741510663311</v>
       </c>
       <c r="D38" t="n">
-        <v>7.754246351458283</v>
+        <v>1.894272978834699</v>
       </c>
       <c r="E38" t="n">
-        <v>2509.10771369551</v>
+        <v>2455.15615795727</v>
       </c>
       <c r="F38" t="n">
-        <v>8212.152122815436</v>
+        <v>3027.201154883639</v>
       </c>
       <c r="G38" t="n">
-        <v>1255.384588777215</v>
+        <v>1265.043864183473</v>
       </c>
       <c r="H38" t="n">
-        <v>16512.30920432305</v>
+        <v>8343.712040919478</v>
       </c>
       <c r="I38" t="n">
-        <v>109.0917838560822</v>
+        <v>103.4519725153766</v>
       </c>
       <c r="J38" t="n">
-        <v>1983.811854674758</v>
+        <v>663.2437844771877</v>
       </c>
     </row>
     <row r="39">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-4892349.313586939</v>
+        <v>-387476.5219001342</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0362750945287481</v>
+        <v>0.007712800219490962</v>
       </c>
       <c r="D39" t="n">
-        <v>6.167791011090618</v>
+        <v>2.82742638957636</v>
       </c>
       <c r="E39" t="n">
-        <v>2510.565831525945</v>
+        <v>2583.653678330606</v>
       </c>
       <c r="F39" t="n">
-        <v>8201.681710484665</v>
+        <v>3037.967793699589</v>
       </c>
       <c r="G39" t="n">
-        <v>1255.029242901052</v>
+        <v>1267.384148832741</v>
       </c>
       <c r="H39" t="n">
-        <v>17472.77249810152</v>
+        <v>8862.354955383016</v>
       </c>
       <c r="I39" t="n">
-        <v>101.0342029520661</v>
+        <v>101.1039625386306</v>
       </c>
       <c r="J39" t="n">
-        <v>1967.520786279073</v>
+        <v>663.1846178332044</v>
       </c>
     </row>
     <row r="40">
@@ -1779,31 +1779,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-4600340.419759238</v>
+        <v>-577783.1765601775</v>
       </c>
       <c r="C40" t="n">
-        <v>0.01683499347028236</v>
+        <v>0.03131794915676247</v>
       </c>
       <c r="D40" t="n">
-        <v>1.660020998405209</v>
+        <v>5.478368258111366</v>
       </c>
       <c r="E40" t="n">
-        <v>2568.689545807602</v>
+        <v>2564.300699897325</v>
       </c>
       <c r="F40" t="n">
-        <v>7756.217709558556</v>
+        <v>3076.6935390318</v>
       </c>
       <c r="G40" t="n">
-        <v>1255.001649157395</v>
+        <v>1264.068358082626</v>
       </c>
       <c r="H40" t="n">
-        <v>19052.34798562045</v>
+        <v>7869.102379038946</v>
       </c>
       <c r="I40" t="n">
-        <v>98.76559409480002</v>
+        <v>103.2733872398987</v>
       </c>
       <c r="J40" t="n">
-        <v>1953.971687405852</v>
+        <v>659.1527453573634</v>
       </c>
     </row>
     <row r="41">
@@ -1813,31 +1813,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4858730.182917642</v>
+        <v>-217704.600870715</v>
       </c>
       <c r="C41" t="n">
-        <v>0.03358167510646164</v>
+        <v>0.004402497449926205</v>
       </c>
       <c r="D41" t="n">
-        <v>5.265293830398665</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>2440.707883546773</v>
+        <v>2454.834311139775</v>
       </c>
       <c r="F41" t="n">
-        <v>8165.706948368557</v>
+        <v>3033.181319913271</v>
       </c>
       <c r="G41" t="n">
-        <v>1256.09979571145</v>
+        <v>1457.895981027802</v>
       </c>
       <c r="H41" t="n">
-        <v>17658.94602306865</v>
+        <v>9009.05629545511</v>
       </c>
       <c r="I41" t="n">
-        <v>102.7376527050134</v>
+        <v>106.8125081751433</v>
       </c>
       <c r="J41" t="n">
-        <v>1934.748055641917</v>
+        <v>662.6208666625281</v>
       </c>
     </row>
     <row r="42">
@@ -1847,31 +1847,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-5503528.795713481</v>
+        <v>-319273.1874295124</v>
       </c>
       <c r="C42" t="n">
-        <v>0.09695014533969344</v>
+        <v>0.005754491598955245</v>
       </c>
       <c r="D42" t="n">
-        <v>10.02978599873765</v>
+        <v>2.284637149849345</v>
       </c>
       <c r="E42" t="n">
-        <v>2483.325845528352</v>
+        <v>2597.337577370409</v>
       </c>
       <c r="F42" t="n">
-        <v>8161.855091722919</v>
+        <v>3023.172942161057</v>
       </c>
       <c r="G42" t="n">
-        <v>1255.180967616242</v>
+        <v>1320.182290261197</v>
       </c>
       <c r="H42" t="n">
-        <v>14236.42770990912</v>
+        <v>9010.898079417138</v>
       </c>
       <c r="I42" t="n">
-        <v>130.7424130459194</v>
+        <v>107.3567377598729</v>
       </c>
       <c r="J42" t="n">
-        <v>2094.686363669468</v>
+        <v>662.0030897370088</v>
       </c>
     </row>
     <row r="43">
@@ -1881,31 +1881,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-5370585.764781444</v>
+        <v>-447456.2116727289</v>
       </c>
       <c r="C43" t="n">
-        <v>0.08218963116474862</v>
+        <v>0.01215156596074693</v>
       </c>
       <c r="D43" t="n">
-        <v>9.248550699512503</v>
+        <v>1.68444436800379</v>
       </c>
       <c r="E43" t="n">
-        <v>2474.781577790494</v>
+        <v>2455.724782210189</v>
       </c>
       <c r="F43" t="n">
-        <v>8185.554375083798</v>
+        <v>3039.411961869188</v>
       </c>
       <c r="G43" t="n">
-        <v>1256.619262558703</v>
+        <v>1264.042852935223</v>
       </c>
       <c r="H43" t="n">
-        <v>14941.93007722241</v>
+        <v>8567.876680800657</v>
       </c>
       <c r="I43" t="n">
-        <v>92.27940260787993</v>
+        <v>136.6404048296624</v>
       </c>
       <c r="J43" t="n">
-        <v>2020.047763448135</v>
+        <v>661.1794066404187</v>
       </c>
     </row>
     <row r="44">
@@ -1915,31 +1915,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-5226674.097093882</v>
+        <v>-940495.6085161632</v>
       </c>
       <c r="C44" t="n">
-        <v>0.06631193857543215</v>
+        <v>0.09715196487827965</v>
       </c>
       <c r="D44" t="n">
-        <v>4.531151578462477</v>
+        <v>10.97589894709071</v>
       </c>
       <c r="E44" t="n">
-        <v>2482.717179967476</v>
+        <v>2603.366095538227</v>
       </c>
       <c r="F44" t="n">
-        <v>7749.991637935958</v>
+        <v>3094.964521314998</v>
       </c>
       <c r="G44" t="n">
-        <v>1255.001174717437</v>
+        <v>1264.095685272923</v>
       </c>
       <c r="H44" t="n">
-        <v>15744.26261889275</v>
+        <v>5947.742282707191</v>
       </c>
       <c r="I44" t="n">
-        <v>98.73795270604548</v>
+        <v>108.2844467840465</v>
       </c>
       <c r="J44" t="n">
-        <v>2055.903002319106</v>
+        <v>659.3731776844797</v>
       </c>
     </row>
     <row r="45">
@@ -1949,31 +1949,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-5102952.663079329</v>
+        <v>-896219.454751987</v>
       </c>
       <c r="C45" t="n">
-        <v>0.05355629367245274</v>
+        <v>0.08826160534930964</v>
       </c>
       <c r="D45" t="n">
-        <v>7.280710232612564</v>
+        <v>9.893750983586413</v>
       </c>
       <c r="E45" t="n">
-        <v>2439.510241007569</v>
+        <v>2592.030230764881</v>
       </c>
       <c r="F45" t="n">
-        <v>8201.614286559106</v>
+        <v>3083.556757043163</v>
       </c>
       <c r="G45" t="n">
-        <v>1255.064374456588</v>
+        <v>1264.140368404923</v>
       </c>
       <c r="H45" t="n">
-        <v>16367.89001685039</v>
+        <v>6176.455716887857</v>
       </c>
       <c r="I45" t="n">
-        <v>84.91777154915486</v>
+        <v>104.5160996757606</v>
       </c>
       <c r="J45" t="n">
-        <v>1978.032828096574</v>
+        <v>738.8444777166693</v>
       </c>
     </row>
     <row r="46">
@@ -1983,31 +1983,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-5244728.141297955</v>
+        <v>-711804.7996134465</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0683590669546829</v>
+        <v>0.05207054967430293</v>
       </c>
       <c r="D46" t="n">
-        <v>8.524145448137777</v>
+        <v>7.530235182183642</v>
       </c>
       <c r="E46" t="n">
-        <v>2463.594245503822</v>
+        <v>2574.374849967199</v>
       </c>
       <c r="F46" t="n">
-        <v>8212.75603916084</v>
+        <v>3085.748406264954</v>
       </c>
       <c r="G46" t="n">
-        <v>1258.265308903365</v>
+        <v>1264.817849283527</v>
       </c>
       <c r="H46" t="n">
-        <v>15603.14471430659</v>
+        <v>7149.039153491547</v>
       </c>
       <c r="I46" t="n">
-        <v>125.8619426250893</v>
+        <v>120.4997484973792</v>
       </c>
       <c r="J46" t="n">
-        <v>1935.587911706854</v>
+        <v>722.4365031421953</v>
       </c>
     </row>
     <row r="47">
@@ -2017,31 +2017,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-4526239.750547319</v>
+        <v>25795.34746046364</v>
       </c>
       <c r="C47" t="n">
-        <v>0.01317655485188307</v>
+        <v>0.001239192591251191</v>
       </c>
       <c r="D47" t="n">
-        <v>3.601521945695674</v>
+        <v>2.220446049250313e-14</v>
       </c>
       <c r="E47" t="n">
-        <v>2477.980136999559</v>
+        <v>2465.961434880859</v>
       </c>
       <c r="F47" t="n">
-        <v>8188.718882289706</v>
+        <v>2926.871496294141</v>
       </c>
       <c r="G47" t="n">
-        <v>1255.745181239897</v>
+        <v>1782.661484831079</v>
       </c>
       <c r="H47" t="n">
-        <v>19410.9788975321</v>
+        <v>9002.115792144326</v>
       </c>
       <c r="I47" t="n">
-        <v>98.76559409480002</v>
+        <v>101.3257529492159</v>
       </c>
       <c r="J47" t="n">
-        <v>1932.399909849296</v>
+        <v>695.5145571041164</v>
       </c>
     </row>
     <row r="48">
@@ -2051,31 +2051,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-4619915.059664169</v>
+        <v>-654010.9789904528</v>
       </c>
       <c r="C48" t="n">
-        <v>0.01804196308879566</v>
+        <v>0.04369309868109746</v>
       </c>
       <c r="D48" t="n">
-        <v>2.060545888794396</v>
+        <v>3.113937466142336</v>
       </c>
       <c r="E48" t="n">
-        <v>2476.557634015469</v>
+        <v>2461.114717020154</v>
       </c>
       <c r="F48" t="n">
-        <v>7927.795650528826</v>
+        <v>2962.391915931721</v>
       </c>
       <c r="G48" t="n">
-        <v>1255.51657614506</v>
+        <v>1269.195173205379</v>
       </c>
       <c r="H48" t="n">
-        <v>18933.24693519417</v>
+        <v>7462.419585498384</v>
       </c>
       <c r="I48" t="n">
-        <v>132.9818642207859</v>
+        <v>112.3227803782716</v>
       </c>
       <c r="J48" t="n">
-        <v>1988.226624815904</v>
+        <v>694.6803474936657</v>
       </c>
     </row>
     <row r="49">
@@ -2085,31 +2085,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-5081065.674501826</v>
+        <v>-549281.37954643</v>
       </c>
       <c r="C49" t="n">
-        <v>0.05193353579417021</v>
+        <v>0.02697970831079994</v>
       </c>
       <c r="D49" t="n">
-        <v>4.147025244496206</v>
+        <v>5.135272532579527</v>
       </c>
       <c r="E49" t="n">
-        <v>2509.10771369551</v>
+        <v>2569.17104379028</v>
       </c>
       <c r="F49" t="n">
-        <v>7780.138228195602</v>
+        <v>3077.546992072284</v>
       </c>
       <c r="G49" t="n">
-        <v>1255.384182569081</v>
+        <v>1264.008296423387</v>
       </c>
       <c r="H49" t="n">
-        <v>16512.30920432305</v>
+        <v>8018.350975030876</v>
       </c>
       <c r="I49" t="n">
-        <v>109.1807898677032</v>
+        <v>109.0460262382915</v>
       </c>
       <c r="J49" t="n">
-        <v>1980.661163847135</v>
+        <v>663.4335050511652</v>
       </c>
     </row>
     <row r="50">
@@ -2119,31 +2119,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-5326770.596060876</v>
+        <v>-681953.4231144716</v>
       </c>
       <c r="C50" t="n">
-        <v>0.07717331081578066</v>
+        <v>0.0474176943899275</v>
       </c>
       <c r="D50" t="n">
-        <v>5.07302060329593</v>
+        <v>4.235097274344524</v>
       </c>
       <c r="E50" t="n">
-        <v>2454.914052489735</v>
+        <v>2557.103716553123</v>
       </c>
       <c r="F50" t="n">
-        <v>7780.307295895598</v>
+        <v>2925.867997066648</v>
       </c>
       <c r="G50" t="n">
-        <v>1255.260793505338</v>
+        <v>1264.244458562835</v>
       </c>
       <c r="H50" t="n">
-        <v>15222.1829795744</v>
+        <v>7331.441917425313</v>
       </c>
       <c r="I50" t="n">
-        <v>115.0819771070584</v>
+        <v>109.0923060734245</v>
       </c>
       <c r="J50" t="n">
-        <v>1956.734926623041</v>
+        <v>670.8407753416441</v>
       </c>
     </row>
     <row r="51">
@@ -2153,31 +2153,31 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-5165765.407297585</v>
+        <v>-604745.9509582645</v>
       </c>
       <c r="C51" t="n">
-        <v>0.05976841780138462</v>
+        <v>0.03643368826264153</v>
       </c>
       <c r="D51" t="n">
-        <v>4.734037018895965</v>
+        <v>6.080964064207439</v>
       </c>
       <c r="E51" t="n">
-        <v>2487.112752057426</v>
+        <v>2587.409398439981</v>
       </c>
       <c r="F51" t="n">
-        <v>7788.284000274549</v>
+        <v>3082.177121855804</v>
       </c>
       <c r="G51" t="n">
-        <v>1259.733203907482</v>
+        <v>1271.293180500726</v>
       </c>
       <c r="H51" t="n">
-        <v>16052.22631645302</v>
+        <v>7681.435812661402</v>
       </c>
       <c r="I51" t="n">
-        <v>102.2714839658116</v>
+        <v>109.0460262382915</v>
       </c>
       <c r="J51" t="n">
-        <v>1953.116649975475</v>
+        <v>799.7029253262298</v>
       </c>
     </row>
     <row r="52">
@@ -2187,31 +2187,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-4840463.900817614</v>
+        <v>-705479.9557400984</v>
       </c>
       <c r="C52" t="n">
-        <v>0.03217169125250845</v>
+        <v>0.05094281152645695</v>
       </c>
       <c r="D52" t="n">
-        <v>3.067245194301449</v>
+        <v>7.901835510800959</v>
       </c>
       <c r="E52" t="n">
-        <v>2561.730569889617</v>
+        <v>2597.292550370013</v>
       </c>
       <c r="F52" t="n">
-        <v>7788.284000274549</v>
+        <v>3092.376481717291</v>
       </c>
       <c r="G52" t="n">
-        <v>1255.098353436334</v>
+        <v>1265.454719263452</v>
       </c>
       <c r="H52" t="n">
-        <v>17781.00724018748</v>
+        <v>7183.75935055739</v>
       </c>
       <c r="I52" t="n">
-        <v>102.2802057121545</v>
+        <v>102.6861446616811</v>
       </c>
       <c r="J52" t="n">
-        <v>1957.308381641483</v>
+        <v>669.127503413455</v>
       </c>
     </row>
     <row r="53">
@@ -2221,31 +2221,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-4936427.371340033</v>
+        <v>-727878.0438603102</v>
       </c>
       <c r="C53" t="n">
-        <v>0.03988330901545426</v>
+        <v>0.05457892586105077</v>
       </c>
       <c r="D53" t="n">
-        <v>6.155591044443931</v>
+        <v>4.996638135418852</v>
       </c>
       <c r="E53" t="n">
-        <v>2510.086822049452</v>
+        <v>2461.804301860107</v>
       </c>
       <c r="F53" t="n">
-        <v>8165.950754338794</v>
+        <v>3036.620048438254</v>
       </c>
       <c r="G53" t="n">
-        <v>1256.10040829</v>
+        <v>1265.739062154282</v>
       </c>
       <c r="H53" t="n">
-        <v>17242.03127002849</v>
+        <v>7081.003914181478</v>
       </c>
       <c r="I53" t="n">
-        <v>102.7376527050134</v>
+        <v>109.0460262382915</v>
       </c>
       <c r="J53" t="n">
-        <v>1934.510427796211</v>
+        <v>678.6332046021952</v>
       </c>
     </row>
     <row r="54">
@@ -2255,31 +2255,31 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-5519988.665747834</v>
+        <v>-505159.6776785278</v>
       </c>
       <c r="C54" t="n">
-        <v>0.09843171354371447</v>
+        <v>0.02044564839480128</v>
       </c>
       <c r="D54" t="n">
-        <v>10.88988920489602</v>
+        <v>0.3853972227278346</v>
       </c>
       <c r="E54" t="n">
-        <v>2549.396203199878</v>
+        <v>2457.715307114932</v>
       </c>
       <c r="F54" t="n">
-        <v>8191.917331594314</v>
+        <v>2920.523450358954</v>
       </c>
       <c r="G54" t="n">
-        <v>1255.026870053335</v>
+        <v>1264.004496685516</v>
       </c>
       <c r="H54" t="n">
-        <v>14157.44678325964</v>
+        <v>8276.329977381494</v>
       </c>
       <c r="I54" t="n">
-        <v>90.10982389012359</v>
+        <v>116.6723949272143</v>
       </c>
       <c r="J54" t="n">
-        <v>1960.157602404039</v>
+        <v>659.1379824012004</v>
       </c>
     </row>
     <row r="55">
@@ -2289,31 +2289,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-5171515.984815619</v>
+        <v>-692071.59648673</v>
       </c>
       <c r="C55" t="n">
-        <v>0.06019956693683273</v>
+        <v>0.04910894795758706</v>
       </c>
       <c r="D55" t="n">
-        <v>7.855086073497375</v>
+        <v>3.560615243074983</v>
       </c>
       <c r="E55" t="n">
-        <v>2438.955569292856</v>
+        <v>2466.210839065182</v>
       </c>
       <c r="F55" t="n">
-        <v>8216.138234137128</v>
+        <v>2958.178977485117</v>
       </c>
       <c r="G55" t="n">
-        <v>1255.748614426199</v>
+        <v>1265.68023740631</v>
       </c>
       <c r="H55" t="n">
-        <v>16002.30998511903</v>
+        <v>7278.806424518832</v>
       </c>
       <c r="I55" t="n">
-        <v>91.47111743497874</v>
+        <v>109.8274779742263</v>
       </c>
       <c r="J55" t="n">
-        <v>1965.85875253177</v>
+        <v>660.795675375451</v>
       </c>
     </row>
     <row r="56">
@@ -2323,31 +2323,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-5204929.931988206</v>
+        <v>-94942.1752528986</v>
       </c>
       <c r="C56" t="n">
-        <v>0.06406119967749896</v>
+        <v>0.002767174465894103</v>
       </c>
       <c r="D56" t="n">
-        <v>5.003487341482948</v>
+        <v>0.759163084329495</v>
       </c>
       <c r="E56" t="n">
-        <v>2486.81292378771</v>
+        <v>2598.602979940271</v>
       </c>
       <c r="F56" t="n">
-        <v>7788.284000274549</v>
+        <v>2965.266227281439</v>
       </c>
       <c r="G56" t="n">
-        <v>1259.733203907482</v>
+        <v>1616.892797443225</v>
       </c>
       <c r="H56" t="n">
-        <v>15844.60738964249</v>
+        <v>9014.63952885546</v>
       </c>
       <c r="I56" t="n">
-        <v>106.9708080845436</v>
+        <v>100.3653556690185</v>
       </c>
       <c r="J56" t="n">
-        <v>1957.286213228019</v>
+        <v>661.5155964088278</v>
       </c>
     </row>
     <row r="57">
@@ -2357,31 +2357,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-5270919.191655843</v>
+        <v>-496995.6487207855</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0713943260280509</v>
+        <v>0.01908778665341809</v>
       </c>
       <c r="D57" t="n">
-        <v>9.568621525552679</v>
+        <v>3.007661231011904</v>
       </c>
       <c r="E57" t="n">
-        <v>2574.493354587281</v>
+        <v>2463.754778569552</v>
       </c>
       <c r="F57" t="n">
-        <v>8206.484528945562</v>
+        <v>3080.253984273574</v>
       </c>
       <c r="G57" t="n">
-        <v>1255.253169555717</v>
+        <v>1264.114335090788</v>
       </c>
       <c r="H57" t="n">
-        <v>15450.7350734365</v>
+        <v>8303.460873853281</v>
       </c>
       <c r="I57" t="n">
-        <v>84.50589787288011</v>
+        <v>115.2740576032216</v>
       </c>
       <c r="J57" t="n">
-        <v>2150.899378702939</v>
+        <v>661.1572451880561</v>
       </c>
     </row>
     <row r="58">
@@ -2391,31 +2391,31 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-4306997.176461095</v>
+        <v>-629335.5324579682</v>
       </c>
       <c r="C58" t="n">
-        <v>0.006684531796669171</v>
+        <v>0.03926118670199145</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3201795464947255</v>
+        <v>6.778097627812352</v>
       </c>
       <c r="E58" t="n">
-        <v>2469.098342243915</v>
+        <v>2599.844893648</v>
       </c>
       <c r="F58" t="n">
-        <v>7821.202802604879</v>
+        <v>3082.039630905748</v>
       </c>
       <c r="G58" t="n">
-        <v>1255.193869945822</v>
+        <v>1264.859791548107</v>
       </c>
       <c r="H58" t="n">
-        <v>20604.26748290098</v>
+        <v>7588.877138875784</v>
       </c>
       <c r="I58" t="n">
-        <v>107.4668627791198</v>
+        <v>109.0005973363496</v>
       </c>
       <c r="J58" t="n">
-        <v>1942.599627834065</v>
+        <v>663.3652199646453</v>
       </c>
     </row>
     <row r="59">
@@ -2425,31 +2425,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-5468047.096578842</v>
+        <v>-77561.9372847015</v>
       </c>
       <c r="C59" t="n">
-        <v>0.09268334270847396</v>
+        <v>0.002562316765731773</v>
       </c>
       <c r="D59" t="n">
-        <v>10.66159296629966</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>2585.981914236754</v>
+        <v>2454.835587589957</v>
       </c>
       <c r="F59" t="n">
-        <v>8173.605762116894</v>
+        <v>3033.181319913271</v>
       </c>
       <c r="G59" t="n">
-        <v>1255.015148759647</v>
+        <v>1642.904573753019</v>
       </c>
       <c r="H59" t="n">
-        <v>14430.90205885456</v>
+        <v>9009.05629545511</v>
       </c>
       <c r="I59" t="n">
-        <v>99.02848105207883</v>
+        <v>106.8125081751433</v>
       </c>
       <c r="J59" t="n">
-        <v>1941.208395095426</v>
+        <v>662.5434408199003</v>
       </c>
     </row>
     <row r="60">
@@ -2459,31 +2459,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-5182604.46081673</v>
+        <v>-806302.2333935234</v>
       </c>
       <c r="C60" t="n">
-        <v>0.06132281099400774</v>
+        <v>0.06954158104429384</v>
       </c>
       <c r="D60" t="n">
-        <v>5.134990245809822</v>
+        <v>8.998426318622677</v>
       </c>
       <c r="E60" t="n">
-        <v>2559.019996203059</v>
+        <v>2600.551950513532</v>
       </c>
       <c r="F60" t="n">
-        <v>7794.119082669431</v>
+        <v>3081.001821387835</v>
       </c>
       <c r="G60" t="n">
-        <v>1255.10533582891</v>
+        <v>1264.130408332057</v>
       </c>
       <c r="H60" t="n">
-        <v>15974.73730060442</v>
+        <v>6658.33894078152</v>
       </c>
       <c r="I60" t="n">
-        <v>97.94681114712324</v>
+        <v>101.3807522030913</v>
       </c>
       <c r="J60" t="n">
-        <v>1953.961962473518</v>
+        <v>660.5315035456969</v>
       </c>
     </row>
     <row r="61">
@@ -2493,31 +2493,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-5342550.729796441</v>
+        <v>-809608.7941204831</v>
       </c>
       <c r="C61" t="n">
-        <v>0.07888574446311061</v>
+        <v>0.07017596790947132</v>
       </c>
       <c r="D61" t="n">
-        <v>9.112528903737049</v>
+        <v>6.451282933290803</v>
       </c>
       <c r="E61" t="n">
-        <v>2465.157070276316</v>
+        <v>2588.58888960435</v>
       </c>
       <c r="F61" t="n">
-        <v>8204.708915973926</v>
+        <v>2920.523450358954</v>
       </c>
       <c r="G61" t="n">
-        <v>1255.011890769073</v>
+        <v>1264.003536616868</v>
       </c>
       <c r="H61" t="n">
-        <v>15101.30060558328</v>
+        <v>6657.392565841939</v>
       </c>
       <c r="I61" t="n">
-        <v>102.3970942194325</v>
+        <v>103.9410986186889</v>
       </c>
       <c r="J61" t="n">
-        <v>1947.874876310771</v>
+        <v>659.1379824012004</v>
       </c>
     </row>
     <row r="62">
@@ -2527,31 +2527,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-4640514.050270997</v>
+        <v>-936437.3516816064</v>
       </c>
       <c r="C62" t="n">
-        <v>0.01901182453750033</v>
+        <v>0.09624041695167089</v>
       </c>
       <c r="D62" t="n">
-        <v>1.365947405181545</v>
+        <v>8.10143420029441</v>
       </c>
       <c r="E62" t="n">
-        <v>2514.997049418864</v>
+        <v>2588.58888960435</v>
       </c>
       <c r="F62" t="n">
-        <v>7779.981955012998</v>
+        <v>2920.523450358954</v>
       </c>
       <c r="G62" t="n">
-        <v>1255.384182569081</v>
+        <v>1264.046558389344</v>
       </c>
       <c r="H62" t="n">
-        <v>18838.10624153302</v>
+        <v>5987.822779869754</v>
       </c>
       <c r="I62" t="n">
-        <v>109.1807898677032</v>
+        <v>100.551663522206</v>
       </c>
       <c r="J62" t="n">
-        <v>1980.661163847135</v>
+        <v>659.1360767326823</v>
       </c>
     </row>
     <row r="63">
@@ -2561,31 +2561,31 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-4967482.547674109</v>
+        <v>-866856.8777424046</v>
       </c>
       <c r="C63" t="n">
-        <v>0.04260854348261988</v>
+        <v>0.08188833316708598</v>
       </c>
       <c r="D63" t="n">
-        <v>6.961378918986972</v>
+        <v>7.026922063585928</v>
       </c>
       <c r="E63" t="n">
-        <v>2495.651009896355</v>
+        <v>2453.346707794302</v>
       </c>
       <c r="F63" t="n">
-        <v>8216.566723001479</v>
+        <v>3039.411961869188</v>
       </c>
       <c r="G63" t="n">
-        <v>1258.239781347412</v>
+        <v>1264.052370397947</v>
       </c>
       <c r="H63" t="n">
-        <v>17058.99665184658</v>
+        <v>6356.300786248406</v>
       </c>
       <c r="I63" t="n">
-        <v>94.32951825409658</v>
+        <v>106.8368176153094</v>
       </c>
       <c r="J63" t="n">
-        <v>2019.668696392658</v>
+        <v>660.7077499724096</v>
       </c>
     </row>
     <row r="64">
@@ -2595,31 +2595,31 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-5341563.371619412</v>
+        <v>-123377.0691628624</v>
       </c>
       <c r="C64" t="n">
-        <v>0.07913935235583129</v>
+        <v>0.003157772442939293</v>
       </c>
       <c r="D64" t="n">
-        <v>8.889003218241875</v>
+        <v>2.220446049250313e-14</v>
       </c>
       <c r="E64" t="n">
-        <v>2439.068484314829</v>
+        <v>2459.869557600378</v>
       </c>
       <c r="F64" t="n">
-        <v>8199.381775111735</v>
+        <v>2927.287240476256</v>
       </c>
       <c r="G64" t="n">
-        <v>1260.260220640117</v>
+        <v>1585.667000919369</v>
       </c>
       <c r="H64" t="n">
-        <v>15086.65166915146</v>
+        <v>9006.346487072775</v>
       </c>
       <c r="I64" t="n">
-        <v>102.7440196188687</v>
+        <v>100.8756368296399</v>
       </c>
       <c r="J64" t="n">
-        <v>1967.442890482333</v>
+        <v>659.3477470071257</v>
       </c>
     </row>
     <row r="65">
@@ -2629,31 +2629,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-5233556.286334843</v>
+        <v>-663848.1830777838</v>
       </c>
       <c r="C65" t="n">
-        <v>0.06687132715334036</v>
+        <v>0.04456742881264818</v>
       </c>
       <c r="D65" t="n">
-        <v>7.616958054973299</v>
+        <v>4.764615925737193</v>
       </c>
       <c r="E65" t="n">
-        <v>2439.4750088122</v>
+        <v>2465.296710431283</v>
       </c>
       <c r="F65" t="n">
-        <v>8133.4181230451</v>
+        <v>3064.41768778086</v>
       </c>
       <c r="G65" t="n">
-        <v>1255.430075444035</v>
+        <v>1264.085941058783</v>
       </c>
       <c r="H65" t="n">
-        <v>15687.1079728604</v>
+        <v>7424.876481255605</v>
       </c>
       <c r="I65" t="n">
-        <v>90.60002265493661</v>
+        <v>102.5838768873162</v>
       </c>
       <c r="J65" t="n">
-        <v>1929.695487455846</v>
+        <v>662.9980861590938</v>
       </c>
     </row>
     <row r="66">
@@ -2663,31 +2663,31 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-4696078.484109431</v>
+        <v>-231550.5941292518</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0220191971924462</v>
+        <v>0.004646864615659431</v>
       </c>
       <c r="D66" t="n">
-        <v>1.223851753959526</v>
+        <v>0.9253108960406098</v>
       </c>
       <c r="E66" t="n">
-        <v>2486.81292378771</v>
+        <v>2592.809106152296</v>
       </c>
       <c r="F66" t="n">
-        <v>7753.804697302319</v>
+        <v>2954.655885965859</v>
       </c>
       <c r="G66" t="n">
-        <v>1255.509709976747</v>
+        <v>1440.058159423532</v>
       </c>
       <c r="H66" t="n">
-        <v>18546.11755301013</v>
+        <v>9002.117705924846</v>
       </c>
       <c r="I66" t="n">
-        <v>102.1019554821396</v>
+        <v>102.5855418979966</v>
       </c>
       <c r="J66" t="n">
-        <v>2022.337696612046</v>
+        <v>659.6681439763122</v>
       </c>
     </row>
     <row r="67">
@@ -2697,31 +2697,31 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-5498392.250621079</v>
+        <v>-856642.7598780422</v>
       </c>
       <c r="C67" t="n">
-        <v>0.09602323809307377</v>
+        <v>0.07981108003192149</v>
       </c>
       <c r="D67" t="n">
-        <v>6.734117283333418</v>
+        <v>9.740004968318372</v>
       </c>
       <c r="E67" t="n">
-        <v>2485.055486813118</v>
+        <v>2600.508166978718</v>
       </c>
       <c r="F67" t="n">
-        <v>7755.604483375063</v>
+        <v>3094.654963701435</v>
       </c>
       <c r="G67" t="n">
-        <v>1255.50927433805</v>
+        <v>1264.085261675936</v>
       </c>
       <c r="H67" t="n">
-        <v>14316.54653439611</v>
+        <v>6391.424855588903</v>
       </c>
       <c r="I67" t="n">
-        <v>115.510140052735</v>
+        <v>101.3807522030913</v>
       </c>
       <c r="J67" t="n">
-        <v>1932.88558510729</v>
+        <v>660.5315035456969</v>
       </c>
     </row>
     <row r="68">
@@ -2731,31 +2731,31 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-4833749.077012093</v>
+        <v>-344523.909660914</v>
       </c>
       <c r="C68" t="n">
-        <v>0.03174858259782366</v>
+        <v>0.006099325807678743</v>
       </c>
       <c r="D68" t="n">
-        <v>1.967516887830811</v>
+        <v>2.811011363758897</v>
       </c>
       <c r="E68" t="n">
-        <v>2436.629491336082</v>
+        <v>2592.542000976259</v>
       </c>
       <c r="F68" t="n">
-        <v>7777.80217928589</v>
+        <v>3056.981762589917</v>
       </c>
       <c r="G68" t="n">
-        <v>1255.956165283309</v>
+        <v>1281.884047603591</v>
       </c>
       <c r="H68" t="n">
-        <v>17823.9183728047</v>
+        <v>9014.63952885546</v>
       </c>
       <c r="I68" t="n">
-        <v>91.95105129283434</v>
+        <v>100.3653556690185</v>
       </c>
       <c r="J68" t="n">
-        <v>1989.824630705073</v>
+        <v>812.9158778289321</v>
       </c>
     </row>
     <row r="69">
@@ -2765,31 +2765,31 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-5493205.655179165</v>
+        <v>-467591.9654210121</v>
       </c>
       <c r="C69" t="n">
-        <v>0.09555393634396607</v>
+        <v>0.01469903594906556</v>
       </c>
       <c r="D69" t="n">
-        <v>10.18138554493085</v>
+        <v>2.175229468900608</v>
       </c>
       <c r="E69" t="n">
-        <v>2480.559666664724</v>
+        <v>2601.827351688885</v>
       </c>
       <c r="F69" t="n">
-        <v>8195.156986868762</v>
+        <v>2918.982555021298</v>
       </c>
       <c r="G69" t="n">
-        <v>1255.50927433805</v>
+        <v>1265.74033773906</v>
       </c>
       <c r="H69" t="n">
-        <v>14300.1116353524</v>
+        <v>8455.655950615186</v>
       </c>
       <c r="I69" t="n">
-        <v>115.510140052735</v>
+        <v>100.8154160651619</v>
       </c>
       <c r="J69" t="n">
-        <v>1967.466606955419</v>
+        <v>659.0989164968357</v>
       </c>
     </row>
     <row r="70">
@@ -2799,31 +2799,31 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-5377166.784444997</v>
+        <v>-949442.7448543659</v>
       </c>
       <c r="C70" t="n">
-        <v>0.08350893510215436</v>
+        <v>0.09918425220994832</v>
       </c>
       <c r="D70" t="n">
-        <v>7.31206981346647</v>
+        <v>10.60642322106617</v>
       </c>
       <c r="E70" t="n">
-        <v>2575.535110991356</v>
+        <v>2597.986743311546</v>
       </c>
       <c r="F70" t="n">
-        <v>7833.694035625397</v>
+        <v>3093.679300866719</v>
       </c>
       <c r="G70" t="n">
-        <v>1256.025230395052</v>
+        <v>1265.787445944027</v>
       </c>
       <c r="H70" t="n">
-        <v>14901.68411051628</v>
+        <v>5895.167955092041</v>
       </c>
       <c r="I70" t="n">
-        <v>100.4297897480496</v>
+        <v>100.1869665380485</v>
       </c>
       <c r="J70" t="n">
-        <v>2344.741622202006</v>
+        <v>659.0455415467682</v>
       </c>
     </row>
     <row r="71">
@@ -2833,31 +2833,31 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-4910417.842328825</v>
+        <v>-908349.4409658657</v>
       </c>
       <c r="C71" t="n">
-        <v>0.03791087709486255</v>
+        <v>0.09161677691758351</v>
       </c>
       <c r="D71" t="n">
-        <v>5.913286011218455</v>
+        <v>9.558433806557986</v>
       </c>
       <c r="E71" t="n">
-        <v>2511.071694061482</v>
+        <v>2586.965064165037</v>
       </c>
       <c r="F71" t="n">
-        <v>8150.618817529073</v>
+        <v>3049.284198282142</v>
       </c>
       <c r="G71" t="n">
-        <v>1255.757424900388</v>
+        <v>1274.019526363944</v>
       </c>
       <c r="H71" t="n">
-        <v>17371.92099496725</v>
+        <v>6084.268249193617</v>
       </c>
       <c r="I71" t="n">
-        <v>107.6524422432934</v>
+        <v>100.4770827710329</v>
       </c>
       <c r="J71" t="n">
-        <v>2038.369265676572</v>
+        <v>660.4890938521805</v>
       </c>
     </row>
     <row r="72">
@@ -2867,31 +2867,31 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-4222586.424179119</v>
+        <v>-44860.19063623622</v>
       </c>
       <c r="C72" t="n">
-        <v>0.004409315398213045</v>
+        <v>0.002256711789137689</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>0.1974798515468668</v>
       </c>
       <c r="E72" t="n">
-        <v>2464.050188742262</v>
+        <v>2578.802058330032</v>
       </c>
       <c r="F72" t="n">
-        <v>7780.307295895598</v>
+        <v>2965.266227281439</v>
       </c>
       <c r="G72" t="n">
-        <v>1255.233594426257</v>
+        <v>1687.608451784083</v>
       </c>
       <c r="H72" t="n">
-        <v>21051.25163204323</v>
+        <v>8994.645078260433</v>
       </c>
       <c r="I72" t="n">
-        <v>115.046493970844</v>
+        <v>100.3193901505986</v>
       </c>
       <c r="J72" t="n">
-        <v>1965.799436996922</v>
+        <v>698.8831492553159</v>
       </c>
     </row>
     <row r="73">
@@ -2901,31 +2901,31 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-4482585.74859315</v>
+        <v>-368383.124380264</v>
       </c>
       <c r="C73" t="n">
-        <v>0.01152283895836657</v>
+        <v>0.006520421848559885</v>
       </c>
       <c r="D73" t="n">
-        <v>2.267296742169467</v>
+        <v>0.557383512360321</v>
       </c>
       <c r="E73" t="n">
-        <v>2561.714895727501</v>
+        <v>2565.888489250847</v>
       </c>
       <c r="F73" t="n">
-        <v>7971.384359417307</v>
+        <v>2915.506791394191</v>
       </c>
       <c r="G73" t="n">
-        <v>1255.299689489241</v>
+        <v>1264.008296423387</v>
       </c>
       <c r="H73" t="n">
-        <v>19653.54782230453</v>
+        <v>8989.4224993512</v>
       </c>
       <c r="I73" t="n">
-        <v>98.76559409480002</v>
+        <v>109.0460262382915</v>
       </c>
       <c r="J73" t="n">
-        <v>1953.961962473518</v>
+        <v>659.1928462021078</v>
       </c>
     </row>
     <row r="74">
@@ -2935,31 +2935,31 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-4377713.845440855</v>
+        <v>-858450.1843636222</v>
       </c>
       <c r="C74" t="n">
-        <v>0.00857613528289242</v>
+        <v>0.08056205137428027</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1294196701506989</v>
+        <v>7.197973920798207</v>
       </c>
       <c r="E74" t="n">
-        <v>2487.272422961994</v>
+        <v>2587.177003726374</v>
       </c>
       <c r="F74" t="n">
-        <v>7759.229404232497</v>
+        <v>2927.37225817771</v>
       </c>
       <c r="G74" t="n">
-        <v>1255.557521033971</v>
+        <v>1265.488048829049</v>
       </c>
       <c r="H74" t="n">
-        <v>20232.23816010924</v>
+        <v>6386.647720862426</v>
       </c>
       <c r="I74" t="n">
-        <v>113.6662281230495</v>
+        <v>102.8652675869633</v>
       </c>
       <c r="J74" t="n">
-        <v>1949.119589541992</v>
+        <v>728.7482458530574</v>
       </c>
     </row>
     <row r="75">
@@ -2969,31 +2969,31 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-5100355.846024428</v>
+        <v>61800.74334586365</v>
       </c>
       <c r="C75" t="n">
-        <v>0.05340378773463268</v>
+        <v>0.0006813639375464674</v>
       </c>
       <c r="D75" t="n">
-        <v>7.569354944979157</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>2466.614919425309</v>
+        <v>2464.92091033508</v>
       </c>
       <c r="F75" t="n">
-        <v>8212.396711167774</v>
+        <v>2956.961351106597</v>
       </c>
       <c r="G75" t="n">
-        <v>1255.748614426199</v>
+        <v>1826.706312602801</v>
       </c>
       <c r="H75" t="n">
-        <v>16372.48804584764</v>
+        <v>9014.526413932996</v>
       </c>
       <c r="I75" t="n">
-        <v>91.47111743497874</v>
+        <v>121.079390179241</v>
       </c>
       <c r="J75" t="n">
-        <v>2001.122173696595</v>
+        <v>662.7400051946022</v>
       </c>
     </row>
     <row r="76">
@@ -3003,31 +3003,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-5181170.234024459</v>
+        <v>-476034.3611569479</v>
       </c>
       <c r="C76" t="n">
-        <v>0.06145815101929018</v>
+        <v>0.01603361370749481</v>
       </c>
       <c r="D76" t="n">
-        <v>4.838600500585699</v>
+        <v>2.508738000015343</v>
       </c>
       <c r="E76" t="n">
-        <v>2486.81292378771</v>
+        <v>2467.618373881062</v>
       </c>
       <c r="F76" t="n">
-        <v>7788.284000274549</v>
+        <v>3063.707329356251</v>
       </c>
       <c r="G76" t="n">
-        <v>1259.733203907482</v>
+        <v>1266.001081053548</v>
       </c>
       <c r="H76" t="n">
-        <v>15970.51935438183</v>
+        <v>8408.524130910915</v>
       </c>
       <c r="I76" t="n">
-        <v>102.2802057121545</v>
+        <v>106.8126418594116</v>
       </c>
       <c r="J76" t="n">
-        <v>1957.286213228019</v>
+        <v>661.8014720429138</v>
       </c>
     </row>
     <row r="77">
@@ -3037,31 +3037,31 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-5260950.41625172</v>
+        <v>117524.1065252065</v>
       </c>
       <c r="C77" t="n">
-        <v>0.06998936952842759</v>
+        <v>7.978441057063015e-05</v>
       </c>
       <c r="D77" t="n">
-        <v>9.070459847506774</v>
+        <v>0.8486525421912861</v>
       </c>
       <c r="E77" t="n">
-        <v>2545.699468391321</v>
+        <v>2453.448656999844</v>
       </c>
       <c r="F77" t="n">
-        <v>8184.192555972839</v>
+        <v>2920.550835159474</v>
       </c>
       <c r="G77" t="n">
-        <v>1255.571170823853</v>
+        <v>1906.599016992352</v>
       </c>
       <c r="H77" t="n">
-        <v>15522.43550003021</v>
+        <v>8994.515139572704</v>
       </c>
       <c r="I77" t="n">
-        <v>103.1363312423891</v>
+        <v>106.8368176153094</v>
       </c>
       <c r="J77" t="n">
-        <v>1965.753575481235</v>
+        <v>668.5765969496706</v>
       </c>
     </row>
     <row r="78">
@@ -3071,31 +3071,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-5339031.141301891</v>
+        <v>-270605.3695502793</v>
       </c>
       <c r="C78" t="n">
-        <v>0.07909707110124974</v>
+        <v>0.00541208339878625</v>
       </c>
       <c r="D78" t="n">
-        <v>8.747220711089444</v>
+        <v>0.7690767279532884</v>
       </c>
       <c r="E78" t="n">
-        <v>2439.068484314829</v>
+        <v>2582.423014608789</v>
       </c>
       <c r="F78" t="n">
-        <v>8179.118486069965</v>
+        <v>2942.653884253504</v>
       </c>
       <c r="G78" t="n">
-        <v>1264.075909024716</v>
+        <v>1397.999417188156</v>
       </c>
       <c r="H78" t="n">
-        <v>15086.65166915146</v>
+        <v>8966.164061952075</v>
       </c>
       <c r="I78" t="n">
-        <v>102.7440196188687</v>
+        <v>103.2435112548875</v>
       </c>
       <c r="J78" t="n">
-        <v>1967.442890482333</v>
+        <v>659.7596295556585</v>
       </c>
     </row>
     <row r="79">
@@ -3105,31 +3105,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-5445053.107985483</v>
+        <v>-617846.7202967196</v>
       </c>
       <c r="C79" t="n">
-        <v>0.09018676837019297</v>
+        <v>0.03811049999083145</v>
       </c>
       <c r="D79" t="n">
-        <v>9.532233674919798</v>
+        <v>4.501496159106377</v>
       </c>
       <c r="E79" t="n">
-        <v>2485.16882835969</v>
+        <v>2465.710948587578</v>
       </c>
       <c r="F79" t="n">
-        <v>8150.036898050281</v>
+        <v>3075.475490576278</v>
       </c>
       <c r="G79" t="n">
-        <v>1255.432444068512</v>
+        <v>1269.544011161801</v>
       </c>
       <c r="H79" t="n">
-        <v>14561.47047407296</v>
+        <v>7640.970392222604</v>
       </c>
       <c r="I79" t="n">
-        <v>102.5542991252319</v>
+        <v>146.0636990911815</v>
       </c>
       <c r="J79" t="n">
-        <v>1948.482376477148</v>
+        <v>660.4206617541282</v>
       </c>
     </row>
     <row r="80">
@@ -3139,31 +3139,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-4593338.711699007</v>
+        <v>-615512.7144391742</v>
       </c>
       <c r="C80" t="n">
-        <v>0.01646713634148808</v>
+        <v>0.03765435869612534</v>
       </c>
       <c r="D80" t="n">
-        <v>0.5864690835132413</v>
+        <v>6.157117635713972</v>
       </c>
       <c r="E80" t="n">
-        <v>2485.314993985168</v>
+        <v>2594.691240047617</v>
       </c>
       <c r="F80" t="n">
-        <v>7756.519386763222</v>
+        <v>3075.475490576278</v>
       </c>
       <c r="G80" t="n">
-        <v>1256.105203733453</v>
+        <v>1269.544011161801</v>
       </c>
       <c r="H80" t="n">
-        <v>19087.34782365341</v>
+        <v>7640.970392222604</v>
       </c>
       <c r="I80" t="n">
-        <v>89.52047015742495</v>
+        <v>146.0636990911815</v>
       </c>
       <c r="J80" t="n">
-        <v>2022.337696612046</v>
+        <v>660.4206617541282</v>
       </c>
     </row>
     <row r="81">
@@ -3173,31 +3173,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4292243.054534852</v>
+        <v>-401379.2868124745</v>
       </c>
       <c r="C81" t="n">
-        <v>0.006289958514110348</v>
+        <v>0.00846678077856588</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3182248365442453</v>
+        <v>3.970909135570944</v>
       </c>
       <c r="E81" t="n">
-        <v>2467.742674294681</v>
+        <v>2600.772015345846</v>
       </c>
       <c r="F81" t="n">
-        <v>7821.202802604879</v>
+        <v>3087.067719644182</v>
       </c>
       <c r="G81" t="n">
-        <v>1255.367314930004</v>
+        <v>1266.700150306489</v>
       </c>
       <c r="H81" t="n">
-        <v>20681.61279929433</v>
+        <v>8784.911752603562</v>
       </c>
       <c r="I81" t="n">
-        <v>107.4668627791198</v>
+        <v>101.2185144787549</v>
       </c>
       <c r="J81" t="n">
-        <v>1942.599627834065</v>
+        <v>668.9263898386641</v>
       </c>
     </row>
     <row r="82">
@@ -3207,31 +3207,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-4378010.62986298</v>
+        <v>-797409.9012231627</v>
       </c>
       <c r="C82" t="n">
-        <v>0.00857767963492026</v>
+        <v>0.06771631098635936</v>
       </c>
       <c r="D82" t="n">
-        <v>0.8253138949636973</v>
+        <v>4.028979280413115</v>
       </c>
       <c r="E82" t="n">
-        <v>2487.272422961994</v>
+        <v>2461.621205037419</v>
       </c>
       <c r="F82" t="n">
-        <v>7755.985402463376</v>
+        <v>2915.825341902252</v>
       </c>
       <c r="G82" t="n">
-        <v>1255.263195975544</v>
+        <v>1264.196234202306</v>
       </c>
       <c r="H82" t="n">
-        <v>20232.23816010924</v>
+        <v>6732.981036519729</v>
       </c>
       <c r="I82" t="n">
-        <v>112.7546669479291</v>
+        <v>107.7452953035793</v>
       </c>
       <c r="J82" t="n">
-        <v>1949.119589541992</v>
+        <v>661.974919214913</v>
       </c>
     </row>
     <row r="83">
@@ -3241,31 +3241,31 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-5214085.329688484</v>
+        <v>-675476.6830257881</v>
       </c>
       <c r="C83" t="n">
-        <v>0.06480249713079528</v>
+        <v>0.04637688953175689</v>
       </c>
       <c r="D83" t="n">
-        <v>6.369770994946789</v>
+        <v>5.969272164409267</v>
       </c>
       <c r="E83" t="n">
-        <v>2460.694288809373</v>
+        <v>2565.56609987618</v>
       </c>
       <c r="F83" t="n">
-        <v>7973.475535970632</v>
+        <v>3023.607270956733</v>
       </c>
       <c r="G83" t="n">
-        <v>1255.14116255774</v>
+        <v>1264.002433134844</v>
       </c>
       <c r="H83" t="n">
-        <v>15799.55831452257</v>
+        <v>7355.03255830239</v>
       </c>
       <c r="I83" t="n">
-        <v>87.1851986441485</v>
+        <v>137.672142648437</v>
       </c>
       <c r="J83" t="n">
-        <v>1980.576588665195</v>
+        <v>659.2280585501709</v>
       </c>
     </row>
     <row r="84">
@@ -3275,31 +3275,31 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-5462126.790368449</v>
+        <v>-412248.9379104464</v>
       </c>
       <c r="C84" t="n">
-        <v>0.09197452243287943</v>
+        <v>0.008889597195060108</v>
       </c>
       <c r="D84" t="n">
-        <v>6.469389692984495</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>2451.131891734442</v>
+        <v>2467.520451570045</v>
       </c>
       <c r="F84" t="n">
-        <v>7787.956318755813</v>
+        <v>2962.391915931721</v>
       </c>
       <c r="G84" t="n">
-        <v>1255.014280830339</v>
+        <v>1269.195173205379</v>
       </c>
       <c r="H84" t="n">
-        <v>14511.54640157627</v>
+        <v>8738.515612092535</v>
       </c>
       <c r="I84" t="n">
-        <v>101.9911223925</v>
+        <v>111.5181166313781</v>
       </c>
       <c r="J84" t="n">
-        <v>1932.829738439393</v>
+        <v>694.6803474936657</v>
       </c>
     </row>
     <row r="85">
@@ -3309,31 +3309,31 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-4921427.714283964</v>
+        <v>-878807.6308763949</v>
       </c>
       <c r="C85" t="n">
-        <v>0.03863260051038481</v>
+        <v>0.08454309858216377</v>
       </c>
       <c r="D85" t="n">
-        <v>5.993082932013949</v>
+        <v>9.932087147846968</v>
       </c>
       <c r="E85" t="n">
-        <v>2463.622652879647</v>
+        <v>2598.621610962663</v>
       </c>
       <c r="F85" t="n">
-        <v>8202.033580847337</v>
+        <v>3094.805921840994</v>
       </c>
       <c r="G85" t="n">
-        <v>1255.723949052234</v>
+        <v>1264.140429066491</v>
       </c>
       <c r="H85" t="n">
-        <v>17324.87732971011</v>
+        <v>6269.851724417769</v>
       </c>
       <c r="I85" t="n">
-        <v>84.20394449576358</v>
+        <v>105.1418831841844</v>
       </c>
       <c r="J85" t="n">
-        <v>1942.107552209469</v>
+        <v>704.6424646534978</v>
       </c>
     </row>
     <row r="86">
@@ -3343,31 +3343,31 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-4920937.447117816</v>
+        <v>46139.98295876617</v>
       </c>
       <c r="C86" t="n">
-        <v>0.03896121050644072</v>
+        <v>0.001037861117323273</v>
       </c>
       <c r="D86" t="n">
-        <v>2.640260534327277</v>
+        <v>2.220446049250313e-14</v>
       </c>
       <c r="E86" t="n">
-        <v>2463.622652879647</v>
+        <v>2464.92091033508</v>
       </c>
       <c r="F86" t="n">
-        <v>7761.218946986049</v>
+        <v>2956.961351106597</v>
       </c>
       <c r="G86" t="n">
-        <v>1255.147555726393</v>
+        <v>1811.961527558896</v>
       </c>
       <c r="H86" t="n">
-        <v>17355.87536886432</v>
+        <v>8992.777108101815</v>
       </c>
       <c r="I86" t="n">
-        <v>101.5375921393414</v>
+        <v>100.4773588888113</v>
       </c>
       <c r="J86" t="n">
-        <v>2085.494443316891</v>
+        <v>662.7400051946022</v>
       </c>
     </row>
     <row r="87">
@@ -3377,31 +3377,31 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-5395639.69157475</v>
+        <v>-951076.4295159467</v>
       </c>
       <c r="C87" t="n">
-        <v>0.08539410238637518</v>
+        <v>0.09939047208005294</v>
       </c>
       <c r="D87" t="n">
-        <v>9.37589637241153</v>
+        <v>10.7466714328536</v>
       </c>
       <c r="E87" t="n">
-        <v>2466.711357950993</v>
+        <v>2588.434196836915</v>
       </c>
       <c r="F87" t="n">
-        <v>8185.685627818119</v>
+        <v>3084.616197836447</v>
       </c>
       <c r="G87" t="n">
-        <v>1263.964404568589</v>
+        <v>1264.200380799297</v>
       </c>
       <c r="H87" t="n">
-        <v>14781.40840692102</v>
+        <v>5893.211826137929</v>
       </c>
       <c r="I87" t="n">
-        <v>105.8466479789357</v>
+        <v>115.0354970072811</v>
       </c>
       <c r="J87" t="n">
-        <v>2001.893664302716</v>
+        <v>659.2330498123778</v>
       </c>
     </row>
     <row r="88">
@@ -3411,31 +3411,31 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-5261727.749019803</v>
+        <v>-455996.1853328282</v>
       </c>
       <c r="C88" t="n">
-        <v>0.07025082815069064</v>
+        <v>0.01335904961710514</v>
       </c>
       <c r="D88" t="n">
-        <v>8.612721837517689</v>
+        <v>2.753816015734067</v>
       </c>
       <c r="E88" t="n">
-        <v>2463.594245503822</v>
+        <v>2471.261318710392</v>
       </c>
       <c r="F88" t="n">
-        <v>8209.345173751541</v>
+        <v>3086.736438170248</v>
       </c>
       <c r="G88" t="n">
-        <v>1258.215520085859</v>
+        <v>1266.878740912615</v>
       </c>
       <c r="H88" t="n">
-        <v>15512.32044190985</v>
+        <v>8502.376628974163</v>
       </c>
       <c r="I88" t="n">
-        <v>125.8619426250893</v>
+        <v>100.9088110411733</v>
       </c>
       <c r="J88" t="n">
-        <v>1952.461515025369</v>
+        <v>731.6122091237421</v>
       </c>
     </row>
     <row r="89">
@@ -3445,31 +3445,31 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-4965674.748130498</v>
+        <v>-670214.3169546034</v>
       </c>
       <c r="C89" t="n">
-        <v>0.04293046471581998</v>
+        <v>0.04558059258093085</v>
       </c>
       <c r="D89" t="n">
-        <v>2.892380317116972</v>
+        <v>5.951166447759992</v>
       </c>
       <c r="E89" t="n">
-        <v>2478.197147990667</v>
+        <v>2569.728766966582</v>
       </c>
       <c r="F89" t="n">
-        <v>7743.795551513714</v>
+        <v>3023.607270956733</v>
       </c>
       <c r="G89" t="n">
-        <v>1264.068404714532</v>
+        <v>1264.002433134844</v>
       </c>
       <c r="H89" t="n">
-        <v>17089.75216626409</v>
+        <v>7382.035397775718</v>
       </c>
       <c r="I89" t="n">
-        <v>84.68663506493601</v>
+        <v>137.672142648437</v>
       </c>
       <c r="J89" t="n">
-        <v>2043.140291264604</v>
+        <v>663.379482370953</v>
       </c>
     </row>
     <row r="90">
@@ -3479,31 +3479,31 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-5095844.334660021</v>
+        <v>-720820.5064174705</v>
       </c>
       <c r="C90" t="n">
-        <v>0.05314160646054523</v>
+        <v>0.05332310840729242</v>
       </c>
       <c r="D90" t="n">
-        <v>4.225574734901572</v>
+        <v>4.677176227836888</v>
       </c>
       <c r="E90" t="n">
-        <v>2509.10771369551</v>
+        <v>2561.138218790255</v>
       </c>
       <c r="F90" t="n">
-        <v>7780.138228195602</v>
+        <v>2925.867997066648</v>
       </c>
       <c r="G90" t="n">
-        <v>1255.210737584945</v>
+        <v>1264.244458562835</v>
       </c>
       <c r="H90" t="n">
-        <v>16434.96385471136</v>
+        <v>7126.92142549605</v>
       </c>
       <c r="I90" t="n">
-        <v>109.1807898677032</v>
+        <v>109.0923060734245</v>
       </c>
       <c r="J90" t="n">
-        <v>1980.661163847135</v>
+        <v>659.01487299593</v>
       </c>
     </row>
     <row r="91">
@@ -3513,31 +3513,31 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-4978618.751596168</v>
+        <v>-693078.8755399343</v>
       </c>
       <c r="C91" t="n">
-        <v>0.04368841559958235</v>
+        <v>0.04897280909320578</v>
       </c>
       <c r="D91" t="n">
-        <v>3.151856100529804</v>
+        <v>6.449759511584019</v>
       </c>
       <c r="E91" t="n">
-        <v>2496.296085247841</v>
+        <v>2587.70342476054</v>
       </c>
       <c r="F91" t="n">
-        <v>7746.540866181781</v>
+        <v>3019.04948073994</v>
       </c>
       <c r="G91" t="n">
-        <v>1258.239781347412</v>
+        <v>1264.160644836903</v>
       </c>
       <c r="H91" t="n">
-        <v>17044.05569773833</v>
+        <v>7263.017771712869</v>
       </c>
       <c r="I91" t="n">
-        <v>94.32951825409658</v>
+        <v>100.2071836151251</v>
       </c>
       <c r="J91" t="n">
-        <v>2019.061799953132</v>
+        <v>662.6898739374051</v>
       </c>
     </row>
     <row r="92">
@@ -3547,31 +3547,31 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-4187010.021228179</v>
+        <v>-865020.8160379454</v>
       </c>
       <c r="C92" t="n">
-        <v>0.003687885979999048</v>
+        <v>0.08151504009457271</v>
       </c>
       <c r="D92" t="n">
-        <v>1.728885721880014</v>
+        <v>7.093756786916739</v>
       </c>
       <c r="E92" t="n">
-        <v>2544.533458458555</v>
+        <v>2459.310686402987</v>
       </c>
       <c r="F92" t="n">
-        <v>8161.445423660882</v>
+        <v>3039.411961869188</v>
       </c>
       <c r="G92" t="n">
-        <v>1257.816919862456</v>
+        <v>1264.052370397947</v>
       </c>
       <c r="H92" t="n">
-        <v>21190.33187647179</v>
+        <v>6365.356979615413</v>
       </c>
       <c r="I92" t="n">
-        <v>92.21816433653068</v>
+        <v>106.8368176153094</v>
       </c>
       <c r="J92" t="n">
-        <v>1937.58342848447</v>
+        <v>661.450150123788</v>
       </c>
     </row>
     <row r="93">
@@ -3581,31 +3581,31 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-5054938.670591385</v>
+        <v>-761805.034713577</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04972508470601622</v>
+        <v>0.06045807115348854</v>
       </c>
       <c r="D93" t="n">
-        <v>7.749286212045392</v>
+        <v>7.708407420065644</v>
       </c>
       <c r="E93" t="n">
-        <v>2583.791876012651</v>
+        <v>2593.541915202128</v>
       </c>
       <c r="F93" t="n">
-        <v>8154.9075510609</v>
+        <v>3038.702660782436</v>
       </c>
       <c r="G93" t="n">
-        <v>1259.465527711358</v>
+        <v>1264.121080354627</v>
       </c>
       <c r="H93" t="n">
-        <v>16597.43982076561</v>
+        <v>6898.122110872126</v>
       </c>
       <c r="I93" t="n">
-        <v>90.83045118193783</v>
+        <v>100.3795649012709</v>
       </c>
       <c r="J93" t="n">
-        <v>1939.377950905123</v>
+        <v>659.8488557294044</v>
       </c>
     </row>
     <row r="94">
@@ -3615,31 +3615,31 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-4987469.747487668</v>
+        <v>-363512.7801149669</v>
       </c>
       <c r="C94" t="n">
-        <v>0.04510427272083675</v>
+        <v>0.006392430064092593</v>
       </c>
       <c r="D94" t="n">
-        <v>6.573857484329459</v>
+        <v>1.243081098430243</v>
       </c>
       <c r="E94" t="n">
-        <v>2480.059156245241</v>
+        <v>2465.986208987913</v>
       </c>
       <c r="F94" t="n">
-        <v>8207.640012743414</v>
+        <v>3075.30689113332</v>
       </c>
       <c r="G94" t="n">
-        <v>1272.606893348136</v>
+        <v>1264.01997172911</v>
       </c>
       <c r="H94" t="n">
-        <v>16886.97298015234</v>
+        <v>9002.676517899326</v>
       </c>
       <c r="I94" t="n">
-        <v>84.03382942057493</v>
+        <v>113.9922940762312</v>
       </c>
       <c r="J94" t="n">
-        <v>2151.659187539085</v>
+        <v>729.6517922056039</v>
       </c>
     </row>
     <row r="95">
@@ -3649,31 +3649,31 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-5511938.621013692</v>
+        <v>-269525.5052230428</v>
       </c>
       <c r="C95" t="n">
-        <v>0.09749221003339677</v>
+        <v>0.005162391255769596</v>
       </c>
       <c r="D95" t="n">
-        <v>11.01914512599294</v>
+        <v>0.7103288323934698</v>
       </c>
       <c r="E95" t="n">
-        <v>2558.185308929768</v>
+        <v>2582.423014608789</v>
       </c>
       <c r="F95" t="n">
-        <v>8206.484528945562</v>
+        <v>2942.653884253504</v>
       </c>
       <c r="G95" t="n">
-        <v>1255.00447774289</v>
+        <v>1391.203434123868</v>
       </c>
       <c r="H95" t="n">
-        <v>14200.1560769448</v>
+        <v>8999.050248082422</v>
       </c>
       <c r="I95" t="n">
-        <v>93.87855623110815</v>
+        <v>103.2435112548875</v>
       </c>
       <c r="J95" t="n">
-        <v>1931.541741568791</v>
+        <v>659.7596295556585</v>
       </c>
     </row>
     <row r="96">
@@ -3683,31 +3683,31 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-4709868.017454644</v>
+        <v>-873253.8537991955</v>
       </c>
       <c r="C96" t="n">
-        <v>0.02321834257772881</v>
+        <v>0.08320546141290133</v>
       </c>
       <c r="D96" t="n">
-        <v>2.380641311907028</v>
+        <v>7.925925522175103</v>
       </c>
       <c r="E96" t="n">
-        <v>2569.523078495736</v>
+        <v>2466.795535647158</v>
       </c>
       <c r="F96" t="n">
-        <v>7794.714384855599</v>
+        <v>3082.039630905748</v>
       </c>
       <c r="G96" t="n">
-        <v>1256.025230395052</v>
+        <v>1264.119816929523</v>
       </c>
       <c r="H96" t="n">
-        <v>18429.58655305488</v>
+        <v>6317.381296853728</v>
       </c>
       <c r="I96" t="n">
-        <v>100.4297897480496</v>
+        <v>102.5838768873162</v>
       </c>
       <c r="J96" t="n">
-        <v>2344.741622202006</v>
+        <v>660.8469414107459</v>
       </c>
     </row>
     <row r="97">
@@ -3717,31 +3717,31 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-5386543.584488722</v>
+        <v>-33464.00269932812</v>
       </c>
       <c r="C97" t="n">
-        <v>0.08384765103073251</v>
+        <v>0.001960228209029035</v>
       </c>
       <c r="D97" t="n">
-        <v>9.426201261852396</v>
+        <v>1.470710329034575</v>
       </c>
       <c r="E97" t="n">
-        <v>2485.432873715014</v>
+        <v>2455.477772677678</v>
       </c>
       <c r="F97" t="n">
-        <v>8186.247115269192</v>
+        <v>3077.430474782773</v>
       </c>
       <c r="G97" t="n">
-        <v>1255.568345854221</v>
+        <v>1698.952381623787</v>
       </c>
       <c r="H97" t="n">
-        <v>14862.37898817654</v>
+        <v>9013.680148403828</v>
       </c>
       <c r="I97" t="n">
-        <v>128.5831802783165</v>
+        <v>108.5876175743381</v>
       </c>
       <c r="J97" t="n">
-        <v>1965.80741355986</v>
+        <v>659.1618963012039</v>
       </c>
     </row>
     <row r="98">
@@ -3751,31 +3751,31 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-4001897.133103886</v>
+        <v>89724.02972645732</v>
       </c>
       <c r="C98" t="n">
-        <v>5.799556634528432e-18</v>
+        <v>0.0006052149695892453</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1010270010697645</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>2454.914052489735</v>
+        <v>2476.854872009972</v>
       </c>
       <c r="F98" t="n">
-        <v>7799.121213392675</v>
+        <v>3046.085902808221</v>
       </c>
       <c r="G98" t="n">
-        <v>1257.97510366496</v>
+        <v>1870.965431029441</v>
       </c>
       <c r="H98" t="n">
-        <v>22206.09834728213</v>
+        <v>8976.791122694003</v>
       </c>
       <c r="I98" t="n">
-        <v>109.8799099459591</v>
+        <v>106.8125081751433</v>
       </c>
       <c r="J98" t="n">
-        <v>1956.734926623041</v>
+        <v>663.3094330265334</v>
       </c>
     </row>
     <row r="99">
@@ -3785,31 +3785,31 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-5274731.914293238</v>
+        <v>-829504.22317247</v>
       </c>
       <c r="C99" t="n">
-        <v>0.07140556435428699</v>
+        <v>0.07459153804903802</v>
       </c>
       <c r="D99" t="n">
-        <v>9.49825939250889</v>
+        <v>7.427020123839267</v>
       </c>
       <c r="E99" t="n">
-        <v>2574.493354587281</v>
+        <v>2596.372316550699</v>
       </c>
       <c r="F99" t="n">
-        <v>8200.460665721332</v>
+        <v>2958.178977485117</v>
       </c>
       <c r="G99" t="n">
-        <v>1255.253169555717</v>
+        <v>1265.68023740631</v>
       </c>
       <c r="H99" t="n">
-        <v>15450.7350734365</v>
+        <v>6537.187662684955</v>
       </c>
       <c r="I99" t="n">
-        <v>84.50589787288011</v>
+        <v>146.0814554212862</v>
       </c>
       <c r="J99" t="n">
-        <v>1941.21050430932</v>
+        <v>660.795675375451</v>
       </c>
     </row>
     <row r="100">
@@ -3819,31 +3819,31 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-4469726.629230129</v>
+        <v>-881333.2543162801</v>
       </c>
       <c r="C100" t="n">
-        <v>0.01130662674270547</v>
+        <v>0.08518921163204587</v>
       </c>
       <c r="D100" t="n">
-        <v>3.203350164119834</v>
+        <v>9.915157154880205</v>
       </c>
       <c r="E100" t="n">
-        <v>2463.273290354301</v>
+        <v>2594.428652603251</v>
       </c>
       <c r="F100" t="n">
-        <v>8198.204317372103</v>
+        <v>3094.617343197567</v>
       </c>
       <c r="G100" t="n">
-        <v>1257.643416849234</v>
+        <v>1264.454207711197</v>
       </c>
       <c r="H100" t="n">
-        <v>19693.61208989197</v>
+        <v>6253.35174823322</v>
       </c>
       <c r="I100" t="n">
-        <v>102.1019554821396</v>
+        <v>173.436237842826</v>
       </c>
       <c r="J100" t="n">
-        <v>2022.337696612046</v>
+        <v>659.6488109254489</v>
       </c>
     </row>
     <row r="101">
@@ -3853,31 +3853,31 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-4709866.363586869</v>
+        <v>-47142.6304411781</v>
       </c>
       <c r="C101" t="n">
-        <v>0.02321782007355564</v>
+        <v>0.002260222835349736</v>
       </c>
       <c r="D101" t="n">
-        <v>2.29898344760997</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>2569.523078495736</v>
+        <v>2466.420043197903</v>
       </c>
       <c r="F101" t="n">
-        <v>7793.276727699611</v>
+        <v>2965.266227281439</v>
       </c>
       <c r="G101" t="n">
-        <v>1256.075020231994</v>
+        <v>1687.255457252479</v>
       </c>
       <c r="H101" t="n">
-        <v>18429.58655305488</v>
+        <v>8994.645078260433</v>
       </c>
       <c r="I101" t="n">
-        <v>100.4297897480496</v>
+        <v>101.3472382690627</v>
       </c>
       <c r="J101" t="n">
-        <v>2344.139000223059</v>
+        <v>698.8831492553159</v>
       </c>
     </row>
     <row r="102">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>

--- a/output_data/Offgrid_Pareto_Results_3D.xlsx
+++ b/output_data/Offgrid_Pareto_Results_3D.xlsx
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>302600.4375273865</v>
+        <v>-938792.6514294473</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.09999972166528819</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>6.228117397732502</v>
       </c>
       <c r="E2" t="n">
-        <v>2454.359737971311</v>
+        <v>2459.062197732333</v>
       </c>
       <c r="F2" t="n">
-        <v>2960.434845345824</v>
+        <v>2915.377749321438</v>
       </c>
       <c r="G2" t="n">
-        <v>2230.095223922531</v>
+        <v>1264.826771146343</v>
       </c>
       <c r="H2" t="n">
-        <v>8675.514169274191</v>
+        <v>5979.200359509959</v>
       </c>
       <c r="I2" t="n">
-        <v>100.4364177857256</v>
+        <v>100.235887068947</v>
       </c>
       <c r="J2" t="n">
-        <v>659.136535958222</v>
+        <v>623.1625478280099</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-954402.0918039726</v>
+        <v>-939049.5738733923</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09999540812959239</v>
+        <v>0.09997844271228384</v>
       </c>
       <c r="D3" t="n">
-        <v>8.301774116405092</v>
+        <v>6.41422223614454</v>
       </c>
       <c r="E3" t="n">
-        <v>2588.58888960435</v>
+        <v>2463.029169958663</v>
       </c>
       <c r="F3" t="n">
-        <v>2921.44556046302</v>
+        <v>2923.300087151228</v>
       </c>
       <c r="G3" t="n">
-        <v>1264.046558389344</v>
+        <v>1264.325771181391</v>
       </c>
       <c r="H3" t="n">
-        <v>5892.646911059362</v>
+        <v>5979.200359509959</v>
       </c>
       <c r="I3" t="n">
-        <v>102.921918415785</v>
+        <v>103.747152711068</v>
       </c>
       <c r="J3" t="n">
-        <v>659.1360767326823</v>
+        <v>614.5194226382388</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-950698.7851677081</v>
+        <v>-924416.8613478653</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09924701512664022</v>
+        <v>0.09728898445753881</v>
       </c>
       <c r="D4" t="n">
-        <v>11.0275596804852</v>
+        <v>10.88158912687289</v>
       </c>
       <c r="E4" t="n">
-        <v>2597.986743311546</v>
+        <v>2602.469632563345</v>
       </c>
       <c r="F4" t="n">
-        <v>3094.964521314998</v>
+        <v>3088.38787642479</v>
       </c>
       <c r="G4" t="n">
-        <v>1264.095685272923</v>
+        <v>1264.250852369031</v>
       </c>
       <c r="H4" t="n">
-        <v>5895.167955092041</v>
+        <v>6020.852304798743</v>
       </c>
       <c r="I4" t="n">
-        <v>100.1869665380485</v>
+        <v>163.6333460490836</v>
       </c>
       <c r="J4" t="n">
-        <v>659.201248680894</v>
+        <v>630.1753075936035</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>117680.7061045798</v>
+        <v>483988.3288623453</v>
       </c>
       <c r="C5" t="n">
-        <v>3.141060155051287e-18</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2453.574241963405</v>
+        <v>2459.197450605906</v>
       </c>
       <c r="F5" t="n">
-        <v>2915.096811801545</v>
+        <v>2931.680060029543</v>
       </c>
       <c r="G5" t="n">
-        <v>1902.303635602449</v>
+        <v>2386.768791839745</v>
       </c>
       <c r="H5" t="n">
-        <v>9013.680148403828</v>
+        <v>9001.304573296673</v>
       </c>
       <c r="I5" t="n">
-        <v>109.1242885764577</v>
+        <v>112.6736350291269</v>
       </c>
       <c r="J5" t="n">
-        <v>659.1684521035145</v>
+        <v>627.8726955694112</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>302317.4915887844</v>
+        <v>-47306.10301425261</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.007311233538544728</v>
       </c>
       <c r="D6" t="n">
-        <v>2.220446049250313e-14</v>
+        <v>2.678101296424673</v>
       </c>
       <c r="E6" t="n">
-        <v>2454.527809840055</v>
+        <v>2599.12970176709</v>
       </c>
       <c r="F6" t="n">
-        <v>2939.693558482216</v>
+        <v>3081.185066013964</v>
       </c>
       <c r="G6" t="n">
-        <v>2230.095223922531</v>
+        <v>1686.264634370313</v>
       </c>
       <c r="H6" t="n">
-        <v>8675.514169274191</v>
+        <v>8964.333490151888</v>
       </c>
       <c r="I6" t="n">
-        <v>104.8010431982274</v>
+        <v>109.2505608531475</v>
       </c>
       <c r="J6" t="n">
-        <v>659.2289473958849</v>
+        <v>697.2428783739668</v>
       </c>
     </row>
     <row r="7">
@@ -657,31 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-165838.7820244692</v>
+        <v>-523288.66580607</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003655968324573565</v>
+        <v>0.02458041585900693</v>
       </c>
       <c r="D7" t="n">
-        <v>1.076332618885356</v>
+        <v>0.9988442638376838</v>
       </c>
       <c r="E7" t="n">
-        <v>2454.051598136455</v>
+        <v>2466.303816719954</v>
       </c>
       <c r="F7" t="n">
-        <v>2916.658383892748</v>
+        <v>2913.5097347404</v>
       </c>
       <c r="G7" t="n">
-        <v>1528.045051662658</v>
+        <v>1264.482560576602</v>
       </c>
       <c r="H7" t="n">
-        <v>9014.113697816458</v>
+        <v>8174.31514716168</v>
       </c>
       <c r="I7" t="n">
-        <v>100.447566217883</v>
+        <v>107.2467204072428</v>
       </c>
       <c r="J7" t="n">
-        <v>660.3033523889835</v>
+        <v>614.108481307537</v>
       </c>
     </row>
     <row r="8">
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-833502.1981422273</v>
+        <v>-543430.5486241039</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07516528316686058</v>
+        <v>0.0276178162537731</v>
       </c>
       <c r="D8" t="n">
-        <v>8.975616829619081</v>
+        <v>1.249698815556988</v>
       </c>
       <c r="E8" t="n">
-        <v>2564.300699897325</v>
+        <v>2466.303816719954</v>
       </c>
       <c r="F8" t="n">
-        <v>3091.006087529586</v>
+        <v>2913.887370500718</v>
       </c>
       <c r="G8" t="n">
-        <v>1264.007291463638</v>
+        <v>1264.176539172637</v>
       </c>
       <c r="H8" t="n">
-        <v>6515.177633326085</v>
+        <v>8069.672688874644</v>
       </c>
       <c r="I8" t="n">
-        <v>129.381423971176</v>
+        <v>101.7361450525104</v>
       </c>
       <c r="J8" t="n">
-        <v>659.2270947298247</v>
+        <v>614.0879819979549</v>
       </c>
     </row>
     <row r="9">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-524395.7410627506</v>
+        <v>-496624.8033568966</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02341873871804938</v>
+        <v>0.02051929019415631</v>
       </c>
       <c r="D9" t="n">
-        <v>3.259925530483476</v>
+        <v>1.378570208171304</v>
       </c>
       <c r="E9" t="n">
-        <v>2476.000353336311</v>
+        <v>2487.204199180762</v>
       </c>
       <c r="F9" t="n">
-        <v>3063.707329356251</v>
+        <v>2923.992229794539</v>
       </c>
       <c r="G9" t="n">
-        <v>1266.001081053548</v>
+        <v>1264.013066609295</v>
       </c>
       <c r="H9" t="n">
-        <v>8152.34956294245</v>
+        <v>8313.418863320603</v>
       </c>
       <c r="I9" t="n">
-        <v>106.8126418594116</v>
+        <v>102.2801572041625</v>
       </c>
       <c r="J9" t="n">
-        <v>661.8014720429138</v>
+        <v>625.6006478749449</v>
       </c>
     </row>
     <row r="10">
@@ -759,31 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-648964.8220931799</v>
+        <v>46573.85560867423</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04241612832209076</v>
+        <v>0.005831945807627614</v>
       </c>
       <c r="D10" t="n">
-        <v>4.548165511955937</v>
+        <v>1.846578328083148</v>
       </c>
       <c r="E10" t="n">
-        <v>2465.156176227782</v>
+        <v>2602.889772426048</v>
       </c>
       <c r="F10" t="n">
-        <v>3062.316038792906</v>
+        <v>3041.375841163024</v>
       </c>
       <c r="G10" t="n">
-        <v>1264.201104919608</v>
+        <v>1805.176194841129</v>
       </c>
       <c r="H10" t="n">
-        <v>7499.349798462164</v>
+        <v>8995.030060303357</v>
       </c>
       <c r="I10" t="n">
-        <v>146.0348590322824</v>
+        <v>105.511141234645</v>
       </c>
       <c r="J10" t="n">
-        <v>659.9512919502162</v>
+        <v>623.383921955498</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-907354.1463182936</v>
+        <v>-385701.536026042</v>
       </c>
       <c r="C11" t="n">
-        <v>0.09149902562090255</v>
+        <v>0.0122290628434072</v>
       </c>
       <c r="D11" t="n">
-        <v>10.10966077090077</v>
+        <v>1.186807806361356</v>
       </c>
       <c r="E11" t="n">
-        <v>2586.965064165037</v>
+        <v>2469.609062601906</v>
       </c>
       <c r="F11" t="n">
-        <v>3076.305861438036</v>
+        <v>3042.928801278003</v>
       </c>
       <c r="G11" t="n">
-        <v>1274.649286597097</v>
+        <v>1264.080376693519</v>
       </c>
       <c r="H11" t="n">
-        <v>6084.268249193617</v>
+        <v>8889.982827967109</v>
       </c>
       <c r="I11" t="n">
-        <v>102.7230901215207</v>
+        <v>108.4207326882549</v>
       </c>
       <c r="J11" t="n">
-        <v>660.4890938521805</v>
+        <v>613.7508636955605</v>
       </c>
     </row>
     <row r="12">
@@ -827,31 +827,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-929605.9422906162</v>
+        <v>-506289.0971195218</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09491675377797523</v>
+        <v>0.02205799658435859</v>
       </c>
       <c r="D12" t="n">
-        <v>10.45902177967086</v>
+        <v>1.557710735915696</v>
       </c>
       <c r="E12" t="n">
-        <v>2587.948163348668</v>
+        <v>2466.705267682119</v>
       </c>
       <c r="F12" t="n">
-        <v>3084.610680100116</v>
+        <v>2935.835044590414</v>
       </c>
       <c r="G12" t="n">
-        <v>1264.120152521927</v>
+        <v>1264.669114250497</v>
       </c>
       <c r="H12" t="n">
-        <v>6006.930750454039</v>
+        <v>8258.553316185968</v>
       </c>
       <c r="I12" t="n">
-        <v>115.2914057433549</v>
+        <v>115.3139802233383</v>
       </c>
       <c r="J12" t="n">
-        <v>659.2330881844097</v>
+        <v>634.3519205837946</v>
       </c>
     </row>
     <row r="13">
@@ -861,31 +861,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-777912.1805606764</v>
+        <v>-101054.575247983</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06387306981317006</v>
+        <v>0.007699678130365551</v>
       </c>
       <c r="D13" t="n">
-        <v>6.636116632656231</v>
+        <v>0.9423427666585882</v>
       </c>
       <c r="E13" t="n">
-        <v>2454.494875779611</v>
+        <v>2456.350983385819</v>
       </c>
       <c r="F13" t="n">
-        <v>3088.654973526817</v>
+        <v>3083.360711300846</v>
       </c>
       <c r="G13" t="n">
-        <v>1264.104009506432</v>
+        <v>1605.724180237512</v>
       </c>
       <c r="H13" t="n">
-        <v>6817.952305920225</v>
+        <v>9007.113728950015</v>
       </c>
       <c r="I13" t="n">
-        <v>108.4287628145966</v>
+        <v>231.6907367860759</v>
       </c>
       <c r="J13" t="n">
-        <v>692.4118040967981</v>
+        <v>668.3321226972279</v>
       </c>
     </row>
     <row r="14">
@@ -895,31 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-824739.9313409519</v>
+        <v>-893022.9736479279</v>
       </c>
       <c r="C14" t="n">
-        <v>0.07351045283083733</v>
+        <v>0.09052590948901386</v>
       </c>
       <c r="D14" t="n">
-        <v>6.824608520827113</v>
+        <v>9.201524307981035</v>
       </c>
       <c r="E14" t="n">
-        <v>2470.13285625801</v>
+        <v>2603.964291758673</v>
       </c>
       <c r="F14" t="n">
-        <v>3046.333752785451</v>
+        <v>3026.863777031846</v>
       </c>
       <c r="G14" t="n">
-        <v>1266.002001007868</v>
+        <v>1264.067629715317</v>
       </c>
       <c r="H14" t="n">
-        <v>6568.601303950204</v>
+        <v>6199.395462697594</v>
       </c>
       <c r="I14" t="n">
-        <v>106.5707793157358</v>
+        <v>103.4569675138847</v>
       </c>
       <c r="J14" t="n">
-        <v>661.5226218273632</v>
+        <v>622.8429965717053</v>
       </c>
     </row>
     <row r="15">
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-5624.887555170804</v>
+        <v>-423357.4365982153</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001675520313081665</v>
+        <v>0.014415441452353</v>
       </c>
       <c r="D15" t="n">
-        <v>1.172425897386298</v>
+        <v>3.808981422310309</v>
       </c>
       <c r="E15" t="n">
-        <v>2572.285623320831</v>
+        <v>2574.924579711491</v>
       </c>
       <c r="F15" t="n">
-        <v>2928.709594628872</v>
+        <v>3069.810372840679</v>
       </c>
       <c r="G15" t="n">
-        <v>1738.52423797798</v>
+        <v>1265.808227226574</v>
       </c>
       <c r="H15" t="n">
-        <v>9002.393740718649</v>
+        <v>8661.646011989265</v>
       </c>
       <c r="I15" t="n">
-        <v>101.5788378921921</v>
+        <v>114.546123426206</v>
       </c>
       <c r="J15" t="n">
-        <v>695.5145571041164</v>
+        <v>714.7290420575038</v>
       </c>
     </row>
     <row r="16">
@@ -963,31 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-794838.0876630894</v>
+        <v>-556964.0388482087</v>
       </c>
       <c r="C16" t="n">
-        <v>0.06721718499724776</v>
+        <v>0.02958055438896848</v>
       </c>
       <c r="D16" t="n">
-        <v>6.410444339551025</v>
+        <v>3.339771603953068</v>
       </c>
       <c r="E16" t="n">
-        <v>2595.366139457452</v>
+        <v>2469.914218660594</v>
       </c>
       <c r="F16" t="n">
-        <v>2923.44377166731</v>
+        <v>3041.055268534169</v>
       </c>
       <c r="G16" t="n">
-        <v>1264.196234202306</v>
+        <v>1264.033493575763</v>
       </c>
       <c r="H16" t="n">
-        <v>6732.981036519729</v>
+        <v>7986.51340867676</v>
       </c>
       <c r="I16" t="n">
-        <v>107.9352916538794</v>
+        <v>101.9687259773904</v>
       </c>
       <c r="J16" t="n">
-        <v>662.7383494409092</v>
+        <v>614.4229708422733</v>
       </c>
     </row>
     <row r="17">
@@ -997,31 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-532945.1195389885</v>
+        <v>-924158.3266934468</v>
       </c>
       <c r="C17" t="n">
-        <v>0.02472333870726673</v>
+        <v>0.0972471404161384</v>
       </c>
       <c r="D17" t="n">
-        <v>3.74476781819495</v>
+        <v>10.40016679082617</v>
       </c>
       <c r="E17" t="n">
-        <v>2471.261318710392</v>
+        <v>2602.427233530964</v>
       </c>
       <c r="F17" t="n">
-        <v>3089.606663804324</v>
+        <v>3092.872811091714</v>
       </c>
       <c r="G17" t="n">
-        <v>1264.01997172911</v>
+        <v>1264.828195966049</v>
       </c>
       <c r="H17" t="n">
-        <v>8106.828494955463</v>
+        <v>6020.944882237057</v>
       </c>
       <c r="I17" t="n">
-        <v>104.9307364597616</v>
+        <v>102.4243989441488</v>
       </c>
       <c r="J17" t="n">
-        <v>731.6122091237421</v>
+        <v>677.2920237577462</v>
       </c>
     </row>
     <row r="18">
@@ -1031,31 +1031,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-896316.7728934493</v>
+        <v>-785632.6707778471</v>
       </c>
       <c r="C18" t="n">
-        <v>0.08929504780156892</v>
+        <v>0.06965192725825893</v>
       </c>
       <c r="D18" t="n">
-        <v>6.248049956595714</v>
+        <v>7.058415268476425</v>
       </c>
       <c r="E18" t="n">
-        <v>2454.359737971311</v>
+        <v>2586.345702391739</v>
       </c>
       <c r="F18" t="n">
-        <v>2960.434845345824</v>
+        <v>2968.592478644375</v>
       </c>
       <c r="G18" t="n">
-        <v>1275.907455105359</v>
+        <v>1271.639983788881</v>
       </c>
       <c r="H18" t="n">
-        <v>6161.339985674605</v>
+        <v>6734.989535824748</v>
       </c>
       <c r="I18" t="n">
-        <v>100.4364177857256</v>
+        <v>103.7045789347795</v>
       </c>
       <c r="J18" t="n">
-        <v>659.2361386367932</v>
+        <v>711.6919120822992</v>
       </c>
     </row>
     <row r="19">
@@ -1065,31 +1065,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-778856.5087451385</v>
+        <v>-644485.0975698684</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06406021457430401</v>
+        <v>0.04309245909892636</v>
       </c>
       <c r="D19" t="n">
-        <v>5.604287083923132</v>
+        <v>2.273867479713909</v>
       </c>
       <c r="E19" t="n">
-        <v>2454.494875779611</v>
+        <v>2456.963541878687</v>
       </c>
       <c r="F19" t="n">
-        <v>3022.604671167619</v>
+        <v>2917.480103002983</v>
       </c>
       <c r="G19" t="n">
-        <v>1265.095210462723</v>
+        <v>1264.097460786217</v>
       </c>
       <c r="H19" t="n">
-        <v>6817.952305920225</v>
+        <v>7535.968456791475</v>
       </c>
       <c r="I19" t="n">
-        <v>109.442522175316</v>
+        <v>102.715083333423</v>
       </c>
       <c r="J19" t="n">
-        <v>661.5168318147252</v>
+        <v>623.3324339674734</v>
       </c>
     </row>
     <row r="20">
@@ -1099,31 +1099,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-849893.3442024658</v>
+        <v>188289.6450619609</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0787091252360389</v>
+        <v>0.003826831819866496</v>
       </c>
       <c r="D20" t="n">
-        <v>9.232519290101814</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2564.01998251193</v>
+        <v>2458.354843292067</v>
       </c>
       <c r="F20" t="n">
-        <v>3094.617343197567</v>
+        <v>2939.262531879023</v>
       </c>
       <c r="G20" t="n">
-        <v>1264.088011412587</v>
+        <v>1994.54520509884</v>
       </c>
       <c r="H20" t="n">
-        <v>6423.078100494287</v>
+        <v>9007.576916581886</v>
       </c>
       <c r="I20" t="n">
-        <v>180.3796084032732</v>
+        <v>127.2944382005159</v>
       </c>
       <c r="J20" t="n">
-        <v>659.6488109254489</v>
+        <v>618.7926401465737</v>
       </c>
     </row>
     <row r="21">
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-558945.7969092336</v>
+        <v>359577.671925222</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02912419456673532</v>
+        <v>0.001831591224127488</v>
       </c>
       <c r="D21" t="n">
-        <v>3.810487818265096</v>
+        <v>0.4291345787438172</v>
       </c>
       <c r="E21" t="n">
-        <v>2461.321235046245</v>
+        <v>2456.920673317376</v>
       </c>
       <c r="F21" t="n">
-        <v>3079.640237388961</v>
+        <v>2957.198198631132</v>
       </c>
       <c r="G21" t="n">
-        <v>1269.653202975438</v>
+        <v>2228.591164695605</v>
       </c>
       <c r="H21" t="n">
-        <v>7951.370559842803</v>
+        <v>8973.041967884166</v>
       </c>
       <c r="I21" t="n">
-        <v>149.1465623774301</v>
+        <v>122.7295238904736</v>
       </c>
       <c r="J21" t="n">
-        <v>659.6407743467212</v>
+        <v>637.4525495026571</v>
       </c>
     </row>
     <row r="22">
@@ -1167,31 +1167,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-766394.4512698576</v>
+        <v>-200159.9224067023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06138967448314243</v>
+        <v>0.009318530797988757</v>
       </c>
       <c r="D22" t="n">
-        <v>5.749719340398962</v>
+        <v>3.074010838108931</v>
       </c>
       <c r="E22" t="n">
-        <v>2592.123962361539</v>
+        <v>2602.116745054462</v>
       </c>
       <c r="F22" t="n">
-        <v>2937.066474079016</v>
+        <v>3075.044555799876</v>
       </c>
       <c r="G22" t="n">
-        <v>1264.121080354627</v>
+        <v>1484.505726947051</v>
       </c>
       <c r="H22" t="n">
-        <v>6883.146739798627</v>
+        <v>8964.333490151888</v>
       </c>
       <c r="I22" t="n">
-        <v>100.9233360741876</v>
+        <v>109.2505608531475</v>
       </c>
       <c r="J22" t="n">
-        <v>663.1746258288041</v>
+        <v>699.1118153594023</v>
       </c>
     </row>
     <row r="23">
@@ -1201,31 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-585970.6487126942</v>
+        <v>97146.88648430072</v>
       </c>
       <c r="C23" t="n">
-        <v>0.03279125721083113</v>
+        <v>0.005777607221935071</v>
       </c>
       <c r="D23" t="n">
-        <v>3.508524317295725</v>
+        <v>0.8153141746917947</v>
       </c>
       <c r="E23" t="n">
-        <v>2467.3571137865</v>
+        <v>2566.508280708342</v>
       </c>
       <c r="F23" t="n">
-        <v>3038.310210264528</v>
+        <v>2990.883770767774</v>
       </c>
       <c r="G23" t="n">
-        <v>1264.046513845323</v>
+        <v>1895.730561084314</v>
       </c>
       <c r="H23" t="n">
-        <v>7834.61732604952</v>
+        <v>8907.30568175334</v>
       </c>
       <c r="I23" t="n">
-        <v>137.3376515718435</v>
+        <v>112.2846640520006</v>
       </c>
       <c r="J23" t="n">
-        <v>669.1080964237093</v>
+        <v>624.4662896566941</v>
       </c>
     </row>
     <row r="24">
@@ -1235,31 +1235,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-602451.1065021688</v>
+        <v>279934.0447898577</v>
       </c>
       <c r="C24" t="n">
-        <v>0.03515852951086217</v>
+        <v>0.002982866614879118</v>
       </c>
       <c r="D24" t="n">
-        <v>6.168065657615518</v>
+        <v>0.2436177558255204</v>
       </c>
       <c r="E24" t="n">
-        <v>2586.965064165037</v>
+        <v>2454.949651364508</v>
       </c>
       <c r="F24" t="n">
-        <v>3077.546992072284</v>
+        <v>3083.289997600795</v>
       </c>
       <c r="G24" t="n">
-        <v>1264.869314649435</v>
+        <v>2124.562972806262</v>
       </c>
       <c r="H24" t="n">
-        <v>7732.717161586336</v>
+        <v>8960.990803842698</v>
       </c>
       <c r="I24" t="n">
-        <v>109.0460262382915</v>
+        <v>104.3493034103863</v>
       </c>
       <c r="J24" t="n">
-        <v>660.4890938521805</v>
+        <v>613.6628779648954</v>
       </c>
     </row>
     <row r="25">
@@ -1269,31 +1269,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-888496.1217478928</v>
+        <v>-697061.8534540352</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08637833937724862</v>
+        <v>0.05124977921081596</v>
       </c>
       <c r="D25" t="n">
-        <v>9.725855988727394</v>
+        <v>5.198041480223403</v>
       </c>
       <c r="E25" t="n">
-        <v>2585.600179553976</v>
+        <v>2459.156742166847</v>
       </c>
       <c r="F25" t="n">
-        <v>3083.556757043163</v>
+        <v>3075.268355075816</v>
       </c>
       <c r="G25" t="n">
-        <v>1264.140429066491</v>
+        <v>1264.060383982735</v>
       </c>
       <c r="H25" t="n">
-        <v>6225.091836444712</v>
+        <v>7235.280339422375</v>
       </c>
       <c r="I25" t="n">
-        <v>104.6966351853381</v>
+        <v>102.7113069987598</v>
       </c>
       <c r="J25" t="n">
-        <v>661.1025884053366</v>
+        <v>711.9103810621465</v>
       </c>
     </row>
     <row r="26">
@@ -1303,31 +1303,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-631742.3364727302</v>
+        <v>-747352.4419284808</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03973171832919841</v>
+        <v>0.06078647173092974</v>
       </c>
       <c r="D26" t="n">
-        <v>4.663636610072519</v>
+        <v>3.692067095363161</v>
       </c>
       <c r="E26" t="n">
-        <v>2466.795535647158</v>
+        <v>2472.990083031628</v>
       </c>
       <c r="F26" t="n">
-        <v>3082.039630905748</v>
+        <v>2919.780231147646</v>
       </c>
       <c r="G26" t="n">
-        <v>1264.859791548107</v>
+        <v>1264.296772612704</v>
       </c>
       <c r="H26" t="n">
-        <v>7588.877138875784</v>
+        <v>6985.449877251613</v>
       </c>
       <c r="I26" t="n">
-        <v>109.0005973363496</v>
+        <v>144.0243829502808</v>
       </c>
       <c r="J26" t="n">
-        <v>663.4124614202801</v>
+        <v>632.2681256015393</v>
       </c>
     </row>
     <row r="27">
@@ -1337,31 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-738855.0093042157</v>
+        <v>-803797.0395651702</v>
       </c>
       <c r="C27" t="n">
-        <v>0.05595751879442328</v>
+        <v>0.07217820483522069</v>
       </c>
       <c r="D27" t="n">
-        <v>7.300577802142838</v>
+        <v>6.860459723739187</v>
       </c>
       <c r="E27" t="n">
-        <v>2585.693911150631</v>
+        <v>2575.545851636009</v>
       </c>
       <c r="F27" t="n">
-        <v>3037.86476434554</v>
+        <v>2955.954979295814</v>
       </c>
       <c r="G27" t="n">
-        <v>1264.121141016195</v>
+        <v>1264.03368565149</v>
       </c>
       <c r="H27" t="n">
-        <v>7019.757687252127</v>
+        <v>6679.925761354905</v>
       </c>
       <c r="I27" t="n">
-        <v>101.1039625386306</v>
+        <v>103.7008957005112</v>
       </c>
       <c r="J27" t="n">
-        <v>663.1846178332044</v>
+        <v>623.6563303825209</v>
       </c>
     </row>
     <row r="28">
@@ -1371,31 +1371,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-836374.2817356889</v>
+        <v>-763837.5885763364</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0761242422463925</v>
+        <v>0.06399756047671909</v>
       </c>
       <c r="D28" t="n">
-        <v>4.458076758761676</v>
+        <v>3.584985658840223</v>
       </c>
       <c r="E28" t="n">
-        <v>2454.754600323166</v>
+        <v>2459.062197732333</v>
       </c>
       <c r="F28" t="n">
-        <v>2927.37225817771</v>
+        <v>2914.386163950966</v>
       </c>
       <c r="G28" t="n">
-        <v>1265.486407687956</v>
+        <v>1264.825898695659</v>
       </c>
       <c r="H28" t="n">
-        <v>6513.388111879618</v>
+        <v>6903.670773267095</v>
       </c>
       <c r="I28" t="n">
-        <v>128.9474035306305</v>
+        <v>100.5727213116294</v>
       </c>
       <c r="J28" t="n">
-        <v>728.7482458530574</v>
+        <v>617.254208611796</v>
       </c>
     </row>
     <row r="29">
@@ -1405,31 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-548359.2030811096</v>
+        <v>-147221.4282991369</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02689108716201273</v>
+        <v>0.008367202160422893</v>
       </c>
       <c r="D29" t="n">
-        <v>5.359852598308413</v>
+        <v>0.8653426261183816</v>
       </c>
       <c r="E29" t="n">
-        <v>2586.965064165037</v>
+        <v>2483.649285510834</v>
       </c>
       <c r="F29" t="n">
-        <v>3077.546992072284</v>
+        <v>2913.517616226648</v>
       </c>
       <c r="G29" t="n">
-        <v>1264.869314649435</v>
+        <v>1556.004500400504</v>
       </c>
       <c r="H29" t="n">
-        <v>8018.350975030876</v>
+        <v>8989.20138245648</v>
       </c>
       <c r="I29" t="n">
-        <v>109.0460262382915</v>
+        <v>120.7872316500316</v>
       </c>
       <c r="J29" t="n">
-        <v>660.4890938521805</v>
+        <v>634.546412231344</v>
       </c>
     </row>
     <row r="30">
@@ -1439,31 +1439,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-307219.9377984572</v>
+        <v>-754686.1949231508</v>
       </c>
       <c r="C30" t="n">
-        <v>0.005556012533310286</v>
+        <v>0.06260757384765236</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2743961184428878</v>
+        <v>4.050226818647474</v>
       </c>
       <c r="E30" t="n">
-        <v>2469.936412431849</v>
+        <v>2472.852909053969</v>
       </c>
       <c r="F30" t="n">
-        <v>2919.099809665691</v>
+        <v>2935.321685561644</v>
       </c>
       <c r="G30" t="n">
-        <v>1342.030666864206</v>
+        <v>1268.833595080179</v>
       </c>
       <c r="H30" t="n">
-        <v>9008.945879822892</v>
+        <v>6932.227578535227</v>
       </c>
       <c r="I30" t="n">
-        <v>108.9019389860996</v>
+        <v>101.9294177800057</v>
       </c>
       <c r="J30" t="n">
-        <v>661.4239277928276</v>
+        <v>620.8456277342713</v>
       </c>
     </row>
     <row r="31">
@@ -1473,31 +1473,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-845577.5644497126</v>
+        <v>-625864.0246406784</v>
       </c>
       <c r="C31" t="n">
-        <v>0.07762852167879841</v>
+        <v>0.04024756307715972</v>
       </c>
       <c r="D31" t="n">
-        <v>9.41884459717539</v>
+        <v>6.511349263167466</v>
       </c>
       <c r="E31" t="n">
-        <v>2583.936222451917</v>
+        <v>2603.964291758673</v>
       </c>
       <c r="F31" t="n">
-        <v>3093.561227568808</v>
+        <v>3050.545566696258</v>
       </c>
       <c r="G31" t="n">
-        <v>1264.935870762397</v>
+        <v>1264.067629715317</v>
       </c>
       <c r="H31" t="n">
-        <v>6448.366595171121</v>
+        <v>7600.531342462953</v>
       </c>
       <c r="I31" t="n">
-        <v>100.2077822930924</v>
+        <v>158.6225031553898</v>
       </c>
       <c r="J31" t="n">
-        <v>659.2844264458279</v>
+        <v>645.586974260782</v>
       </c>
     </row>
     <row r="32">
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-484458.523151808</v>
+        <v>-772166.0931725441</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01704517883194842</v>
+        <v>0.06599378491656292</v>
       </c>
       <c r="D32" t="n">
-        <v>4.778167361078589</v>
+        <v>7.049398018056607</v>
       </c>
       <c r="E32" t="n">
-        <v>2595.383742149232</v>
+        <v>2576.483655164186</v>
       </c>
       <c r="F32" t="n">
-        <v>3077.462181701395</v>
+        <v>2992.834285560097</v>
       </c>
       <c r="G32" t="n">
-        <v>1264.129513871299</v>
+        <v>1264.780243122121</v>
       </c>
       <c r="H32" t="n">
-        <v>8358.26368626158</v>
+        <v>6834.804005251392</v>
       </c>
       <c r="I32" t="n">
-        <v>103.0579631255053</v>
+        <v>120.9697341183674</v>
       </c>
       <c r="J32" t="n">
-        <v>663.1835408745006</v>
+        <v>666.3185976690111</v>
       </c>
     </row>
     <row r="33">
@@ -1541,31 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-924560.3326751054</v>
+        <v>-39622.65912989993</v>
       </c>
       <c r="C33" t="n">
-        <v>0.09384401265864807</v>
+        <v>0.006887144277000243</v>
       </c>
       <c r="D33" t="n">
-        <v>9.074444076977761</v>
+        <v>2.632913766187517</v>
       </c>
       <c r="E33" t="n">
-        <v>2569.38025094354</v>
+        <v>2603.589724431766</v>
       </c>
       <c r="F33" t="n">
-        <v>3022.931013529485</v>
+        <v>3082.171784148726</v>
       </c>
       <c r="G33" t="n">
-        <v>1264.147607880569</v>
+        <v>1686.264634370313</v>
       </c>
       <c r="H33" t="n">
-        <v>6041.351125305911</v>
+        <v>9008.278196550385</v>
       </c>
       <c r="I33" t="n">
-        <v>110.953707767348</v>
+        <v>100.5654006052857</v>
       </c>
       <c r="J33" t="n">
-        <v>659.8632385808544</v>
+        <v>664.4526239253796</v>
       </c>
     </row>
     <row r="34">
@@ -1575,31 +1575,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-510252.8463912932</v>
+        <v>-457322.9714344265</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02119456147500085</v>
+        <v>0.01654636924460729</v>
       </c>
       <c r="D34" t="n">
-        <v>2.112734423474116</v>
+        <v>0.990848021112023</v>
       </c>
       <c r="E34" t="n">
-        <v>2453.079557047171</v>
+        <v>2466.738026633139</v>
       </c>
       <c r="F34" t="n">
-        <v>3021.569396919227</v>
+        <v>2962.633983634271</v>
       </c>
       <c r="G34" t="n">
-        <v>1264.121347894295</v>
+        <v>1264.03368565149</v>
       </c>
       <c r="H34" t="n">
-        <v>8238.925736554625</v>
+        <v>8519.237344225334</v>
       </c>
       <c r="I34" t="n">
-        <v>123.472029143791</v>
+        <v>103.7008957005112</v>
       </c>
       <c r="J34" t="n">
-        <v>663.471799137271</v>
+        <v>623.9592435134236</v>
       </c>
     </row>
     <row r="35">
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-814194.5833421941</v>
+        <v>-578126.5723836212</v>
       </c>
       <c r="C35" t="n">
-        <v>0.07144513693997749</v>
+        <v>0.0328671847843551</v>
       </c>
       <c r="D35" t="n">
-        <v>9.065934117861341</v>
+        <v>4.129230828426955</v>
       </c>
       <c r="E35" t="n">
-        <v>2579.357998608352</v>
+        <v>2466.755857230165</v>
       </c>
       <c r="F35" t="n">
-        <v>3094.65331616696</v>
+        <v>3080.119230062126</v>
       </c>
       <c r="G35" t="n">
-        <v>1264.068283871091</v>
+        <v>1264.160999930134</v>
       </c>
       <c r="H35" t="n">
-        <v>6609.806891585564</v>
+        <v>7868.616352622506</v>
       </c>
       <c r="I35" t="n">
-        <v>185.0834250513102</v>
+        <v>105.6623654085709</v>
       </c>
       <c r="J35" t="n">
-        <v>659.005539229359</v>
+        <v>635.2146862555861</v>
       </c>
     </row>
     <row r="36">
@@ -1643,31 +1643,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-752841.4479023656</v>
+        <v>-683554.1931968192</v>
       </c>
       <c r="C36" t="n">
-        <v>0.05924855878504808</v>
+        <v>0.04885676155157422</v>
       </c>
       <c r="D36" t="n">
-        <v>8.19795160659833</v>
+        <v>7.154222206999606</v>
       </c>
       <c r="E36" t="n">
-        <v>2595.998580222385</v>
+        <v>2603.964291758673</v>
       </c>
       <c r="F36" t="n">
-        <v>3073.58995529692</v>
+        <v>3045.511113994951</v>
       </c>
       <c r="G36" t="n">
-        <v>1264.12968918328</v>
+        <v>1264.067629715317</v>
       </c>
       <c r="H36" t="n">
-        <v>6926.12781482853</v>
+        <v>7303.76239778769</v>
       </c>
       <c r="I36" t="n">
-        <v>103.362075636616</v>
+        <v>103.6199689525953</v>
       </c>
       <c r="J36" t="n">
-        <v>826.0964420533061</v>
+        <v>622.6591657785781</v>
       </c>
     </row>
     <row r="37">
@@ -1677,31 +1677,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-747953.1378341606</v>
+        <v>-592400.3135933899</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05764874556387757</v>
+        <v>0.03630759624994939</v>
       </c>
       <c r="D37" t="n">
-        <v>7.511103847860601</v>
+        <v>3.440840854291149</v>
       </c>
       <c r="E37" t="n">
-        <v>2592.123962361539</v>
+        <v>2559.620257773315</v>
       </c>
       <c r="F37" t="n">
-        <v>3037.86476434554</v>
+        <v>2924.089624144875</v>
       </c>
       <c r="G37" t="n">
-        <v>1264.121080354627</v>
+        <v>1277.612355075499</v>
       </c>
       <c r="H37" t="n">
-        <v>6971.121567695291</v>
+        <v>7743.061453681602</v>
       </c>
       <c r="I37" t="n">
-        <v>100.9233360741876</v>
+        <v>103.747152711068</v>
       </c>
       <c r="J37" t="n">
-        <v>663.1446751812931</v>
+        <v>659.3073705034576</v>
       </c>
     </row>
     <row r="38">
@@ -1711,31 +1711,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-489939.3245343454</v>
+        <v>-644554.1659430629</v>
       </c>
       <c r="C38" t="n">
-        <v>0.01810741510663311</v>
+        <v>0.04310586753055664</v>
       </c>
       <c r="D38" t="n">
-        <v>1.894272978834699</v>
+        <v>2.217585709885295</v>
       </c>
       <c r="E38" t="n">
-        <v>2455.15615795727</v>
+        <v>2456.963541878687</v>
       </c>
       <c r="F38" t="n">
-        <v>3027.201154883639</v>
+        <v>2913.572415693537</v>
       </c>
       <c r="G38" t="n">
-        <v>1265.043864183473</v>
+        <v>1264.097460786217</v>
       </c>
       <c r="H38" t="n">
-        <v>8343.712040919478</v>
+        <v>7535.968456791475</v>
       </c>
       <c r="I38" t="n">
-        <v>103.4519725153766</v>
+        <v>102.715083333423</v>
       </c>
       <c r="J38" t="n">
-        <v>663.2437844771877</v>
+        <v>623.3324339674734</v>
       </c>
     </row>
     <row r="39">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-387476.5219001342</v>
+        <v>-867094.2865192518</v>
       </c>
       <c r="C39" t="n">
-        <v>0.007712800219490962</v>
+        <v>0.08556872911173206</v>
       </c>
       <c r="D39" t="n">
-        <v>2.82742638957636</v>
+        <v>9.864602416334932</v>
       </c>
       <c r="E39" t="n">
-        <v>2583.653678330606</v>
+        <v>2603.868260033973</v>
       </c>
       <c r="F39" t="n">
-        <v>3037.967793699589</v>
+        <v>3092.817699474055</v>
       </c>
       <c r="G39" t="n">
-        <v>1267.384148832741</v>
+        <v>1264.812017907528</v>
       </c>
       <c r="H39" t="n">
-        <v>8862.354955383016</v>
+        <v>6320.257227438204</v>
       </c>
       <c r="I39" t="n">
-        <v>101.1039625386306</v>
+        <v>124.6029400260108</v>
       </c>
       <c r="J39" t="n">
-        <v>663.1846178332044</v>
+        <v>675.4576826249807</v>
       </c>
     </row>
     <row r="40">
@@ -1779,31 +1779,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-577783.1765601775</v>
+        <v>-284036.421862361</v>
       </c>
       <c r="C40" t="n">
-        <v>0.03131794915676247</v>
+        <v>0.01009510687147984</v>
       </c>
       <c r="D40" t="n">
-        <v>5.478368258111366</v>
+        <v>2.971749418742298</v>
       </c>
       <c r="E40" t="n">
-        <v>2564.300699897325</v>
+        <v>2572.157774151584</v>
       </c>
       <c r="F40" t="n">
-        <v>3076.6935390318</v>
+        <v>3087.981568394082</v>
       </c>
       <c r="G40" t="n">
-        <v>1264.068358082626</v>
+        <v>1363.580786286091</v>
       </c>
       <c r="H40" t="n">
-        <v>7869.102379038946</v>
+        <v>9008.528507900981</v>
       </c>
       <c r="I40" t="n">
-        <v>103.2733872398987</v>
+        <v>154.0431670551134</v>
       </c>
       <c r="J40" t="n">
-        <v>659.1527453573634</v>
+        <v>634.4794486879515</v>
       </c>
     </row>
     <row r="41">
@@ -1813,31 +1813,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-217704.600870715</v>
+        <v>-468725.0387445386</v>
       </c>
       <c r="C41" t="n">
-        <v>0.004402497449926205</v>
+        <v>0.01767504588994668</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.5094901832184862</v>
       </c>
       <c r="E41" t="n">
-        <v>2454.834311139775</v>
+        <v>2466.303816719954</v>
       </c>
       <c r="F41" t="n">
-        <v>3033.181319913271</v>
+        <v>2936.281521849166</v>
       </c>
       <c r="G41" t="n">
-        <v>1457.895981027802</v>
+        <v>1264.492074107309</v>
       </c>
       <c r="H41" t="n">
-        <v>9009.05629545511</v>
+        <v>8460.287273838263</v>
       </c>
       <c r="I41" t="n">
-        <v>106.8125081751433</v>
+        <v>107.2465936497329</v>
       </c>
       <c r="J41" t="n">
-        <v>662.6208666625281</v>
+        <v>613.9930657080351</v>
       </c>
     </row>
     <row r="42">
@@ -1847,31 +1847,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-319273.1874295124</v>
+        <v>420147.1298749801</v>
       </c>
       <c r="C42" t="n">
-        <v>0.005754491598955245</v>
+        <v>0.001125136754110983</v>
       </c>
       <c r="D42" t="n">
-        <v>2.284637149849345</v>
+        <v>0.6065261182913062</v>
       </c>
       <c r="E42" t="n">
-        <v>2597.337577370409</v>
+        <v>2481.874170576646</v>
       </c>
       <c r="F42" t="n">
-        <v>3023.172942161057</v>
+        <v>3086.601293732182</v>
       </c>
       <c r="G42" t="n">
-        <v>1320.182290261197</v>
+        <v>2306.624512385587</v>
       </c>
       <c r="H42" t="n">
-        <v>9010.898079417138</v>
+        <v>8965.7989912423</v>
       </c>
       <c r="I42" t="n">
-        <v>107.3567377598729</v>
+        <v>117.8717587642537</v>
       </c>
       <c r="J42" t="n">
-        <v>662.0030897370088</v>
+        <v>647.6356924077554</v>
       </c>
     </row>
     <row r="43">
@@ -1881,31 +1881,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-447456.2116727289</v>
+        <v>-836272.2626084415</v>
       </c>
       <c r="C43" t="n">
-        <v>0.01215156596074693</v>
+        <v>0.07886619404967705</v>
       </c>
       <c r="D43" t="n">
-        <v>1.68444436800379</v>
+        <v>4.326754990790727</v>
       </c>
       <c r="E43" t="n">
-        <v>2455.724782210189</v>
+        <v>2459.062197732333</v>
       </c>
       <c r="F43" t="n">
-        <v>3039.411961869188</v>
+        <v>2914.386163950966</v>
       </c>
       <c r="G43" t="n">
-        <v>1264.042852935223</v>
+        <v>1264.825898695659</v>
       </c>
       <c r="H43" t="n">
-        <v>8567.876680800657</v>
+        <v>6521.449084441338</v>
       </c>
       <c r="I43" t="n">
-        <v>136.6404048296624</v>
+        <v>100.5727213116294</v>
       </c>
       <c r="J43" t="n">
-        <v>661.1794066404187</v>
+        <v>614.3437865055748</v>
       </c>
     </row>
     <row r="44">
@@ -1915,31 +1915,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-940495.6085161632</v>
+        <v>242064.7200241373</v>
       </c>
       <c r="C44" t="n">
-        <v>0.09715196487827965</v>
+        <v>0.003497807977162494</v>
       </c>
       <c r="D44" t="n">
-        <v>10.97589894709071</v>
+        <v>0.7662168853573736</v>
       </c>
       <c r="E44" t="n">
-        <v>2603.366095538227</v>
+        <v>2591.535137226242</v>
       </c>
       <c r="F44" t="n">
-        <v>3094.964521314998</v>
+        <v>2970.498023887134</v>
       </c>
       <c r="G44" t="n">
-        <v>1264.095685272923</v>
+        <v>2072.635951701473</v>
       </c>
       <c r="H44" t="n">
-        <v>5947.742282707191</v>
+        <v>8961.164890578779</v>
       </c>
       <c r="I44" t="n">
-        <v>108.2844467840465</v>
+        <v>101.5521555374175</v>
       </c>
       <c r="J44" t="n">
-        <v>659.3731776844797</v>
+        <v>670.5235690376755</v>
       </c>
     </row>
     <row r="45">
@@ -1949,31 +1949,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-896219.454751987</v>
+        <v>-881245.439895907</v>
       </c>
       <c r="C45" t="n">
-        <v>0.08826160534930964</v>
+        <v>0.08817018165163094</v>
       </c>
       <c r="D45" t="n">
-        <v>9.893750983586413</v>
+        <v>5.926106289292266</v>
       </c>
       <c r="E45" t="n">
-        <v>2592.030230764881</v>
+        <v>2481.874170576646</v>
       </c>
       <c r="F45" t="n">
-        <v>3083.556757043163</v>
+        <v>2922.42555991094</v>
       </c>
       <c r="G45" t="n">
-        <v>1264.140368404923</v>
+        <v>1264.826771146343</v>
       </c>
       <c r="H45" t="n">
-        <v>6176.455716887857</v>
+        <v>6279.490973784273</v>
       </c>
       <c r="I45" t="n">
-        <v>104.5160996757606</v>
+        <v>102.9707644061558</v>
       </c>
       <c r="J45" t="n">
-        <v>738.8444777166693</v>
+        <v>628.4137421757412</v>
       </c>
     </row>
     <row r="46">
@@ -1983,31 +1983,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-711804.7996134465</v>
+        <v>-792795.2920317068</v>
       </c>
       <c r="C46" t="n">
-        <v>0.05207054967430293</v>
+        <v>0.07003360477787335</v>
       </c>
       <c r="D46" t="n">
-        <v>7.530235182183642</v>
+        <v>6.712544571568923</v>
       </c>
       <c r="E46" t="n">
-        <v>2574.374849967199</v>
+        <v>2573.445962685178</v>
       </c>
       <c r="F46" t="n">
-        <v>3085.748406264954</v>
+        <v>2957.189201790772</v>
       </c>
       <c r="G46" t="n">
-        <v>1264.817849283527</v>
+        <v>1264.17898177313</v>
       </c>
       <c r="H46" t="n">
-        <v>7149.039153491547</v>
+        <v>6734.989535824748</v>
       </c>
       <c r="I46" t="n">
-        <v>120.4997484973792</v>
+        <v>103.7501651888404</v>
       </c>
       <c r="J46" t="n">
-        <v>722.4365031421953</v>
+        <v>650.7723822365357</v>
       </c>
     </row>
     <row r="47">
@@ -2017,31 +2017,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25795.34746046364</v>
+        <v>150535.3320489801</v>
       </c>
       <c r="C47" t="n">
-        <v>0.001239192591251191</v>
+        <v>0.004322440262500966</v>
       </c>
       <c r="D47" t="n">
         <v>2.220446049250313e-14</v>
       </c>
       <c r="E47" t="n">
-        <v>2465.961434880859</v>
+        <v>2458.354843292067</v>
       </c>
       <c r="F47" t="n">
-        <v>2926.871496294141</v>
+        <v>2939.262531879023</v>
       </c>
       <c r="G47" t="n">
-        <v>1782.661484831079</v>
+        <v>1944.730252467773</v>
       </c>
       <c r="H47" t="n">
-        <v>9002.115792144326</v>
+        <v>9007.576916581886</v>
       </c>
       <c r="I47" t="n">
-        <v>101.3257529492159</v>
+        <v>126.2175939022473</v>
       </c>
       <c r="J47" t="n">
-        <v>695.5145571041164</v>
+        <v>618.7926401465737</v>
       </c>
     </row>
     <row r="48">
@@ -2051,31 +2051,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-654010.9789904528</v>
+        <v>-741193.9951065294</v>
       </c>
       <c r="C48" t="n">
-        <v>0.04369309868109746</v>
+        <v>0.05954436046131583</v>
       </c>
       <c r="D48" t="n">
-        <v>3.113937466142336</v>
+        <v>5.472297228699475</v>
       </c>
       <c r="E48" t="n">
-        <v>2461.114717020154</v>
+        <v>2576.173691902142</v>
       </c>
       <c r="F48" t="n">
-        <v>2962.391915931721</v>
+        <v>2919.300375886819</v>
       </c>
       <c r="G48" t="n">
-        <v>1269.195173205379</v>
+        <v>1264.922814553345</v>
       </c>
       <c r="H48" t="n">
-        <v>7462.419585498384</v>
+        <v>7007.568899385081</v>
       </c>
       <c r="I48" t="n">
-        <v>112.3227803782716</v>
+        <v>142.1323856580339</v>
       </c>
       <c r="J48" t="n">
-        <v>694.6803474936657</v>
+        <v>613.6517496999968</v>
       </c>
     </row>
     <row r="49">
@@ -2085,31 +2085,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-549281.37954643</v>
+        <v>-845987.8436188987</v>
       </c>
       <c r="C49" t="n">
-        <v>0.02697970831079994</v>
+        <v>0.08087661832213774</v>
       </c>
       <c r="D49" t="n">
-        <v>5.135272532579527</v>
+        <v>5.314154445638552</v>
       </c>
       <c r="E49" t="n">
-        <v>2569.17104379028</v>
+        <v>2482.413467014506</v>
       </c>
       <c r="F49" t="n">
-        <v>3077.546992072284</v>
+        <v>2914.386163950966</v>
       </c>
       <c r="G49" t="n">
-        <v>1264.008296423387</v>
+        <v>1264.825291813765</v>
       </c>
       <c r="H49" t="n">
-        <v>8018.350975030876</v>
+        <v>6467.645130988124</v>
       </c>
       <c r="I49" t="n">
-        <v>109.0460262382915</v>
+        <v>100.5727213116294</v>
       </c>
       <c r="J49" t="n">
-        <v>663.4335050511652</v>
+        <v>617.254208611796</v>
       </c>
     </row>
     <row r="50">
@@ -2119,31 +2119,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-681953.4231144716</v>
+        <v>-291917.7140641022</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0474176943899275</v>
+        <v>0.01018811212410254</v>
       </c>
       <c r="D50" t="n">
-        <v>4.235097274344524</v>
+        <v>0.3867220639267033</v>
       </c>
       <c r="E50" t="n">
-        <v>2557.103716553123</v>
+        <v>2462.563309742004</v>
       </c>
       <c r="F50" t="n">
-        <v>2925.867997066648</v>
+        <v>2923.911869976611</v>
       </c>
       <c r="G50" t="n">
-        <v>1264.244458562835</v>
+        <v>1363.580786286091</v>
       </c>
       <c r="H50" t="n">
-        <v>7331.441917425313</v>
+        <v>8998.891177059031</v>
       </c>
       <c r="I50" t="n">
-        <v>109.0923060734245</v>
+        <v>100.2372258838696</v>
       </c>
       <c r="J50" t="n">
-        <v>670.8407753416441</v>
+        <v>623.1966058009137</v>
       </c>
     </row>
     <row r="51">
@@ -2153,31 +2153,31 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-604745.9509582645</v>
+        <v>-669315.0427797544</v>
       </c>
       <c r="C51" t="n">
-        <v>0.03643368826264153</v>
+        <v>0.04716782798987258</v>
       </c>
       <c r="D51" t="n">
-        <v>6.080964064207439</v>
+        <v>3.189221421816157</v>
       </c>
       <c r="E51" t="n">
-        <v>2587.409398439981</v>
+        <v>2483.17395341116</v>
       </c>
       <c r="F51" t="n">
-        <v>3082.177121855804</v>
+        <v>2929.846273192178</v>
       </c>
       <c r="G51" t="n">
-        <v>1271.293180500726</v>
+        <v>1264.695476833016</v>
       </c>
       <c r="H51" t="n">
-        <v>7681.435812661402</v>
+        <v>7389.9187411352</v>
       </c>
       <c r="I51" t="n">
-        <v>109.0460262382915</v>
+        <v>121.3351864416263</v>
       </c>
       <c r="J51" t="n">
-        <v>799.7029253262298</v>
+        <v>699.4515263460506</v>
       </c>
     </row>
     <row r="52">
@@ -2187,31 +2187,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-705479.9557400984</v>
+        <v>-924778.9699306735</v>
       </c>
       <c r="C52" t="n">
-        <v>0.05094281152645695</v>
+        <v>0.0972993125822912</v>
       </c>
       <c r="D52" t="n">
-        <v>7.901835510800959</v>
+        <v>10.0905389024618</v>
       </c>
       <c r="E52" t="n">
-        <v>2597.292550370013</v>
+        <v>2602.469632563345</v>
       </c>
       <c r="F52" t="n">
-        <v>3092.376481717291</v>
+        <v>3069.290865208293</v>
       </c>
       <c r="G52" t="n">
-        <v>1265.454719263452</v>
+        <v>1265.637912136044</v>
       </c>
       <c r="H52" t="n">
-        <v>7183.75935055739</v>
+        <v>6020.852304798743</v>
       </c>
       <c r="I52" t="n">
-        <v>102.6861446616811</v>
+        <v>104.1503100238455</v>
       </c>
       <c r="J52" t="n">
-        <v>669.127503413455</v>
+        <v>630.2391504792823</v>
       </c>
     </row>
     <row r="53">
@@ -2221,31 +2221,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-727878.0438603102</v>
+        <v>-853525.5066770869</v>
       </c>
       <c r="C53" t="n">
-        <v>0.05457892586105077</v>
+        <v>0.08261080209260196</v>
       </c>
       <c r="D53" t="n">
-        <v>4.996638135418852</v>
+        <v>7.94971575801301</v>
       </c>
       <c r="E53" t="n">
-        <v>2461.804301860107</v>
+        <v>2466.755857230165</v>
       </c>
       <c r="F53" t="n">
-        <v>3036.620048438254</v>
+        <v>3092.725343357699</v>
       </c>
       <c r="G53" t="n">
-        <v>1265.739062154282</v>
+        <v>1264.160999930134</v>
       </c>
       <c r="H53" t="n">
-        <v>7081.003914181478</v>
+        <v>6409.437864613627</v>
       </c>
       <c r="I53" t="n">
-        <v>109.0460262382915</v>
+        <v>105.6623654085709</v>
       </c>
       <c r="J53" t="n">
-        <v>678.6332046021952</v>
+        <v>675.3945346695616</v>
       </c>
     </row>
     <row r="54">
@@ -2255,31 +2255,31 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-505159.6776785278</v>
+        <v>-708924.5300376499</v>
       </c>
       <c r="C54" t="n">
-        <v>0.02044564839480128</v>
+        <v>0.05297584343985078</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3853972227278346</v>
+        <v>4.898397195035731</v>
       </c>
       <c r="E54" t="n">
-        <v>2457.715307114932</v>
+        <v>2461.90572508749</v>
       </c>
       <c r="F54" t="n">
-        <v>2920.523450358954</v>
+        <v>3045.511113994951</v>
       </c>
       <c r="G54" t="n">
-        <v>1264.004496685516</v>
+        <v>1264.734396962809</v>
       </c>
       <c r="H54" t="n">
-        <v>8276.329977381494</v>
+        <v>7178.15734153369</v>
       </c>
       <c r="I54" t="n">
-        <v>116.6723949272143</v>
+        <v>138.8965776361088</v>
       </c>
       <c r="J54" t="n">
-        <v>659.1379824012004</v>
+        <v>613.7965356256701</v>
       </c>
     </row>
     <row r="55">
@@ -2289,31 +2289,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-692071.59648673</v>
+        <v>-902932.1649568207</v>
       </c>
       <c r="C55" t="n">
-        <v>0.04910894795758706</v>
+        <v>0.0926722588951729</v>
       </c>
       <c r="D55" t="n">
-        <v>3.560615243074983</v>
+        <v>9.769871653675089</v>
       </c>
       <c r="E55" t="n">
-        <v>2466.210839065182</v>
+        <v>2599.298010578806</v>
       </c>
       <c r="F55" t="n">
-        <v>2958.178977485117</v>
+        <v>3065.968700638495</v>
       </c>
       <c r="G55" t="n">
-        <v>1265.68023740631</v>
+        <v>1264.120674343296</v>
       </c>
       <c r="H55" t="n">
-        <v>7278.806424518832</v>
+        <v>6141.140903393048</v>
       </c>
       <c r="I55" t="n">
-        <v>109.8274779742263</v>
+        <v>124.3206242115262</v>
       </c>
       <c r="J55" t="n">
-        <v>660.795675375451</v>
+        <v>628.4045253500761</v>
       </c>
     </row>
     <row r="56">
@@ -2323,31 +2323,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-94942.1752528986</v>
+        <v>-33635.02652497496</v>
       </c>
       <c r="C56" t="n">
-        <v>0.002767174465894103</v>
+        <v>0.006855320165378554</v>
       </c>
       <c r="D56" t="n">
-        <v>0.759163084329495</v>
+        <v>1.815293521428274</v>
       </c>
       <c r="E56" t="n">
-        <v>2598.602979940271</v>
+        <v>2570.163640178743</v>
       </c>
       <c r="F56" t="n">
-        <v>2965.266227281439</v>
+        <v>3066.370074057098</v>
       </c>
       <c r="G56" t="n">
-        <v>1616.892797443225</v>
+        <v>1695.763993021172</v>
       </c>
       <c r="H56" t="n">
-        <v>9014.63952885546</v>
+        <v>9001.782701055814</v>
       </c>
       <c r="I56" t="n">
-        <v>100.3653556690185</v>
+        <v>185.0206844026052</v>
       </c>
       <c r="J56" t="n">
-        <v>661.5155964088278</v>
+        <v>629.2521838668918</v>
       </c>
     </row>
     <row r="57">
@@ -2357,31 +2357,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-496995.6487207855</v>
+        <v>-269629.4353374057</v>
       </c>
       <c r="C57" t="n">
-        <v>0.01908778665341809</v>
+        <v>0.009895192383383581</v>
       </c>
       <c r="D57" t="n">
-        <v>3.007661231011904</v>
+        <v>1.141129443350908</v>
       </c>
       <c r="E57" t="n">
-        <v>2463.754778569552</v>
+        <v>2460.115459841503</v>
       </c>
       <c r="F57" t="n">
-        <v>3080.253984273574</v>
+        <v>2934.924794601593</v>
       </c>
       <c r="G57" t="n">
-        <v>1264.114335090788</v>
+        <v>1392.987977951261</v>
       </c>
       <c r="H57" t="n">
-        <v>8303.460873853281</v>
+        <v>8998.927226770653</v>
       </c>
       <c r="I57" t="n">
-        <v>115.2740576032216</v>
+        <v>102.0694373675874</v>
       </c>
       <c r="J57" t="n">
-        <v>661.1572451880561</v>
+        <v>613.125385072711</v>
       </c>
     </row>
     <row r="58">
@@ -2391,31 +2391,31 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-629335.5324579682</v>
+        <v>-796701.311373713</v>
       </c>
       <c r="C58" t="n">
-        <v>0.03926118670199145</v>
+        <v>0.0709484482174606</v>
       </c>
       <c r="D58" t="n">
-        <v>6.778097627812352</v>
+        <v>8.437148860989929</v>
       </c>
       <c r="E58" t="n">
-        <v>2599.844893648</v>
+        <v>2603.354389833386</v>
       </c>
       <c r="F58" t="n">
-        <v>3082.039630905748</v>
+        <v>3040.371712361824</v>
       </c>
       <c r="G58" t="n">
-        <v>1264.859791548107</v>
+        <v>1264.067629715317</v>
       </c>
       <c r="H58" t="n">
-        <v>7588.877138875784</v>
+        <v>6701.52896668283</v>
       </c>
       <c r="I58" t="n">
-        <v>109.0005973363496</v>
+        <v>131.1982237717899</v>
       </c>
       <c r="J58" t="n">
-        <v>663.3652199646453</v>
+        <v>651.1548909956525</v>
       </c>
     </row>
     <row r="59">
@@ -2425,31 +2425,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-77561.9372847015</v>
+        <v>-867297.4348017238</v>
       </c>
       <c r="C59" t="n">
-        <v>0.002562316765731773</v>
+        <v>0.08560823458852093</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>9.699976194940174</v>
       </c>
       <c r="E59" t="n">
-        <v>2454.835587589957</v>
+        <v>2601.094599487658</v>
       </c>
       <c r="F59" t="n">
-        <v>3033.181319913271</v>
+        <v>3084.163861652127</v>
       </c>
       <c r="G59" t="n">
-        <v>1642.904573753019</v>
+        <v>1264.812017907528</v>
       </c>
       <c r="H59" t="n">
-        <v>9009.05629545511</v>
+        <v>6320.257227438204</v>
       </c>
       <c r="I59" t="n">
-        <v>106.8125081751433</v>
+        <v>124.6029400260108</v>
       </c>
       <c r="J59" t="n">
-        <v>662.5434408199003</v>
+        <v>675.4576826249807</v>
       </c>
     </row>
     <row r="60">
@@ -2459,31 +2459,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-806302.2333935234</v>
+        <v>-912159.7719019316</v>
       </c>
       <c r="C60" t="n">
-        <v>0.06954158104429384</v>
+        <v>0.09502115392514188</v>
       </c>
       <c r="D60" t="n">
-        <v>8.998426318622677</v>
+        <v>8.671092458329188</v>
       </c>
       <c r="E60" t="n">
-        <v>2600.551950513532</v>
+        <v>2481.874170576646</v>
       </c>
       <c r="F60" t="n">
-        <v>3081.001821387835</v>
+        <v>3086.601293732182</v>
       </c>
       <c r="G60" t="n">
-        <v>1264.130408332057</v>
+        <v>1268.710431644871</v>
       </c>
       <c r="H60" t="n">
-        <v>6658.33894078152</v>
+        <v>6085.218309175002</v>
       </c>
       <c r="I60" t="n">
-        <v>101.3807522030913</v>
+        <v>104.7598465022565</v>
       </c>
       <c r="J60" t="n">
-        <v>660.5315035456969</v>
+        <v>628.4137421757412</v>
       </c>
     </row>
     <row r="61">
@@ -2493,31 +2493,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-809608.7941204831</v>
+        <v>-635387.8509600842</v>
       </c>
       <c r="C61" t="n">
-        <v>0.07017596790947132</v>
+        <v>0.04163331372573564</v>
       </c>
       <c r="D61" t="n">
-        <v>6.451282933290803</v>
+        <v>4.731092626448518</v>
       </c>
       <c r="E61" t="n">
-        <v>2588.58888960435</v>
+        <v>2598.555295897143</v>
       </c>
       <c r="F61" t="n">
-        <v>2920.523450358954</v>
+        <v>2954.769070134144</v>
       </c>
       <c r="G61" t="n">
-        <v>1264.003536616868</v>
+        <v>1264.011384902439</v>
       </c>
       <c r="H61" t="n">
-        <v>6657.392565841939</v>
+        <v>7564.737052256321</v>
       </c>
       <c r="I61" t="n">
-        <v>103.9410986186889</v>
+        <v>103.3513114922797</v>
       </c>
       <c r="J61" t="n">
-        <v>659.1379824012004</v>
+        <v>650.5788255222772</v>
       </c>
     </row>
     <row r="62">
@@ -2527,31 +2527,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-936437.3516816064</v>
+        <v>-916353.920046886</v>
       </c>
       <c r="C62" t="n">
-        <v>0.09624041695167089</v>
+        <v>0.09556186954942961</v>
       </c>
       <c r="D62" t="n">
-        <v>8.10143420029441</v>
+        <v>10.3205244866214</v>
       </c>
       <c r="E62" t="n">
-        <v>2588.58888960435</v>
+        <v>2602.427233530964</v>
       </c>
       <c r="F62" t="n">
-        <v>2920.523450358954</v>
+        <v>3092.872811091714</v>
       </c>
       <c r="G62" t="n">
-        <v>1264.046558389344</v>
+        <v>1264.086105019015</v>
       </c>
       <c r="H62" t="n">
-        <v>5987.822779869754</v>
+        <v>6064.690953953123</v>
       </c>
       <c r="I62" t="n">
-        <v>100.551663522206</v>
+        <v>104.1587915803968</v>
       </c>
       <c r="J62" t="n">
-        <v>659.1360767326823</v>
+        <v>680.1629107523318</v>
       </c>
     </row>
     <row r="63">
@@ -2561,31 +2561,31 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-866856.8777424046</v>
+        <v>11386.98610646883</v>
       </c>
       <c r="C63" t="n">
-        <v>0.08188833316708598</v>
+        <v>0.006230788608373177</v>
       </c>
       <c r="D63" t="n">
-        <v>7.026922063585928</v>
+        <v>0.02026550420107798</v>
       </c>
       <c r="E63" t="n">
-        <v>2453.346707794302</v>
+        <v>2460.563482705139</v>
       </c>
       <c r="F63" t="n">
-        <v>3039.411961869188</v>
+        <v>2919.996660970261</v>
       </c>
       <c r="G63" t="n">
-        <v>1264.052370397947</v>
+        <v>1764.987584126856</v>
       </c>
       <c r="H63" t="n">
-        <v>6356.300786248406</v>
+        <v>8995.13298396661</v>
       </c>
       <c r="I63" t="n">
-        <v>106.8368176153094</v>
+        <v>103.038811386316</v>
       </c>
       <c r="J63" t="n">
-        <v>660.7077499724096</v>
+        <v>623.5050332232005</v>
       </c>
     </row>
     <row r="64">
@@ -2595,31 +2595,31 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-123377.0691628624</v>
+        <v>-935726.6331554381</v>
       </c>
       <c r="C64" t="n">
-        <v>0.003157772442939293</v>
+        <v>0.09933280211586708</v>
       </c>
       <c r="D64" t="n">
-        <v>2.220446049250313e-14</v>
+        <v>8.935666604941384</v>
       </c>
       <c r="E64" t="n">
-        <v>2459.869557600378</v>
+        <v>2485.508302277541</v>
       </c>
       <c r="F64" t="n">
-        <v>2927.287240476256</v>
+        <v>3088.28804109938</v>
       </c>
       <c r="G64" t="n">
-        <v>1585.667000919369</v>
+        <v>1264.325771181391</v>
       </c>
       <c r="H64" t="n">
-        <v>9006.346487072775</v>
+        <v>5979.200359509959</v>
       </c>
       <c r="I64" t="n">
-        <v>100.8756368296399</v>
+        <v>103.747152711068</v>
       </c>
       <c r="J64" t="n">
-        <v>659.3477470071257</v>
+        <v>614.5194226382388</v>
       </c>
     </row>
     <row r="65">
@@ -2629,31 +2629,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-663848.1830777838</v>
+        <v>238358.5083608008</v>
       </c>
       <c r="C65" t="n">
-        <v>0.04456742881264818</v>
+        <v>0.003251174930552487</v>
       </c>
       <c r="D65" t="n">
-        <v>4.764615925737193</v>
+        <v>1.74810426084866</v>
       </c>
       <c r="E65" t="n">
-        <v>2465.296710431283</v>
+        <v>2575.043864987977</v>
       </c>
       <c r="F65" t="n">
-        <v>3064.41768778086</v>
+        <v>2924.210613414921</v>
       </c>
       <c r="G65" t="n">
-        <v>1264.085941058783</v>
+        <v>2060.831212175728</v>
       </c>
       <c r="H65" t="n">
-        <v>7424.876481255605</v>
+        <v>8998.891177059031</v>
       </c>
       <c r="I65" t="n">
-        <v>102.5838768873162</v>
+        <v>101.5397157402841</v>
       </c>
       <c r="J65" t="n">
-        <v>662.9980861590938</v>
+        <v>625.7281759790161</v>
       </c>
     </row>
     <row r="66">
@@ -2663,31 +2663,31 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-231550.5941292518</v>
+        <v>225408.6513371733</v>
       </c>
       <c r="C66" t="n">
-        <v>0.004646864615659431</v>
+        <v>0.003696155952025057</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9253108960406098</v>
+        <v>0.01645062117190399</v>
       </c>
       <c r="E66" t="n">
-        <v>2592.809106152296</v>
+        <v>2566.81276109392</v>
       </c>
       <c r="F66" t="n">
-        <v>2954.655885965859</v>
+        <v>2919.996660970261</v>
       </c>
       <c r="G66" t="n">
-        <v>1440.058159423532</v>
+        <v>2053.75118213197</v>
       </c>
       <c r="H66" t="n">
-        <v>9002.117705924846</v>
+        <v>8960.080638111573</v>
       </c>
       <c r="I66" t="n">
-        <v>102.5855418979966</v>
+        <v>102.9619154867742</v>
       </c>
       <c r="J66" t="n">
-        <v>659.6681439763122</v>
+        <v>623.5050332232005</v>
       </c>
     </row>
     <row r="67">
@@ -2697,31 +2697,31 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-856642.7598780422</v>
+        <v>-734175.7895498695</v>
       </c>
       <c r="C67" t="n">
-        <v>0.07981108003192149</v>
+        <v>0.05792493057940541</v>
       </c>
       <c r="D67" t="n">
-        <v>9.740004968318372</v>
+        <v>5.24088178396489</v>
       </c>
       <c r="E67" t="n">
-        <v>2600.508166978718</v>
+        <v>2596.396704083135</v>
       </c>
       <c r="F67" t="n">
-        <v>3094.654963701435</v>
+        <v>2917.726254026204</v>
       </c>
       <c r="G67" t="n">
-        <v>1264.085261675936</v>
+        <v>1264.487837588131</v>
       </c>
       <c r="H67" t="n">
-        <v>6391.424855588903</v>
+        <v>7048.255936233536</v>
       </c>
       <c r="I67" t="n">
-        <v>101.3807522030913</v>
+        <v>100.4836468749297</v>
       </c>
       <c r="J67" t="n">
-        <v>660.5315035456969</v>
+        <v>616.9406880964326</v>
       </c>
     </row>
     <row r="68">
@@ -2731,31 +2731,31 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-344523.909660914</v>
+        <v>-246304.2497974662</v>
       </c>
       <c r="C68" t="n">
-        <v>0.006099325807678743</v>
+        <v>0.009614445445426167</v>
       </c>
       <c r="D68" t="n">
-        <v>2.811011363758897</v>
+        <v>0.807340524408684</v>
       </c>
       <c r="E68" t="n">
-        <v>2592.542000976259</v>
+        <v>2596.64366985297</v>
       </c>
       <c r="F68" t="n">
-        <v>3056.981762589917</v>
+        <v>2928.166046352153</v>
       </c>
       <c r="G68" t="n">
-        <v>1281.884047603591</v>
+        <v>1420.082427798407</v>
       </c>
       <c r="H68" t="n">
-        <v>9014.63952885546</v>
+        <v>9000.086184010384</v>
       </c>
       <c r="I68" t="n">
-        <v>100.3653556690185</v>
+        <v>112.3371641120157</v>
       </c>
       <c r="J68" t="n">
-        <v>812.9158778289321</v>
+        <v>615.6559832743944</v>
       </c>
     </row>
     <row r="69">
@@ -2765,31 +2765,31 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-467591.9654210121</v>
+        <v>-330866.1027658852</v>
       </c>
       <c r="C69" t="n">
-        <v>0.01469903594906556</v>
+        <v>0.01115813773383342</v>
       </c>
       <c r="D69" t="n">
-        <v>2.175229468900608</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2601.827351688885</v>
+        <v>2483.17395341116</v>
       </c>
       <c r="F69" t="n">
-        <v>2918.982555021298</v>
+        <v>2934.40341235645</v>
       </c>
       <c r="G69" t="n">
-        <v>1265.74033773906</v>
+        <v>1323.743064688217</v>
       </c>
       <c r="H69" t="n">
-        <v>8455.655950615186</v>
+        <v>8939.4456194102</v>
       </c>
       <c r="I69" t="n">
-        <v>100.8154160651619</v>
+        <v>121.3351864416263</v>
       </c>
       <c r="J69" t="n">
-        <v>659.0989164968357</v>
+        <v>710.6646638565589</v>
       </c>
     </row>
     <row r="70">
@@ -2799,31 +2799,31 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-949442.7448543659</v>
+        <v>-712122.9451421476</v>
       </c>
       <c r="C70" t="n">
-        <v>0.09918425220994832</v>
+        <v>0.05405086148531174</v>
       </c>
       <c r="D70" t="n">
-        <v>10.60642322106617</v>
+        <v>5.845870603648462</v>
       </c>
       <c r="E70" t="n">
-        <v>2597.986743311546</v>
+        <v>2485.043757665635</v>
       </c>
       <c r="F70" t="n">
-        <v>3093.679300866719</v>
+        <v>3053.94752776755</v>
       </c>
       <c r="G70" t="n">
-        <v>1265.787445944027</v>
+        <v>1264.81863045824</v>
       </c>
       <c r="H70" t="n">
-        <v>5895.167955092041</v>
+        <v>7146.369597489059</v>
       </c>
       <c r="I70" t="n">
-        <v>100.1869665380485</v>
+        <v>106.2083480561796</v>
       </c>
       <c r="J70" t="n">
-        <v>659.0455415467682</v>
+        <v>771.1536621308638</v>
       </c>
     </row>
     <row r="71">
@@ -2833,31 +2833,31 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-908349.4409658657</v>
+        <v>-186180.3971804422</v>
       </c>
       <c r="C71" t="n">
-        <v>0.09161677691758351</v>
+        <v>0.008780193747342919</v>
       </c>
       <c r="D71" t="n">
-        <v>9.558433806557986</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>2586.965064165037</v>
+        <v>2474.23417692976</v>
       </c>
       <c r="F71" t="n">
-        <v>3049.284198282142</v>
+        <v>2916.049856578193</v>
       </c>
       <c r="G71" t="n">
-        <v>1274.019526363944</v>
+        <v>1501.86995602723</v>
       </c>
       <c r="H71" t="n">
-        <v>6084.268249193617</v>
+        <v>9002.215440836961</v>
       </c>
       <c r="I71" t="n">
-        <v>100.4770827710329</v>
+        <v>121.318981369025</v>
       </c>
       <c r="J71" t="n">
-        <v>660.4890938521805</v>
+        <v>617.5396574275018</v>
       </c>
     </row>
     <row r="72">
@@ -2867,31 +2867,31 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-44860.19063623622</v>
+        <v>-771182.1322925021</v>
       </c>
       <c r="C72" t="n">
-        <v>0.002256711789137689</v>
+        <v>0.0657044875909238</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1974798515468668</v>
+        <v>7.031073606259353</v>
       </c>
       <c r="E72" t="n">
-        <v>2578.802058330032</v>
+        <v>2576.483655164186</v>
       </c>
       <c r="F72" t="n">
-        <v>2965.266227281439</v>
+        <v>2992.834285560097</v>
       </c>
       <c r="G72" t="n">
-        <v>1687.608451784083</v>
+        <v>1264.008343305033</v>
       </c>
       <c r="H72" t="n">
-        <v>8994.645078260433</v>
+        <v>6843.030516852697</v>
       </c>
       <c r="I72" t="n">
-        <v>100.3193901505986</v>
+        <v>121.5654158308767</v>
       </c>
       <c r="J72" t="n">
-        <v>698.8831492553159</v>
+        <v>666.3185976690111</v>
       </c>
     </row>
     <row r="73">
@@ -2901,31 +2901,31 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-368383.124380264</v>
+        <v>-822404.4713139753</v>
       </c>
       <c r="C73" t="n">
-        <v>0.006520421848559885</v>
+        <v>0.07605418495958771</v>
       </c>
       <c r="D73" t="n">
-        <v>0.557383512360321</v>
+        <v>7.594358457839522</v>
       </c>
       <c r="E73" t="n">
-        <v>2565.888489250847</v>
+        <v>2602.795116373055</v>
       </c>
       <c r="F73" t="n">
-        <v>2915.506791394191</v>
+        <v>2961.429602181307</v>
       </c>
       <c r="G73" t="n">
-        <v>1264.008296423387</v>
+        <v>1264.799530989197</v>
       </c>
       <c r="H73" t="n">
-        <v>8989.4224993512</v>
+        <v>6576.543293212429</v>
       </c>
       <c r="I73" t="n">
-        <v>109.0460262382915</v>
+        <v>101.8599644414961</v>
       </c>
       <c r="J73" t="n">
-        <v>659.1928462021078</v>
+        <v>614.2615006776001</v>
       </c>
     </row>
     <row r="74">
@@ -2935,31 +2935,31 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-858450.1843636222</v>
+        <v>-857508.1689959625</v>
       </c>
       <c r="C74" t="n">
-        <v>0.08056205137428027</v>
+        <v>0.08359700641037808</v>
       </c>
       <c r="D74" t="n">
-        <v>7.197973920798207</v>
+        <v>9.4840452099054</v>
       </c>
       <c r="E74" t="n">
-        <v>2587.177003726374</v>
+        <v>2594.849838986541</v>
       </c>
       <c r="F74" t="n">
-        <v>2927.37225817771</v>
+        <v>3081.33468029602</v>
       </c>
       <c r="G74" t="n">
-        <v>1265.488048829049</v>
+        <v>1264.525923812901</v>
       </c>
       <c r="H74" t="n">
-        <v>6386.647720862426</v>
+        <v>6373.069120951248</v>
       </c>
       <c r="I74" t="n">
-        <v>102.8652675869633</v>
+        <v>123.1076670318766</v>
       </c>
       <c r="J74" t="n">
-        <v>728.7482458530574</v>
+        <v>686.4787793719721</v>
       </c>
     </row>
     <row r="75">
@@ -2969,31 +2969,31 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>61800.74334586365</v>
+        <v>-815190.6585766622</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0006813639375464674</v>
+        <v>0.0745394825238752</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>6.34062157903722</v>
       </c>
       <c r="E75" t="n">
-        <v>2464.92091033508</v>
+        <v>2575.161764549583</v>
       </c>
       <c r="F75" t="n">
-        <v>2956.961351106597</v>
+        <v>2913.023659952513</v>
       </c>
       <c r="G75" t="n">
-        <v>1826.706312602801</v>
+        <v>1264.482560576602</v>
       </c>
       <c r="H75" t="n">
-        <v>9014.526413932996</v>
+        <v>6622.587949699889</v>
       </c>
       <c r="I75" t="n">
-        <v>121.079390179241</v>
+        <v>107.2467204072428</v>
       </c>
       <c r="J75" t="n">
-        <v>662.7400051946022</v>
+        <v>613.8290662963597</v>
       </c>
     </row>
     <row r="76">
@@ -3003,31 +3003,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-476034.3611569479</v>
+        <v>-846409.9445829163</v>
       </c>
       <c r="C76" t="n">
-        <v>0.01603361370749481</v>
+        <v>0.08095919738271661</v>
       </c>
       <c r="D76" t="n">
-        <v>2.508738000015343</v>
+        <v>4.431171154959468</v>
       </c>
       <c r="E76" t="n">
-        <v>2467.618373881062</v>
+        <v>2459.062197732333</v>
       </c>
       <c r="F76" t="n">
-        <v>3063.707329356251</v>
+        <v>2914.386163950966</v>
       </c>
       <c r="G76" t="n">
-        <v>1266.001081053548</v>
+        <v>1264.825898695659</v>
       </c>
       <c r="H76" t="n">
-        <v>8408.524130910915</v>
+        <v>6467.645130988124</v>
       </c>
       <c r="I76" t="n">
-        <v>106.8126418594116</v>
+        <v>100.5727213116294</v>
       </c>
       <c r="J76" t="n">
-        <v>661.8014720429138</v>
+        <v>617.254208611796</v>
       </c>
     </row>
     <row r="77">
@@ -3037,31 +3037,31 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>117524.1065252065</v>
+        <v>-555234.6806468861</v>
       </c>
       <c r="C77" t="n">
-        <v>7.978441057063015e-05</v>
+        <v>0.02937453436334575</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8486525421912861</v>
+        <v>4.129785553304077</v>
       </c>
       <c r="E77" t="n">
-        <v>2453.448656999844</v>
+        <v>2472.377016471204</v>
       </c>
       <c r="F77" t="n">
-        <v>2920.550835159474</v>
+        <v>3092.147992520021</v>
       </c>
       <c r="G77" t="n">
-        <v>1906.599016992352</v>
+        <v>1264.770379876804</v>
       </c>
       <c r="H77" t="n">
-        <v>8994.515139572704</v>
+        <v>7986.51340867676</v>
       </c>
       <c r="I77" t="n">
-        <v>106.8368176153094</v>
+        <v>105.6990204449248</v>
       </c>
       <c r="J77" t="n">
-        <v>668.5765969496706</v>
+        <v>623.2509066923809</v>
       </c>
     </row>
     <row r="78">
@@ -3071,31 +3071,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-270605.3695502793</v>
+        <v>286828.0114439689</v>
       </c>
       <c r="C78" t="n">
-        <v>0.00541208339878625</v>
+        <v>0.00275010184826087</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7690767279532884</v>
+        <v>0.4769317391812189</v>
       </c>
       <c r="E78" t="n">
-        <v>2582.423014608789</v>
+        <v>2455.211472503432</v>
       </c>
       <c r="F78" t="n">
-        <v>2942.653884253504</v>
+        <v>3009.01421205537</v>
       </c>
       <c r="G78" t="n">
-        <v>1397.999417188156</v>
+        <v>2130.088110500229</v>
       </c>
       <c r="H78" t="n">
-        <v>8966.164061952075</v>
+        <v>8979.414187473878</v>
       </c>
       <c r="I78" t="n">
-        <v>103.2435112548875</v>
+        <v>124.4861692511967</v>
       </c>
       <c r="J78" t="n">
-        <v>659.7596295556585</v>
+        <v>622.9098282046252</v>
       </c>
     </row>
     <row r="79">
@@ -3105,31 +3105,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-617846.7202967196</v>
+        <v>-682841.6115302215</v>
       </c>
       <c r="C79" t="n">
-        <v>0.03811049999083145</v>
+        <v>0.04970916112429233</v>
       </c>
       <c r="D79" t="n">
-        <v>4.501496159106377</v>
+        <v>5.678598350823827</v>
       </c>
       <c r="E79" t="n">
-        <v>2465.710948587578</v>
+        <v>2584.48590354059</v>
       </c>
       <c r="F79" t="n">
-        <v>3075.475490576278</v>
+        <v>2968.592478644375</v>
       </c>
       <c r="G79" t="n">
-        <v>1269.544011161801</v>
+        <v>1271.639983788881</v>
       </c>
       <c r="H79" t="n">
-        <v>7640.970392222604</v>
+        <v>7278.009810162881</v>
       </c>
       <c r="I79" t="n">
-        <v>146.0636990911815</v>
+        <v>103.1657479821287</v>
       </c>
       <c r="J79" t="n">
-        <v>660.4206617541282</v>
+        <v>711.6919120822992</v>
       </c>
     </row>
     <row r="80">
@@ -3139,31 +3139,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-615512.7144391742</v>
+        <v>-662028.8100112905</v>
       </c>
       <c r="C80" t="n">
-        <v>0.03765435869612534</v>
+        <v>0.04590993080636842</v>
       </c>
       <c r="D80" t="n">
-        <v>6.157117635713972</v>
+        <v>5.696574735792392</v>
       </c>
       <c r="E80" t="n">
-        <v>2594.691240047617</v>
+        <v>2483.81490323984</v>
       </c>
       <c r="F80" t="n">
-        <v>3075.475490576278</v>
+        <v>3088.71447005062</v>
       </c>
       <c r="G80" t="n">
-        <v>1269.544011161801</v>
+        <v>1264.013066609295</v>
       </c>
       <c r="H80" t="n">
-        <v>7640.970392222604</v>
+        <v>7415.163458975868</v>
       </c>
       <c r="I80" t="n">
-        <v>146.0636990911815</v>
+        <v>133.9015716746328</v>
       </c>
       <c r="J80" t="n">
-        <v>660.4206617541282</v>
+        <v>698.0623867890347</v>
       </c>
     </row>
     <row r="81">
@@ -3173,31 +3173,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-401379.2868124745</v>
+        <v>-468809.245403673</v>
       </c>
       <c r="C81" t="n">
-        <v>0.00846678077856588</v>
+        <v>0.0176429496642753</v>
       </c>
       <c r="D81" t="n">
-        <v>3.970909135570944</v>
+        <v>1.249524872803032</v>
       </c>
       <c r="E81" t="n">
-        <v>2600.772015345846</v>
+        <v>2466.303816719954</v>
       </c>
       <c r="F81" t="n">
-        <v>3087.067719644182</v>
+        <v>2913.887370500718</v>
       </c>
       <c r="G81" t="n">
-        <v>1266.700150306489</v>
+        <v>1264.482560576602</v>
       </c>
       <c r="H81" t="n">
-        <v>8784.911752603562</v>
+        <v>8461.960008892813</v>
       </c>
       <c r="I81" t="n">
-        <v>101.2185144787549</v>
+        <v>107.2467204072428</v>
       </c>
       <c r="J81" t="n">
-        <v>668.9263898386641</v>
+        <v>614.108481307537</v>
       </c>
     </row>
     <row r="82">
@@ -3207,31 +3207,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-797409.9012231627</v>
+        <v>-736200.7192661692</v>
       </c>
       <c r="C82" t="n">
-        <v>0.06771631098635936</v>
+        <v>0.05862531875123872</v>
       </c>
       <c r="D82" t="n">
-        <v>4.028979280413115</v>
+        <v>8.111428413324139</v>
       </c>
       <c r="E82" t="n">
-        <v>2461.621205037419</v>
+        <v>2599.14493115406</v>
       </c>
       <c r="F82" t="n">
-        <v>2915.825341902252</v>
+        <v>3067.059281563915</v>
       </c>
       <c r="G82" t="n">
-        <v>1264.196234202306</v>
+        <v>1264.4686539866</v>
       </c>
       <c r="H82" t="n">
-        <v>6732.981036519729</v>
+        <v>7016.606030265667</v>
       </c>
       <c r="I82" t="n">
-        <v>107.7452953035793</v>
+        <v>103.9337981365689</v>
       </c>
       <c r="J82" t="n">
-        <v>661.974919214913</v>
+        <v>686.6253682408791</v>
       </c>
     </row>
     <row r="83">
@@ -3241,31 +3241,31 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-675476.6830257881</v>
+        <v>-715840.5477073663</v>
       </c>
       <c r="C83" t="n">
-        <v>0.04637688953175689</v>
+        <v>0.05523280802882549</v>
       </c>
       <c r="D83" t="n">
-        <v>5.969272164409267</v>
+        <v>4.541731933487114</v>
       </c>
       <c r="E83" t="n">
-        <v>2565.56609987618</v>
+        <v>2486.94794261014</v>
       </c>
       <c r="F83" t="n">
-        <v>3023.607270956733</v>
+        <v>2983.625572884874</v>
       </c>
       <c r="G83" t="n">
-        <v>1264.002433134844</v>
+        <v>1264.81863045824</v>
       </c>
       <c r="H83" t="n">
-        <v>7355.03255830239</v>
+        <v>7121.82721484692</v>
       </c>
       <c r="I83" t="n">
-        <v>137.672142648437</v>
+        <v>106.2083480561796</v>
       </c>
       <c r="J83" t="n">
-        <v>659.2280585501709</v>
+        <v>892.1490729821567</v>
       </c>
     </row>
     <row r="84">
@@ -3275,31 +3275,31 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-412248.9379104464</v>
+        <v>-860334.9228380769</v>
       </c>
       <c r="C84" t="n">
-        <v>0.008889597195060108</v>
+        <v>0.0841099507584131</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>8.027704605706443</v>
       </c>
       <c r="E84" t="n">
-        <v>2467.520451570045</v>
+        <v>2485.035588541747</v>
       </c>
       <c r="F84" t="n">
-        <v>2962.391915931721</v>
+        <v>3077.607615837996</v>
       </c>
       <c r="G84" t="n">
-        <v>1269.195173205379</v>
+        <v>1264.14831226316</v>
       </c>
       <c r="H84" t="n">
-        <v>8738.515612092535</v>
+        <v>6370.584083740697</v>
       </c>
       <c r="I84" t="n">
-        <v>111.5181166313781</v>
+        <v>123.1076670318766</v>
       </c>
       <c r="J84" t="n">
-        <v>694.6803474936657</v>
+        <v>685.5139740837914</v>
       </c>
     </row>
     <row r="85">
@@ -3309,31 +3309,31 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-878807.6308763949</v>
+        <v>-810558.9916475099</v>
       </c>
       <c r="C85" t="n">
-        <v>0.08454309858216377</v>
+        <v>0.07358369164429113</v>
       </c>
       <c r="D85" t="n">
-        <v>9.932087147846968</v>
+        <v>4.063220466179363</v>
       </c>
       <c r="E85" t="n">
-        <v>2598.621610962663</v>
+        <v>2459.062197732333</v>
       </c>
       <c r="F85" t="n">
-        <v>3094.805921840994</v>
+        <v>2914.386163950966</v>
       </c>
       <c r="G85" t="n">
-        <v>1264.140429066491</v>
+        <v>1264.825898695659</v>
       </c>
       <c r="H85" t="n">
-        <v>6269.851724417769</v>
+        <v>6657.244144606443</v>
       </c>
       <c r="I85" t="n">
-        <v>105.1418831841844</v>
+        <v>100.5727213116294</v>
       </c>
       <c r="J85" t="n">
-        <v>704.6424646534978</v>
+        <v>614.1786630071493</v>
       </c>
     </row>
     <row r="86">
@@ -3343,31 +3343,31 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>46139.98295876617</v>
+        <v>-346222.3762494838</v>
       </c>
       <c r="C86" t="n">
-        <v>0.001037861117323273</v>
+        <v>0.01101982230818791</v>
       </c>
       <c r="D86" t="n">
-        <v>2.220446049250313e-14</v>
+        <v>3.063078341730463</v>
       </c>
       <c r="E86" t="n">
-        <v>2464.92091033508</v>
+        <v>2602.889772426048</v>
       </c>
       <c r="F86" t="n">
-        <v>2956.961351106597</v>
+        <v>3050.814483649123</v>
       </c>
       <c r="G86" t="n">
-        <v>1811.961527558896</v>
+        <v>1283.728616673372</v>
       </c>
       <c r="H86" t="n">
-        <v>8992.777108101815</v>
+        <v>8995.030060303357</v>
       </c>
       <c r="I86" t="n">
-        <v>100.4773588888113</v>
+        <v>160.0800866083894</v>
       </c>
       <c r="J86" t="n">
-        <v>662.7400051946022</v>
+        <v>682.5641232181059</v>
       </c>
     </row>
     <row r="87">
@@ -3377,31 +3377,31 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-951076.4295159467</v>
+        <v>449362.2859096555</v>
       </c>
       <c r="C87" t="n">
-        <v>0.09939047208005294</v>
+        <v>0.000419963343872484</v>
       </c>
       <c r="D87" t="n">
-        <v>10.7466714328536</v>
+        <v>0.07180953099594767</v>
       </c>
       <c r="E87" t="n">
-        <v>2588.434196836915</v>
+        <v>2553.593582605816</v>
       </c>
       <c r="F87" t="n">
-        <v>3084.616197836447</v>
+        <v>3069.766842428724</v>
       </c>
       <c r="G87" t="n">
-        <v>1264.200380799297</v>
+        <v>2333.776199738304</v>
       </c>
       <c r="H87" t="n">
-        <v>5893.211826137929</v>
+        <v>9010.878589378244</v>
       </c>
       <c r="I87" t="n">
-        <v>115.0354970072811</v>
+        <v>102.4600533351929</v>
       </c>
       <c r="J87" t="n">
-        <v>659.2330498123778</v>
+        <v>613.0907430877305</v>
       </c>
     </row>
     <row r="88">
@@ -3411,31 +3411,31 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-455996.1853328282</v>
+        <v>-656266.6546640545</v>
       </c>
       <c r="C88" t="n">
-        <v>0.01335904961710514</v>
+        <v>0.04506635007689501</v>
       </c>
       <c r="D88" t="n">
-        <v>2.753816015734067</v>
+        <v>5.206083900296599</v>
       </c>
       <c r="E88" t="n">
-        <v>2471.261318710392</v>
+        <v>2483.556664570399</v>
       </c>
       <c r="F88" t="n">
-        <v>3086.736438170248</v>
+        <v>3084.790550451763</v>
       </c>
       <c r="G88" t="n">
-        <v>1266.878740912615</v>
+        <v>1264.026094420852</v>
       </c>
       <c r="H88" t="n">
-        <v>8502.376628974163</v>
+        <v>7444.784299079018</v>
       </c>
       <c r="I88" t="n">
-        <v>100.9088110411733</v>
+        <v>160.4394040547739</v>
       </c>
       <c r="J88" t="n">
-        <v>731.6122091237421</v>
+        <v>683.1624895613285</v>
       </c>
     </row>
     <row r="89">
@@ -3445,31 +3445,31 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-670214.3169546034</v>
+        <v>319877.6954142018</v>
       </c>
       <c r="C89" t="n">
-        <v>0.04558059258093085</v>
+        <v>0.002310867550145103</v>
       </c>
       <c r="D89" t="n">
-        <v>5.951166447759992</v>
+        <v>0.4522235515940998</v>
       </c>
       <c r="E89" t="n">
-        <v>2569.728766966582</v>
+        <v>2455.211472503432</v>
       </c>
       <c r="F89" t="n">
-        <v>3023.607270956733</v>
+        <v>3009.01421205537</v>
       </c>
       <c r="G89" t="n">
-        <v>1264.002433134844</v>
+        <v>2174.236744527262</v>
       </c>
       <c r="H89" t="n">
-        <v>7382.035397775718</v>
+        <v>8979.414187473878</v>
       </c>
       <c r="I89" t="n">
-        <v>137.672142648437</v>
+        <v>102.7736402945339</v>
       </c>
       <c r="J89" t="n">
-        <v>663.379482370953</v>
+        <v>622.9098282046252</v>
       </c>
     </row>
     <row r="90">
@@ -3479,31 +3479,31 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-720820.5064174705</v>
+        <v>-894186.5927654565</v>
       </c>
       <c r="C90" t="n">
-        <v>0.05332310840729242</v>
+        <v>0.09074794860585833</v>
       </c>
       <c r="D90" t="n">
-        <v>4.677176227836888</v>
+        <v>8.391671450923122</v>
       </c>
       <c r="E90" t="n">
-        <v>2561.138218790255</v>
+        <v>2603.964291758673</v>
       </c>
       <c r="F90" t="n">
-        <v>2925.867997066648</v>
+        <v>2962.153789837323</v>
       </c>
       <c r="G90" t="n">
-        <v>1264.244458562835</v>
+        <v>1264.067629715317</v>
       </c>
       <c r="H90" t="n">
-        <v>7126.92142549605</v>
+        <v>6199.395462697594</v>
       </c>
       <c r="I90" t="n">
-        <v>109.0923060734245</v>
+        <v>102.3589194992582</v>
       </c>
       <c r="J90" t="n">
-        <v>659.01487299593</v>
+        <v>622.8429965717053</v>
       </c>
     </row>
     <row r="91">
@@ -3513,31 +3513,31 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-693078.8755399343</v>
+        <v>-441025.7932719388</v>
       </c>
       <c r="C91" t="n">
-        <v>0.04897280909320578</v>
+        <v>0.01499363329079234</v>
       </c>
       <c r="D91" t="n">
-        <v>6.449759511584019</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>2587.70342476054</v>
+        <v>2466.705267682119</v>
       </c>
       <c r="F91" t="n">
-        <v>3019.04948073994</v>
+        <v>2935.325037489032</v>
       </c>
       <c r="G91" t="n">
-        <v>1264.160644836903</v>
+        <v>1264.669114250497</v>
       </c>
       <c r="H91" t="n">
-        <v>7263.017771712869</v>
+        <v>8602.907330138414</v>
       </c>
       <c r="I91" t="n">
-        <v>100.2071836151251</v>
+        <v>115.3139802233383</v>
       </c>
       <c r="J91" t="n">
-        <v>662.6898739374051</v>
+        <v>637.7622080437903</v>
       </c>
     </row>
     <row r="92">
@@ -3547,31 +3547,31 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-865020.8160379454</v>
+        <v>-128997.8446612777</v>
       </c>
       <c r="C92" t="n">
-        <v>0.08151504009457271</v>
+        <v>0.008125717914654423</v>
       </c>
       <c r="D92" t="n">
-        <v>7.093756786916739</v>
+        <v>0.654034620209698</v>
       </c>
       <c r="E92" t="n">
-        <v>2459.310686402987</v>
+        <v>2456.350983385819</v>
       </c>
       <c r="F92" t="n">
-        <v>3039.411961869188</v>
+        <v>3079.289427193935</v>
       </c>
       <c r="G92" t="n">
-        <v>1264.052370397947</v>
+        <v>1576.560650882638</v>
       </c>
       <c r="H92" t="n">
-        <v>6365.356979615413</v>
+        <v>8993.032400910679</v>
       </c>
       <c r="I92" t="n">
-        <v>106.8368176153094</v>
+        <v>100.4976965409022</v>
       </c>
       <c r="J92" t="n">
-        <v>661.450150123788</v>
+        <v>626.5082419521648</v>
       </c>
     </row>
     <row r="93">
@@ -3581,31 +3581,31 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-761805.034713577</v>
+        <v>-364191.0400988925</v>
       </c>
       <c r="C93" t="n">
-        <v>0.06045807115348854</v>
+        <v>0.01144884761762217</v>
       </c>
       <c r="D93" t="n">
-        <v>7.708407420065644</v>
+        <v>2.0396993474181</v>
       </c>
       <c r="E93" t="n">
-        <v>2593.541915202128</v>
+        <v>2492.238052286471</v>
       </c>
       <c r="F93" t="n">
-        <v>3038.702660782436</v>
+        <v>3081.185066013964</v>
       </c>
       <c r="G93" t="n">
-        <v>1264.121080354627</v>
+        <v>1270.381788914234</v>
       </c>
       <c r="H93" t="n">
-        <v>6898.122110872126</v>
+        <v>8964.333490151888</v>
       </c>
       <c r="I93" t="n">
-        <v>100.3795649012709</v>
+        <v>111.8798048328169</v>
       </c>
       <c r="J93" t="n">
-        <v>659.8488557294044</v>
+        <v>699.1118153594023</v>
       </c>
     </row>
     <row r="94">
@@ -3615,31 +3615,31 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-363512.7801149669</v>
+        <v>-689201.5976637001</v>
       </c>
       <c r="C94" t="n">
-        <v>0.006392430064092593</v>
+        <v>0.04987691424979039</v>
       </c>
       <c r="D94" t="n">
-        <v>1.243081098430243</v>
+        <v>7.892048430968968</v>
       </c>
       <c r="E94" t="n">
-        <v>2465.986208987913</v>
+        <v>2603.929461280735</v>
       </c>
       <c r="F94" t="n">
-        <v>3075.30689113332</v>
+        <v>3086.350712007325</v>
       </c>
       <c r="G94" t="n">
-        <v>1264.01997172911</v>
+        <v>1264.067610285334</v>
       </c>
       <c r="H94" t="n">
-        <v>9002.676517899326</v>
+        <v>7263.689887942829</v>
       </c>
       <c r="I94" t="n">
-        <v>113.9922940762312</v>
+        <v>161.987241723893</v>
       </c>
       <c r="J94" t="n">
-        <v>729.6517922056039</v>
+        <v>631.9337204980144</v>
       </c>
     </row>
     <row r="95">
@@ -3649,31 +3649,31 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-269525.5052230428</v>
+        <v>448279.1066657961</v>
       </c>
       <c r="C95" t="n">
-        <v>0.005162391255769596</v>
+        <v>0.000475596023183798</v>
       </c>
       <c r="D95" t="n">
-        <v>0.7103288323934698</v>
+        <v>0.0861737276643515</v>
       </c>
       <c r="E95" t="n">
-        <v>2582.423014608789</v>
+        <v>2553.593582605816</v>
       </c>
       <c r="F95" t="n">
-        <v>2942.653884253504</v>
+        <v>3069.766842428724</v>
       </c>
       <c r="G95" t="n">
-        <v>1391.203434123868</v>
+        <v>2333.776199738304</v>
       </c>
       <c r="H95" t="n">
-        <v>8999.050248082422</v>
+        <v>9005.113855440879</v>
       </c>
       <c r="I95" t="n">
-        <v>103.2435112548875</v>
+        <v>102.930727736974</v>
       </c>
       <c r="J95" t="n">
-        <v>659.7596295556585</v>
+        <v>613.0907430877305</v>
       </c>
     </row>
     <row r="96">
@@ -3683,31 +3683,31 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-873253.8537991955</v>
+        <v>-828996.4332672479</v>
       </c>
       <c r="C96" t="n">
-        <v>0.08320546141290133</v>
+        <v>0.07736643946056689</v>
       </c>
       <c r="D96" t="n">
-        <v>7.925925522175103</v>
+        <v>9.076103239768795</v>
       </c>
       <c r="E96" t="n">
-        <v>2466.795535647158</v>
+        <v>2588.667429874109</v>
       </c>
       <c r="F96" t="n">
-        <v>3082.039630905748</v>
+        <v>3079.204112476186</v>
       </c>
       <c r="G96" t="n">
-        <v>1264.119816929523</v>
+        <v>1264.229571009777</v>
       </c>
       <c r="H96" t="n">
-        <v>6317.381296853728</v>
+        <v>6534.288978148626</v>
       </c>
       <c r="I96" t="n">
-        <v>102.5838768873162</v>
+        <v>101.7252739484677</v>
       </c>
       <c r="J96" t="n">
-        <v>660.8469414107459</v>
+        <v>615.2866081099837</v>
       </c>
     </row>
     <row r="97">
@@ -3717,31 +3717,31 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-33464.00269932812</v>
+        <v>-246520.2609234885</v>
       </c>
       <c r="C97" t="n">
-        <v>0.001960228209029035</v>
+        <v>0.009625703977446705</v>
       </c>
       <c r="D97" t="n">
-        <v>1.470710329034575</v>
+        <v>0.3814039434566929</v>
       </c>
       <c r="E97" t="n">
-        <v>2455.477772677678</v>
+        <v>2575.547301679528</v>
       </c>
       <c r="F97" t="n">
-        <v>3077.430474782773</v>
+        <v>2928.166046352153</v>
       </c>
       <c r="G97" t="n">
-        <v>1698.952381623787</v>
+        <v>1420.082427798407</v>
       </c>
       <c r="H97" t="n">
-        <v>9013.680148403828</v>
+        <v>8998.919559601365</v>
       </c>
       <c r="I97" t="n">
-        <v>108.5876175743381</v>
+        <v>133.858132571304</v>
       </c>
       <c r="J97" t="n">
-        <v>659.1618963012039</v>
+        <v>615.4995405830521</v>
       </c>
     </row>
     <row r="98">
@@ -3751,31 +3751,31 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>89724.02972645732</v>
+        <v>323760.1860246002</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0006052149695892453</v>
+        <v>0.002588504557920925</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-14</v>
       </c>
       <c r="E98" t="n">
-        <v>2476.854872009972</v>
+        <v>2485.201230633213</v>
       </c>
       <c r="F98" t="n">
-        <v>3046.085902808221</v>
+        <v>3054.253694699619</v>
       </c>
       <c r="G98" t="n">
-        <v>1870.965431029441</v>
+        <v>2183.180226428697</v>
       </c>
       <c r="H98" t="n">
-        <v>8976.791122694003</v>
+        <v>8941.424978474377</v>
       </c>
       <c r="I98" t="n">
-        <v>106.8125081751433</v>
+        <v>108.4489311740324</v>
       </c>
       <c r="J98" t="n">
-        <v>663.3094330265334</v>
+        <v>784.5512927538979</v>
       </c>
     </row>
     <row r="99">
@@ -3785,31 +3785,31 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-829504.22317247</v>
+        <v>391850.5865952969</v>
       </c>
       <c r="C99" t="n">
-        <v>0.07459153804903802</v>
+        <v>0.001207327276108661</v>
       </c>
       <c r="D99" t="n">
-        <v>7.427020123839267</v>
+        <v>0.4157464588038451</v>
       </c>
       <c r="E99" t="n">
-        <v>2596.372316550699</v>
+        <v>2460.115459841503</v>
       </c>
       <c r="F99" t="n">
-        <v>2958.178977485117</v>
+        <v>2934.924794601593</v>
       </c>
       <c r="G99" t="n">
-        <v>1265.68023740631</v>
+        <v>2266.228930997732</v>
       </c>
       <c r="H99" t="n">
-        <v>6537.187662684955</v>
+        <v>8998.927226770653</v>
       </c>
       <c r="I99" t="n">
-        <v>146.0814554212862</v>
+        <v>102.0694373675874</v>
       </c>
       <c r="J99" t="n">
-        <v>660.795675375451</v>
+        <v>613.125385072711</v>
       </c>
     </row>
     <row r="100">
@@ -3819,31 +3819,31 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-881333.2543162801</v>
+        <v>-614485.8724090806</v>
       </c>
       <c r="C100" t="n">
-        <v>0.08518921163204587</v>
+        <v>0.03846117088385053</v>
       </c>
       <c r="D100" t="n">
-        <v>9.915157154880205</v>
+        <v>3.756174305735271</v>
       </c>
       <c r="E100" t="n">
-        <v>2594.428652603251</v>
+        <v>2577.434076313101</v>
       </c>
       <c r="F100" t="n">
-        <v>3094.617343197567</v>
+        <v>2919.300375886819</v>
       </c>
       <c r="G100" t="n">
-        <v>1264.454207711197</v>
+        <v>1264.073836106526</v>
       </c>
       <c r="H100" t="n">
-        <v>6253.35174823322</v>
+        <v>7681.024295284121</v>
       </c>
       <c r="I100" t="n">
-        <v>173.436237842826</v>
+        <v>102.4632778348105</v>
       </c>
       <c r="J100" t="n">
-        <v>659.6488109254489</v>
+        <v>642.542619852613</v>
       </c>
     </row>
     <row r="101">
@@ -3853,31 +3853,31 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-47142.6304411781</v>
+        <v>2522.969503590371</v>
       </c>
       <c r="C101" t="n">
-        <v>0.002260222835349736</v>
+        <v>0.00637822850685175</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>0.8927392225125841</v>
       </c>
       <c r="E101" t="n">
-        <v>2466.420043197903</v>
+        <v>2457.365998714005</v>
       </c>
       <c r="F101" t="n">
-        <v>2965.266227281439</v>
+        <v>3051.339895193773</v>
       </c>
       <c r="G101" t="n">
-        <v>1687.255457252479</v>
+        <v>1750.267834845549</v>
       </c>
       <c r="H101" t="n">
-        <v>8994.645078260433</v>
+        <v>8995.030060303357</v>
       </c>
       <c r="I101" t="n">
-        <v>101.3472382690627</v>
+        <v>105.4818062652589</v>
       </c>
       <c r="J101" t="n">
-        <v>698.8831492553159</v>
+        <v>623.3831713145669</v>
       </c>
     </row>
     <row r="102">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>

--- a/output_data/Offgrid_Pareto_Results_3D.xlsx
+++ b/output_data/Offgrid_Pareto_Results_3D.xlsx
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-938792.6514294473</v>
+        <v>-930270.0972381597</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09999972166528819</v>
+        <v>0.09909354936675367</v>
       </c>
       <c r="D2" t="n">
-        <v>6.228117397732502</v>
+        <v>11.00143800709898</v>
       </c>
       <c r="E2" t="n">
-        <v>2459.062197732333</v>
+        <v>2603.718710660987</v>
       </c>
       <c r="F2" t="n">
-        <v>2915.377749321438</v>
+        <v>3069.655590266634</v>
       </c>
       <c r="G2" t="n">
-        <v>1264.826771146343</v>
+        <v>1264.170149323742</v>
       </c>
       <c r="H2" t="n">
-        <v>5979.200359509959</v>
+        <v>5918.660311139157</v>
       </c>
       <c r="I2" t="n">
-        <v>100.235887068947</v>
+        <v>111.0611338325044</v>
       </c>
       <c r="J2" t="n">
-        <v>623.1625478280099</v>
+        <v>633.4309514296116</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-939049.5738733923</v>
+        <v>387406.9454846894</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09997844271228384</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>6.41422223614454</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2463.029169958663</v>
+        <v>2465.11794040327</v>
       </c>
       <c r="F3" t="n">
-        <v>2923.300087151228</v>
+        <v>2948.459662807371</v>
       </c>
       <c r="G3" t="n">
-        <v>1264.325771181391</v>
+        <v>2252.616566557774</v>
       </c>
       <c r="H3" t="n">
-        <v>5979.200359509959</v>
+        <v>8947.186454434108</v>
       </c>
       <c r="I3" t="n">
-        <v>103.747152711068</v>
+        <v>111.6858057000059</v>
       </c>
       <c r="J3" t="n">
-        <v>614.5194226382388</v>
+        <v>635.7321553834892</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-924416.8613478653</v>
+        <v>-934729.1723853401</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09728898445753881</v>
+        <v>0.0999986401697255</v>
       </c>
       <c r="D4" t="n">
-        <v>10.88158912687289</v>
+        <v>8.765350398943871</v>
       </c>
       <c r="E4" t="n">
-        <v>2602.469632563345</v>
+        <v>2599.598807729493</v>
       </c>
       <c r="F4" t="n">
-        <v>3088.38787642479</v>
+        <v>2924.736905249363</v>
       </c>
       <c r="G4" t="n">
-        <v>1264.250852369031</v>
+        <v>1264.131997689392</v>
       </c>
       <c r="H4" t="n">
-        <v>6020.852304798743</v>
+        <v>5908.715858381142</v>
       </c>
       <c r="I4" t="n">
-        <v>163.6333460490836</v>
+        <v>116.185510361208</v>
       </c>
       <c r="J4" t="n">
-        <v>630.1753075936035</v>
+        <v>633.2225456455351</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>483988.3288623453</v>
+        <v>-472653.6341763483</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.02007535520628776</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2.584257782660615</v>
       </c>
       <c r="E5" t="n">
-        <v>2459.197450605906</v>
+        <v>2455.006986526397</v>
       </c>
       <c r="F5" t="n">
-        <v>2931.680060029543</v>
+        <v>3051.254512538642</v>
       </c>
       <c r="G5" t="n">
-        <v>2386.768791839745</v>
+        <v>1264.040082484087</v>
       </c>
       <c r="H5" t="n">
-        <v>9001.304573296673</v>
+        <v>8352.161639187801</v>
       </c>
       <c r="I5" t="n">
-        <v>112.6736350291269</v>
+        <v>100.0368601560412</v>
       </c>
       <c r="J5" t="n">
-        <v>627.8726955694112</v>
+        <v>638.3231571554076</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-47306.10301425261</v>
+        <v>-440188.6243215217</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007311233538544728</v>
+        <v>0.01713753852604482</v>
       </c>
       <c r="D6" t="n">
-        <v>2.678101296424673</v>
+        <v>3.476215753188405</v>
       </c>
       <c r="E6" t="n">
-        <v>2599.12970176709</v>
+        <v>2557.968037132192</v>
       </c>
       <c r="F6" t="n">
-        <v>3081.185066013964</v>
+        <v>3030.608842888562</v>
       </c>
       <c r="G6" t="n">
-        <v>1686.264634370313</v>
+        <v>1264.467768290315</v>
       </c>
       <c r="H6" t="n">
-        <v>8964.333490151888</v>
+        <v>8503.606938698902</v>
       </c>
       <c r="I6" t="n">
-        <v>109.2505608531475</v>
+        <v>103.9716609345526</v>
       </c>
       <c r="J6" t="n">
-        <v>697.2428783739668</v>
+        <v>745.345898998908</v>
       </c>
     </row>
     <row r="7">
@@ -657,31 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-523288.66580607</v>
+        <v>106174.0504140435</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02458041585900693</v>
+        <v>0.003615602531340646</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9988442638376838</v>
+        <v>1.435856206896668</v>
       </c>
       <c r="E7" t="n">
-        <v>2466.303816719954</v>
+        <v>2557.083282681394</v>
       </c>
       <c r="F7" t="n">
-        <v>2913.5097347404</v>
+        <v>3060.301477871629</v>
       </c>
       <c r="G7" t="n">
-        <v>1264.482560576602</v>
+        <v>1869.433958773768</v>
       </c>
       <c r="H7" t="n">
-        <v>8174.31514716168</v>
+        <v>8963.243118234588</v>
       </c>
       <c r="I7" t="n">
-        <v>107.2467204072428</v>
+        <v>199.6665177012148</v>
       </c>
       <c r="J7" t="n">
-        <v>614.108481307537</v>
+        <v>678.3981655691365</v>
       </c>
     </row>
     <row r="8">
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-543430.5486241039</v>
+        <v>-816079.8127046213</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0276178162537731</v>
+        <v>0.07566867531178469</v>
       </c>
       <c r="D8" t="n">
-        <v>1.249698815556988</v>
+        <v>7.076236948180082</v>
       </c>
       <c r="E8" t="n">
-        <v>2466.303816719954</v>
+        <v>2469.684039152169</v>
       </c>
       <c r="F8" t="n">
-        <v>2913.887370500718</v>
+        <v>3033.973408226307</v>
       </c>
       <c r="G8" t="n">
-        <v>1264.176539172637</v>
+        <v>1264.087175126683</v>
       </c>
       <c r="H8" t="n">
-        <v>8069.672688874644</v>
+        <v>6531.685656454114</v>
       </c>
       <c r="I8" t="n">
-        <v>101.7361450525104</v>
+        <v>173.5011214865662</v>
       </c>
       <c r="J8" t="n">
-        <v>614.0879819979549</v>
+        <v>638.3933702665031</v>
       </c>
     </row>
     <row r="9">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-496624.8033568966</v>
+        <v>155332.9982847078</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02051929019415631</v>
+        <v>0.003193011041785512</v>
       </c>
       <c r="D9" t="n">
-        <v>1.378570208171304</v>
+        <v>1.059098687237103</v>
       </c>
       <c r="E9" t="n">
-        <v>2487.204199180762</v>
+        <v>2584.789843826061</v>
       </c>
       <c r="F9" t="n">
-        <v>2923.992229794539</v>
+        <v>3007.447000671906</v>
       </c>
       <c r="G9" t="n">
-        <v>1264.013066609295</v>
+        <v>1941.212287041167</v>
       </c>
       <c r="H9" t="n">
-        <v>8313.418863320603</v>
+        <v>8932.941115372494</v>
       </c>
       <c r="I9" t="n">
-        <v>102.2801572041625</v>
+        <v>164.0815915270595</v>
       </c>
       <c r="J9" t="n">
-        <v>625.6006478749449</v>
+        <v>769.0388708103047</v>
       </c>
     </row>
     <row r="10">
@@ -759,31 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46573.85560867423</v>
+        <v>-906215.0076111164</v>
       </c>
       <c r="C10" t="n">
-        <v>0.005831945807627614</v>
+        <v>0.09417957346864599</v>
       </c>
       <c r="D10" t="n">
-        <v>1.846578328083148</v>
+        <v>10.47848912180128</v>
       </c>
       <c r="E10" t="n">
-        <v>2602.889772426048</v>
+        <v>2602.775889988833</v>
       </c>
       <c r="F10" t="n">
-        <v>3041.375841163024</v>
+        <v>3056.012524698865</v>
       </c>
       <c r="G10" t="n">
-        <v>1805.176194841129</v>
+        <v>1264.073544228907</v>
       </c>
       <c r="H10" t="n">
-        <v>8995.030060303357</v>
+        <v>6045.130483725835</v>
       </c>
       <c r="I10" t="n">
-        <v>105.511141234645</v>
+        <v>100.0626335711341</v>
       </c>
       <c r="J10" t="n">
-        <v>623.383921955498</v>
+        <v>669.3691913210897</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-385701.536026042</v>
+        <v>-799412.7562282369</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0122290628434072</v>
+        <v>0.07209193333950614</v>
       </c>
       <c r="D11" t="n">
-        <v>1.186807806361356</v>
+        <v>6.696071401057502</v>
       </c>
       <c r="E11" t="n">
-        <v>2469.609062601906</v>
+        <v>2467.027624309361</v>
       </c>
       <c r="F11" t="n">
-        <v>3042.928801278003</v>
+        <v>3028.584048642864</v>
       </c>
       <c r="G11" t="n">
-        <v>1264.080376693519</v>
+        <v>1264.69880259126</v>
       </c>
       <c r="H11" t="n">
-        <v>8889.982827967109</v>
+        <v>6623.526926294311</v>
       </c>
       <c r="I11" t="n">
-        <v>108.4207326882549</v>
+        <v>105.0812076386139</v>
       </c>
       <c r="J11" t="n">
-        <v>613.7508636955605</v>
+        <v>649.2986333245392</v>
       </c>
     </row>
     <row r="12">
@@ -827,31 +827,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-506289.0971195218</v>
+        <v>-499628.0238599717</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02205799658435859</v>
+        <v>0.02412906246590704</v>
       </c>
       <c r="D12" t="n">
-        <v>1.557710735915696</v>
+        <v>4.837090042780401</v>
       </c>
       <c r="E12" t="n">
-        <v>2466.705267682119</v>
+        <v>2593.150708623594</v>
       </c>
       <c r="F12" t="n">
-        <v>2935.835044590414</v>
+        <v>3043.329802812634</v>
       </c>
       <c r="G12" t="n">
-        <v>1264.669114250497</v>
+        <v>1265.384485547651</v>
       </c>
       <c r="H12" t="n">
-        <v>8258.553316185968</v>
+        <v>8181.494599996926</v>
       </c>
       <c r="I12" t="n">
-        <v>115.3139802233383</v>
+        <v>204.1283417451027</v>
       </c>
       <c r="J12" t="n">
-        <v>634.3519205837946</v>
+        <v>643.0709316127461</v>
       </c>
     </row>
     <row r="13">
@@ -861,31 +861,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-101054.575247983</v>
+        <v>-222942.2579557323</v>
       </c>
       <c r="C13" t="n">
-        <v>0.007699678130365551</v>
+        <v>0.00788106789129441</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9423427666585882</v>
+        <v>1.782060548610565</v>
       </c>
       <c r="E13" t="n">
-        <v>2456.350983385819</v>
+        <v>2561.389800528896</v>
       </c>
       <c r="F13" t="n">
-        <v>3083.360711300846</v>
+        <v>3012.596735098024</v>
       </c>
       <c r="G13" t="n">
-        <v>1605.724180237512</v>
+        <v>1435.282784070931</v>
       </c>
       <c r="H13" t="n">
-        <v>9007.113728950015</v>
+        <v>8969.769364456899</v>
       </c>
       <c r="I13" t="n">
-        <v>231.6907367860759</v>
+        <v>203.835071487996</v>
       </c>
       <c r="J13" t="n">
-        <v>668.3321226972279</v>
+        <v>633.539123646364</v>
       </c>
     </row>
     <row r="14">
@@ -895,31 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-893022.9736479279</v>
+        <v>-740577.8516670298</v>
       </c>
       <c r="C14" t="n">
-        <v>0.09052590948901386</v>
+        <v>0.06092058933558869</v>
       </c>
       <c r="D14" t="n">
-        <v>9.201524307981035</v>
+        <v>4.615136989458035</v>
       </c>
       <c r="E14" t="n">
-        <v>2603.964291758673</v>
+        <v>2487.97803843435</v>
       </c>
       <c r="F14" t="n">
-        <v>3026.863777031846</v>
+        <v>2949.810578270846</v>
       </c>
       <c r="G14" t="n">
-        <v>1264.067629715317</v>
+        <v>1265.520563495165</v>
       </c>
       <c r="H14" t="n">
-        <v>6199.395462697594</v>
+        <v>6937.198099100013</v>
       </c>
       <c r="I14" t="n">
-        <v>103.4569675138847</v>
+        <v>107.5770145467553</v>
       </c>
       <c r="J14" t="n">
-        <v>622.8429965717053</v>
+        <v>636.7942207153245</v>
       </c>
     </row>
     <row r="15">
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-423357.4365982153</v>
+        <v>-895121.9915093952</v>
       </c>
       <c r="C15" t="n">
-        <v>0.014415441452353</v>
+        <v>0.09174124533605896</v>
       </c>
       <c r="D15" t="n">
-        <v>3.808981422310309</v>
+        <v>8.09515749758517</v>
       </c>
       <c r="E15" t="n">
-        <v>2574.924579711491</v>
+        <v>2455.132222823772</v>
       </c>
       <c r="F15" t="n">
-        <v>3069.810372840679</v>
+        <v>3050.610004112591</v>
       </c>
       <c r="G15" t="n">
-        <v>1265.808227226574</v>
+        <v>1264.089609459507</v>
       </c>
       <c r="H15" t="n">
-        <v>8661.646011989265</v>
+        <v>6120.982190623148</v>
       </c>
       <c r="I15" t="n">
-        <v>114.546123426206</v>
+        <v>101.8527194018787</v>
       </c>
       <c r="J15" t="n">
-        <v>714.7290420575038</v>
+        <v>638.3231571554076</v>
       </c>
     </row>
     <row r="16">
@@ -963,31 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-556964.0388482087</v>
+        <v>-292493.7328380714</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02958055438896848</v>
+        <v>0.008917779320036477</v>
       </c>
       <c r="D16" t="n">
-        <v>3.339771603953068</v>
+        <v>1.634712971588692</v>
       </c>
       <c r="E16" t="n">
-        <v>2469.914218660594</v>
+        <v>2599.279445637249</v>
       </c>
       <c r="F16" t="n">
-        <v>3041.055268534169</v>
+        <v>2955.30904440067</v>
       </c>
       <c r="G16" t="n">
-        <v>1264.033493575763</v>
+        <v>1351.597416901887</v>
       </c>
       <c r="H16" t="n">
-        <v>7986.51340867676</v>
+        <v>8948.846207593377</v>
       </c>
       <c r="I16" t="n">
-        <v>101.9687259773904</v>
+        <v>100.9821049354616</v>
       </c>
       <c r="J16" t="n">
-        <v>614.4229708422733</v>
+        <v>633.0095027100266</v>
       </c>
     </row>
     <row r="17">
@@ -997,31 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-924158.3266934468</v>
+        <v>-687602.7239290946</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0972471404161384</v>
+        <v>0.05283537655357599</v>
       </c>
       <c r="D17" t="n">
-        <v>10.40016679082617</v>
+        <v>5.055096154772643</v>
       </c>
       <c r="E17" t="n">
-        <v>2602.427233530964</v>
+        <v>2455.877360468316</v>
       </c>
       <c r="F17" t="n">
-        <v>3092.872811091714</v>
+        <v>3053.110638766103</v>
       </c>
       <c r="G17" t="n">
-        <v>1264.828195966049</v>
+        <v>1264.700597243602</v>
       </c>
       <c r="H17" t="n">
-        <v>6020.944882237057</v>
+        <v>7208.39497990157</v>
       </c>
       <c r="I17" t="n">
-        <v>102.4243989441488</v>
+        <v>138.762286910851</v>
       </c>
       <c r="J17" t="n">
-        <v>677.2920237577462</v>
+        <v>661.0702789699633</v>
       </c>
     </row>
     <row r="18">
@@ -1031,31 +1031,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-785632.6707778471</v>
+        <v>-544659.8678657506</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06965192725825893</v>
+        <v>0.03074634229715819</v>
       </c>
       <c r="D18" t="n">
-        <v>7.058415268476425</v>
+        <v>3.55303380947749</v>
       </c>
       <c r="E18" t="n">
-        <v>2586.345702391739</v>
+        <v>2462.505714890364</v>
       </c>
       <c r="F18" t="n">
-        <v>2968.592478644375</v>
+        <v>3043.825693941514</v>
       </c>
       <c r="G18" t="n">
-        <v>1271.639983788881</v>
+        <v>1264.110892440459</v>
       </c>
       <c r="H18" t="n">
-        <v>6734.989535824748</v>
+        <v>7970.634327921287</v>
       </c>
       <c r="I18" t="n">
-        <v>103.7045789347795</v>
+        <v>113.252242767626</v>
       </c>
       <c r="J18" t="n">
-        <v>711.6919120822992</v>
+        <v>635.3996838079619</v>
       </c>
     </row>
     <row r="19">
@@ -1065,31 +1065,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-644485.0975698684</v>
+        <v>-768813.112364288</v>
       </c>
       <c r="C19" t="n">
-        <v>0.04309245909892636</v>
+        <v>0.06584469188400749</v>
       </c>
       <c r="D19" t="n">
-        <v>2.273867479713909</v>
+        <v>5.72477345084863</v>
       </c>
       <c r="E19" t="n">
-        <v>2456.963541878687</v>
+        <v>2460.659127632587</v>
       </c>
       <c r="F19" t="n">
-        <v>2917.480103002983</v>
+        <v>3038.633645427748</v>
       </c>
       <c r="G19" t="n">
-        <v>1264.097460786217</v>
+        <v>1264.243665080757</v>
       </c>
       <c r="H19" t="n">
-        <v>7535.968456791475</v>
+        <v>6784.333256774328</v>
       </c>
       <c r="I19" t="n">
-        <v>102.715083333423</v>
+        <v>109.9663828691273</v>
       </c>
       <c r="J19" t="n">
-        <v>623.3324339674734</v>
+        <v>668.5872900713491</v>
       </c>
     </row>
     <row r="20">
@@ -1099,31 +1099,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>188289.6450619609</v>
+        <v>-701305.2668636348</v>
       </c>
       <c r="C20" t="n">
-        <v>0.003826831819866496</v>
+        <v>0.05476300917339258</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>6.363131663661914</v>
       </c>
       <c r="E20" t="n">
-        <v>2458.354843292067</v>
+        <v>2603.155599797199</v>
       </c>
       <c r="F20" t="n">
-        <v>2939.262531879023</v>
+        <v>2956.26036387294</v>
       </c>
       <c r="G20" t="n">
-        <v>1994.54520509884</v>
+        <v>1264.072433443056</v>
       </c>
       <c r="H20" t="n">
-        <v>9007.576916581886</v>
+        <v>7136.086524392142</v>
       </c>
       <c r="I20" t="n">
-        <v>127.2944382005159</v>
+        <v>118.1134822555216</v>
       </c>
       <c r="J20" t="n">
-        <v>618.7926401465737</v>
+        <v>654.6809364105055</v>
       </c>
     </row>
     <row r="21">
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>359577.671925222</v>
+        <v>-242673.8409577077</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001831591224127488</v>
+        <v>0.008164727076827303</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4291345787438172</v>
+        <v>2.140721746649876</v>
       </c>
       <c r="E21" t="n">
-        <v>2456.920673317376</v>
+        <v>2454.953307271966</v>
       </c>
       <c r="F21" t="n">
-        <v>2957.198198631132</v>
+        <v>3050.256056484938</v>
       </c>
       <c r="G21" t="n">
-        <v>2228.591164695605</v>
+        <v>1413.162589677424</v>
       </c>
       <c r="H21" t="n">
-        <v>8973.041967884166</v>
+        <v>8963.243118234588</v>
       </c>
       <c r="I21" t="n">
-        <v>122.7295238904736</v>
+        <v>173.1044056366904</v>
       </c>
       <c r="J21" t="n">
-        <v>637.4525495026571</v>
+        <v>637.8897699813972</v>
       </c>
     </row>
     <row r="22">
@@ -1167,31 +1167,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-200159.9224067023</v>
+        <v>-431596.1069797943</v>
       </c>
       <c r="C22" t="n">
-        <v>0.009318530797988757</v>
+        <v>0.0162527198189174</v>
       </c>
       <c r="D22" t="n">
-        <v>3.074010838108931</v>
+        <v>4.324022632072988</v>
       </c>
       <c r="E22" t="n">
-        <v>2602.116745054462</v>
+        <v>2595.087029893021</v>
       </c>
       <c r="F22" t="n">
-        <v>3075.044555799876</v>
+        <v>3057.713504674452</v>
       </c>
       <c r="G22" t="n">
-        <v>1484.505726947051</v>
+        <v>1265.279183509131</v>
       </c>
       <c r="H22" t="n">
-        <v>8964.333490151888</v>
+        <v>8548.515883715214</v>
       </c>
       <c r="I22" t="n">
-        <v>109.2505608531475</v>
+        <v>110.2313286921653</v>
       </c>
       <c r="J22" t="n">
-        <v>699.1118153594023</v>
+        <v>644.027140468753</v>
       </c>
     </row>
     <row r="23">
@@ -1201,31 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>97146.88648430072</v>
+        <v>283721.781892926</v>
       </c>
       <c r="C23" t="n">
-        <v>0.005777607221935071</v>
+        <v>0.001230376280371132</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8153141746917947</v>
+        <v>0.8038145269838703</v>
       </c>
       <c r="E23" t="n">
-        <v>2566.508280708342</v>
+        <v>2461.714991316332</v>
       </c>
       <c r="F23" t="n">
-        <v>2990.883770767774</v>
+        <v>3046.316647536939</v>
       </c>
       <c r="G23" t="n">
-        <v>1895.730561084314</v>
+        <v>2110.225424691186</v>
       </c>
       <c r="H23" t="n">
-        <v>8907.30568175334</v>
+        <v>8961.638658439218</v>
       </c>
       <c r="I23" t="n">
-        <v>112.2846640520006</v>
+        <v>101.4282698044864</v>
       </c>
       <c r="J23" t="n">
-        <v>624.4662896566941</v>
+        <v>633.2889244419437</v>
       </c>
     </row>
     <row r="24">
@@ -1235,31 +1235,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>279934.0447898577</v>
+        <v>-514891.7642985224</v>
       </c>
       <c r="C24" t="n">
-        <v>0.002982866614879118</v>
+        <v>0.02655448624365921</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2436177558255204</v>
+        <v>3.292938027017756</v>
       </c>
       <c r="E24" t="n">
-        <v>2454.949651364508</v>
+        <v>2577.258215987888</v>
       </c>
       <c r="F24" t="n">
-        <v>3083.289997600795</v>
+        <v>2938.828731922368</v>
       </c>
       <c r="G24" t="n">
-        <v>2124.562972806262</v>
+        <v>1266.658123683947</v>
       </c>
       <c r="H24" t="n">
-        <v>8960.990803842698</v>
+        <v>8110.911819057567</v>
       </c>
       <c r="I24" t="n">
-        <v>104.3493034103863</v>
+        <v>133.9098514266094</v>
       </c>
       <c r="J24" t="n">
-        <v>613.6628779648954</v>
+        <v>673.8148771454042</v>
       </c>
     </row>
     <row r="25">
@@ -1269,31 +1269,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-697061.8534540352</v>
+        <v>-647288.7612009756</v>
       </c>
       <c r="C25" t="n">
-        <v>0.05124977921081596</v>
+        <v>0.04672432666251096</v>
       </c>
       <c r="D25" t="n">
-        <v>5.198041480223403</v>
+        <v>3.123970620910854</v>
       </c>
       <c r="E25" t="n">
-        <v>2459.156742166847</v>
+        <v>2462.914038074554</v>
       </c>
       <c r="F25" t="n">
-        <v>3075.268355075816</v>
+        <v>2939.024551676172</v>
       </c>
       <c r="G25" t="n">
-        <v>1264.060383982735</v>
+        <v>1264.037912059427</v>
       </c>
       <c r="H25" t="n">
-        <v>7235.280339422375</v>
+        <v>7432.368736453564</v>
       </c>
       <c r="I25" t="n">
-        <v>102.7113069987598</v>
+        <v>180.9558647092629</v>
       </c>
       <c r="J25" t="n">
-        <v>711.9103810621465</v>
+        <v>634.2824826844363</v>
       </c>
     </row>
     <row r="26">
@@ -1303,31 +1303,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-747352.4419284808</v>
+        <v>-526480.8650159976</v>
       </c>
       <c r="C26" t="n">
-        <v>0.06078647173092974</v>
+        <v>0.02821143284795623</v>
       </c>
       <c r="D26" t="n">
-        <v>3.692067095363161</v>
+        <v>1.970186398660911</v>
       </c>
       <c r="E26" t="n">
-        <v>2472.990083031628</v>
+        <v>2483.229233541364</v>
       </c>
       <c r="F26" t="n">
-        <v>2919.780231147646</v>
+        <v>2944.005176663512</v>
       </c>
       <c r="G26" t="n">
-        <v>1264.296772612704</v>
+        <v>1264.117013021796</v>
       </c>
       <c r="H26" t="n">
-        <v>6985.449877251613</v>
+        <v>8067.297020865448</v>
       </c>
       <c r="I26" t="n">
-        <v>144.0243829502808</v>
+        <v>113.2955310140325</v>
       </c>
       <c r="J26" t="n">
-        <v>632.2681256015393</v>
+        <v>706.539938376439</v>
       </c>
     </row>
     <row r="27">
@@ -1337,31 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-803797.0395651702</v>
+        <v>34606.65218643565</v>
       </c>
       <c r="C27" t="n">
-        <v>0.07217820483522069</v>
+        <v>0.004526427725100556</v>
       </c>
       <c r="D27" t="n">
-        <v>6.860459723739187</v>
+        <v>0.8601671602730288</v>
       </c>
       <c r="E27" t="n">
-        <v>2575.545851636009</v>
+        <v>2462.096398798486</v>
       </c>
       <c r="F27" t="n">
-        <v>2955.954979295814</v>
+        <v>2958.005642335779</v>
       </c>
       <c r="G27" t="n">
-        <v>1264.03368565149</v>
+        <v>1776.418800939025</v>
       </c>
       <c r="H27" t="n">
-        <v>6679.925761354905</v>
+        <v>8964.955032403834</v>
       </c>
       <c r="I27" t="n">
-        <v>103.7008957005112</v>
+        <v>114.1911229174377</v>
       </c>
       <c r="J27" t="n">
-        <v>623.6563303825209</v>
+        <v>884.4001060054147</v>
       </c>
     </row>
     <row r="28">
@@ -1371,31 +1371,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-763837.5885763364</v>
+        <v>341784.2188711124</v>
       </c>
       <c r="C28" t="n">
-        <v>0.06399756047671909</v>
+        <v>0.0006904052849154495</v>
       </c>
       <c r="D28" t="n">
-        <v>3.584985658840223</v>
+        <v>0.9339455762792492</v>
       </c>
       <c r="E28" t="n">
-        <v>2459.062197732333</v>
+        <v>2584.789843826061</v>
       </c>
       <c r="F28" t="n">
-        <v>2914.386163950966</v>
+        <v>3004.07816991756</v>
       </c>
       <c r="G28" t="n">
-        <v>1264.825898695659</v>
+        <v>2186.062656356431</v>
       </c>
       <c r="H28" t="n">
-        <v>6903.670773267095</v>
+        <v>8939.28934712336</v>
       </c>
       <c r="I28" t="n">
-        <v>100.5727213116294</v>
+        <v>164.0815915270595</v>
       </c>
       <c r="J28" t="n">
-        <v>617.254208611796</v>
+        <v>759.6704705757405</v>
       </c>
     </row>
     <row r="29">
@@ -1405,31 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-147221.4282991369</v>
+        <v>-390040.969532954</v>
       </c>
       <c r="C29" t="n">
-        <v>0.008367202160422893</v>
+        <v>0.01176779223153947</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8653426261183816</v>
+        <v>1.305982392387739</v>
       </c>
       <c r="E29" t="n">
-        <v>2483.649285510834</v>
+        <v>2453.325544949878</v>
       </c>
       <c r="F29" t="n">
-        <v>2913.517616226648</v>
+        <v>3034.251417460277</v>
       </c>
       <c r="G29" t="n">
-        <v>1556.004500400504</v>
+        <v>1264.174028799797</v>
       </c>
       <c r="H29" t="n">
-        <v>8989.20138245648</v>
+        <v>8781.527639275995</v>
       </c>
       <c r="I29" t="n">
-        <v>120.7872316500316</v>
+        <v>189.3241134055013</v>
       </c>
       <c r="J29" t="n">
-        <v>634.546412231344</v>
+        <v>633.5278859240898</v>
       </c>
     </row>
     <row r="30">
@@ -1439,31 +1439,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-754686.1949231508</v>
+        <v>-755536.9507411448</v>
       </c>
       <c r="C30" t="n">
-        <v>0.06260757384765236</v>
+        <v>0.06323194041124941</v>
       </c>
       <c r="D30" t="n">
-        <v>4.050226818647474</v>
+        <v>5.77727715180435</v>
       </c>
       <c r="E30" t="n">
-        <v>2472.852909053969</v>
+        <v>2480.342813706122</v>
       </c>
       <c r="F30" t="n">
-        <v>2935.321685561644</v>
+        <v>2992.959478911693</v>
       </c>
       <c r="G30" t="n">
-        <v>1268.833595080179</v>
+        <v>1264.287463384491</v>
       </c>
       <c r="H30" t="n">
-        <v>6932.227578535227</v>
+        <v>6854.623156183046</v>
       </c>
       <c r="I30" t="n">
-        <v>101.9294177800057</v>
+        <v>156.8494071009048</v>
       </c>
       <c r="J30" t="n">
-        <v>620.8456277342713</v>
+        <v>642.2532309752663</v>
       </c>
     </row>
     <row r="31">
@@ -1473,31 +1473,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-625864.0246406784</v>
+        <v>-538180.9077435997</v>
       </c>
       <c r="C31" t="n">
-        <v>0.04024756307715972</v>
+        <v>0.03007056375718086</v>
       </c>
       <c r="D31" t="n">
-        <v>6.511349263167466</v>
+        <v>3.854236388058085</v>
       </c>
       <c r="E31" t="n">
-        <v>2603.964291758673</v>
+        <v>2465.215341074787</v>
       </c>
       <c r="F31" t="n">
-        <v>3050.545566696258</v>
+        <v>3064.496988494394</v>
       </c>
       <c r="G31" t="n">
-        <v>1264.067629715317</v>
+        <v>1267.332274504126</v>
       </c>
       <c r="H31" t="n">
-        <v>7600.531342462953</v>
+        <v>7987.824312088997</v>
       </c>
       <c r="I31" t="n">
-        <v>158.6225031553898</v>
+        <v>112.1125016431397</v>
       </c>
       <c r="J31" t="n">
-        <v>645.586974260782</v>
+        <v>657.4441787185406</v>
       </c>
     </row>
     <row r="32">
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-772166.0931725441</v>
+        <v>-728883.5219217003</v>
       </c>
       <c r="C32" t="n">
-        <v>0.06599378491656292</v>
+        <v>0.05914669864622265</v>
       </c>
       <c r="D32" t="n">
-        <v>7.049398018056607</v>
+        <v>6.112752641177133</v>
       </c>
       <c r="E32" t="n">
-        <v>2576.483655164186</v>
+        <v>2463.067097041801</v>
       </c>
       <c r="F32" t="n">
-        <v>2992.834285560097</v>
+        <v>3053.394845624141</v>
       </c>
       <c r="G32" t="n">
-        <v>1264.780243122121</v>
+        <v>1265.376253903132</v>
       </c>
       <c r="H32" t="n">
-        <v>6834.804005251392</v>
+        <v>6989.254475421857</v>
       </c>
       <c r="I32" t="n">
-        <v>120.9697341183674</v>
+        <v>107.0868343280006</v>
       </c>
       <c r="J32" t="n">
-        <v>666.3185976690111</v>
+        <v>669.2847742108814</v>
       </c>
     </row>
     <row r="33">
@@ -1541,31 +1541,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-39622.65912989993</v>
+        <v>-770858.1169693568</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006887144277000243</v>
+        <v>0.06762568482513316</v>
       </c>
       <c r="D33" t="n">
-        <v>2.632913766187517</v>
+        <v>4.529482899084591</v>
       </c>
       <c r="E33" t="n">
-        <v>2603.589724431766</v>
+        <v>2468.607936987829</v>
       </c>
       <c r="F33" t="n">
-        <v>3082.171784148726</v>
+        <v>2938.316019195373</v>
       </c>
       <c r="G33" t="n">
-        <v>1686.264634370313</v>
+        <v>1276.212302557282</v>
       </c>
       <c r="H33" t="n">
-        <v>9008.278196550385</v>
+        <v>6734.144166327438</v>
       </c>
       <c r="I33" t="n">
-        <v>100.5654006052857</v>
+        <v>103.3406572641032</v>
       </c>
       <c r="J33" t="n">
-        <v>664.4526239253796</v>
+        <v>676.6485772266863</v>
       </c>
     </row>
     <row r="34">
@@ -1575,31 +1575,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-457322.9714344265</v>
+        <v>-892581.6560827773</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01654636924460729</v>
+        <v>0.09123889215397105</v>
       </c>
       <c r="D34" t="n">
-        <v>0.990848021112023</v>
+        <v>10.13052657955897</v>
       </c>
       <c r="E34" t="n">
-        <v>2466.738026633139</v>
+        <v>2597.057102510456</v>
       </c>
       <c r="F34" t="n">
-        <v>2962.633983634271</v>
+        <v>3050.610004112591</v>
       </c>
       <c r="G34" t="n">
-        <v>1264.03368565149</v>
+        <v>1264.070409888056</v>
       </c>
       <c r="H34" t="n">
-        <v>8519.237344225334</v>
+        <v>6120.982190623148</v>
       </c>
       <c r="I34" t="n">
-        <v>103.7008957005112</v>
+        <v>101.1138826527951</v>
       </c>
       <c r="J34" t="n">
-        <v>623.9592435134236</v>
+        <v>638.3231571554076</v>
       </c>
     </row>
     <row r="35">
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-578126.5723836212</v>
+        <v>-409074.4792781272</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0328671847843551</v>
+        <v>0.01371484274683916</v>
       </c>
       <c r="D35" t="n">
-        <v>4.129230828426955</v>
+        <v>1.592606539047392</v>
       </c>
       <c r="E35" t="n">
-        <v>2466.755857230165</v>
+        <v>2454.107866887537</v>
       </c>
       <c r="F35" t="n">
-        <v>3080.119230062126</v>
+        <v>3037.711213766245</v>
       </c>
       <c r="G35" t="n">
-        <v>1264.160999930134</v>
+        <v>1264.169059583463</v>
       </c>
       <c r="H35" t="n">
-        <v>7868.616352622506</v>
+        <v>8680.869527907755</v>
       </c>
       <c r="I35" t="n">
-        <v>105.6623654085709</v>
+        <v>177.0870416126606</v>
       </c>
       <c r="J35" t="n">
-        <v>635.2146862555861</v>
+        <v>643.6277796218244</v>
       </c>
     </row>
     <row r="36">
@@ -1643,31 +1643,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-683554.1931968192</v>
+        <v>-564415.490075185</v>
       </c>
       <c r="C36" t="n">
-        <v>0.04885676155157422</v>
+        <v>0.03554865689462079</v>
       </c>
       <c r="D36" t="n">
-        <v>7.154222206999606</v>
+        <v>2.390047387282346</v>
       </c>
       <c r="E36" t="n">
-        <v>2603.964291758673</v>
+        <v>2459.276303855995</v>
       </c>
       <c r="F36" t="n">
-        <v>3045.511113994951</v>
+        <v>2949.77857333525</v>
       </c>
       <c r="G36" t="n">
-        <v>1264.067629715317</v>
+        <v>1280.831982917726</v>
       </c>
       <c r="H36" t="n">
-        <v>7303.76239778769</v>
+        <v>7799.41603352333</v>
       </c>
       <c r="I36" t="n">
-        <v>103.6199689525953</v>
+        <v>203.1713517743055</v>
       </c>
       <c r="J36" t="n">
-        <v>622.6591657785781</v>
+        <v>640.8410861356365</v>
       </c>
     </row>
     <row r="37">
@@ -1677,31 +1677,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-592400.3135933899</v>
+        <v>-418896.2312218091</v>
       </c>
       <c r="C37" t="n">
-        <v>0.03630759624994939</v>
+        <v>0.01484152257855256</v>
       </c>
       <c r="D37" t="n">
-        <v>3.440840854291149</v>
+        <v>3.663758444564957</v>
       </c>
       <c r="E37" t="n">
-        <v>2559.620257773315</v>
+        <v>2561.622790956676</v>
       </c>
       <c r="F37" t="n">
-        <v>2924.089624144875</v>
+        <v>3055.784332552881</v>
       </c>
       <c r="G37" t="n">
-        <v>1277.612355075499</v>
+        <v>1264.057381104423</v>
       </c>
       <c r="H37" t="n">
-        <v>7743.061453681602</v>
+        <v>8622.734894903473</v>
       </c>
       <c r="I37" t="n">
-        <v>103.747152711068</v>
+        <v>127.6607803219415</v>
       </c>
       <c r="J37" t="n">
-        <v>659.3073705034576</v>
+        <v>638.0541159515317</v>
       </c>
     </row>
     <row r="38">
@@ -1711,31 +1711,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-644554.1659430629</v>
+        <v>-834726.1219498953</v>
       </c>
       <c r="C38" t="n">
-        <v>0.04310586753055664</v>
+        <v>0.07975676925817606</v>
       </c>
       <c r="D38" t="n">
-        <v>2.217585709885295</v>
+        <v>7.460981407978807</v>
       </c>
       <c r="E38" t="n">
-        <v>2456.963541878687</v>
+        <v>2454.880508360579</v>
       </c>
       <c r="F38" t="n">
-        <v>2913.572415693537</v>
+        <v>3058.660094572063</v>
       </c>
       <c r="G38" t="n">
-        <v>1264.097460786217</v>
+        <v>1264.808012878694</v>
       </c>
       <c r="H38" t="n">
-        <v>7535.968456791475</v>
+        <v>6425.249690383215</v>
       </c>
       <c r="I38" t="n">
-        <v>102.715083333423</v>
+        <v>192.3886590897532</v>
       </c>
       <c r="J38" t="n">
-        <v>623.3324339674734</v>
+        <v>664.063896122119</v>
       </c>
     </row>
     <row r="39">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-867094.2865192518</v>
+        <v>-639601.1384496996</v>
       </c>
       <c r="C39" t="n">
-        <v>0.08556872911173206</v>
+        <v>0.04533908816512947</v>
       </c>
       <c r="D39" t="n">
-        <v>9.864602416334932</v>
+        <v>4.056345698735841</v>
       </c>
       <c r="E39" t="n">
-        <v>2603.868260033973</v>
+        <v>2453.055805701133</v>
       </c>
       <c r="F39" t="n">
-        <v>3092.817699474055</v>
+        <v>3021.606461951409</v>
       </c>
       <c r="G39" t="n">
-        <v>1264.812017907528</v>
+        <v>1264.46694344758</v>
       </c>
       <c r="H39" t="n">
-        <v>6320.257227438204</v>
+        <v>7471.088365336082</v>
       </c>
       <c r="I39" t="n">
-        <v>124.6029400260108</v>
+        <v>109.1604757785546</v>
       </c>
       <c r="J39" t="n">
-        <v>675.4576826249807</v>
+        <v>637.0013971506693</v>
       </c>
     </row>
     <row r="40">
@@ -1779,31 +1779,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-284036.421862361</v>
+        <v>-796899.281702592</v>
       </c>
       <c r="C40" t="n">
-        <v>0.01009510687147984</v>
+        <v>0.07157303400536794</v>
       </c>
       <c r="D40" t="n">
-        <v>2.971749418742298</v>
+        <v>6.599058318924101</v>
       </c>
       <c r="E40" t="n">
-        <v>2572.157774151584</v>
+        <v>2459.359251990328</v>
       </c>
       <c r="F40" t="n">
-        <v>3087.981568394082</v>
+        <v>3031.952192632894</v>
       </c>
       <c r="G40" t="n">
-        <v>1363.580786286091</v>
+        <v>1264.69880259126</v>
       </c>
       <c r="H40" t="n">
-        <v>9008.528507900981</v>
+        <v>6637.23788178585</v>
       </c>
       <c r="I40" t="n">
-        <v>154.0431670551134</v>
+        <v>104.8709919444255</v>
       </c>
       <c r="J40" t="n">
-        <v>634.4794486879515</v>
+        <v>649.2986333245392</v>
       </c>
     </row>
     <row r="41">
@@ -1813,31 +1813,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-468725.0387445386</v>
+        <v>-865531.6067968225</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01767504588994668</v>
+        <v>0.0858316534762152</v>
       </c>
       <c r="D41" t="n">
-        <v>0.5094901832184862</v>
+        <v>9.349768041314633</v>
       </c>
       <c r="E41" t="n">
-        <v>2466.303816719954</v>
+        <v>2561.622790956676</v>
       </c>
       <c r="F41" t="n">
-        <v>2936.281521849166</v>
+        <v>3055.418757199448</v>
       </c>
       <c r="G41" t="n">
-        <v>1264.492074107309</v>
+        <v>1264.057381104423</v>
       </c>
       <c r="H41" t="n">
-        <v>8460.287273838263</v>
+        <v>6261.421686598915</v>
       </c>
       <c r="I41" t="n">
-        <v>107.2465936497329</v>
+        <v>127.6607803219415</v>
       </c>
       <c r="J41" t="n">
-        <v>613.9930657080351</v>
+        <v>668.8758863636634</v>
       </c>
     </row>
     <row r="42">
@@ -1847,31 +1847,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>420147.1298749801</v>
+        <v>-871813.7435357482</v>
       </c>
       <c r="C42" t="n">
-        <v>0.001125136754110983</v>
+        <v>0.08748279042574351</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6065261182913062</v>
+        <v>9.536222187665588</v>
       </c>
       <c r="E42" t="n">
-        <v>2481.874170576646</v>
+        <v>2603.790314079603</v>
       </c>
       <c r="F42" t="n">
-        <v>3086.601293732182</v>
+        <v>3022.247399156591</v>
       </c>
       <c r="G42" t="n">
-        <v>2306.624512385587</v>
+        <v>1265.938101600293</v>
       </c>
       <c r="H42" t="n">
-        <v>8965.7989912423</v>
+        <v>6216.578471146899</v>
       </c>
       <c r="I42" t="n">
-        <v>117.8717587642537</v>
+        <v>123.4905687891409</v>
       </c>
       <c r="J42" t="n">
-        <v>647.6356924077554</v>
+        <v>707.5809583544128</v>
       </c>
     </row>
     <row r="43">
@@ -1881,31 +1881,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-836272.2626084415</v>
+        <v>-483730.8517788374</v>
       </c>
       <c r="C43" t="n">
-        <v>0.07886619404967705</v>
+        <v>0.02141103432191472</v>
       </c>
       <c r="D43" t="n">
-        <v>4.326754990790727</v>
+        <v>2.7022062972196</v>
       </c>
       <c r="E43" t="n">
-        <v>2459.062197732333</v>
+        <v>2453.238347784038</v>
       </c>
       <c r="F43" t="n">
-        <v>2914.386163950966</v>
+        <v>3051.254512538642</v>
       </c>
       <c r="G43" t="n">
-        <v>1264.825898695659</v>
+        <v>1264.040082484087</v>
       </c>
       <c r="H43" t="n">
-        <v>6521.449084441338</v>
+        <v>8292.71845767742</v>
       </c>
       <c r="I43" t="n">
-        <v>100.5727213116294</v>
+        <v>100.0333696990405</v>
       </c>
       <c r="J43" t="n">
-        <v>614.3437865055748</v>
+        <v>650.3120143364716</v>
       </c>
     </row>
     <row r="44">
@@ -1915,31 +1915,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>242064.7200241373</v>
+        <v>-511661.5894565117</v>
       </c>
       <c r="C44" t="n">
-        <v>0.003497807977162494</v>
+        <v>0.02602392905026614</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7662168853573736</v>
+        <v>3.842981428565717</v>
       </c>
       <c r="E44" t="n">
-        <v>2591.535137226242</v>
+        <v>2487.97803843435</v>
       </c>
       <c r="F44" t="n">
-        <v>2970.498023887134</v>
+        <v>3061.561249493604</v>
       </c>
       <c r="G44" t="n">
-        <v>2072.635951701473</v>
+        <v>1265.523234956137</v>
       </c>
       <c r="H44" t="n">
-        <v>8961.164890578779</v>
+        <v>8126.73101324637</v>
       </c>
       <c r="I44" t="n">
-        <v>101.5521555374175</v>
+        <v>199.8133562042491</v>
       </c>
       <c r="J44" t="n">
-        <v>670.5235690376755</v>
+        <v>636.9162225593811</v>
       </c>
     </row>
     <row r="45">
@@ -1949,31 +1949,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-881245.439895907</v>
+        <v>-659991.8608750585</v>
       </c>
       <c r="C45" t="n">
-        <v>0.08817018165163094</v>
+        <v>0.04836315932904534</v>
       </c>
       <c r="D45" t="n">
-        <v>5.926106289292266</v>
+        <v>5.425007301404284</v>
       </c>
       <c r="E45" t="n">
-        <v>2481.874170576646</v>
+        <v>2462.340367367064</v>
       </c>
       <c r="F45" t="n">
-        <v>2922.42555991094</v>
+        <v>3070.211418281191</v>
       </c>
       <c r="G45" t="n">
-        <v>1264.826771146343</v>
+        <v>1264.00078870219</v>
       </c>
       <c r="H45" t="n">
-        <v>6279.490973784273</v>
+        <v>7360.443523549149</v>
       </c>
       <c r="I45" t="n">
-        <v>102.9707644061558</v>
+        <v>100.9059578874164</v>
       </c>
       <c r="J45" t="n">
-        <v>628.4137421757412</v>
+        <v>639.1527184559483</v>
       </c>
     </row>
     <row r="46">
@@ -1983,31 +1983,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-792795.2920317068</v>
+        <v>-124300.3132389183</v>
       </c>
       <c r="C46" t="n">
-        <v>0.07003360477787335</v>
+        <v>0.006828392715687228</v>
       </c>
       <c r="D46" t="n">
-        <v>6.712544571568923</v>
+        <v>0.6308375668326649</v>
       </c>
       <c r="E46" t="n">
-        <v>2573.445962685178</v>
+        <v>2460.104878935975</v>
       </c>
       <c r="F46" t="n">
-        <v>2957.189201790772</v>
+        <v>3012.596735098024</v>
       </c>
       <c r="G46" t="n">
-        <v>1264.17898177313</v>
+        <v>1578.615291094861</v>
       </c>
       <c r="H46" t="n">
-        <v>6734.989535824748</v>
+        <v>8930.851287838268</v>
       </c>
       <c r="I46" t="n">
-        <v>103.7501651888404</v>
+        <v>163.5228338365441</v>
       </c>
       <c r="J46" t="n">
-        <v>650.7723822365357</v>
+        <v>633.539123646364</v>
       </c>
     </row>
     <row r="47">
@@ -2017,31 +2017,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>150535.3320489801</v>
+        <v>6794.82130829012</v>
       </c>
       <c r="C47" t="n">
-        <v>0.004322440262500966</v>
+        <v>0.004894725272595183</v>
       </c>
       <c r="D47" t="n">
-        <v>2.220446049250313e-14</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>2458.354843292067</v>
+        <v>2453.718518308718</v>
       </c>
       <c r="F47" t="n">
-        <v>2939.262531879023</v>
+        <v>3031.786987339126</v>
       </c>
       <c r="G47" t="n">
-        <v>1944.730252467773</v>
+        <v>1745.569342049128</v>
       </c>
       <c r="H47" t="n">
-        <v>9007.576916581886</v>
+        <v>8958.676358477967</v>
       </c>
       <c r="I47" t="n">
-        <v>126.2175939022473</v>
+        <v>106.7480083592746</v>
       </c>
       <c r="J47" t="n">
-        <v>618.7926401465737</v>
+        <v>642.6952642675398</v>
       </c>
     </row>
     <row r="48">
@@ -2051,31 +2051,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-741193.9951065294</v>
+        <v>-851673.9205334024</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05954436046131583</v>
+        <v>0.08288130583440197</v>
       </c>
       <c r="D48" t="n">
-        <v>5.472297228699475</v>
+        <v>9.860270108224434</v>
       </c>
       <c r="E48" t="n">
-        <v>2576.173691902142</v>
+        <v>2601.127740244665</v>
       </c>
       <c r="F48" t="n">
-        <v>2919.300375886819</v>
+        <v>3073.956852916852</v>
       </c>
       <c r="G48" t="n">
-        <v>1264.922814553345</v>
+        <v>1264.085725799134</v>
       </c>
       <c r="H48" t="n">
-        <v>7007.568899385081</v>
+        <v>6331.310754077549</v>
       </c>
       <c r="I48" t="n">
-        <v>142.1323856580339</v>
+        <v>111.2576205109814</v>
       </c>
       <c r="J48" t="n">
-        <v>613.6517496999968</v>
+        <v>660.6872600286521</v>
       </c>
     </row>
     <row r="49">
@@ -2085,31 +2085,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-845987.8436188987</v>
+        <v>-721498.4190735966</v>
       </c>
       <c r="C49" t="n">
-        <v>0.08087661832213774</v>
+        <v>0.05811710821632868</v>
       </c>
       <c r="D49" t="n">
-        <v>5.314154445638552</v>
+        <v>5.437308917915395</v>
       </c>
       <c r="E49" t="n">
-        <v>2482.413467014506</v>
+        <v>2577.258215987888</v>
       </c>
       <c r="F49" t="n">
-        <v>2914.386163950966</v>
+        <v>2938.828731922368</v>
       </c>
       <c r="G49" t="n">
-        <v>1264.825291813765</v>
+        <v>1266.658123683947</v>
       </c>
       <c r="H49" t="n">
-        <v>6467.645130988124</v>
+        <v>7023.045638939749</v>
       </c>
       <c r="I49" t="n">
-        <v>100.5727213116294</v>
+        <v>101.1953085615692</v>
       </c>
       <c r="J49" t="n">
-        <v>617.254208611796</v>
+        <v>673.8148771454042</v>
       </c>
     </row>
     <row r="50">
@@ -2119,31 +2119,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-291917.7140641022</v>
+        <v>-559268.5688243839</v>
       </c>
       <c r="C50" t="n">
-        <v>0.01018811212410254</v>
+        <v>0.03352270967854475</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3867220639267033</v>
+        <v>4.162474796854355</v>
       </c>
       <c r="E50" t="n">
-        <v>2462.563309742004</v>
+        <v>2599.703055747876</v>
       </c>
       <c r="F50" t="n">
-        <v>2923.911869976611</v>
+        <v>2942.109291063686</v>
       </c>
       <c r="G50" t="n">
-        <v>1363.580786286091</v>
+        <v>1268.087083012384</v>
       </c>
       <c r="H50" t="n">
-        <v>8998.891177059031</v>
+        <v>7866.134298389895</v>
       </c>
       <c r="I50" t="n">
-        <v>100.2372258838696</v>
+        <v>171.3823787191322</v>
       </c>
       <c r="J50" t="n">
-        <v>623.1966058009137</v>
+        <v>659.8552272733326</v>
       </c>
     </row>
     <row r="51">
@@ -2153,31 +2153,31 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-669315.0427797544</v>
+        <v>-927045.4012927935</v>
       </c>
       <c r="C51" t="n">
-        <v>0.04716782798987258</v>
+        <v>0.09863248713548965</v>
       </c>
       <c r="D51" t="n">
-        <v>3.189221421816157</v>
+        <v>10.77190762938342</v>
       </c>
       <c r="E51" t="n">
-        <v>2483.17395341116</v>
+        <v>2603.056520677393</v>
       </c>
       <c r="F51" t="n">
-        <v>2929.846273192178</v>
+        <v>3056.603589288642</v>
       </c>
       <c r="G51" t="n">
-        <v>1264.695476833016</v>
+        <v>1264.197012427016</v>
       </c>
       <c r="H51" t="n">
-        <v>7389.9187411352</v>
+        <v>5931.572350396019</v>
       </c>
       <c r="I51" t="n">
-        <v>121.3351864416263</v>
+        <v>165.9434299090679</v>
       </c>
       <c r="J51" t="n">
-        <v>699.4515263460506</v>
+        <v>633.9212385289277</v>
       </c>
     </row>
     <row r="52">
@@ -2187,31 +2187,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-924778.9699306735</v>
+        <v>-823149.4899982759</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0972993125822912</v>
+        <v>0.07892462909220603</v>
       </c>
       <c r="D52" t="n">
-        <v>10.0905389024618</v>
+        <v>8.671214890901702</v>
       </c>
       <c r="E52" t="n">
-        <v>2602.469632563345</v>
+        <v>2534.564946147408</v>
       </c>
       <c r="F52" t="n">
-        <v>3069.290865208293</v>
+        <v>3061.996355312454</v>
       </c>
       <c r="G52" t="n">
-        <v>1265.637912136044</v>
+        <v>1278.302940306884</v>
       </c>
       <c r="H52" t="n">
-        <v>6020.852304798743</v>
+        <v>6425.249690383215</v>
       </c>
       <c r="I52" t="n">
-        <v>104.1503100238455</v>
+        <v>184.2818045133982</v>
       </c>
       <c r="J52" t="n">
-        <v>630.2391504792823</v>
+        <v>664.063896122119</v>
       </c>
     </row>
     <row r="53">
@@ -2221,31 +2221,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-853525.5066770869</v>
+        <v>-73402.20427540038</v>
       </c>
       <c r="C53" t="n">
-        <v>0.08261080209260196</v>
+        <v>0.005997087106910478</v>
       </c>
       <c r="D53" t="n">
-        <v>7.94971575801301</v>
+        <v>0.2948132487154087</v>
       </c>
       <c r="E53" t="n">
-        <v>2466.755857230165</v>
+        <v>2574.161191948837</v>
       </c>
       <c r="F53" t="n">
-        <v>3092.725343357699</v>
+        <v>2942.419562626806</v>
       </c>
       <c r="G53" t="n">
-        <v>1264.160999930134</v>
+        <v>1637.166831213514</v>
       </c>
       <c r="H53" t="n">
-        <v>6409.437864613627</v>
+        <v>8956.446492355866</v>
       </c>
       <c r="I53" t="n">
-        <v>105.6623654085709</v>
+        <v>202.929225506059</v>
       </c>
       <c r="J53" t="n">
-        <v>675.3945346695616</v>
+        <v>642.6803663468824</v>
       </c>
     </row>
     <row r="54">
@@ -2255,31 +2255,31 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-708924.5300376499</v>
+        <v>121905.4666922726</v>
       </c>
       <c r="C54" t="n">
-        <v>0.05297584343985078</v>
+        <v>0.003273391620989812</v>
       </c>
       <c r="D54" t="n">
-        <v>4.898397195035731</v>
+        <v>2.181877472261862</v>
       </c>
       <c r="E54" t="n">
-        <v>2461.90572508749</v>
+        <v>2535.742797798942</v>
       </c>
       <c r="F54" t="n">
-        <v>3045.511113994951</v>
+        <v>3001.543346606875</v>
       </c>
       <c r="G54" t="n">
-        <v>1264.734396962809</v>
+        <v>1891.977087170074</v>
       </c>
       <c r="H54" t="n">
-        <v>7178.15734153369</v>
+        <v>8975.387641829115</v>
       </c>
       <c r="I54" t="n">
-        <v>138.8965776361088</v>
+        <v>114.6288360741221</v>
       </c>
       <c r="J54" t="n">
-        <v>613.7965356256701</v>
+        <v>639.8510031296281</v>
       </c>
     </row>
     <row r="55">
@@ -2289,31 +2289,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-902932.1649568207</v>
+        <v>141240.0891326042</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0926722588951729</v>
+        <v>0.00306394419332176</v>
       </c>
       <c r="D55" t="n">
-        <v>9.769871653675089</v>
+        <v>2.466664503346405</v>
       </c>
       <c r="E55" t="n">
-        <v>2599.298010578806</v>
+        <v>2591.764922579744</v>
       </c>
       <c r="F55" t="n">
-        <v>3065.968700638495</v>
+        <v>2991.014414697737</v>
       </c>
       <c r="G55" t="n">
-        <v>1264.120674343296</v>
+        <v>1916.184936051908</v>
       </c>
       <c r="H55" t="n">
-        <v>6141.140903393048</v>
+        <v>8972.088116080131</v>
       </c>
       <c r="I55" t="n">
-        <v>124.3206242115262</v>
+        <v>130.9982326144194</v>
       </c>
       <c r="J55" t="n">
-        <v>628.4045253500761</v>
+        <v>668.0342318694787</v>
       </c>
     </row>
     <row r="56">
@@ -2323,31 +2323,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-33635.02652497496</v>
+        <v>-856389.2214309806</v>
       </c>
       <c r="C56" t="n">
-        <v>0.006855320165378554</v>
+        <v>0.08456795240591992</v>
       </c>
       <c r="D56" t="n">
-        <v>1.815293521428274</v>
+        <v>9.071867725021898</v>
       </c>
       <c r="E56" t="n">
-        <v>2570.163640178743</v>
+        <v>2593.210591048342</v>
       </c>
       <c r="F56" t="n">
-        <v>3066.370074057098</v>
+        <v>3012.596735098024</v>
       </c>
       <c r="G56" t="n">
-        <v>1695.763993021172</v>
+        <v>1268.220987209733</v>
       </c>
       <c r="H56" t="n">
-        <v>9001.782701055814</v>
+        <v>6290.261990462315</v>
       </c>
       <c r="I56" t="n">
-        <v>185.0206844026052</v>
+        <v>201.5269642197891</v>
       </c>
       <c r="J56" t="n">
-        <v>629.2521838668918</v>
+        <v>633.539123646364</v>
       </c>
     </row>
     <row r="57">
@@ -2357,31 +2357,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-269629.4353374057</v>
+        <v>-817672.5054566846</v>
       </c>
       <c r="C57" t="n">
-        <v>0.009895192383383581</v>
+        <v>0.07594432856867116</v>
       </c>
       <c r="D57" t="n">
-        <v>1.141129443350908</v>
+        <v>6.792053502768214</v>
       </c>
       <c r="E57" t="n">
-        <v>2460.115459841503</v>
+        <v>2464.126541978335</v>
       </c>
       <c r="F57" t="n">
-        <v>2934.924794601593</v>
+        <v>3019.903421528825</v>
       </c>
       <c r="G57" t="n">
-        <v>1392.987977951261</v>
+        <v>1264.015247544478</v>
       </c>
       <c r="H57" t="n">
-        <v>8998.927226770653</v>
+        <v>6526.434664783871</v>
       </c>
       <c r="I57" t="n">
-        <v>102.0694373675874</v>
+        <v>162.7213266796505</v>
       </c>
       <c r="J57" t="n">
-        <v>613.125385072711</v>
+        <v>638.4229525402687</v>
       </c>
     </row>
     <row r="58">
@@ -2391,31 +2391,31 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-796701.311373713</v>
+        <v>-855488.1030238545</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0709484482174606</v>
+        <v>0.08395326311601824</v>
       </c>
       <c r="D58" t="n">
-        <v>8.437148860989929</v>
+        <v>10.00638532849565</v>
       </c>
       <c r="E58" t="n">
-        <v>2603.354389833386</v>
+        <v>2601.140587154247</v>
       </c>
       <c r="F58" t="n">
-        <v>3040.371712361824</v>
+        <v>3075.418537675594</v>
       </c>
       <c r="G58" t="n">
-        <v>1264.067629715317</v>
+        <v>1264.085180018482</v>
       </c>
       <c r="H58" t="n">
-        <v>6701.52896668283</v>
+        <v>6303.893889418777</v>
       </c>
       <c r="I58" t="n">
-        <v>131.1982237717899</v>
+        <v>117.7969288767674</v>
       </c>
       <c r="J58" t="n">
-        <v>651.1548909956525</v>
+        <v>730.4975963906267</v>
       </c>
     </row>
     <row r="59">
@@ -2425,31 +2425,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-867297.4348017238</v>
+        <v>193956.2120426819</v>
       </c>
       <c r="C59" t="n">
-        <v>0.08560823458852093</v>
+        <v>0.00248992784026475</v>
       </c>
       <c r="D59" t="n">
-        <v>9.699976194940174</v>
+        <v>0.8402263147354483</v>
       </c>
       <c r="E59" t="n">
-        <v>2601.094599487658</v>
+        <v>2591.764922579744</v>
       </c>
       <c r="F59" t="n">
-        <v>3084.163861652127</v>
+        <v>3001.902464477558</v>
       </c>
       <c r="G59" t="n">
-        <v>1264.812017907528</v>
+        <v>1987.372678853033</v>
       </c>
       <c r="H59" t="n">
-        <v>6320.257227438204</v>
+        <v>8958.052407500303</v>
       </c>
       <c r="I59" t="n">
-        <v>124.6029400260108</v>
+        <v>131.0807287973535</v>
       </c>
       <c r="J59" t="n">
-        <v>675.4576826249807</v>
+        <v>739.0656849667646</v>
       </c>
     </row>
     <row r="60">
@@ -2459,31 +2459,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-912159.7719019316</v>
+        <v>-354297.3074618056</v>
       </c>
       <c r="C60" t="n">
-        <v>0.09502115392514188</v>
+        <v>0.009574488463139729</v>
       </c>
       <c r="D60" t="n">
-        <v>8.671092458329188</v>
+        <v>0.7513181840155703</v>
       </c>
       <c r="E60" t="n">
-        <v>2481.874170576646</v>
+        <v>2454.82691523891</v>
       </c>
       <c r="F60" t="n">
-        <v>3086.601293732182</v>
+        <v>3027.065592818429</v>
       </c>
       <c r="G60" t="n">
-        <v>1268.710431644871</v>
+        <v>1264.02789022001</v>
       </c>
       <c r="H60" t="n">
-        <v>6085.218309175002</v>
+        <v>8971.219857291484</v>
       </c>
       <c r="I60" t="n">
-        <v>104.7598465022565</v>
+        <v>190.6344052785654</v>
       </c>
       <c r="J60" t="n">
-        <v>628.4137421757412</v>
+        <v>633.9538174276083</v>
       </c>
     </row>
     <row r="61">
@@ -2493,31 +2493,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-635387.8509600842</v>
+        <v>-34309.48402797058</v>
       </c>
       <c r="C61" t="n">
-        <v>0.04163331372573564</v>
+        <v>0.005393760412127861</v>
       </c>
       <c r="D61" t="n">
-        <v>4.731092626448518</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>2598.555295897143</v>
+        <v>2465.278243514566</v>
       </c>
       <c r="F61" t="n">
-        <v>2954.769070134144</v>
+        <v>2948.026783973458</v>
       </c>
       <c r="G61" t="n">
-        <v>1264.011384902439</v>
+        <v>1692.510629445711</v>
       </c>
       <c r="H61" t="n">
-        <v>7564.737052256321</v>
+        <v>8961.77545834014</v>
       </c>
       <c r="I61" t="n">
-        <v>103.3513114922797</v>
+        <v>102.4230222874162</v>
       </c>
       <c r="J61" t="n">
-        <v>650.5788255222772</v>
+        <v>634.2268277944798</v>
       </c>
     </row>
     <row r="62">
@@ -2527,31 +2527,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-916353.920046886</v>
+        <v>-178827.3016862981</v>
       </c>
       <c r="C62" t="n">
-        <v>0.09556186954942961</v>
+        <v>0.007480612998656662</v>
       </c>
       <c r="D62" t="n">
-        <v>10.3205244866214</v>
+        <v>1.35944845752507</v>
       </c>
       <c r="E62" t="n">
-        <v>2602.427233530964</v>
+        <v>2467.031420336896</v>
       </c>
       <c r="F62" t="n">
-        <v>3092.872811091714</v>
+        <v>3006.295182264449</v>
       </c>
       <c r="G62" t="n">
-        <v>1264.086105019015</v>
+        <v>1504.345864469426</v>
       </c>
       <c r="H62" t="n">
-        <v>6064.690953953123</v>
+        <v>8939.977645649058</v>
       </c>
       <c r="I62" t="n">
-        <v>104.1587915803968</v>
+        <v>143.742238037352</v>
       </c>
       <c r="J62" t="n">
-        <v>680.1629107523318</v>
+        <v>653.215671502162</v>
       </c>
     </row>
     <row r="63">
@@ -2561,31 +2561,31 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>11386.98610646883</v>
+        <v>350821.9106321582</v>
       </c>
       <c r="C63" t="n">
-        <v>0.006230788608373177</v>
+        <v>0.0002846773593941023</v>
       </c>
       <c r="D63" t="n">
-        <v>0.02026550420107798</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>2460.563482705139</v>
+        <v>2456.15311007642</v>
       </c>
       <c r="F63" t="n">
-        <v>2919.996660970261</v>
+        <v>3008.903170088965</v>
       </c>
       <c r="G63" t="n">
-        <v>1764.987584126856</v>
+        <v>2191.631788208687</v>
       </c>
       <c r="H63" t="n">
-        <v>8995.13298396661</v>
+        <v>8975.500542743412</v>
       </c>
       <c r="I63" t="n">
-        <v>103.038811386316</v>
+        <v>162.4389998376968</v>
       </c>
       <c r="J63" t="n">
-        <v>623.5050332232005</v>
+        <v>772.8987757699634</v>
       </c>
     </row>
     <row r="64">
@@ -2595,31 +2595,31 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-935726.6331554381</v>
+        <v>-882906.3373032627</v>
       </c>
       <c r="C64" t="n">
-        <v>0.09933280211586708</v>
+        <v>0.08982364053220294</v>
       </c>
       <c r="D64" t="n">
-        <v>8.935666604941384</v>
+        <v>9.654522856980174</v>
       </c>
       <c r="E64" t="n">
-        <v>2485.508302277541</v>
+        <v>2599.023695847636</v>
       </c>
       <c r="F64" t="n">
-        <v>3088.28804109938</v>
+        <v>3030.209506407894</v>
       </c>
       <c r="G64" t="n">
-        <v>1264.325771181391</v>
+        <v>1266.950667814308</v>
       </c>
       <c r="H64" t="n">
-        <v>5979.200359509959</v>
+        <v>6155.69375566264</v>
       </c>
       <c r="I64" t="n">
-        <v>103.747152711068</v>
+        <v>171.2710781304356</v>
       </c>
       <c r="J64" t="n">
-        <v>614.5194226382388</v>
+        <v>636.9347275200143</v>
       </c>
     </row>
     <row r="65">
@@ -2629,31 +2629,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>238358.5083608008</v>
+        <v>-585103.0344590703</v>
       </c>
       <c r="C65" t="n">
-        <v>0.003251174930552487</v>
+        <v>0.03690074832028618</v>
       </c>
       <c r="D65" t="n">
-        <v>1.74810426084866</v>
+        <v>4.20239328283073</v>
       </c>
       <c r="E65" t="n">
-        <v>2575.043864987977</v>
+        <v>2455.132222823772</v>
       </c>
       <c r="F65" t="n">
-        <v>2924.210613414921</v>
+        <v>3070.211418281191</v>
       </c>
       <c r="G65" t="n">
-        <v>2060.831212175728</v>
+        <v>1264.000351067539</v>
       </c>
       <c r="H65" t="n">
-        <v>8998.891177059031</v>
+        <v>7756.398630488632</v>
       </c>
       <c r="I65" t="n">
-        <v>101.5397157402841</v>
+        <v>103.1996170906186</v>
       </c>
       <c r="J65" t="n">
-        <v>625.7281759790161</v>
+        <v>638.818418891854</v>
       </c>
     </row>
     <row r="66">
@@ -2663,31 +2663,31 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>225408.6513371733</v>
+        <v>-27728.62594294176</v>
       </c>
       <c r="C66" t="n">
-        <v>0.003696155952025057</v>
+        <v>0.005304663435436239</v>
       </c>
       <c r="D66" t="n">
-        <v>0.01645062117190399</v>
+        <v>2.220446049250313e-14</v>
       </c>
       <c r="E66" t="n">
-        <v>2566.81276109392</v>
+        <v>2454.820384911144</v>
       </c>
       <c r="F66" t="n">
-        <v>2919.996660970261</v>
+        <v>2948.026783973458</v>
       </c>
       <c r="G66" t="n">
-        <v>2053.75118213197</v>
+        <v>1701.446942164993</v>
       </c>
       <c r="H66" t="n">
-        <v>8960.080638111573</v>
+        <v>8961.77545834014</v>
       </c>
       <c r="I66" t="n">
-        <v>102.9619154867742</v>
+        <v>102.4230222874162</v>
       </c>
       <c r="J66" t="n">
-        <v>623.5050332232005</v>
+        <v>634.2746278783904</v>
       </c>
     </row>
     <row r="67">
@@ -2697,31 +2697,31 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-734175.7895498695</v>
+        <v>-785101.55901819</v>
       </c>
       <c r="C67" t="n">
-        <v>0.05792493057940541</v>
+        <v>0.06933400324977607</v>
       </c>
       <c r="D67" t="n">
-        <v>5.24088178396489</v>
+        <v>8.938222671536057</v>
       </c>
       <c r="E67" t="n">
-        <v>2596.396704083135</v>
+        <v>2602.27688380959</v>
       </c>
       <c r="F67" t="n">
-        <v>2917.726254026204</v>
+        <v>3056.612309880056</v>
       </c>
       <c r="G67" t="n">
-        <v>1264.487837588131</v>
+        <v>1265.376253903132</v>
       </c>
       <c r="H67" t="n">
-        <v>7048.255936233536</v>
+        <v>6678.808714315981</v>
       </c>
       <c r="I67" t="n">
-        <v>100.4836468749297</v>
+        <v>106.9013293311034</v>
       </c>
       <c r="J67" t="n">
-        <v>616.9406880964326</v>
+        <v>669.2847742108814</v>
       </c>
     </row>
     <row r="68">
@@ -2731,31 +2731,31 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-246304.2497974662</v>
+        <v>-788187.8901132648</v>
       </c>
       <c r="C68" t="n">
-        <v>0.009614445445426167</v>
+        <v>0.07074808966276667</v>
       </c>
       <c r="D68" t="n">
-        <v>0.807340524408684</v>
+        <v>8.431110234867955</v>
       </c>
       <c r="E68" t="n">
-        <v>2596.64366985297</v>
+        <v>2603.002012522956</v>
       </c>
       <c r="F68" t="n">
-        <v>2928.166046352153</v>
+        <v>3012.975424519483</v>
       </c>
       <c r="G68" t="n">
-        <v>1420.082427798407</v>
+        <v>1268.143192900758</v>
       </c>
       <c r="H68" t="n">
-        <v>9000.086184010384</v>
+        <v>6643.487292362393</v>
       </c>
       <c r="I68" t="n">
-        <v>112.3371641120157</v>
+        <v>206.8143244414362</v>
       </c>
       <c r="J68" t="n">
-        <v>615.6559832743944</v>
+        <v>695.1324760348849</v>
       </c>
     </row>
     <row r="69">
@@ -2765,31 +2765,31 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-330866.1027658852</v>
+        <v>-676090.1824727934</v>
       </c>
       <c r="C69" t="n">
-        <v>0.01115813773383342</v>
+        <v>0.05103536564353848</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>5.370559353284587</v>
       </c>
       <c r="E69" t="n">
-        <v>2483.17395341116</v>
+        <v>2460.082509976711</v>
       </c>
       <c r="F69" t="n">
-        <v>2934.40341235645</v>
+        <v>3054.575218785927</v>
       </c>
       <c r="G69" t="n">
-        <v>1323.743064688217</v>
+        <v>1264.076955318224</v>
       </c>
       <c r="H69" t="n">
-        <v>8939.4456194102</v>
+        <v>7270.391349117605</v>
       </c>
       <c r="I69" t="n">
-        <v>121.3351864416263</v>
+        <v>139.7914848635141</v>
       </c>
       <c r="J69" t="n">
-        <v>710.6646638565589</v>
+        <v>668.0734735032005</v>
       </c>
     </row>
     <row r="70">
@@ -2799,31 +2799,31 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-712122.9451421476</v>
+        <v>-781881.3492232556</v>
       </c>
       <c r="C70" t="n">
-        <v>0.05405086148531174</v>
+        <v>0.06860087262132993</v>
       </c>
       <c r="D70" t="n">
-        <v>5.845870603648462</v>
+        <v>8.893107460594695</v>
       </c>
       <c r="E70" t="n">
-        <v>2485.043757665635</v>
+        <v>2601.382670778446</v>
       </c>
       <c r="F70" t="n">
-        <v>3053.94752776755</v>
+        <v>3057.4851909768</v>
       </c>
       <c r="G70" t="n">
-        <v>1264.81863045824</v>
+        <v>1265.516018382482</v>
       </c>
       <c r="H70" t="n">
-        <v>7146.369597489059</v>
+        <v>6697.476208213232</v>
       </c>
       <c r="I70" t="n">
-        <v>106.2083480561796</v>
+        <v>108.3924707396916</v>
       </c>
       <c r="J70" t="n">
-        <v>771.1536621308638</v>
+        <v>643.9920701214567</v>
       </c>
     </row>
     <row r="71">
@@ -2833,31 +2833,31 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-186180.3971804422</v>
+        <v>-495927.4209899828</v>
       </c>
       <c r="C71" t="n">
-        <v>0.008780193747342919</v>
+        <v>0.02354029708601248</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>5.186500940912642</v>
       </c>
       <c r="E71" t="n">
-        <v>2474.23417692976</v>
+        <v>2598.49519044162</v>
       </c>
       <c r="F71" t="n">
-        <v>2916.049856578193</v>
+        <v>3064.001097515456</v>
       </c>
       <c r="G71" t="n">
-        <v>1501.86995602723</v>
+        <v>1265.384485547651</v>
       </c>
       <c r="H71" t="n">
-        <v>9002.215440836961</v>
+        <v>8198.684584164635</v>
       </c>
       <c r="I71" t="n">
-        <v>121.318981369025</v>
+        <v>202.9424637631471</v>
       </c>
       <c r="J71" t="n">
-        <v>617.5396574275018</v>
+        <v>643.332944763506</v>
       </c>
     </row>
     <row r="72">
@@ -2867,31 +2867,31 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-771182.1322925021</v>
+        <v>-684948.391709188</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0657044875909238</v>
+        <v>0.05232874493154513</v>
       </c>
       <c r="D72" t="n">
-        <v>7.031073606259353</v>
+        <v>7.609053464578297</v>
       </c>
       <c r="E72" t="n">
-        <v>2576.483655164186</v>
+        <v>2599.069048245405</v>
       </c>
       <c r="F72" t="n">
-        <v>2992.834285560097</v>
+        <v>3053.110638766103</v>
       </c>
       <c r="G72" t="n">
-        <v>1264.008343305033</v>
+        <v>1264.667898280191</v>
       </c>
       <c r="H72" t="n">
-        <v>6843.030516852697</v>
+        <v>7208.39497990157</v>
       </c>
       <c r="I72" t="n">
-        <v>121.5654158308767</v>
+        <v>143.621348460479</v>
       </c>
       <c r="J72" t="n">
-        <v>666.3185976690111</v>
+        <v>661.0702789699633</v>
       </c>
     </row>
     <row r="73">
@@ -2901,31 +2901,31 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-822404.4713139753</v>
+        <v>-921762.875466248</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07605418495958771</v>
+        <v>0.09821167657053165</v>
       </c>
       <c r="D73" t="n">
-        <v>7.594358457839522</v>
+        <v>9.687905166962985</v>
       </c>
       <c r="E73" t="n">
-        <v>2602.795116373055</v>
+        <v>2590.296002766146</v>
       </c>
       <c r="F73" t="n">
-        <v>2961.429602181307</v>
+        <v>3012.599747618693</v>
       </c>
       <c r="G73" t="n">
-        <v>1264.799530989197</v>
+        <v>1268.340247299783</v>
       </c>
       <c r="H73" t="n">
-        <v>6576.543293212429</v>
+        <v>5943.081825177254</v>
       </c>
       <c r="I73" t="n">
-        <v>101.8599644414961</v>
+        <v>205.7636123741848</v>
       </c>
       <c r="J73" t="n">
-        <v>614.2615006776001</v>
+        <v>648.2080473222229</v>
       </c>
     </row>
     <row r="74">
@@ -2935,31 +2935,31 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-857508.1689959625</v>
+        <v>-665678.2238570689</v>
       </c>
       <c r="C74" t="n">
-        <v>0.08359700641037808</v>
+        <v>0.04989579867566973</v>
       </c>
       <c r="D74" t="n">
-        <v>9.4840452099054</v>
+        <v>5.612618769888289</v>
       </c>
       <c r="E74" t="n">
-        <v>2594.849838986541</v>
+        <v>2460.310509076298</v>
       </c>
       <c r="F74" t="n">
-        <v>3081.33468029602</v>
+        <v>3075.406762727628</v>
       </c>
       <c r="G74" t="n">
-        <v>1264.525923812901</v>
+        <v>1270.674515104883</v>
       </c>
       <c r="H74" t="n">
-        <v>6373.069120951248</v>
+        <v>7300.370316298712</v>
       </c>
       <c r="I74" t="n">
-        <v>123.1076670318766</v>
+        <v>107.7953686531926</v>
       </c>
       <c r="J74" t="n">
-        <v>686.4787793719721</v>
+        <v>664.8889292762001</v>
       </c>
     </row>
     <row r="75">
@@ -2969,31 +2969,31 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-815190.6585766622</v>
+        <v>-610518.7622777321</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0745394825238752</v>
+        <v>0.04146472895771834</v>
       </c>
       <c r="D75" t="n">
-        <v>6.34062157903722</v>
+        <v>2.764254689614321</v>
       </c>
       <c r="E75" t="n">
-        <v>2575.161764549583</v>
+        <v>2458.478136102136</v>
       </c>
       <c r="F75" t="n">
-        <v>2913.023659952513</v>
+        <v>2942.809424010386</v>
       </c>
       <c r="G75" t="n">
-        <v>1264.482560576602</v>
+        <v>1269.050138448561</v>
       </c>
       <c r="H75" t="n">
-        <v>6622.587949699889</v>
+        <v>7608.577013975164</v>
       </c>
       <c r="I75" t="n">
-        <v>107.2467204072428</v>
+        <v>141.4192819217189</v>
       </c>
       <c r="J75" t="n">
-        <v>613.8290662963597</v>
+        <v>653.1009276509083</v>
       </c>
     </row>
     <row r="76">
@@ -3003,31 +3003,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-846409.9445829163</v>
+        <v>116772.0242586676</v>
       </c>
       <c r="C76" t="n">
-        <v>0.08095919738271661</v>
+        <v>0.003467577052543155</v>
       </c>
       <c r="D76" t="n">
-        <v>4.431171154959468</v>
+        <v>0.04668717362334984</v>
       </c>
       <c r="E76" t="n">
-        <v>2459.062197732333</v>
+        <v>2534.902860711179</v>
       </c>
       <c r="F76" t="n">
-        <v>2914.386163950966</v>
+        <v>3002.8503143179</v>
       </c>
       <c r="G76" t="n">
-        <v>1264.825898695659</v>
+        <v>1889.540021625175</v>
       </c>
       <c r="H76" t="n">
-        <v>6467.645130988124</v>
+        <v>8957.821162772148</v>
       </c>
       <c r="I76" t="n">
-        <v>100.5727213116294</v>
+        <v>116.5003355393616</v>
       </c>
       <c r="J76" t="n">
-        <v>617.254208611796</v>
+        <v>639.7106383726594</v>
       </c>
     </row>
     <row r="77">
@@ -3037,31 +3037,31 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-555234.6806468861</v>
+        <v>-848381.3747776779</v>
       </c>
       <c r="C77" t="n">
-        <v>0.02937453436334575</v>
+        <v>0.08206135314612584</v>
       </c>
       <c r="D77" t="n">
-        <v>4.129785553304077</v>
+        <v>9.234968948953348</v>
       </c>
       <c r="E77" t="n">
-        <v>2472.377016471204</v>
+        <v>2557.198761669651</v>
       </c>
       <c r="F77" t="n">
-        <v>3092.147992520021</v>
+        <v>3070.211418281191</v>
       </c>
       <c r="G77" t="n">
-        <v>1264.770379876804</v>
+        <v>1264.053229544309</v>
       </c>
       <c r="H77" t="n">
-        <v>7986.51340867676</v>
+        <v>6356.581806141116</v>
       </c>
       <c r="I77" t="n">
-        <v>105.6990204449248</v>
+        <v>100.0063743611178</v>
       </c>
       <c r="J77" t="n">
-        <v>623.2509066923809</v>
+        <v>637.8408040919159</v>
       </c>
     </row>
     <row r="78">
@@ -3071,31 +3071,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>286828.0114439689</v>
+        <v>222036.7619156963</v>
       </c>
       <c r="C78" t="n">
-        <v>0.00275010184826087</v>
+        <v>0.002076860380023888</v>
       </c>
       <c r="D78" t="n">
-        <v>0.4769317391812189</v>
+        <v>0.4347941810770695</v>
       </c>
       <c r="E78" t="n">
-        <v>2455.211472503432</v>
+        <v>2461.714991316332</v>
       </c>
       <c r="F78" t="n">
-        <v>3009.01421205537</v>
+        <v>3054.191095128714</v>
       </c>
       <c r="G78" t="n">
-        <v>2130.088110500229</v>
+        <v>2029.027123780914</v>
       </c>
       <c r="H78" t="n">
-        <v>8979.414187473878</v>
+        <v>8957.821162772148</v>
       </c>
       <c r="I78" t="n">
-        <v>124.4861692511967</v>
+        <v>114.1977965053211</v>
       </c>
       <c r="J78" t="n">
-        <v>622.9098282046252</v>
+        <v>643.2111375194206</v>
       </c>
     </row>
     <row r="79">
@@ -3105,31 +3105,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-682841.6115302215</v>
+        <v>-163632.1337338118</v>
       </c>
       <c r="C79" t="n">
-        <v>0.04970916112429233</v>
+        <v>0.007113663891888099</v>
       </c>
       <c r="D79" t="n">
-        <v>5.678598350823827</v>
+        <v>0.3078961239826428</v>
       </c>
       <c r="E79" t="n">
-        <v>2584.48590354059</v>
+        <v>2476.381177180263</v>
       </c>
       <c r="F79" t="n">
-        <v>2968.592478644375</v>
+        <v>3010.805021605903</v>
       </c>
       <c r="G79" t="n">
-        <v>1271.639983788881</v>
+        <v>1517.625467841186</v>
       </c>
       <c r="H79" t="n">
-        <v>7278.009810162881</v>
+        <v>8964.230142914406</v>
       </c>
       <c r="I79" t="n">
-        <v>103.1657479821287</v>
+        <v>159.7326651092602</v>
       </c>
       <c r="J79" t="n">
-        <v>711.6919120822992</v>
+        <v>653.4865950453516</v>
       </c>
     </row>
     <row r="80">
@@ -3139,31 +3139,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-662028.8100112905</v>
+        <v>-325783.994293096</v>
       </c>
       <c r="C80" t="n">
-        <v>0.04590993080636842</v>
+        <v>0.009238951469727049</v>
       </c>
       <c r="D80" t="n">
-        <v>5.696574735792392</v>
+        <v>0.5495683922022487</v>
       </c>
       <c r="E80" t="n">
-        <v>2483.81490323984</v>
+        <v>2462.148821166158</v>
       </c>
       <c r="F80" t="n">
-        <v>3088.71447005062</v>
+        <v>3010.878272320474</v>
       </c>
       <c r="G80" t="n">
-        <v>1264.013066609295</v>
+        <v>1304.068979287227</v>
       </c>
       <c r="H80" t="n">
-        <v>7415.163458975868</v>
+        <v>8964.635158208395</v>
       </c>
       <c r="I80" t="n">
-        <v>133.9015716746328</v>
+        <v>162.6850924842028</v>
       </c>
       <c r="J80" t="n">
-        <v>698.0623867890347</v>
+        <v>638.9635258134738</v>
       </c>
     </row>
     <row r="81">
@@ -3173,31 +3173,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-468809.245403673</v>
+        <v>-866980.7578301588</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0176429496642753</v>
+        <v>0.08613374907641859</v>
       </c>
       <c r="D81" t="n">
-        <v>1.249524872803032</v>
+        <v>7.720833218785394</v>
       </c>
       <c r="E81" t="n">
-        <v>2466.303816719954</v>
+        <v>2562.712480779158</v>
       </c>
       <c r="F81" t="n">
-        <v>2913.887370500718</v>
+        <v>2943.890585293948</v>
       </c>
       <c r="G81" t="n">
-        <v>1264.482560576602</v>
+        <v>1264.057381104423</v>
       </c>
       <c r="H81" t="n">
-        <v>8461.960008892813</v>
+        <v>6263.395691673999</v>
       </c>
       <c r="I81" t="n">
-        <v>107.2467204072428</v>
+        <v>127.6607803219415</v>
       </c>
       <c r="J81" t="n">
-        <v>614.108481307537</v>
+        <v>676.1496260291296</v>
       </c>
     </row>
     <row r="82">
@@ -3207,31 +3207,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-736200.7192661692</v>
+        <v>-609069.210401101</v>
       </c>
       <c r="C82" t="n">
-        <v>0.05862531875123872</v>
+        <v>0.04139992510018105</v>
       </c>
       <c r="D82" t="n">
-        <v>8.111428413324139</v>
+        <v>3.089029509236063</v>
       </c>
       <c r="E82" t="n">
-        <v>2599.14493115406</v>
+        <v>2458.99589711395</v>
       </c>
       <c r="F82" t="n">
-        <v>3067.059281563915</v>
+        <v>2961.121556880494</v>
       </c>
       <c r="G82" t="n">
-        <v>1264.4686539866</v>
+        <v>1269.050138448561</v>
       </c>
       <c r="H82" t="n">
-        <v>7016.606030265667</v>
+        <v>7608.577013975164</v>
       </c>
       <c r="I82" t="n">
-        <v>103.9337981365689</v>
+        <v>203.1713517743055</v>
       </c>
       <c r="J82" t="n">
-        <v>686.6253682408791</v>
+        <v>653.0477704873961</v>
       </c>
     </row>
     <row r="83">
@@ -3241,31 +3241,31 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-715840.5477073663</v>
+        <v>-590775.3496202687</v>
       </c>
       <c r="C83" t="n">
-        <v>0.05523280802882549</v>
+        <v>0.03780653467157404</v>
       </c>
       <c r="D83" t="n">
-        <v>4.541731933487114</v>
+        <v>6.315289197374108</v>
       </c>
       <c r="E83" t="n">
-        <v>2486.94794261014</v>
+        <v>2603.635671438062</v>
       </c>
       <c r="F83" t="n">
-        <v>2983.625572884874</v>
+        <v>3076.156413939387</v>
       </c>
       <c r="G83" t="n">
-        <v>1264.81863045824</v>
+        <v>1264.006160948242</v>
       </c>
       <c r="H83" t="n">
-        <v>7121.82721484692</v>
+        <v>7706.323637222874</v>
       </c>
       <c r="I83" t="n">
-        <v>106.2083480561796</v>
+        <v>139.5039714390379</v>
       </c>
       <c r="J83" t="n">
-        <v>892.1490729821567</v>
+        <v>659.0111603063638</v>
       </c>
     </row>
     <row r="84">
@@ -3275,31 +3275,31 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-860334.9228380769</v>
+        <v>-562245.7488660659</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0841099507584131</v>
+        <v>0.03362085887664967</v>
       </c>
       <c r="D84" t="n">
-        <v>8.027704605706443</v>
+        <v>4.223359396770665</v>
       </c>
       <c r="E84" t="n">
-        <v>2485.035588541747</v>
+        <v>2603.862211391574</v>
       </c>
       <c r="F84" t="n">
-        <v>3077.607615837996</v>
+        <v>2942.109291063686</v>
       </c>
       <c r="G84" t="n">
-        <v>1264.14831226316</v>
+        <v>1264.312733067099</v>
       </c>
       <c r="H84" t="n">
-        <v>6370.584083740697</v>
+        <v>7866.134298389895</v>
       </c>
       <c r="I84" t="n">
-        <v>123.1076670318766</v>
+        <v>175.9338720531404</v>
       </c>
       <c r="J84" t="n">
-        <v>685.5139740837914</v>
+        <v>644.2548645998521</v>
       </c>
     </row>
     <row r="85">
@@ -3309,31 +3309,31 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-810558.9916475099</v>
+        <v>-880194.7155250371</v>
       </c>
       <c r="C85" t="n">
-        <v>0.07358369164429113</v>
+        <v>0.08874941489198293</v>
       </c>
       <c r="D85" t="n">
-        <v>4.063220466179363</v>
+        <v>8.393321434383372</v>
       </c>
       <c r="E85" t="n">
-        <v>2459.062197732333</v>
+        <v>2462.486209460948</v>
       </c>
       <c r="F85" t="n">
-        <v>2914.386163950966</v>
+        <v>3075.505601382334</v>
       </c>
       <c r="G85" t="n">
-        <v>1264.825898695659</v>
+        <v>1264.135836449625</v>
       </c>
       <c r="H85" t="n">
-        <v>6657.244144606443</v>
+        <v>6194.253990215584</v>
       </c>
       <c r="I85" t="n">
-        <v>100.5727213116294</v>
+        <v>103.0329211171654</v>
       </c>
       <c r="J85" t="n">
-        <v>614.1786630071493</v>
+        <v>662.1958055130937</v>
       </c>
     </row>
     <row r="86">
@@ -3343,31 +3343,31 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-346222.3762494838</v>
+        <v>-624932.4792744988</v>
       </c>
       <c r="C86" t="n">
-        <v>0.01101982230818791</v>
+        <v>0.04340225284774444</v>
       </c>
       <c r="D86" t="n">
-        <v>3.063078341730463</v>
+        <v>6.32836506586295</v>
       </c>
       <c r="E86" t="n">
-        <v>2602.889772426048</v>
+        <v>2580.969823982637</v>
       </c>
       <c r="F86" t="n">
-        <v>3050.814483649123</v>
+        <v>3034.578415087277</v>
       </c>
       <c r="G86" t="n">
-        <v>1283.728616673372</v>
+        <v>1268.366516908145</v>
       </c>
       <c r="H86" t="n">
-        <v>8995.030060303357</v>
+        <v>7516.65845485246</v>
       </c>
       <c r="I86" t="n">
-        <v>160.0800866083894</v>
+        <v>108.770046501922</v>
       </c>
       <c r="J86" t="n">
-        <v>682.5641232181059</v>
+        <v>668.0040388639485</v>
       </c>
     </row>
     <row r="87">
@@ -3377,31 +3377,31 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>449362.2859096555</v>
+        <v>-711546.3056934671</v>
       </c>
       <c r="C87" t="n">
-        <v>0.000419963343872484</v>
+        <v>0.05626112904282926</v>
       </c>
       <c r="D87" t="n">
-        <v>0.07180953099594767</v>
+        <v>6.00893115152833</v>
       </c>
       <c r="E87" t="n">
-        <v>2553.593582605816</v>
+        <v>2455.132222823772</v>
       </c>
       <c r="F87" t="n">
-        <v>3069.766842428724</v>
+        <v>3070.211418281191</v>
       </c>
       <c r="G87" t="n">
-        <v>2333.776199738304</v>
+        <v>1264.000351067539</v>
       </c>
       <c r="H87" t="n">
-        <v>9010.878589378244</v>
+        <v>7089.106051294893</v>
       </c>
       <c r="I87" t="n">
-        <v>102.4600533351929</v>
+        <v>100.0243166258742</v>
       </c>
       <c r="J87" t="n">
-        <v>613.0907430877305</v>
+        <v>637.8408040919159</v>
       </c>
     </row>
     <row r="88">
@@ -3411,31 +3411,31 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-656266.6546640545</v>
+        <v>-572749.1111065913</v>
       </c>
       <c r="C88" t="n">
-        <v>0.04506635007689501</v>
+        <v>0.03568111505038997</v>
       </c>
       <c r="D88" t="n">
-        <v>5.206083900296599</v>
+        <v>2.136237533570751</v>
       </c>
       <c r="E88" t="n">
-        <v>2483.556664570399</v>
+        <v>2458.478136102136</v>
       </c>
       <c r="F88" t="n">
-        <v>3084.790550451763</v>
+        <v>2938.823792950676</v>
       </c>
       <c r="G88" t="n">
-        <v>1264.026094420852</v>
+        <v>1269.050138448561</v>
       </c>
       <c r="H88" t="n">
-        <v>7444.784299079018</v>
+        <v>7808.392708761283</v>
       </c>
       <c r="I88" t="n">
-        <v>160.4394040547739</v>
+        <v>141.4192819217189</v>
       </c>
       <c r="J88" t="n">
-        <v>683.1624895613285</v>
+        <v>653.1009276509083</v>
       </c>
     </row>
     <row r="89">
@@ -3445,31 +3445,31 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>319877.6954142018</v>
+        <v>-625196.4532349166</v>
       </c>
       <c r="C89" t="n">
-        <v>0.002310867550145103</v>
+        <v>0.04341275197096262</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4522235515940998</v>
+        <v>6.309673051953368</v>
       </c>
       <c r="E89" t="n">
-        <v>2455.211472503432</v>
+        <v>2579.66456934773</v>
       </c>
       <c r="F89" t="n">
-        <v>3009.01421205537</v>
+        <v>3034.578415087277</v>
       </c>
       <c r="G89" t="n">
-        <v>2174.236744527262</v>
+        <v>1268.170197547079</v>
       </c>
       <c r="H89" t="n">
-        <v>8979.414187473878</v>
+        <v>7516.65845485246</v>
       </c>
       <c r="I89" t="n">
-        <v>102.7736402945339</v>
+        <v>115.1662313181259</v>
       </c>
       <c r="J89" t="n">
-        <v>622.9098282046252</v>
+        <v>656.2707054277831</v>
       </c>
     </row>
     <row r="90">
@@ -3479,31 +3479,31 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-894186.5927654565</v>
+        <v>-914642.1172787049</v>
       </c>
       <c r="C90" t="n">
-        <v>0.09074794860585833</v>
+        <v>0.09637175083050495</v>
       </c>
       <c r="D90" t="n">
-        <v>8.391671450923122</v>
+        <v>7.928180201384394</v>
       </c>
       <c r="E90" t="n">
-        <v>2603.964291758673</v>
+        <v>2460.104878935975</v>
       </c>
       <c r="F90" t="n">
-        <v>2962.153789837323</v>
+        <v>3013.228245496541</v>
       </c>
       <c r="G90" t="n">
-        <v>1264.067629715317</v>
+        <v>1264.449005816163</v>
       </c>
       <c r="H90" t="n">
-        <v>6199.395462697594</v>
+        <v>6005.564205382064</v>
       </c>
       <c r="I90" t="n">
-        <v>102.3589194992582</v>
+        <v>201.5350390016212</v>
       </c>
       <c r="J90" t="n">
-        <v>622.8429965717053</v>
+        <v>685.3848845163556</v>
       </c>
     </row>
     <row r="91">
@@ -3513,31 +3513,31 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-441025.7932719388</v>
+        <v>-88951.24517085776</v>
       </c>
       <c r="C91" t="n">
-        <v>0.01499363329079234</v>
+        <v>0.006495357150319397</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>3.072257542794865</v>
       </c>
       <c r="E91" t="n">
-        <v>2466.705267682119</v>
+        <v>2599.591842267431</v>
       </c>
       <c r="F91" t="n">
-        <v>2935.325037489032</v>
+        <v>3069.630875877621</v>
       </c>
       <c r="G91" t="n">
-        <v>1264.669114250497</v>
+        <v>1619.854941884094</v>
       </c>
       <c r="H91" t="n">
-        <v>8602.907330138414</v>
+        <v>8922.772308597321</v>
       </c>
       <c r="I91" t="n">
-        <v>115.3139802233383</v>
+        <v>212.2596740758283</v>
       </c>
       <c r="J91" t="n">
-        <v>637.7622080437903</v>
+        <v>702.8938207840923</v>
       </c>
     </row>
     <row r="92">
@@ -3547,31 +3547,31 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-128997.8446612777</v>
+        <v>-372446.5136134657</v>
       </c>
       <c r="C92" t="n">
-        <v>0.008125717914654423</v>
+        <v>0.01064672648360209</v>
       </c>
       <c r="D92" t="n">
-        <v>0.654034620209698</v>
+        <v>3.003052019042063</v>
       </c>
       <c r="E92" t="n">
-        <v>2456.350983385819</v>
+        <v>2554.93388627691</v>
       </c>
       <c r="F92" t="n">
-        <v>3079.289427193935</v>
+        <v>3059.038849119049</v>
       </c>
       <c r="G92" t="n">
-        <v>1576.560650882638</v>
+        <v>1264.287463384491</v>
       </c>
       <c r="H92" t="n">
-        <v>8993.032400910679</v>
+        <v>8860.082048871747</v>
       </c>
       <c r="I92" t="n">
-        <v>100.4976965409022</v>
+        <v>200.4461193613526</v>
       </c>
       <c r="J92" t="n">
-        <v>626.5082419521648</v>
+        <v>642.2532309752663</v>
       </c>
     </row>
     <row r="93">
@@ -3581,31 +3581,31 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-364191.0400988925</v>
+        <v>-599328.0194136468</v>
       </c>
       <c r="C93" t="n">
-        <v>0.01144884761762217</v>
+        <v>0.03917292530963899</v>
       </c>
       <c r="D93" t="n">
-        <v>2.0396993474181</v>
+        <v>3.70995566709863</v>
       </c>
       <c r="E93" t="n">
-        <v>2492.238052286471</v>
+        <v>2455.41839850592</v>
       </c>
       <c r="F93" t="n">
-        <v>3081.185066013964</v>
+        <v>3015.64402530775</v>
       </c>
       <c r="G93" t="n">
-        <v>1270.381788914234</v>
+        <v>1264.582435750683</v>
       </c>
       <c r="H93" t="n">
-        <v>8964.333490151888</v>
+        <v>7683.915894561435</v>
       </c>
       <c r="I93" t="n">
-        <v>111.8798048328169</v>
+        <v>109.9264937939354</v>
       </c>
       <c r="J93" t="n">
-        <v>699.1118153594023</v>
+        <v>633.051836591141</v>
       </c>
     </row>
     <row r="94">
@@ -3615,31 +3615,31 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-689201.5976637001</v>
+        <v>-842408.4672297738</v>
       </c>
       <c r="C94" t="n">
-        <v>0.04987691424979039</v>
+        <v>0.08091017410356513</v>
       </c>
       <c r="D94" t="n">
-        <v>7.892048430968968</v>
+        <v>9.726839187018033</v>
       </c>
       <c r="E94" t="n">
-        <v>2603.929461280735</v>
+        <v>2603.993402582165</v>
       </c>
       <c r="F94" t="n">
-        <v>3086.350712007325</v>
+        <v>3067.95023868555</v>
       </c>
       <c r="G94" t="n">
-        <v>1264.067610285334</v>
+        <v>1264.000351067539</v>
       </c>
       <c r="H94" t="n">
-        <v>7263.689887942829</v>
+        <v>6382.10995436476</v>
       </c>
       <c r="I94" t="n">
-        <v>161.987241723893</v>
+        <v>124.0864440503679</v>
       </c>
       <c r="J94" t="n">
-        <v>631.9337204980144</v>
+        <v>634.2198322650642</v>
       </c>
     </row>
     <row r="95">
@@ -3649,31 +3649,31 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>448279.1066657961</v>
+        <v>-890748.7732087635</v>
       </c>
       <c r="C95" t="n">
-        <v>0.000475596023183798</v>
+        <v>0.09083543378306375</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0861737276643515</v>
+        <v>8.034382052281597</v>
       </c>
       <c r="E95" t="n">
-        <v>2553.593582605816</v>
+        <v>2455.138246578657</v>
       </c>
       <c r="F95" t="n">
-        <v>3069.766842428724</v>
+        <v>3050.347104294633</v>
       </c>
       <c r="G95" t="n">
-        <v>2333.776199738304</v>
+        <v>1264.089609459507</v>
       </c>
       <c r="H95" t="n">
-        <v>9005.113855440879</v>
+        <v>6144.063477117019</v>
       </c>
       <c r="I95" t="n">
-        <v>102.930727736974</v>
+        <v>101.8527194018787</v>
       </c>
       <c r="J95" t="n">
-        <v>613.0907430877305</v>
+        <v>638.7043407635036</v>
       </c>
     </row>
     <row r="96">
@@ -3683,31 +3683,31 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-828996.4332672479</v>
+        <v>244861.9096270343</v>
       </c>
       <c r="C96" t="n">
-        <v>0.07736643946056689</v>
+        <v>0.001707340857898384</v>
       </c>
       <c r="D96" t="n">
-        <v>9.076103239768795</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>2588.667429874109</v>
+        <v>2523.96586335056</v>
       </c>
       <c r="F96" t="n">
-        <v>3079.204112476186</v>
+        <v>3017.453518746366</v>
       </c>
       <c r="G96" t="n">
-        <v>1264.229571009777</v>
+        <v>2053.207406641209</v>
       </c>
       <c r="H96" t="n">
-        <v>6534.288978148626</v>
+        <v>8971.101628987673</v>
       </c>
       <c r="I96" t="n">
-        <v>101.7252739484677</v>
+        <v>197.6136569972485</v>
       </c>
       <c r="J96" t="n">
-        <v>615.2866081099837</v>
+        <v>643.6055309368456</v>
       </c>
     </row>
     <row r="97">
@@ -3717,31 +3717,31 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-246520.2609234885</v>
+        <v>-635937.2961389408</v>
       </c>
       <c r="C97" t="n">
-        <v>0.009625703977446705</v>
+        <v>0.04482242002109485</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3814039434566929</v>
+        <v>5.922753609068343</v>
       </c>
       <c r="E97" t="n">
-        <v>2575.547301679528</v>
+        <v>2579.66456934773</v>
       </c>
       <c r="F97" t="n">
-        <v>2928.166046352153</v>
+        <v>3035.124300364376</v>
       </c>
       <c r="G97" t="n">
-        <v>1420.082427798407</v>
+        <v>1265.532155832878</v>
       </c>
       <c r="H97" t="n">
-        <v>8998.919559601365</v>
+        <v>7470.726480386173</v>
       </c>
       <c r="I97" t="n">
-        <v>133.858132571304</v>
+        <v>115.1662313181259</v>
       </c>
       <c r="J97" t="n">
-        <v>615.4995405830521</v>
+        <v>653.226452910893</v>
       </c>
     </row>
     <row r="98">
@@ -3751,31 +3751,31 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>323760.1860246002</v>
+        <v>-76821.88353697443</v>
       </c>
       <c r="C98" t="n">
-        <v>0.002588504557920925</v>
+        <v>0.006214444488062828</v>
       </c>
       <c r="D98" t="n">
-        <v>2.220446049250313e-14</v>
+        <v>0.2465322747772891</v>
       </c>
       <c r="E98" t="n">
-        <v>2485.201230633213</v>
+        <v>2567.188046129372</v>
       </c>
       <c r="F98" t="n">
-        <v>3054.253694699619</v>
+        <v>2942.419562626806</v>
       </c>
       <c r="G98" t="n">
-        <v>2183.180226428697</v>
+        <v>1640.102102035557</v>
       </c>
       <c r="H98" t="n">
-        <v>8941.424978474377</v>
+        <v>8930.945525410292</v>
       </c>
       <c r="I98" t="n">
-        <v>108.4489311740324</v>
+        <v>164.9250951227125</v>
       </c>
       <c r="J98" t="n">
-        <v>784.5512927538979</v>
+        <v>642.6803663468824</v>
       </c>
     </row>
     <row r="99">
@@ -3785,31 +3785,31 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>391850.5865952969</v>
+        <v>-599270.3239724352</v>
       </c>
       <c r="C99" t="n">
-        <v>0.001207327276108661</v>
+        <v>0.03917484000253712</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4157464588038451</v>
+        <v>3.701615261170055</v>
       </c>
       <c r="E99" t="n">
-        <v>2460.115459841503</v>
+        <v>2454.878282499006</v>
       </c>
       <c r="F99" t="n">
-        <v>2934.924794601593</v>
+        <v>3015.64402530775</v>
       </c>
       <c r="G99" t="n">
-        <v>2266.228930997732</v>
+        <v>1264.582435750683</v>
       </c>
       <c r="H99" t="n">
-        <v>8998.927226770653</v>
+        <v>7683.915894561435</v>
       </c>
       <c r="I99" t="n">
-        <v>102.0694373675874</v>
+        <v>109.7126804140968</v>
       </c>
       <c r="J99" t="n">
-        <v>613.125385072711</v>
+        <v>637.0879566330052</v>
       </c>
     </row>
     <row r="100">
@@ -3819,31 +3819,31 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-614485.8724090806</v>
+        <v>-747898.7915809476</v>
       </c>
       <c r="C100" t="n">
-        <v>0.03846117088385053</v>
+        <v>0.06225802706995277</v>
       </c>
       <c r="D100" t="n">
-        <v>3.756174305735271</v>
+        <v>7.784030952177767</v>
       </c>
       <c r="E100" t="n">
-        <v>2577.434076313101</v>
+        <v>2603.002012522956</v>
       </c>
       <c r="F100" t="n">
-        <v>2919.300375886819</v>
+        <v>3008.366016639998</v>
       </c>
       <c r="G100" t="n">
-        <v>1264.073836106526</v>
+        <v>1268.171459886073</v>
       </c>
       <c r="H100" t="n">
-        <v>7681.024295284121</v>
+        <v>6867.373867101863</v>
       </c>
       <c r="I100" t="n">
-        <v>102.4632778348105</v>
+        <v>112.5282582077664</v>
       </c>
       <c r="J100" t="n">
-        <v>642.542619852613</v>
+        <v>675.7164887162877</v>
       </c>
     </row>
     <row r="101">
@@ -3853,31 +3853,31 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2522.969503590371</v>
+        <v>-326040.4496653797</v>
       </c>
       <c r="C101" t="n">
-        <v>0.00637822850685175</v>
+        <v>0.009238951469727049</v>
       </c>
       <c r="D101" t="n">
-        <v>0.8927392225125841</v>
+        <v>0.6173534813645354</v>
       </c>
       <c r="E101" t="n">
-        <v>2457.365998714005</v>
+        <v>2466.817623680793</v>
       </c>
       <c r="F101" t="n">
-        <v>3051.339895193773</v>
+        <v>3010.878272320474</v>
       </c>
       <c r="G101" t="n">
-        <v>1750.267834845549</v>
+        <v>1304.068979287227</v>
       </c>
       <c r="H101" t="n">
-        <v>8995.030060303357</v>
+        <v>8964.635158208395</v>
       </c>
       <c r="I101" t="n">
-        <v>105.4818062652589</v>
+        <v>143.6759807382604</v>
       </c>
       <c r="J101" t="n">
-        <v>623.3831713145669</v>
+        <v>639.1357732541703</v>
       </c>
     </row>
     <row r="102">
